--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/9_16_26/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/Round 2 Pods for Testing/Slow Track Pods/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{64697E42-DC9E-4C70-93F7-847F659A0E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31C5D168-C09E-417B-B206-FD88A96FD0A2}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{039B129C-6E1C-9546-893A-9CF2E360C3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1BE152F-2672-42E8-B5E4-026CEDDB8209}"/>
   <bookViews>
-    <workbookView xWindow="-28245" yWindow="420" windowWidth="27705" windowHeight="15015" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView xWindow="-26340" yWindow="1245" windowWidth="23085" windowHeight="13650" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <sheet name="Durability_Permanence" sheetId="10" r:id="rId10"/>
     <sheet name="Project Finance" sheetId="11" r:id="rId11"/>
     <sheet name="Labels_Certifications" sheetId="12" r:id="rId12"/>
+    <sheet name="Additionality" sheetId="14" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Full List'!$A$1:$M$174</definedName>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6394" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7751" uniqueCount="993">
   <si>
     <t>schema</t>
   </si>
@@ -2565,12 +2566,519 @@
   <si>
     <t xml:space="preserve">Recommend use of ISO 3166-2 country subdivision name of where the facility is located </t>
   </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>An itemised breakdown of all costs associated with implementing and operating the project, including both capital expenditure (CapEx) and operational expenditure (OpEx), used as an input to the financial additionality analysis.</t>
+  </si>
+  <si>
+    <t>An itemised breakdown of all revenue streams generated by the project other than carbon credit revenue, including product or service sales, cost savings, and public subsidies or grants, used as an input to the financial additionality analysis.</t>
+  </si>
+  <si>
+    <t>The financial metric selected to assess the project's financial viability (e.g. net present value (NPV), internal rate of return (IRR), or benefit-cost ratio), applied consistently throughout the financial additionality calculations.</t>
+  </si>
+  <si>
+    <t>The underlying calculations used to derive the project's financial indicator for comparison against the chosen financial benchmark, including all assumptions, inputs, and formulas used.</t>
+  </si>
+  <si>
+    <t>Indicates which financial investment analysis method is used to assess additionality: simple cost analysis, investment comparison analysis, or benchmark analysis.</t>
+  </si>
+  <si>
+    <t>The calculations comparing the financial performance (e.g. IRR or NPV) of the project against one or more realistic alternative investment options, used to support the investment comparison analysis.</t>
+  </si>
+  <si>
+    <t>The outcome of comparing the project's financial indicator against the chosen financial benchmark, together with the justification for why this outcome shows the project is not financially viable without carbon credit revenue.</t>
+  </si>
+  <si>
+    <t>The outcome of the investment comparison analysis, which assesses whether the project is less economically attractive than one or more alternative investment options. If the project would not be chosen over more financially viable alternatives without carbon credit revenue, it may be considered additional.</t>
+  </si>
+  <si>
+    <t>The outcome of testing how the project's financial viability conclusion changes when key assumptions (e.g. costs, revenues, discount rate) are varied within a reasonable range, demonstrating whether the conclusion is robust.</t>
+  </si>
+  <si>
+    <t>Supporting evidence and documentation for the sensitivity analysis, including the assumptions tested, the ranges applied, and the sources used to justify those ranges.</t>
+  </si>
+  <si>
+    <t>Details of the simple cost analysis, a financial additionality test that compares a project's expected costs and revenues to determine if it would be economically unattractive without carbon credit income. If the project would not generate sufficient returns, or would operate at a loss, without the added revenue from credits, it may be deemed additional.</t>
+  </si>
+  <si>
+    <t>Supporting evidence and documentation for the simple cost analysis, including the cost and revenue data sources and calculations used to determine that the project would be financially unattractive without carbon credit revenue.</t>
+  </si>
+  <si>
+    <t>Demonstration that at least one plausible alternative to the project does not face the same significant barriers as the project itself.</t>
+  </si>
+  <si>
+    <t>Evidence to (i) demonstrate each barrier identified as preventing the project's implementation, and (ii) show that carbon credit revenue is the key factor in overcoming each barrier.</t>
+  </si>
+  <si>
+    <t>Explanation of the specific barrier(s) selected for the barrier analysis and the results demonstrating that carbon credit revenue is the decisive factor in overcoming them.</t>
+  </si>
+  <si>
+    <t>Indicates which type of barrier analysis is conducted. Examples include: financial barriers, institutional barriers, information barriers, and other barriers specific to the project and/or the region where it is implemented, provided these are explicitly identified and elaborated in the relevant quantification methodology or other programme documents.</t>
+  </si>
+  <si>
+    <t>The name of the standardised additionality approach used, where the project relies on an approach other than financial, barrier, or common practice analysis (e.g. a programme-specific or methodology-specific tool).</t>
+  </si>
+  <si>
+    <t>Description of any barrier type(s) faced by the project that fall outside the standard categories (e.g. financial, institutional, technological, information), including how these barriers were identified and assessed.</t>
+  </si>
+  <si>
+    <t>Supporting evidence and documentation for the common practice analysis, including the data sources used to identify comparable projects or activities and to calculate the level of market penetration.</t>
+  </si>
+  <si>
+    <t>Overview of the approach used to determine additionality and the methodology, carbon-crediting programme, or equivalent entity responsible for setting the threshold for market penetration.</t>
+  </si>
+  <si>
+    <t>Details and justification demonstrating that the project's mitigation activity is the first of its kind, including how it differs from existing practices or technologies within the relevant sector and/or region.</t>
+  </si>
+  <si>
+    <t>Indicates whether the project's mitigation activity implements an innovative approach or technology that sets it apart from existing practices or solutions within a given sector or region.</t>
+  </si>
+  <si>
+    <t>Supporting evidence and documentation substantiating the project's claim to be a first-of-its-kind mitigation activity.</t>
+  </si>
+  <si>
+    <t>Indicates whether the project passes the common practice or market penetration test, which evaluates whether a mitigation activity is already widely adopted in a sector or region. If the activity is already standard practice, it is not considered additional and is ineligible for carbon credits.</t>
+  </si>
+  <si>
+    <t>The threshold or maximum level of market penetration or adoption below which a mitigation activity is not considered common practice, as defined by the applicable methodology or carbon-crediting programme.</t>
+  </si>
+  <si>
+    <t>A summary of the counterfactual scenario outlining what would likely have occurred in the absence of carbon finance. CO2 removals or reductions are considered additional only when measured against a conservative baseline representing this alternative scenario.</t>
+  </si>
+  <si>
+    <t>Supporting documentation for the counterfactual analysis, based on baselines that are project-specific, conservative, and periodically updated.</t>
+  </si>
+  <si>
+    <t>The counterfactual(s), or alternative scenario(s), describing what would plausibly happen if the mitigation activity did not occur.</t>
+  </si>
+  <si>
+    <t>Indicates whether the project's mitigation activity achieves emission reductions and/or removals beyond the applicable performance benchmark, a requirement for demonstrating additionality under a performance-based approach.</t>
+  </si>
+  <si>
+    <t>Supporting evidence and documentation for the alternative scenario barrier analysis, demonstrating that identified alternatives to the project do not face the same barriers as the project.</t>
+  </si>
+  <si>
+    <t>Evidence demonstrating that the project's implementation is contingent on, or directly enabled by, carbon credit revenue (e.g. financial modelling, board minutes, or investment decisions referencing carbon finance).</t>
+  </si>
+  <si>
+    <t>Indicates whether a sensitivity analysis has been conducted to show whether the conclusion regarding financial attractiveness is robust to reasonable variation in the critical assumptions.</t>
+  </si>
+  <si>
+    <t>Indicates whether the project has no other significant income streams and/or minimal capital expenditure relative to operational expenditure — a condition under which a simplified cost analysis, rather than IRR/NPV benchmarking, may be used to demonstrate financial additionality.</t>
+  </si>
+  <si>
+    <t>Indicates whether the project is not financially feasible, or is less financially attractive than alternative activities, in the absence of carbon credit revenue.</t>
+  </si>
+  <si>
+    <t>Indicates whether a benchmark approach is used, comparing the project's expected return (e.g. IRR or NPV) to a predefined financial benchmark. If the project's return falls below this benchmark without carbon credit revenue, it may be considered financially additional.</t>
+  </si>
+  <si>
+    <t>Indicates whether carbon credit revenue is the decisive factor in overcoming an identified implementation barrier (e.g. financial, technical, regulatory, or market-related) that would otherwise prevent the project from being implemented.</t>
+  </si>
+  <si>
+    <t>The additionality approach(es) applied to the project (e.g. financial additionality, barrier analysis, common practice test, performance-based approach), used to ensure carbon credits are granted only to activities that would not have occurred without the incentive provided by carbon credit revenue.</t>
+  </si>
+  <si>
+    <t>Indicates whether carbon revenue was considered or planned for prior to the project's start date. Evidence of such "prior consideration" helps demonstrate that the project would not have been developed without the financial incentive from carbon credits.</t>
+  </si>
+  <si>
+    <t>The outcome of applying the chosen standardised additionality approach (e.g. a positive list, performance benchmark, or activity-specific tool), including the conclusion reached on the project's additionality status.</t>
+  </si>
+  <si>
+    <t>Details of when and how carbon credit revenue was considered or planned for prior to the project's start date, including relevant dates and decisions.</t>
+  </si>
+  <si>
+    <t>Supporting evidence substantiating that carbon credit revenue was considered prior to the project's start date (e.g. feasibility studies, board approvals, letters of intent, or correspondence with buyers or registries dated before the start date).</t>
+  </si>
+  <si>
+    <t>Supporting evidence for any additionality measure(s) used by the project that are not covered by the standard financial, barrier, common practice, or performance-based approaches.</t>
+  </si>
+  <si>
+    <t>Indicates whether the project uses a standardised approach, other than financial, barrier, or common practice analysis, to demonstrate additionality.</t>
+  </si>
+  <si>
+    <t>The activities and/or technologies to which the standardised additionality approach applies. The approach must be defined at an appropriate level of aggregation of technologies/activities and at a high level of stringency.</t>
+  </si>
+  <si>
+    <t>The outcome of the performance-based additionality assessment, showing how the project's actual emission reductions and/or removals compare against the applicable performance threshold or benchmark.</t>
+  </si>
+  <si>
+    <t>Supporting evidence and documentation for the performance-based additionality assessment, including the data and methodology used to measure the project's performance against the applicable benchmark.</t>
+  </si>
+  <si>
+    <t>Overview of the applicable laws and regulations used to justify regulatory additionality, by demonstrating that the mitigation activity is not legally required.</t>
+  </si>
+  <si>
+    <t>Supporting documentation demonstrating that the project's mitigation activity is not mandated by, and/or exceeds the requirements of, applicable laws, regulations, or other binding obligations.</t>
+  </si>
+  <si>
+    <t>Indicates whether the project's mitigation activity goes beyond what is required by existing applicable laws, regulations, or other binding obligations — a condition for demonstrating regulatory additionality.</t>
+  </si>
+  <si>
+    <t>Assessment of whether the project's technology or activity is compatible with the host country's Long-Term Low-Emission Development Strategy (LT-LEDS) and decarbonisation pathway, used to evaluate the risk that the project locks in high-emission infrastructure or practices.</t>
+  </si>
+  <si>
+    <t>The scale of the project (e.g. capacity, output, or size classification), used to assess lock-in risk, since larger-scale, longer-lived assets can pose a greater risk of locking in emissions-intensive infrastructure or practices.</t>
+  </si>
+  <si>
+    <t>The emissions intensity of the technology or activity implemented by the project, relative to lower-carbon alternatives, used to assess the risk that the project locks in higher-emitting technology over its operational lifetime.</t>
+  </si>
+  <si>
+    <t>Description of the specific performance indicator (e.g. emissions per unit of output) used to measure the project's performance against the applicable performance-based additionality benchmark.</t>
+  </si>
+  <si>
+    <t>Description of the performance threshold or benchmark value that the project's performance indicator must meet or exceed to demonstrate additionality under the performance-based approach.</t>
+  </si>
+  <si>
+    <t>The period for which the applicable performance threshold or benchmark remains valid before it must be reviewed or updated (e.g. in line with methodology or programme review cycles).</t>
+  </si>
+  <si>
+    <t>The method used to determine regulatory additionality (e.g. legal analysis of applicable laws and regulations, assessment of enforcement levels, or a positive list of activities), as specified by the applicable methodology or carbon-crediting programme.</t>
+  </si>
+  <si>
+    <t>financial_additionality_project_cost_breakdown</t>
+  </si>
+  <si>
+    <t>financial_additionality_project_revenue_breakdown</t>
+  </si>
+  <si>
+    <t>financial_additionality_financial_indicator</t>
+  </si>
+  <si>
+    <t>financial_additionality_financial_benchmark_calculations</t>
+  </si>
+  <si>
+    <t>financial_additionality_investment_analysis_approach</t>
+  </si>
+  <si>
+    <t>financial_additionality_investment_comparison_calculations</t>
+  </si>
+  <si>
+    <t>financial_additionality_financial_benchmark_results</t>
+  </si>
+  <si>
+    <t>financial_additionality_investment_comparison_results</t>
+  </si>
+  <si>
+    <t>financial_additionality_sensitivity_analysis_results</t>
+  </si>
+  <si>
+    <t>financial_additionality_sensitivity_analysis_documentation</t>
+  </si>
+  <si>
+    <t>financial_additionality_simple_cost_analysis_details</t>
+  </si>
+  <si>
+    <t>financial_additionality_simple_cost_analysis_documentation</t>
+  </si>
+  <si>
+    <t>barriers_alternative_scenario_barrier_details</t>
+  </si>
+  <si>
+    <t>barriers_barrier_demonstration</t>
+  </si>
+  <si>
+    <t>barriers_implementation_barriers</t>
+  </si>
+  <si>
+    <t>barriers_other_additionality_approach_name</t>
+  </si>
+  <si>
+    <t>barriers_other_barrier_types</t>
+  </si>
+  <si>
+    <t>common_practice_common_practice_documentation</t>
+  </si>
+  <si>
+    <t>common_practice_common_practice_test_details</t>
+  </si>
+  <si>
+    <t>common_practice_first_of_kind_details</t>
+  </si>
+  <si>
+    <t>common_practice_first_of_kind</t>
+  </si>
+  <si>
+    <t>common_practice_first_of_kind_documentation</t>
+  </si>
+  <si>
+    <t>common_practice_passes_common_practice_test</t>
+  </si>
+  <si>
+    <t>common_practice_market_penetration_threshold</t>
+  </si>
+  <si>
+    <t>counterfactual_scenario_counterfactual_scenario_results</t>
+  </si>
+  <si>
+    <t>counterfactual_scenario_counterfactual_scenario_documentation</t>
+  </si>
+  <si>
+    <t>counterfactual_scenario_counterfactual_scenarios</t>
+  </si>
+  <si>
+    <t>counterfactual_scenario_exceeds_emissions_benchmark</t>
+  </si>
+  <si>
+    <t>counterfactual_scenario_alternative_scenario_barrier_documentation</t>
+  </si>
+  <si>
+    <t>financial_additionality_carbon_finance_dependency_demonstration</t>
+  </si>
+  <si>
+    <t>financial_additionality_sensitivity_analysis</t>
+  </si>
+  <si>
+    <t>financial_additionality_low_capex_relative_to_opex</t>
+  </si>
+  <si>
+    <t>financial_additionality_direct_result_of_carbon_finance</t>
+  </si>
+  <si>
+    <t>financial_additionality_financial_benchmark_approach</t>
+  </si>
+  <si>
+    <t>financial_additionality_carbon_revenue_decisive_for_barrier</t>
+  </si>
+  <si>
+    <t>general_additionality_approaches_used</t>
+  </si>
+  <si>
+    <t>general_credits_considered_before_start_date</t>
+  </si>
+  <si>
+    <t>general_standardized_additionality_results</t>
+  </si>
+  <si>
+    <t>general_prior_consideration_details</t>
+  </si>
+  <si>
+    <t>general_prior_consideration_evidence</t>
+  </si>
+  <si>
+    <t>general_other_additionality_evidence</t>
+  </si>
+  <si>
+    <t>general_uses_other_standardized_approach</t>
+  </si>
+  <si>
+    <t>lockin_risk_applicable_activities_technologies</t>
+  </si>
+  <si>
+    <t>performance_additionality_performance_based_additionality_results</t>
+  </si>
+  <si>
+    <t>performance_additionality_performance_based_additionality_evidence</t>
+  </si>
+  <si>
+    <t>regulatory_additionality_regulatory_surplus_justification</t>
+  </si>
+  <si>
+    <t>regulatory_additionality_legal_regulatory_additionality_documentation</t>
+  </si>
+  <si>
+    <t>regulatory_additionality_exceeds_legal_requirements</t>
+  </si>
+  <si>
+    <t>lockin_risk_project_scale</t>
+  </si>
+  <si>
+    <t>performance_additionality_performance_indicator_description</t>
+  </si>
+  <si>
+    <t>lockin_risk_technology_emissions_intensity</t>
+  </si>
+  <si>
+    <t>performance_additionality_performance_threshold_description</t>
+  </si>
+  <si>
+    <t>performance_additionality_performance_threshold_validity_period</t>
+  </si>
+  <si>
+    <t>regulatory_additionality_regulatory_additionality_determination_method</t>
+  </si>
+  <si>
+    <t>lockin_risk_country_ltleds_compatibility</t>
+  </si>
+  <si>
+    <t>barriers_chosen_barrier_explanation_and_results</t>
+  </si>
+  <si>
+    <t>project.financial_additionality[].financial_additionality_project_cost_breakdown</t>
+  </si>
+  <si>
+    <t>project.financial_additionality[].financial_additionality_project_revenue_breakdown</t>
+  </si>
+  <si>
+    <t>project.financial_additionality[].financial_additionality_financial_indicator</t>
+  </si>
+  <si>
+    <t>project.financial_additionality[].financial_additionality_financial_benchmark_calculations</t>
+  </si>
+  <si>
+    <t>project.financial_additionality[].financial_additionality_investment_analysis_approach</t>
+  </si>
+  <si>
+    <t>project.financial_additionality[].financial_additionality_investment_comparison_calculations</t>
+  </si>
+  <si>
+    <t>project.financial_additionality[].financial_additionality_financial_benchmark_results</t>
+  </si>
+  <si>
+    <t>project.financial_additionality[].financial_additionality_investment_comparison_results</t>
+  </si>
+  <si>
+    <t>project.financial_additionality[].financial_additionality_sensitivity_analysis_results</t>
+  </si>
+  <si>
+    <t>project.financial_additionality[].financial_additionality_sensitivity_analysis_documentation</t>
+  </si>
+  <si>
+    <t>project.financial_additionality[].financial_additionality_simple_cost_analysis_details</t>
+  </si>
+  <si>
+    <t>project.financial_additionality[].financial_additionality_simple_cost_analysis_documentation</t>
+  </si>
+  <si>
+    <t>project.barriers[].barriers_alternative_scenario_barrier_details</t>
+  </si>
+  <si>
+    <t>project.barriers[].barriers_barrier_demonstration</t>
+  </si>
+  <si>
+    <t>project.barriers[].barriers_chosen_barrier_explanation_and_results</t>
+  </si>
+  <si>
+    <t>project.barriers[].barriers_implementation_barriers</t>
+  </si>
+  <si>
+    <t>project.barriers[].barriers_other_additionality_approach_name</t>
+  </si>
+  <si>
+    <t>project.barriers[].barriers_other_barrier_types</t>
+  </si>
+  <si>
+    <t>project.common_practice[].common_practice_common_practice_documentation</t>
+  </si>
+  <si>
+    <t>project.common_practice[].common_practice_common_practice_test_details</t>
+  </si>
+  <si>
+    <t>project.common_practice[].common_practice_first_of_kind_details</t>
+  </si>
+  <si>
+    <t>project.common_practice[].common_practice_first_of_kind</t>
+  </si>
+  <si>
+    <t>project.common_practice[].common_practice_first_of_kind_documentation</t>
+  </si>
+  <si>
+    <t>project.common_practice[].common_practice_passes_common_practice_test</t>
+  </si>
+  <si>
+    <t>project.common_practice[].common_practice_market_penetration_threshold</t>
+  </si>
+  <si>
+    <t>project.counterfactual_scenario[].counterfactual_scenario_counterfactual_scenario_results</t>
+  </si>
+  <si>
+    <t>project.counterfactual_scenario[].counterfactual_scenario_counterfactual_scenario_documentation</t>
+  </si>
+  <si>
+    <t>project.counterfactual_scenario[].counterfactual_scenario_counterfactual_scenarios</t>
+  </si>
+  <si>
+    <t>project.counterfactual_scenario[].counterfactual_scenario_exceeds_emissions_benchmark</t>
+  </si>
+  <si>
+    <t>project.counterfactual_scenario[].counterfactual_scenario_alternative_scenario_barrier_documentation</t>
+  </si>
+  <si>
+    <t>project.financial_additionality[].financial_additionality_carbon_finance_dependency_demonstration</t>
+  </si>
+  <si>
+    <t>project.financial_additionality[].financial_additionality_sensitivity_analysis</t>
+  </si>
+  <si>
+    <t>project.financial_additionality[].financial_additionality_low_capex_relative_to_opex</t>
+  </si>
+  <si>
+    <t>project.financial_additionality[].financial_additionality_direct_result_of_carbon_finance</t>
+  </si>
+  <si>
+    <t>project.financial_additionality[].financial_additionality_financial_benchmark_approach</t>
+  </si>
+  <si>
+    <t>project.financial_additionality[].financial_additionality_carbon_revenue_decisive_for_barrier</t>
+  </si>
+  <si>
+    <t>project.lockin_risk[].lockin_risk_applicable_activities_technologies</t>
+  </si>
+  <si>
+    <t>project.performance_additionality[].performance_additionality_performance_based_additionality_results</t>
+  </si>
+  <si>
+    <t>project.performance_additionality[].performance_additionality_performance_based_additionality_evidence</t>
+  </si>
+  <si>
+    <t>project.regulatory_additionality[].regulatory_additionality_regulatory_surplus_justification</t>
+  </si>
+  <si>
+    <t>project.regulatory_additionality[].regulatory_additionality_legal_regulatory_additionality_documentation</t>
+  </si>
+  <si>
+    <t>project.regulatory_additionality[].regulatory_additionality_exceeds_legal_requirements</t>
+  </si>
+  <si>
+    <t>project.lockin_risk[].lockin_risk_country_ltleds_compatibility</t>
+  </si>
+  <si>
+    <t>project.lockin_risk[].lockin_risk_project_scale</t>
+  </si>
+  <si>
+    <t>project.lockin_risk[].lockin_risk_technology_emissions_intensity</t>
+  </si>
+  <si>
+    <t>project.performance_additionality[].performance_additionality_performance_indicator_description</t>
+  </si>
+  <si>
+    <t>project.performance_additionality[].performance_additionality_performance_threshold_description</t>
+  </si>
+  <si>
+    <t>project.performance_additionality[].performance_additionality_performance_threshold_validity_period</t>
+  </si>
+  <si>
+    <t>project.regulatory_additionality[].regulatory_additionality_regulatory_additionality_determination_method</t>
+  </si>
+  <si>
+    <t>project.general_additionality[].general_additionality_approaches_used</t>
+  </si>
+  <si>
+    <t>project.general_additionality[].general_credits_considered_before_start_date</t>
+  </si>
+  <si>
+    <t>project.general_additionality[].general_standardized_additionality_results</t>
+  </si>
+  <si>
+    <t>project.general_additionality[].general_prior_consideration_details</t>
+  </si>
+  <si>
+    <t>project.general_additionality[].general_prior_consideration_evidence</t>
+  </si>
+  <si>
+    <t>project.general_additionality[].general_other_additionality_evidence</t>
+  </si>
+  <si>
+    <t>project.general_additionality[].general_uses_other_standardized_approach</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2665,8 +3173,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF434343"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2706,6 +3226,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2757,7 +3283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2819,6 +3345,15 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3153,7 +3688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{752D3095-90A4-45FF-BD20-0492A3C6EFAC}">
-  <dimension ref="A1:M261"/>
+  <dimension ref="A1:M317"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.81640625" customWidth="1"/>
@@ -13869,6 +14404,2302 @@
         <v>797</v>
       </c>
     </row>
+    <row r="262" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A262" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B262" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C262">
+        <v>261</v>
+      </c>
+      <c r="D262" t="s">
+        <v>881</v>
+      </c>
+      <c r="E262" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F262" s="35" t="s">
+        <v>937</v>
+      </c>
+      <c r="G262" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H262" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I262" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J262" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K262" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L262" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M262" s="33" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="263" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A263" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B263" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C263">
+        <v>262</v>
+      </c>
+      <c r="D263" t="s">
+        <v>882</v>
+      </c>
+      <c r="E263" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F263" s="35" t="s">
+        <v>938</v>
+      </c>
+      <c r="G263" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H263" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I263" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J263" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K263" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L263" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M263" s="33" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="264" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A264" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B264" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C264">
+        <v>263</v>
+      </c>
+      <c r="D264" t="s">
+        <v>883</v>
+      </c>
+      <c r="E264" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F264" s="35" t="s">
+        <v>939</v>
+      </c>
+      <c r="G264" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H264" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I264" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J264" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K264" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L264" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M264" s="33" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="265" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A265" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B265" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C265">
+        <v>264</v>
+      </c>
+      <c r="D265" t="s">
+        <v>884</v>
+      </c>
+      <c r="E265" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F265" s="35" t="s">
+        <v>940</v>
+      </c>
+      <c r="G265" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H265" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I265" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J265" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K265" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L265" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M265" s="33" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="266" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A266" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B266" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C266">
+        <v>265</v>
+      </c>
+      <c r="D266" t="s">
+        <v>885</v>
+      </c>
+      <c r="E266" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F266" s="35" t="s">
+        <v>941</v>
+      </c>
+      <c r="G266" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H266" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I266" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J266" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K266" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L266" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M266" s="33" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="267" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A267" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B267" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C267">
+        <v>266</v>
+      </c>
+      <c r="D267" t="s">
+        <v>886</v>
+      </c>
+      <c r="E267" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F267" s="35" t="s">
+        <v>942</v>
+      </c>
+      <c r="G267" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H267" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I267" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J267" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K267" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L267" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M267" s="33" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="268" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A268" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B268" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C268">
+        <v>267</v>
+      </c>
+      <c r="D268" t="s">
+        <v>887</v>
+      </c>
+      <c r="E268" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F268" s="35" t="s">
+        <v>943</v>
+      </c>
+      <c r="G268" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H268" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I268" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J268" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K268" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L268" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M268" s="33" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="269" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A269" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B269" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C269">
+        <v>268</v>
+      </c>
+      <c r="D269" t="s">
+        <v>888</v>
+      </c>
+      <c r="E269" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F269" s="35" t="s">
+        <v>944</v>
+      </c>
+      <c r="G269" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H269" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I269" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J269" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K269" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L269" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M269" s="33" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="270" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A270" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B270" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C270">
+        <v>269</v>
+      </c>
+      <c r="D270" t="s">
+        <v>889</v>
+      </c>
+      <c r="E270" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F270" s="35" t="s">
+        <v>945</v>
+      </c>
+      <c r="G270" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H270" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I270" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J270" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K270" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L270" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M270" s="33" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="271" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A271" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B271" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C271">
+        <v>270</v>
+      </c>
+      <c r="D271" t="s">
+        <v>890</v>
+      </c>
+      <c r="E271" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F271" s="35" t="s">
+        <v>946</v>
+      </c>
+      <c r="G271" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H271" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I271" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J271" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K271" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L271" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M271" s="33" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="272" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A272" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B272" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C272">
+        <v>271</v>
+      </c>
+      <c r="D272" t="s">
+        <v>891</v>
+      </c>
+      <c r="E272" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F272" s="35" t="s">
+        <v>947</v>
+      </c>
+      <c r="G272" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H272" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I272" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J272" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K272" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L272" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M272" s="33" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="273" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A273" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B273" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C273">
+        <v>272</v>
+      </c>
+      <c r="D273" t="s">
+        <v>892</v>
+      </c>
+      <c r="E273" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F273" s="35" t="s">
+        <v>948</v>
+      </c>
+      <c r="G273" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H273" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I273" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J273" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K273" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L273" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M273" s="33" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="274" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A274" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B274" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C274">
+        <v>273</v>
+      </c>
+      <c r="D274" t="s">
+        <v>893</v>
+      </c>
+      <c r="E274" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F274" s="35" t="s">
+        <v>949</v>
+      </c>
+      <c r="G274" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H274" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I274" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J274" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K274" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L274" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M274" s="33" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="275" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A275" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B275" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C275">
+        <v>274</v>
+      </c>
+      <c r="D275" t="s">
+        <v>894</v>
+      </c>
+      <c r="E275" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F275" s="35" t="s">
+        <v>950</v>
+      </c>
+      <c r="G275" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H275" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I275" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J275" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K275" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L275" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M275" s="33" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="276" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A276" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B276" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C276">
+        <v>275</v>
+      </c>
+      <c r="D276" t="s">
+        <v>936</v>
+      </c>
+      <c r="E276" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F276" s="35" t="s">
+        <v>951</v>
+      </c>
+      <c r="G276" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H276" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I276" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J276" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K276" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L276" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M276" s="33" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="277" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A277" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B277" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C277">
+        <v>276</v>
+      </c>
+      <c r="D277" t="s">
+        <v>895</v>
+      </c>
+      <c r="E277" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F277" s="35" t="s">
+        <v>952</v>
+      </c>
+      <c r="G277" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H277" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I277" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J277" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K277" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L277" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M277" s="33" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="278" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A278" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B278" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C278">
+        <v>277</v>
+      </c>
+      <c r="D278" t="s">
+        <v>896</v>
+      </c>
+      <c r="E278" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F278" s="35" t="s">
+        <v>953</v>
+      </c>
+      <c r="G278" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H278" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I278" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J278" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K278" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L278" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M278" s="33" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="279" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A279" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B279" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C279">
+        <v>278</v>
+      </c>
+      <c r="D279" t="s">
+        <v>897</v>
+      </c>
+      <c r="E279" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F279" s="35" t="s">
+        <v>954</v>
+      </c>
+      <c r="G279" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H279" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I279" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J279" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K279" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L279" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M279" s="33" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="280" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A280" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B280" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C280">
+        <v>279</v>
+      </c>
+      <c r="D280" t="s">
+        <v>898</v>
+      </c>
+      <c r="E280" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F280" s="35" t="s">
+        <v>955</v>
+      </c>
+      <c r="G280" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H280" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I280" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J280" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K280" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L280" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M280" s="33" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="281" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A281" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B281" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C281">
+        <v>280</v>
+      </c>
+      <c r="D281" t="s">
+        <v>899</v>
+      </c>
+      <c r="E281" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F281" s="35" t="s">
+        <v>956</v>
+      </c>
+      <c r="G281" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H281" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I281" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J281" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K281" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L281" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M281" s="33" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="282" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A282" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B282" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C282">
+        <v>281</v>
+      </c>
+      <c r="D282" t="s">
+        <v>900</v>
+      </c>
+      <c r="E282" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F282" s="35" t="s">
+        <v>957</v>
+      </c>
+      <c r="G282" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H282" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I282" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J282" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K282" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L282" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M282" s="33" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="283" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A283" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B283" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C283">
+        <v>282</v>
+      </c>
+      <c r="D283" t="s">
+        <v>901</v>
+      </c>
+      <c r="E283" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F283" s="35" t="s">
+        <v>958</v>
+      </c>
+      <c r="G283" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H283" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I283" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J283" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K283" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L283" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M283" s="33" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="284" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A284" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B284" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C284">
+        <v>283</v>
+      </c>
+      <c r="D284" t="s">
+        <v>902</v>
+      </c>
+      <c r="E284" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F284" s="35" t="s">
+        <v>959</v>
+      </c>
+      <c r="G284" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H284" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I284" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J284" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K284" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L284" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M284" s="33" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="285" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A285" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B285" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C285">
+        <v>284</v>
+      </c>
+      <c r="D285" t="s">
+        <v>903</v>
+      </c>
+      <c r="E285" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F285" s="35" t="s">
+        <v>960</v>
+      </c>
+      <c r="G285" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H285" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I285" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J285" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K285" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L285" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M285" s="33" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="286" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A286" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B286" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C286">
+        <v>285</v>
+      </c>
+      <c r="D286" t="s">
+        <v>904</v>
+      </c>
+      <c r="E286" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F286" s="35" t="s">
+        <v>961</v>
+      </c>
+      <c r="G286" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H286" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I286" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J286" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K286" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L286" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M286" s="33" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="287" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A287" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B287" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C287">
+        <v>286</v>
+      </c>
+      <c r="D287" t="s">
+        <v>905</v>
+      </c>
+      <c r="E287" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F287" s="35" t="s">
+        <v>962</v>
+      </c>
+      <c r="G287" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H287" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I287" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J287" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K287" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L287" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M287" s="33" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="288" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A288" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B288" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C288">
+        <v>287</v>
+      </c>
+      <c r="D288" t="s">
+        <v>906</v>
+      </c>
+      <c r="E288" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F288" s="35" t="s">
+        <v>963</v>
+      </c>
+      <c r="G288" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H288" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I288" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J288" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K288" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L288" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M288" s="33" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="289" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A289" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B289" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C289">
+        <v>288</v>
+      </c>
+      <c r="D289" t="s">
+        <v>907</v>
+      </c>
+      <c r="E289" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F289" s="35" t="s">
+        <v>964</v>
+      </c>
+      <c r="G289" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H289" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I289" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J289" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K289" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L289" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M289" s="33" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="290" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A290" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B290" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C290">
+        <v>289</v>
+      </c>
+      <c r="D290" t="s">
+        <v>908</v>
+      </c>
+      <c r="E290" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F290" s="35" t="s">
+        <v>965</v>
+      </c>
+      <c r="G290" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H290" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I290" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J290" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K290" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L290" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M290" s="33" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="291" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A291" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B291" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C291">
+        <v>290</v>
+      </c>
+      <c r="D291" t="s">
+        <v>909</v>
+      </c>
+      <c r="E291" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F291" s="35" t="s">
+        <v>966</v>
+      </c>
+      <c r="G291" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H291" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I291" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J291" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K291" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L291" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M291" s="33" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="292" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A292" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B292" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C292">
+        <v>300</v>
+      </c>
+      <c r="D292" t="s">
+        <v>910</v>
+      </c>
+      <c r="E292" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F292" s="35" t="s">
+        <v>967</v>
+      </c>
+      <c r="G292" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H292" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I292" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J292" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K292" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L292" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M292" s="33" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="293" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A293" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B293" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C293">
+        <v>301</v>
+      </c>
+      <c r="D293" t="s">
+        <v>911</v>
+      </c>
+      <c r="E293" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F293" s="35" t="s">
+        <v>968</v>
+      </c>
+      <c r="G293" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H293" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I293" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J293" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K293" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L293" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M293" s="33" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="294" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A294" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B294" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C294">
+        <v>302</v>
+      </c>
+      <c r="D294" t="s">
+        <v>912</v>
+      </c>
+      <c r="E294" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F294" s="35" t="s">
+        <v>969</v>
+      </c>
+      <c r="G294" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H294" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I294" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J294" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K294" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L294" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M294" s="33" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="295" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A295" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B295" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C295">
+        <v>303</v>
+      </c>
+      <c r="D295" t="s">
+        <v>913</v>
+      </c>
+      <c r="E295" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F295" s="35" t="s">
+        <v>970</v>
+      </c>
+      <c r="G295" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H295" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I295" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J295" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K295" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L295" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M295" s="33" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="296" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A296" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B296" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C296">
+        <v>304</v>
+      </c>
+      <c r="D296" t="s">
+        <v>914</v>
+      </c>
+      <c r="E296" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F296" s="35" t="s">
+        <v>971</v>
+      </c>
+      <c r="G296" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H296" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I296" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J296" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K296" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L296" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M296" s="33" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="297" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A297" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B297" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C297">
+        <v>305</v>
+      </c>
+      <c r="D297" t="s">
+        <v>915</v>
+      </c>
+      <c r="E297" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F297" s="35" t="s">
+        <v>972</v>
+      </c>
+      <c r="G297" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H297" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I297" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J297" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K297" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L297" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M297" s="33" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="298" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A298" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B298" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C298">
+        <v>306</v>
+      </c>
+      <c r="D298" t="s">
+        <v>916</v>
+      </c>
+      <c r="E298" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F298" s="35" t="s">
+        <v>986</v>
+      </c>
+      <c r="G298" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H298" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I298" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J298" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K298" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L298" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M298" s="33" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="299" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A299" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B299" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C299">
+        <v>307</v>
+      </c>
+      <c r="D299" t="s">
+        <v>917</v>
+      </c>
+      <c r="E299" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F299" s="35" t="s">
+        <v>987</v>
+      </c>
+      <c r="G299" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H299" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I299" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J299" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K299" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L299" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M299" s="33" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="300" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A300" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B300" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C300">
+        <v>308</v>
+      </c>
+      <c r="D300" t="s">
+        <v>918</v>
+      </c>
+      <c r="E300" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F300" s="35" t="s">
+        <v>988</v>
+      </c>
+      <c r="G300" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H300" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I300" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J300" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K300" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L300" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M300" s="33" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="301" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A301" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B301" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C301">
+        <v>309</v>
+      </c>
+      <c r="D301" t="s">
+        <v>919</v>
+      </c>
+      <c r="E301" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F301" s="35" t="s">
+        <v>989</v>
+      </c>
+      <c r="G301" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H301" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I301" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J301" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K301" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L301" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M301" s="33" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="302" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A302" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B302" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C302">
+        <v>310</v>
+      </c>
+      <c r="D302" t="s">
+        <v>920</v>
+      </c>
+      <c r="E302" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F302" s="35" t="s">
+        <v>990</v>
+      </c>
+      <c r="G302" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H302" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I302" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J302" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K302" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L302" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M302" s="33" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="303" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A303" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B303" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C303">
+        <v>311</v>
+      </c>
+      <c r="D303" t="s">
+        <v>921</v>
+      </c>
+      <c r="E303" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F303" s="35" t="s">
+        <v>991</v>
+      </c>
+      <c r="G303" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="H303" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I303" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="J303" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K303" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L303" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M303" s="33" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="304" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A304" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B304" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C304">
+        <v>312</v>
+      </c>
+      <c r="D304" t="s">
+        <v>922</v>
+      </c>
+      <c r="E304" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F304" s="35" t="s">
+        <v>992</v>
+      </c>
+      <c r="G304" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H304" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I304" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J304" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K304" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L304" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M304" s="33" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="305" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A305" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B305" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C305">
+        <v>313</v>
+      </c>
+      <c r="D305" t="s">
+        <v>923</v>
+      </c>
+      <c r="E305" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F305" s="35" t="s">
+        <v>973</v>
+      </c>
+      <c r="G305" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="H305" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I305" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="J305" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K305" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L305" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M305" s="33" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="306" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A306" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B306" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C306">
+        <v>314</v>
+      </c>
+      <c r="D306" t="s">
+        <v>924</v>
+      </c>
+      <c r="E306" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F306" s="35" t="s">
+        <v>974</v>
+      </c>
+      <c r="G306" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H306" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I306" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J306" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K306" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L306" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M306" s="33" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="307" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A307" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B307" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C307">
+        <v>315</v>
+      </c>
+      <c r="D307" t="s">
+        <v>925</v>
+      </c>
+      <c r="E307" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F307" s="35" t="s">
+        <v>975</v>
+      </c>
+      <c r="G307" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H307" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I307" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J307" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K307" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L307" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M307" s="33" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="308" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A308" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B308" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C308">
+        <v>316</v>
+      </c>
+      <c r="D308" t="s">
+        <v>926</v>
+      </c>
+      <c r="E308" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F308" s="35" t="s">
+        <v>976</v>
+      </c>
+      <c r="G308" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H308" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I308" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J308" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K308" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L308" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M308" s="33" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="309" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A309" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B309" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C309">
+        <v>317</v>
+      </c>
+      <c r="D309" t="s">
+        <v>927</v>
+      </c>
+      <c r="E309" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F309" s="35" t="s">
+        <v>977</v>
+      </c>
+      <c r="G309" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H309" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I309" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J309" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K309" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L309" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M309" s="33" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="310" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A310" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B310" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C310">
+        <v>318</v>
+      </c>
+      <c r="D310" t="s">
+        <v>928</v>
+      </c>
+      <c r="E310" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F310" s="35" t="s">
+        <v>978</v>
+      </c>
+      <c r="G310" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H310" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I310" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J310" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K310" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L310" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M310" s="33" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="311" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A311" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B311" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C311">
+        <v>319</v>
+      </c>
+      <c r="D311" t="s">
+        <v>935</v>
+      </c>
+      <c r="E311" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F311" s="35" t="s">
+        <v>979</v>
+      </c>
+      <c r="G311" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="H311" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I311" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="J311" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K311" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L311" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M311" s="33" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="312" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A312" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B312" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C312">
+        <v>320</v>
+      </c>
+      <c r="D312" s="34" t="s">
+        <v>929</v>
+      </c>
+      <c r="E312" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F312" s="35" t="s">
+        <v>980</v>
+      </c>
+      <c r="G312" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="H312" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I312" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="J312" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K312" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L312" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M312" s="33" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="313" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A313" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B313" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C313">
+        <v>321</v>
+      </c>
+      <c r="D313" t="s">
+        <v>931</v>
+      </c>
+      <c r="E313" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F313" s="35" t="s">
+        <v>981</v>
+      </c>
+      <c r="G313" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="H313" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I313" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="J313" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K313" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L313" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M313" s="33" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="314" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A314" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B314" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C314">
+        <v>322</v>
+      </c>
+      <c r="D314" t="s">
+        <v>930</v>
+      </c>
+      <c r="E314" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F314" s="35" t="s">
+        <v>982</v>
+      </c>
+      <c r="G314" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H314" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I314" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J314" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K314" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L314" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M314" s="33" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="315" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A315" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B315" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C315">
+        <v>323</v>
+      </c>
+      <c r="D315" t="s">
+        <v>932</v>
+      </c>
+      <c r="E315" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F315" s="35" t="s">
+        <v>983</v>
+      </c>
+      <c r="G315" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H315" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I315" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J315" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K315" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L315" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M315" s="33" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="316" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A316" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B316" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C316">
+        <v>324</v>
+      </c>
+      <c r="D316" t="s">
+        <v>933</v>
+      </c>
+      <c r="E316" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F316" s="35" t="s">
+        <v>984</v>
+      </c>
+      <c r="G316" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H316" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I316" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J316" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K316" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L316" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M316" s="33" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="317" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A317" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B317" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C317">
+        <v>325</v>
+      </c>
+      <c r="D317" t="s">
+        <v>934</v>
+      </c>
+      <c r="E317" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F317" s="35" t="s">
+        <v>985</v>
+      </c>
+      <c r="G317" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H317" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I317" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J317" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K317" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L317" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M317" s="33" t="s">
+        <v>880</v>
+      </c>
+    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="E226 D226:D232 D235:D241 D233:E234" name="Range1"/>
@@ -13876,6 +16707,27 @@
     <protectedRange sqref="L226:M240" name="Range1_2"/>
   </protectedRanges>
   <autoFilter ref="A1:M174" xr:uid="{752D3095-90A4-45FF-BD20-0492A3C6EFAC}"/>
+  <dataValidations count="7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G314:G317 G262:G302 G304 G306:G310" xr:uid="{8421E565-9A34-4BDE-8F04-9D91BB307705}">
+      <formula1>INDIRECT("Table7")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I262:I302 I314:I317 I304 I306:I310" xr:uid="{90EAB20D-316E-4E59-B6FD-56013D0FA9CB}">
+      <formula1>INDIRECT("Table10")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L262:L317" xr:uid="{55CC77D7-E486-4A9F-BA85-85F7AF1EAEEE}">
+      <formula1>INDIRECT("Table9")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J262:J317" xr:uid="{E4919463-1AC7-400A-A26B-9236FFE6379F}">
+      <formula1>INDIRECT("Table8")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H262:H317" xr:uid="{FCBBCFB4-F3D7-4880-91CC-84C98A6F4EE9}">
+      <formula1>INDIRECT("Table11")</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I303 I311:I313 I305 G311:G313 G303 G305" xr:uid="{8917343C-8393-4E87-9CC3-C28726D9C604}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E262:E317" xr:uid="{69352F81-7E45-43DA-A957-451808D9BF44}">
+      <formula1>INDIRECT("Table5")</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13883,7 +16735,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19077895-EC06-4A1E-8356-35FFB51E509C}">
   <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.81640625" customWidth="1"/>
@@ -14152,7 +17004,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F74DE0C-3B16-437D-A7B1-E6329FD0340E}">
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39.81640625" bestFit="1" customWidth="1"/>
@@ -14161,7 +17013,7 @@
     <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.1796875" customWidth="1"/>
     <col min="9" max="9" width="8.453125" customWidth="1"/>
-    <col min="10" max="10" width="18.54296875" customWidth="1"/>
+    <col min="10" max="10" width="18.453125" customWidth="1"/>
     <col min="11" max="11" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.1796875" customWidth="1"/>
     <col min="13" max="13" width="9.1796875" bestFit="1" customWidth="1"/>
@@ -15903,12 +18755,12 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA98A367-0F9C-4A79-8999-97646D5F2CC7}">
   <dimension ref="A1:M20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="41.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.7265625" customWidth="1"/>
+    <col min="4" max="4" width="41.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6328125" customWidth="1"/>
     <col min="6" max="6" width="44" customWidth="1"/>
-    <col min="10" max="10" width="17.7265625" customWidth="1"/>
+    <col min="10" max="10" width="17.6328125" customWidth="1"/>
     <col min="13" max="13" width="17.453125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -16734,6 +19586,2389 @@
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A482C6FC-517B-4372-9F13-36E2DCF6C619}">
+  <dimension ref="A1:M61"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="7.81640625" customWidth="1"/>
+    <col min="4" max="4" width="67.453125" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="43.81640625" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="60.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C2">
+        <v>261</v>
+      </c>
+      <c r="D2" t="s">
+        <v>881</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F2" s="35" t="s">
+        <v>937</v>
+      </c>
+      <c r="G2" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I2" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K2" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L2" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M2" s="33" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C3">
+        <v>262</v>
+      </c>
+      <c r="D3" t="s">
+        <v>882</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>938</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I3" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K3" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L3" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M3" s="33" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C4">
+        <v>263</v>
+      </c>
+      <c r="D4" t="s">
+        <v>883</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F4" s="35" t="s">
+        <v>939</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K4" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L4" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M4" s="33" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C5">
+        <v>264</v>
+      </c>
+      <c r="D5" t="s">
+        <v>884</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F5" s="35" t="s">
+        <v>940</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I5" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K5" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L5" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M5" s="33" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C6">
+        <v>265</v>
+      </c>
+      <c r="D6" t="s">
+        <v>885</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F6" s="35" t="s">
+        <v>941</v>
+      </c>
+      <c r="G6" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I6" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K6" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L6" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M6" s="33" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C7">
+        <v>266</v>
+      </c>
+      <c r="D7" t="s">
+        <v>886</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F7" s="35" t="s">
+        <v>942</v>
+      </c>
+      <c r="G7" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I7" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K7" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L7" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M7" s="33" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8">
+        <v>267</v>
+      </c>
+      <c r="D8" t="s">
+        <v>887</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>943</v>
+      </c>
+      <c r="G8" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I8" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K8" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L8" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M8" s="33" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C9">
+        <v>268</v>
+      </c>
+      <c r="D9" t="s">
+        <v>888</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>944</v>
+      </c>
+      <c r="G9" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I9" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K9" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L9" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M9" s="33" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C10">
+        <v>269</v>
+      </c>
+      <c r="D10" t="s">
+        <v>889</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>945</v>
+      </c>
+      <c r="G10" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I10" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K10" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L10" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M10" s="33" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C11">
+        <v>270</v>
+      </c>
+      <c r="D11" t="s">
+        <v>890</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F11" s="35" t="s">
+        <v>946</v>
+      </c>
+      <c r="G11" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I11" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K11" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L11" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M11" s="33" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C12">
+        <v>271</v>
+      </c>
+      <c r="D12" t="s">
+        <v>891</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F12" s="35" t="s">
+        <v>947</v>
+      </c>
+      <c r="G12" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I12" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K12" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L12" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M12" s="33" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C13">
+        <v>272</v>
+      </c>
+      <c r="D13" t="s">
+        <v>892</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F13" s="35" t="s">
+        <v>948</v>
+      </c>
+      <c r="G13" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I13" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K13" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L13" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="M13" s="33" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A14" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C14">
+        <v>273</v>
+      </c>
+      <c r="D14" t="s">
+        <v>893</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F14" s="35" t="s">
+        <v>949</v>
+      </c>
+      <c r="G14" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I14" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K14" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L14" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M14" s="33" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A15" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C15">
+        <v>274</v>
+      </c>
+      <c r="D15" t="s">
+        <v>894</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F15" s="35" t="s">
+        <v>950</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I15" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K15" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L15" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M15" s="33" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C16">
+        <v>275</v>
+      </c>
+      <c r="D16" t="s">
+        <v>936</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F16" s="35" t="s">
+        <v>951</v>
+      </c>
+      <c r="G16" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I16" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K16" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L16" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M16" s="33" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A17" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C17">
+        <v>276</v>
+      </c>
+      <c r="D17" t="s">
+        <v>895</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F17" s="35" t="s">
+        <v>952</v>
+      </c>
+      <c r="G17" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I17" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K17" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L17" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M17" s="33" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A18" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C18">
+        <v>277</v>
+      </c>
+      <c r="D18" t="s">
+        <v>896</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F18" s="35" t="s">
+        <v>953</v>
+      </c>
+      <c r="G18" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I18" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K18" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L18" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M18" s="33" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A19" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C19">
+        <v>278</v>
+      </c>
+      <c r="D19" t="s">
+        <v>897</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F19" s="35" t="s">
+        <v>954</v>
+      </c>
+      <c r="G19" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I19" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K19" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L19" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M19" s="33" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A20" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C20">
+        <v>279</v>
+      </c>
+      <c r="D20" t="s">
+        <v>898</v>
+      </c>
+      <c r="E20" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F20" s="35" t="s">
+        <v>955</v>
+      </c>
+      <c r="G20" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I20" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K20" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L20" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M20" s="33" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A21" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C21">
+        <v>280</v>
+      </c>
+      <c r="D21" t="s">
+        <v>899</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F21" s="35" t="s">
+        <v>956</v>
+      </c>
+      <c r="G21" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I21" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K21" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L21" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M21" s="33" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A22" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C22">
+        <v>281</v>
+      </c>
+      <c r="D22" t="s">
+        <v>900</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F22" s="35" t="s">
+        <v>957</v>
+      </c>
+      <c r="G22" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I22" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K22" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L22" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M22" s="33" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A23" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C23">
+        <v>282</v>
+      </c>
+      <c r="D23" t="s">
+        <v>901</v>
+      </c>
+      <c r="E23" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F23" s="35" t="s">
+        <v>958</v>
+      </c>
+      <c r="G23" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I23" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K23" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L23" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M23" s="33" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A24" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C24">
+        <v>283</v>
+      </c>
+      <c r="D24" t="s">
+        <v>902</v>
+      </c>
+      <c r="E24" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F24" s="35" t="s">
+        <v>959</v>
+      </c>
+      <c r="G24" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I24" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K24" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L24" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M24" s="33" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A25" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C25">
+        <v>284</v>
+      </c>
+      <c r="D25" t="s">
+        <v>903</v>
+      </c>
+      <c r="E25" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F25" s="35" t="s">
+        <v>960</v>
+      </c>
+      <c r="G25" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I25" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K25" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L25" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M25" s="33" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A26" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C26">
+        <v>285</v>
+      </c>
+      <c r="D26" t="s">
+        <v>904</v>
+      </c>
+      <c r="E26" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F26" s="35" t="s">
+        <v>961</v>
+      </c>
+      <c r="G26" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I26" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K26" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L26" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M26" s="33" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A27" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C27">
+        <v>286</v>
+      </c>
+      <c r="D27" t="s">
+        <v>905</v>
+      </c>
+      <c r="E27" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F27" s="35" t="s">
+        <v>962</v>
+      </c>
+      <c r="G27" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I27" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K27" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L27" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M27" s="33" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A28" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C28">
+        <v>287</v>
+      </c>
+      <c r="D28" t="s">
+        <v>906</v>
+      </c>
+      <c r="E28" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F28" s="35" t="s">
+        <v>963</v>
+      </c>
+      <c r="G28" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I28" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K28" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L28" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M28" s="33" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A29" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C29">
+        <v>288</v>
+      </c>
+      <c r="D29" t="s">
+        <v>907</v>
+      </c>
+      <c r="E29" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F29" s="35" t="s">
+        <v>964</v>
+      </c>
+      <c r="G29" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I29" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J29" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K29" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L29" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M29" s="33" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A30" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C30">
+        <v>289</v>
+      </c>
+      <c r="D30" t="s">
+        <v>908</v>
+      </c>
+      <c r="E30" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F30" s="35" t="s">
+        <v>965</v>
+      </c>
+      <c r="G30" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I30" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K30" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L30" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M30" s="33" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A31" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C31">
+        <v>290</v>
+      </c>
+      <c r="D31" t="s">
+        <v>909</v>
+      </c>
+      <c r="E31" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F31" s="35" t="s">
+        <v>966</v>
+      </c>
+      <c r="G31" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I31" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K31" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L31" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M31" s="33" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A32" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C32">
+        <v>300</v>
+      </c>
+      <c r="D32" t="s">
+        <v>910</v>
+      </c>
+      <c r="E32" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F32" s="35" t="s">
+        <v>967</v>
+      </c>
+      <c r="G32" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I32" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K32" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L32" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M32" s="33" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A33" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C33">
+        <v>301</v>
+      </c>
+      <c r="D33" t="s">
+        <v>911</v>
+      </c>
+      <c r="E33" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F33" s="35" t="s">
+        <v>968</v>
+      </c>
+      <c r="G33" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I33" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K33" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L33" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M33" s="33" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A34" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C34">
+        <v>302</v>
+      </c>
+      <c r="D34" t="s">
+        <v>912</v>
+      </c>
+      <c r="E34" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F34" s="35" t="s">
+        <v>969</v>
+      </c>
+      <c r="G34" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H34" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I34" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K34" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L34" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M34" s="33" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A35" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C35">
+        <v>303</v>
+      </c>
+      <c r="D35" t="s">
+        <v>913</v>
+      </c>
+      <c r="E35" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F35" s="35" t="s">
+        <v>970</v>
+      </c>
+      <c r="G35" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I35" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K35" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L35" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M35" s="33" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A36" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C36">
+        <v>304</v>
+      </c>
+      <c r="D36" t="s">
+        <v>914</v>
+      </c>
+      <c r="E36" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F36" s="35" t="s">
+        <v>971</v>
+      </c>
+      <c r="G36" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I36" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K36" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L36" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M36" s="33" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A37" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B37" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C37">
+        <v>305</v>
+      </c>
+      <c r="D37" t="s">
+        <v>915</v>
+      </c>
+      <c r="E37" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F37" s="35" t="s">
+        <v>972</v>
+      </c>
+      <c r="G37" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H37" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I37" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K37" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L37" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M37" s="33" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A38" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C38">
+        <v>306</v>
+      </c>
+      <c r="D38" t="s">
+        <v>916</v>
+      </c>
+      <c r="E38" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F38" s="35" t="s">
+        <v>986</v>
+      </c>
+      <c r="G38" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I38" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J38" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K38" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L38" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M38" s="33" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A39" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C39">
+        <v>307</v>
+      </c>
+      <c r="D39" t="s">
+        <v>917</v>
+      </c>
+      <c r="E39" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F39" s="35" t="s">
+        <v>987</v>
+      </c>
+      <c r="G39" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H39" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I39" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J39" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K39" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L39" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M39" s="33" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A40" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C40">
+        <v>308</v>
+      </c>
+      <c r="D40" t="s">
+        <v>918</v>
+      </c>
+      <c r="E40" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F40" s="35" t="s">
+        <v>988</v>
+      </c>
+      <c r="G40" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H40" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I40" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K40" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L40" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M40" s="33" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A41" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C41">
+        <v>309</v>
+      </c>
+      <c r="D41" t="s">
+        <v>919</v>
+      </c>
+      <c r="E41" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F41" s="35" t="s">
+        <v>989</v>
+      </c>
+      <c r="G41" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H41" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I41" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K41" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L41" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M41" s="33" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A42" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B42" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C42">
+        <v>310</v>
+      </c>
+      <c r="D42" t="s">
+        <v>920</v>
+      </c>
+      <c r="E42" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F42" s="35" t="s">
+        <v>990</v>
+      </c>
+      <c r="G42" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H42" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I42" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K42" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L42" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M42" s="33" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A43" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C43">
+        <v>311</v>
+      </c>
+      <c r="D43" t="s">
+        <v>921</v>
+      </c>
+      <c r="E43" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F43" s="35" t="s">
+        <v>991</v>
+      </c>
+      <c r="G43" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="H43" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I43" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="J43" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K43" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L43" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M43" s="33" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A44" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C44">
+        <v>312</v>
+      </c>
+      <c r="D44" t="s">
+        <v>922</v>
+      </c>
+      <c r="E44" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F44" s="35" t="s">
+        <v>992</v>
+      </c>
+      <c r="G44" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I44" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K44" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L44" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M44" s="33" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A45" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B45" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C45">
+        <v>313</v>
+      </c>
+      <c r="D45" t="s">
+        <v>923</v>
+      </c>
+      <c r="E45" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F45" s="35" t="s">
+        <v>973</v>
+      </c>
+      <c r="G45" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="H45" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I45" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="J45" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K45" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L45" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M45" s="33" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A46" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C46">
+        <v>314</v>
+      </c>
+      <c r="D46" t="s">
+        <v>924</v>
+      </c>
+      <c r="E46" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F46" s="35" t="s">
+        <v>974</v>
+      </c>
+      <c r="G46" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H46" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I46" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K46" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L46" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M46" s="33" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A47" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C47">
+        <v>315</v>
+      </c>
+      <c r="D47" t="s">
+        <v>925</v>
+      </c>
+      <c r="E47" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F47" s="35" t="s">
+        <v>975</v>
+      </c>
+      <c r="G47" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H47" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I47" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J47" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K47" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L47" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M47" s="33" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A48" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C48">
+        <v>316</v>
+      </c>
+      <c r="D48" t="s">
+        <v>926</v>
+      </c>
+      <c r="E48" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F48" s="35" t="s">
+        <v>976</v>
+      </c>
+      <c r="G48" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H48" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I48" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J48" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K48" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L48" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M48" s="33" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A49" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C49">
+        <v>317</v>
+      </c>
+      <c r="D49" t="s">
+        <v>927</v>
+      </c>
+      <c r="E49" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F49" s="35" t="s">
+        <v>977</v>
+      </c>
+      <c r="G49" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H49" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I49" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J49" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K49" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L49" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M49" s="33" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A50" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B50" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C50">
+        <v>318</v>
+      </c>
+      <c r="D50" t="s">
+        <v>928</v>
+      </c>
+      <c r="E50" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F50" s="35" t="s">
+        <v>978</v>
+      </c>
+      <c r="G50" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H50" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I50" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J50" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K50" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L50" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M50" s="33" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A51" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B51" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C51">
+        <v>319</v>
+      </c>
+      <c r="D51" t="s">
+        <v>935</v>
+      </c>
+      <c r="E51" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F51" s="35" t="s">
+        <v>979</v>
+      </c>
+      <c r="G51" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="H51" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I51" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="J51" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K51" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L51" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M51" s="33" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A52" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B52" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C52">
+        <v>320</v>
+      </c>
+      <c r="D52" s="34" t="s">
+        <v>929</v>
+      </c>
+      <c r="E52" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F52" s="35" t="s">
+        <v>980</v>
+      </c>
+      <c r="G52" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="H52" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I52" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="J52" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K52" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L52" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M52" s="33" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A53" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B53" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C53">
+        <v>321</v>
+      </c>
+      <c r="D53" t="s">
+        <v>931</v>
+      </c>
+      <c r="E53" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F53" s="35" t="s">
+        <v>981</v>
+      </c>
+      <c r="G53" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="H53" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I53" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="J53" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K53" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L53" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M53" s="33" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A54" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B54" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C54">
+        <v>322</v>
+      </c>
+      <c r="D54" t="s">
+        <v>930</v>
+      </c>
+      <c r="E54" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F54" s="35" t="s">
+        <v>982</v>
+      </c>
+      <c r="G54" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H54" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I54" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J54" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K54" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L54" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M54" s="33" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A55" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C55">
+        <v>323</v>
+      </c>
+      <c r="D55" t="s">
+        <v>932</v>
+      </c>
+      <c r="E55" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F55" s="35" t="s">
+        <v>983</v>
+      </c>
+      <c r="G55" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H55" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I55" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J55" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K55" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L55" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M55" s="33" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A56" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B56" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C56">
+        <v>324</v>
+      </c>
+      <c r="D56" t="s">
+        <v>933</v>
+      </c>
+      <c r="E56" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F56" s="35" t="s">
+        <v>984</v>
+      </c>
+      <c r="G56" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H56" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I56" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J56" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K56" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L56" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M56" s="33" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A57" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B57" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C57">
+        <v>325</v>
+      </c>
+      <c r="D57" t="s">
+        <v>934</v>
+      </c>
+      <c r="E57" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="F57" s="35" t="s">
+        <v>985</v>
+      </c>
+      <c r="G57" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H57" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I57" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J57" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="K57" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L57" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M57" s="33" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M61" s="36"/>
+    </row>
+  </sheetData>
+  <dataValidations count="7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E57" xr:uid="{67AB5275-FF72-4E82-82DF-159D3AB1C986}">
+      <formula1>INDIRECT("Table5")</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I43 I51:I53 I45 G51:G53 G43 G45" xr:uid="{9A48FCCC-3AB2-4FA8-BCF2-7796D6D230D5}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H57" xr:uid="{C53359B7-79CF-43CF-8F69-1D2475420017}">
+      <formula1>INDIRECT("Table11")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J57" xr:uid="{68C0FD90-1F22-4205-90DE-A0862FF00E8F}">
+      <formula1>INDIRECT("Table8")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L57" xr:uid="{A1196CE0-7546-40CE-A19A-3824850A8439}">
+      <formula1>INDIRECT("Table9")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I42 I54:I57 I44 I46:I50" xr:uid="{2AC3C20B-57FD-4F35-9E44-26AE20F8A514}">
+      <formula1>INDIRECT("Table10")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G54:G57 G2:G42 G44 G46:G50" xr:uid="{D112DEFD-E2CB-4DDC-BAB0-A4DD9999630C}">
+      <formula1>INDIRECT("Table7")</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -23350,7 +28585,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF34920F-246D-48E3-8E4A-083842820E12}">
   <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.453125" customWidth="1"/>
@@ -23743,13 +28978,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C777F76-2F56-4C54-90B9-B8F9505EC5A0}">
   <dimension ref="A1:M16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="37.81640625" customWidth="1"/>
     <col min="5" max="5" width="15.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="52.81640625" customWidth="1"/>
-    <col min="7" max="7" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.1796875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23.81640625" customWidth="1"/>
     <col min="11" max="11" width="9.1796875" bestFit="1" customWidth="1"/>
@@ -24421,7 +29656,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EBEDDA4-AF1C-47A2-A14A-E46013CE0DAB}">
   <dimension ref="A1:M20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="35.81640625" customWidth="1"/>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/Round 2 Pods for Testing/Slow Track Pods/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{039B129C-6E1C-9546-893A-9CF2E360C3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1BE152F-2672-42E8-B5E4-026CEDDB8209}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{039B129C-6E1C-9546-893A-9CF2E360C3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0295CF91-57BC-48BA-BB52-C4E002EE58DB}"/>
   <bookViews>
-    <workbookView xWindow="-26340" yWindow="1245" windowWidth="23085" windowHeight="13650" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="5" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7751" uniqueCount="993">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7751" uniqueCount="992">
   <si>
     <t>schema</t>
   </si>
@@ -1651,9 +1651,6 @@
   </si>
   <si>
     <t>unit.credit_block[].block_end</t>
-  </si>
-  <si>
-    <t>unit.credit_block[]block_start</t>
   </si>
   <si>
     <t>validation.validation[].validation_id</t>
@@ -3283,7 +3280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3353,7 +3350,6 @@
     <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4645,7 +4641,7 @@
         <v>58</v>
       </c>
       <c r="M23" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
@@ -4686,7 +4682,7 @@
         <v>58</v>
       </c>
       <c r="M24" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
@@ -4727,7 +4723,7 @@
         <v>58</v>
       </c>
       <c r="M25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
@@ -4768,7 +4764,7 @@
         <v>58</v>
       </c>
       <c r="M26" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
@@ -4809,7 +4805,7 @@
         <v>58</v>
       </c>
       <c r="M27" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
@@ -4850,7 +4846,7 @@
         <v>58</v>
       </c>
       <c r="M28" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
@@ -5772,7 +5768,7 @@
         <v>159</v>
       </c>
       <c r="F51" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="G51" t="s">
         <v>30</v>
@@ -9952,7 +9948,7 @@
         <v>438</v>
       </c>
       <c r="F153" t="s">
-        <v>533</v>
+        <v>753</v>
       </c>
       <c r="G153" t="s">
         <v>18</v>
@@ -10034,7 +10030,7 @@
         <v>260</v>
       </c>
       <c r="F155" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="G155" t="s">
         <v>18</v>
@@ -10049,7 +10045,7 @@
         <v>439</v>
       </c>
       <c r="K155" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="L155" t="s">
         <v>140</v>
@@ -10075,7 +10071,7 @@
         <v>260</v>
       </c>
       <c r="F156" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="G156" t="s">
         <v>18</v>
@@ -10116,7 +10112,7 @@
         <v>260</v>
       </c>
       <c r="F157" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="G157" t="s">
         <v>18</v>
@@ -10157,7 +10153,7 @@
         <v>260</v>
       </c>
       <c r="F158" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G158" t="s">
         <v>18</v>
@@ -10198,7 +10194,7 @@
         <v>16</v>
       </c>
       <c r="F159" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G159" t="s">
         <v>30</v>
@@ -10239,7 +10235,7 @@
         <v>16</v>
       </c>
       <c r="F160" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="G160" t="s">
         <v>30</v>
@@ -10280,7 +10276,7 @@
         <v>16</v>
       </c>
       <c r="F161" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G161" t="s">
         <v>30</v>
@@ -10321,7 +10317,7 @@
         <v>16</v>
       </c>
       <c r="F162" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G162" t="s">
         <v>30</v>
@@ -10362,7 +10358,7 @@
         <v>488</v>
       </c>
       <c r="F163" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G163" s="18" t="s">
         <v>18</v>
@@ -10403,7 +10399,7 @@
         <v>488</v>
       </c>
       <c r="F164" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G164" s="18" t="s">
         <v>18</v>
@@ -10444,7 +10440,7 @@
         <v>488</v>
       </c>
       <c r="F165" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G165" s="18" t="s">
         <v>18</v>
@@ -10485,7 +10481,7 @@
         <v>488</v>
       </c>
       <c r="F166" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G166" s="18" t="s">
         <v>30</v>
@@ -10526,7 +10522,7 @@
         <v>488</v>
       </c>
       <c r="F167" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G167" s="6" t="s">
         <v>30</v>
@@ -10567,7 +10563,7 @@
         <v>16</v>
       </c>
       <c r="F168" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G168" s="18" t="s">
         <v>18</v>
@@ -10608,7 +10604,7 @@
         <v>16</v>
       </c>
       <c r="F169" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G169" s="18" t="s">
         <v>18</v>
@@ -10690,7 +10686,7 @@
         <v>260</v>
       </c>
       <c r="F171" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G171" s="18" t="s">
         <v>18</v>
@@ -10731,7 +10727,7 @@
         <v>260</v>
       </c>
       <c r="F172" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G172" s="18" t="s">
         <v>18</v>
@@ -10772,7 +10768,7 @@
         <v>488</v>
       </c>
       <c r="F173" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G173" s="6" t="s">
         <v>30</v>
@@ -10813,7 +10809,7 @@
         <v>488</v>
       </c>
       <c r="F174" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G174" s="6" t="s">
         <v>30</v>
@@ -10854,7 +10850,7 @@
         <v>488</v>
       </c>
       <c r="F175" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G175" s="6" t="s">
         <v>30</v>
@@ -10895,7 +10891,7 @@
         <v>488</v>
       </c>
       <c r="F176" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G176" s="6" t="s">
         <v>30</v>
@@ -10936,7 +10932,7 @@
         <v>488</v>
       </c>
       <c r="F177" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G177" s="18" t="s">
         <v>186</v>
@@ -10971,16 +10967,16 @@
         <v>177</v>
       </c>
       <c r="D178" s="24" t="s">
+        <v>554</v>
+      </c>
+      <c r="E178" t="s">
         <v>555</v>
       </c>
-      <c r="E178" t="s">
+      <c r="F178" t="s">
         <v>556</v>
       </c>
-      <c r="F178" t="s">
+      <c r="G178" s="24" t="s">
         <v>557</v>
-      </c>
-      <c r="G178" s="24" t="s">
-        <v>558</v>
       </c>
       <c r="H178" s="24" t="s">
         <v>137</v>
@@ -10989,7 +10985,7 @@
         <v>20</v>
       </c>
       <c r="J178" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K178" s="24" t="s">
         <v>157</v>
@@ -10998,7 +10994,7 @@
         <v>140</v>
       </c>
       <c r="M178" s="27" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="179" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -11012,16 +11008,16 @@
         <v>178</v>
       </c>
       <c r="D179" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="E179" t="s">
+        <v>555</v>
+      </c>
+      <c r="F179" t="s">
         <v>561</v>
       </c>
-      <c r="E179" t="s">
-        <v>556</v>
-      </c>
-      <c r="F179" t="s">
-        <v>562</v>
-      </c>
       <c r="G179" s="24" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H179" s="24" t="s">
         <v>153</v>
@@ -11030,7 +11026,7 @@
         <v>20</v>
       </c>
       <c r="J179" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K179" s="24" t="s">
         <v>157</v>
@@ -11039,7 +11035,7 @@
         <v>140</v>
       </c>
       <c r="M179" s="27" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.35">
@@ -11053,13 +11049,13 @@
         <v>179</v>
       </c>
       <c r="D180" s="25" t="s">
+        <v>563</v>
+      </c>
+      <c r="E180" t="s">
+        <v>555</v>
+      </c>
+      <c r="F180" t="s">
         <v>564</v>
-      </c>
-      <c r="E180" t="s">
-        <v>556</v>
-      </c>
-      <c r="F180" t="s">
-        <v>565</v>
       </c>
       <c r="G180" s="25" t="s">
         <v>18</v>
@@ -11071,7 +11067,7 @@
         <v>20</v>
       </c>
       <c r="J180" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K180" s="24" t="s">
         <v>157</v>
@@ -11080,7 +11076,7 @@
         <v>140</v>
       </c>
       <c r="M180" s="27" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.35">
@@ -11094,13 +11090,13 @@
         <v>180</v>
       </c>
       <c r="D181" s="26" t="s">
+        <v>566</v>
+      </c>
+      <c r="E181" t="s">
+        <v>555</v>
+      </c>
+      <c r="F181" t="s">
         <v>567</v>
-      </c>
-      <c r="E181" t="s">
-        <v>556</v>
-      </c>
-      <c r="F181" t="s">
-        <v>568</v>
       </c>
       <c r="G181" s="24" t="s">
         <v>30</v>
@@ -11112,7 +11108,7 @@
         <v>138</v>
       </c>
       <c r="J181" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K181" s="24" t="s">
         <v>157</v>
@@ -11121,7 +11117,7 @@
         <v>140</v>
       </c>
       <c r="M181" s="27" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="182" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -11135,13 +11131,13 @@
         <v>181</v>
       </c>
       <c r="D182" s="26" t="s">
+        <v>569</v>
+      </c>
+      <c r="E182" t="s">
+        <v>555</v>
+      </c>
+      <c r="F182" t="s">
         <v>570</v>
-      </c>
-      <c r="E182" t="s">
-        <v>556</v>
-      </c>
-      <c r="F182" t="s">
-        <v>571</v>
       </c>
       <c r="G182" s="24" t="s">
         <v>30</v>
@@ -11153,7 +11149,7 @@
         <v>138</v>
       </c>
       <c r="J182" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K182" s="24" t="s">
         <v>157</v>
@@ -11162,7 +11158,7 @@
         <v>140</v>
       </c>
       <c r="M182" s="27" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.35">
@@ -11176,13 +11172,13 @@
         <v>182</v>
       </c>
       <c r="D183" s="26" t="s">
+        <v>572</v>
+      </c>
+      <c r="E183" t="s">
+        <v>555</v>
+      </c>
+      <c r="F183" t="s">
         <v>573</v>
-      </c>
-      <c r="E183" t="s">
-        <v>556</v>
-      </c>
-      <c r="F183" t="s">
-        <v>574</v>
       </c>
       <c r="G183" s="25" t="s">
         <v>30</v>
@@ -11194,7 +11190,7 @@
         <v>138</v>
       </c>
       <c r="J183" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K183" s="24" t="s">
         <v>157</v>
@@ -11203,7 +11199,7 @@
         <v>140</v>
       </c>
       <c r="M183" s="27" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.35">
@@ -11217,13 +11213,13 @@
         <v>183</v>
       </c>
       <c r="D184" s="25" t="s">
+        <v>575</v>
+      </c>
+      <c r="E184" t="s">
+        <v>555</v>
+      </c>
+      <c r="F184" t="s">
         <v>576</v>
-      </c>
-      <c r="E184" t="s">
-        <v>556</v>
-      </c>
-      <c r="F184" t="s">
-        <v>577</v>
       </c>
       <c r="G184" s="25" t="s">
         <v>30</v>
@@ -11235,7 +11231,7 @@
         <v>138</v>
       </c>
       <c r="J184" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K184" s="24" t="s">
         <v>157</v>
@@ -11244,7 +11240,7 @@
         <v>140</v>
       </c>
       <c r="M184" s="27" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.35">
@@ -11258,13 +11254,13 @@
         <v>184</v>
       </c>
       <c r="D185" s="25" t="s">
+        <v>578</v>
+      </c>
+      <c r="E185" t="s">
+        <v>555</v>
+      </c>
+      <c r="F185" t="s">
         <v>579</v>
-      </c>
-      <c r="E185" t="s">
-        <v>556</v>
-      </c>
-      <c r="F185" t="s">
-        <v>580</v>
       </c>
       <c r="G185" s="25" t="s">
         <v>30</v>
@@ -11276,7 +11272,7 @@
         <v>138</v>
       </c>
       <c r="J185" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K185" s="24" t="s">
         <v>157</v>
@@ -11285,7 +11281,7 @@
         <v>140</v>
       </c>
       <c r="M185" s="27" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.35">
@@ -11299,13 +11295,13 @@
         <v>185</v>
       </c>
       <c r="D186" s="25" t="s">
+        <v>581</v>
+      </c>
+      <c r="E186" t="s">
+        <v>555</v>
+      </c>
+      <c r="F186" t="s">
         <v>582</v>
-      </c>
-      <c r="E186" t="s">
-        <v>556</v>
-      </c>
-      <c r="F186" t="s">
-        <v>583</v>
       </c>
       <c r="G186" s="25" t="s">
         <v>30</v>
@@ -11317,7 +11313,7 @@
         <v>138</v>
       </c>
       <c r="J186" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K186" s="24" t="s">
         <v>157</v>
@@ -11326,7 +11322,7 @@
         <v>140</v>
       </c>
       <c r="M186" s="27" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.35">
@@ -11340,13 +11336,13 @@
         <v>186</v>
       </c>
       <c r="D187" s="25" t="s">
+        <v>584</v>
+      </c>
+      <c r="E187" t="s">
+        <v>555</v>
+      </c>
+      <c r="F187" t="s">
         <v>585</v>
-      </c>
-      <c r="E187" t="s">
-        <v>556</v>
-      </c>
-      <c r="F187" t="s">
-        <v>586</v>
       </c>
       <c r="G187" s="25" t="s">
         <v>30</v>
@@ -11358,7 +11354,7 @@
         <v>138</v>
       </c>
       <c r="J187" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K187" s="24" t="s">
         <v>157</v>
@@ -11367,7 +11363,7 @@
         <v>140</v>
       </c>
       <c r="M187" s="27" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.35">
@@ -11381,13 +11377,13 @@
         <v>187</v>
       </c>
       <c r="D188" s="25" t="s">
+        <v>587</v>
+      </c>
+      <c r="E188" t="s">
+        <v>555</v>
+      </c>
+      <c r="F188" t="s">
         <v>588</v>
-      </c>
-      <c r="E188" t="s">
-        <v>556</v>
-      </c>
-      <c r="F188" t="s">
-        <v>589</v>
       </c>
       <c r="G188" s="25" t="s">
         <v>30</v>
@@ -11399,7 +11395,7 @@
         <v>138</v>
       </c>
       <c r="J188" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K188" s="24" t="s">
         <v>157</v>
@@ -11408,7 +11404,7 @@
         <v>140</v>
       </c>
       <c r="M188" s="27" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="189" spans="1:13" x14ac:dyDescent="0.35">
@@ -11422,13 +11418,13 @@
         <v>188</v>
       </c>
       <c r="D189" s="25" t="s">
+        <v>590</v>
+      </c>
+      <c r="E189" t="s">
+        <v>555</v>
+      </c>
+      <c r="F189" t="s">
         <v>591</v>
-      </c>
-      <c r="E189" t="s">
-        <v>556</v>
-      </c>
-      <c r="F189" t="s">
-        <v>592</v>
       </c>
       <c r="G189" s="25" t="s">
         <v>30</v>
@@ -11440,7 +11436,7 @@
         <v>138</v>
       </c>
       <c r="J189" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K189" s="24" t="s">
         <v>157</v>
@@ -11449,7 +11445,7 @@
         <v>140</v>
       </c>
       <c r="M189" s="27" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.35">
@@ -11463,25 +11459,25 @@
         <v>189</v>
       </c>
       <c r="D190" s="25" t="s">
+        <v>593</v>
+      </c>
+      <c r="E190" t="s">
+        <v>555</v>
+      </c>
+      <c r="F190" t="s">
         <v>594</v>
       </c>
-      <c r="E190" t="s">
-        <v>556</v>
-      </c>
-      <c r="F190" t="s">
+      <c r="G190" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="H190" s="24" t="s">
         <v>595</v>
-      </c>
-      <c r="G190" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="H190" s="24" t="s">
-        <v>596</v>
       </c>
       <c r="I190" s="24" t="s">
         <v>138</v>
       </c>
       <c r="J190" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K190" s="24" t="s">
         <v>157</v>
@@ -11490,7 +11486,7 @@
         <v>140</v>
       </c>
       <c r="M190" s="27" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.35">
@@ -11504,13 +11500,13 @@
         <v>190</v>
       </c>
       <c r="D191" s="24" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E191" s="24" t="s">
+        <v>597</v>
+      </c>
+      <c r="F191" t="s">
         <v>598</v>
-      </c>
-      <c r="F191" t="s">
-        <v>599</v>
       </c>
       <c r="G191" s="24" t="s">
         <v>18</v>
@@ -11522,7 +11518,7 @@
         <v>20</v>
       </c>
       <c r="J191" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K191" s="24" t="s">
         <v>157</v>
@@ -11531,7 +11527,7 @@
         <v>140</v>
       </c>
       <c r="M191" s="27" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="192" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -11545,13 +11541,13 @@
         <v>191</v>
       </c>
       <c r="D192" s="26" t="s">
+        <v>599</v>
+      </c>
+      <c r="E192" s="24" t="s">
+        <v>597</v>
+      </c>
+      <c r="F192" t="s">
         <v>600</v>
-      </c>
-      <c r="E192" s="24" t="s">
-        <v>598</v>
-      </c>
-      <c r="F192" t="s">
-        <v>601</v>
       </c>
       <c r="G192" s="24" t="s">
         <v>30</v>
@@ -11563,7 +11559,7 @@
         <v>138</v>
       </c>
       <c r="J192" s="24" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K192" s="24" t="s">
         <v>157</v>
@@ -11572,7 +11568,7 @@
         <v>140</v>
       </c>
       <c r="M192" s="27" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.35">
@@ -11586,13 +11582,13 @@
         <v>192</v>
       </c>
       <c r="D193" s="26" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E193" s="24" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F193" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G193" s="24" t="s">
         <v>30</v>
@@ -11604,7 +11600,7 @@
         <v>138</v>
       </c>
       <c r="J193" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K193" s="24" t="s">
         <v>157</v>
@@ -11613,7 +11609,7 @@
         <v>140</v>
       </c>
       <c r="M193" s="27" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="194" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -11627,13 +11623,13 @@
         <v>193</v>
       </c>
       <c r="D194" s="24" t="s">
+        <v>604</v>
+      </c>
+      <c r="E194" s="24" t="s">
+        <v>597</v>
+      </c>
+      <c r="F194" t="s">
         <v>605</v>
-      </c>
-      <c r="E194" s="24" t="s">
-        <v>598</v>
-      </c>
-      <c r="F194" t="s">
-        <v>606</v>
       </c>
       <c r="G194" s="24" t="s">
         <v>30</v>
@@ -11645,7 +11641,7 @@
         <v>138</v>
       </c>
       <c r="J194" s="24" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K194" s="24" t="s">
         <v>157</v>
@@ -11654,7 +11650,7 @@
         <v>140</v>
       </c>
       <c r="M194" s="27" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="195" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -11668,13 +11664,13 @@
         <v>194</v>
       </c>
       <c r="D195" s="24" t="s">
+        <v>607</v>
+      </c>
+      <c r="E195" s="24" t="s">
+        <v>597</v>
+      </c>
+      <c r="F195" t="s">
         <v>608</v>
-      </c>
-      <c r="E195" s="24" t="s">
-        <v>598</v>
-      </c>
-      <c r="F195" t="s">
-        <v>609</v>
       </c>
       <c r="G195" s="24" t="s">
         <v>30</v>
@@ -11686,7 +11682,7 @@
         <v>138</v>
       </c>
       <c r="J195" s="24" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K195" s="24" t="s">
         <v>157</v>
@@ -11695,7 +11691,7 @@
         <v>140</v>
       </c>
       <c r="M195" s="27" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="196" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -11709,25 +11705,25 @@
         <v>195</v>
       </c>
       <c r="D196" s="24" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E196" s="24" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F196" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G196" s="24" t="s">
         <v>30</v>
       </c>
       <c r="H196" s="24" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I196" s="24" t="s">
         <v>138</v>
       </c>
       <c r="J196" s="24" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K196" s="24" t="s">
         <v>157</v>
@@ -11736,7 +11732,7 @@
         <v>140</v>
       </c>
       <c r="M196" s="27" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.35">
@@ -11750,13 +11746,13 @@
         <v>196</v>
       </c>
       <c r="D197" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E197" t="s">
         <v>16</v>
       </c>
       <c r="F197" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G197" t="s">
         <v>18</v>
@@ -11777,7 +11773,7 @@
         <v>140</v>
       </c>
       <c r="M197" s="19" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.35">
@@ -11791,13 +11787,13 @@
         <v>197</v>
       </c>
       <c r="D198" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E198" t="s">
         <v>16</v>
       </c>
       <c r="F198" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G198" t="s">
         <v>18</v>
@@ -11818,7 +11814,7 @@
         <v>140</v>
       </c>
       <c r="M198" s="19" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.35">
@@ -11832,13 +11828,13 @@
         <v>198</v>
       </c>
       <c r="D199" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E199" t="s">
         <v>16</v>
       </c>
       <c r="F199" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G199" t="s">
         <v>18</v>
@@ -11859,7 +11855,7 @@
         <v>140</v>
       </c>
       <c r="M199" s="19" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.35">
@@ -11873,13 +11869,13 @@
         <v>199</v>
       </c>
       <c r="D200" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E200" t="s">
         <v>16</v>
       </c>
       <c r="F200" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G200" t="s">
         <v>18</v>
@@ -11900,7 +11896,7 @@
         <v>140</v>
       </c>
       <c r="M200" s="19" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.35">
@@ -11914,19 +11910,19 @@
         <v>200</v>
       </c>
       <c r="D201" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E201" t="s">
         <v>16</v>
       </c>
       <c r="F201" t="s">
+        <v>625</v>
+      </c>
+      <c r="G201" t="s">
+        <v>30</v>
+      </c>
+      <c r="H201" t="s">
         <v>626</v>
-      </c>
-      <c r="G201" t="s">
-        <v>30</v>
-      </c>
-      <c r="H201" t="s">
-        <v>627</v>
       </c>
       <c r="I201" t="s">
         <v>138</v>
@@ -11941,7 +11937,7 @@
         <v>140</v>
       </c>
       <c r="M201" s="18" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="202" spans="1:13" x14ac:dyDescent="0.35">
@@ -11955,13 +11951,13 @@
         <v>201</v>
       </c>
       <c r="D202" s="17" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E202" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F202" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G202" s="17" t="s">
         <v>186</v>
@@ -11982,7 +11978,7 @@
         <v>140</v>
       </c>
       <c r="M202" s="17" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="203" spans="1:13" x14ac:dyDescent="0.35">
@@ -11996,13 +11992,13 @@
         <v>202</v>
       </c>
       <c r="D203" s="17" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E203" s="17" t="s">
         <v>25</v>
       </c>
       <c r="F203" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="G203" s="17" t="s">
         <v>30</v>
@@ -12023,7 +12019,7 @@
         <v>140</v>
       </c>
       <c r="M203" s="17" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="204" spans="1:13" x14ac:dyDescent="0.35">
@@ -12037,13 +12033,13 @@
         <v>203</v>
       </c>
       <c r="D204" s="17" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E204" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F204" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G204" s="17" t="s">
         <v>18</v>
@@ -12064,7 +12060,7 @@
         <v>140</v>
       </c>
       <c r="M204" s="17" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.35">
@@ -12078,13 +12074,13 @@
         <v>204</v>
       </c>
       <c r="D205" s="17" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E205" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F205" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G205" s="17" t="s">
         <v>18</v>
@@ -12105,7 +12101,7 @@
         <v>140</v>
       </c>
       <c r="M205" s="17" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.35">
@@ -12119,13 +12115,13 @@
         <v>205</v>
       </c>
       <c r="D206" s="17" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E206" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F206" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G206" s="17" t="s">
         <v>18</v>
@@ -12146,7 +12142,7 @@
         <v>140</v>
       </c>
       <c r="M206" s="17" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="207" spans="1:13" x14ac:dyDescent="0.35">
@@ -12160,13 +12156,13 @@
         <v>206</v>
       </c>
       <c r="D207" s="17" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E207" s="17" t="s">
         <v>438</v>
       </c>
       <c r="F207" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G207" s="17" t="s">
         <v>18</v>
@@ -12187,7 +12183,7 @@
         <v>248</v>
       </c>
       <c r="M207" s="17" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="208" spans="1:13" x14ac:dyDescent="0.35">
@@ -12201,13 +12197,13 @@
         <v>207</v>
       </c>
       <c r="D208" s="17" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E208" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F208" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G208" s="17" t="s">
         <v>18</v>
@@ -12228,7 +12224,7 @@
         <v>140</v>
       </c>
       <c r="M208" s="17" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="209" spans="1:13" x14ac:dyDescent="0.35">
@@ -12242,13 +12238,13 @@
         <v>208</v>
       </c>
       <c r="D209" s="17" t="s">
+        <v>649</v>
+      </c>
+      <c r="E209" s="17" t="s">
         <v>650</v>
       </c>
-      <c r="E209" s="17" t="s">
+      <c r="F209" t="s">
         <v>651</v>
-      </c>
-      <c r="F209" t="s">
-        <v>652</v>
       </c>
       <c r="G209" s="17" t="s">
         <v>30</v>
@@ -12260,7 +12256,7 @@
         <v>31</v>
       </c>
       <c r="J209" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K209" s="17" t="s">
         <v>157</v>
@@ -12269,7 +12265,7 @@
         <v>140</v>
       </c>
       <c r="M209" s="17" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="210" spans="1:13" x14ac:dyDescent="0.35">
@@ -12283,13 +12279,13 @@
         <v>209</v>
       </c>
       <c r="D210" s="17" t="s">
+        <v>654</v>
+      </c>
+      <c r="E210" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F210" t="s">
         <v>655</v>
-      </c>
-      <c r="E210" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F210" t="s">
-        <v>656</v>
       </c>
       <c r="G210" s="17" t="s">
         <v>30</v>
@@ -12301,7 +12297,7 @@
         <v>20</v>
       </c>
       <c r="J210" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K210" s="17" t="s">
         <v>157</v>
@@ -12310,7 +12306,7 @@
         <v>140</v>
       </c>
       <c r="M210" s="17" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="211" spans="1:13" x14ac:dyDescent="0.35">
@@ -12324,13 +12320,13 @@
         <v>210</v>
       </c>
       <c r="D211" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="E211" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F211" t="s">
         <v>658</v>
-      </c>
-      <c r="E211" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F211" t="s">
-        <v>659</v>
       </c>
       <c r="G211" s="17" t="s">
         <v>30</v>
@@ -12342,7 +12338,7 @@
         <v>31</v>
       </c>
       <c r="J211" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K211" s="17" t="s">
         <v>157</v>
@@ -12351,7 +12347,7 @@
         <v>140</v>
       </c>
       <c r="M211" s="17" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="212" spans="1:13" x14ac:dyDescent="0.35">
@@ -12365,13 +12361,13 @@
         <v>211</v>
       </c>
       <c r="D212" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="E212" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F212" t="s">
         <v>661</v>
-      </c>
-      <c r="E212" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F212" t="s">
-        <v>662</v>
       </c>
       <c r="G212" s="17" t="s">
         <v>30</v>
@@ -12383,7 +12379,7 @@
         <v>31</v>
       </c>
       <c r="J212" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K212" s="17" t="s">
         <v>157</v>
@@ -12392,7 +12388,7 @@
         <v>140</v>
       </c>
       <c r="M212" s="17" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.35">
@@ -12406,13 +12402,13 @@
         <v>212</v>
       </c>
       <c r="D213" s="17" t="s">
+        <v>663</v>
+      </c>
+      <c r="E213" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F213" t="s">
         <v>664</v>
-      </c>
-      <c r="E213" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F213" t="s">
-        <v>665</v>
       </c>
       <c r="G213" s="17" t="s">
         <v>30</v>
@@ -12424,7 +12420,7 @@
         <v>31</v>
       </c>
       <c r="J213" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K213" s="17" t="s">
         <v>157</v>
@@ -12433,7 +12429,7 @@
         <v>140</v>
       </c>
       <c r="M213" s="17" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="214" spans="1:13" x14ac:dyDescent="0.35">
@@ -12447,13 +12443,13 @@
         <v>213</v>
       </c>
       <c r="D214" s="17" t="s">
+        <v>666</v>
+      </c>
+      <c r="E214" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F214" t="s">
         <v>667</v>
-      </c>
-      <c r="E214" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F214" t="s">
-        <v>668</v>
       </c>
       <c r="G214" s="17" t="s">
         <v>30</v>
@@ -12465,7 +12461,7 @@
         <v>31</v>
       </c>
       <c r="J214" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K214" s="17" t="s">
         <v>157</v>
@@ -12474,7 +12470,7 @@
         <v>140</v>
       </c>
       <c r="M214" s="17" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="215" spans="1:13" x14ac:dyDescent="0.35">
@@ -12488,13 +12484,13 @@
         <v>214</v>
       </c>
       <c r="D215" s="17" t="s">
+        <v>669</v>
+      </c>
+      <c r="E215" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F215" t="s">
         <v>670</v>
-      </c>
-      <c r="E215" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F215" t="s">
-        <v>671</v>
       </c>
       <c r="G215" s="17" t="s">
         <v>30</v>
@@ -12506,7 +12502,7 @@
         <v>31</v>
       </c>
       <c r="J215" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K215" s="17" t="s">
         <v>157</v>
@@ -12515,7 +12511,7 @@
         <v>140</v>
       </c>
       <c r="M215" s="17" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="216" spans="1:13" x14ac:dyDescent="0.35">
@@ -12529,13 +12525,13 @@
         <v>215</v>
       </c>
       <c r="D216" s="17" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="E216" s="17" t="s">
         <v>25</v>
       </c>
       <c r="F216" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G216" s="17" t="s">
         <v>30</v>
@@ -12547,7 +12543,7 @@
         <v>31</v>
       </c>
       <c r="J216" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K216" s="17" t="s">
         <v>157</v>
@@ -12556,7 +12552,7 @@
         <v>140</v>
       </c>
       <c r="M216" s="17" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="217" spans="1:13" x14ac:dyDescent="0.35">
@@ -12570,13 +12566,13 @@
         <v>216</v>
       </c>
       <c r="D217" s="17" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E217" s="17" t="s">
         <v>25</v>
       </c>
       <c r="F217" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="G217" s="17" t="s">
         <v>30</v>
@@ -12588,7 +12584,7 @@
         <v>31</v>
       </c>
       <c r="J217" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K217" s="17" t="s">
         <v>157</v>
@@ -12597,7 +12593,7 @@
         <v>140</v>
       </c>
       <c r="M217" s="17" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="218" spans="1:13" x14ac:dyDescent="0.35">
@@ -12611,13 +12607,13 @@
         <v>217</v>
       </c>
       <c r="D218" s="17" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E218" s="17" t="s">
         <v>25</v>
       </c>
       <c r="F218" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G218" s="17" t="s">
         <v>30</v>
@@ -12629,7 +12625,7 @@
         <v>31</v>
       </c>
       <c r="J218" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K218" s="17" t="s">
         <v>157</v>
@@ -12638,7 +12634,7 @@
         <v>140</v>
       </c>
       <c r="M218" s="17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="219" spans="1:13" x14ac:dyDescent="0.35">
@@ -12652,13 +12648,13 @@
         <v>218</v>
       </c>
       <c r="D219" s="17" t="s">
+        <v>681</v>
+      </c>
+      <c r="E219" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F219" t="s">
         <v>682</v>
-      </c>
-      <c r="E219" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F219" t="s">
-        <v>683</v>
       </c>
       <c r="G219" s="17" t="s">
         <v>30</v>
@@ -12670,7 +12666,7 @@
         <v>31</v>
       </c>
       <c r="J219" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K219" s="17" t="s">
         <v>157</v>
@@ -12679,7 +12675,7 @@
         <v>140</v>
       </c>
       <c r="M219" s="17" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="220" spans="1:13" x14ac:dyDescent="0.35">
@@ -12693,13 +12689,13 @@
         <v>219</v>
       </c>
       <c r="D220" s="17" t="s">
+        <v>684</v>
+      </c>
+      <c r="E220" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F220" t="s">
         <v>685</v>
-      </c>
-      <c r="E220" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F220" t="s">
-        <v>686</v>
       </c>
       <c r="G220" s="17" t="s">
         <v>30</v>
@@ -12711,7 +12707,7 @@
         <v>31</v>
       </c>
       <c r="J220" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K220" s="17" t="s">
         <v>157</v>
@@ -12720,7 +12716,7 @@
         <v>140</v>
       </c>
       <c r="M220" s="17" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="221" spans="1:13" x14ac:dyDescent="0.35">
@@ -12734,13 +12730,13 @@
         <v>220</v>
       </c>
       <c r="D221" s="17" t="s">
+        <v>687</v>
+      </c>
+      <c r="E221" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F221" t="s">
         <v>688</v>
-      </c>
-      <c r="E221" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F221" t="s">
-        <v>689</v>
       </c>
       <c r="G221" s="17" t="s">
         <v>30</v>
@@ -12752,7 +12748,7 @@
         <v>31</v>
       </c>
       <c r="J221" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K221" s="17" t="s">
         <v>157</v>
@@ -12761,7 +12757,7 @@
         <v>140</v>
       </c>
       <c r="M221" s="17" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="222" spans="1:13" x14ac:dyDescent="0.35">
@@ -12775,13 +12771,13 @@
         <v>221</v>
       </c>
       <c r="D222" s="17" t="s">
+        <v>690</v>
+      </c>
+      <c r="E222" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F222" t="s">
         <v>691</v>
-      </c>
-      <c r="E222" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F222" t="s">
-        <v>692</v>
       </c>
       <c r="G222" s="17" t="s">
         <v>30</v>
@@ -12793,7 +12789,7 @@
         <v>20</v>
       </c>
       <c r="J222" s="17" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="K222" s="17" t="s">
         <v>157</v>
@@ -12802,7 +12798,7 @@
         <v>140</v>
       </c>
       <c r="M222" s="17" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="223" spans="1:13" x14ac:dyDescent="0.35">
@@ -12816,13 +12812,13 @@
         <v>222</v>
       </c>
       <c r="D223" s="17" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E223" s="17" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="F223" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="G223" s="17" t="s">
         <v>30</v>
@@ -12834,7 +12830,7 @@
         <v>31</v>
       </c>
       <c r="J223" s="17" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="K223" s="17" t="s">
         <v>157</v>
@@ -12843,7 +12839,7 @@
         <v>140</v>
       </c>
       <c r="M223" s="17" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="224" spans="1:13" x14ac:dyDescent="0.35">
@@ -12857,13 +12853,13 @@
         <v>223</v>
       </c>
       <c r="D224" s="17" t="s">
+        <v>696</v>
+      </c>
+      <c r="E224" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F224" t="s">
         <v>697</v>
-      </c>
-      <c r="E224" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F224" t="s">
-        <v>698</v>
       </c>
       <c r="G224" s="17" t="s">
         <v>30</v>
@@ -12875,7 +12871,7 @@
         <v>31</v>
       </c>
       <c r="J224" s="17" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="K224" s="17" t="s">
         <v>157</v>
@@ -12884,7 +12880,7 @@
         <v>140</v>
       </c>
       <c r="M224" s="17" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.35">
@@ -12898,13 +12894,13 @@
         <v>224</v>
       </c>
       <c r="D225" s="17" t="s">
+        <v>699</v>
+      </c>
+      <c r="E225" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F225" t="s">
         <v>700</v>
-      </c>
-      <c r="E225" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F225" t="s">
-        <v>701</v>
       </c>
       <c r="G225" s="17" t="s">
         <v>30</v>
@@ -12916,7 +12912,7 @@
         <v>31</v>
       </c>
       <c r="J225" s="17" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="K225" s="17" t="s">
         <v>157</v>
@@ -12925,7 +12921,7 @@
         <v>140</v>
       </c>
       <c r="M225" s="17" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.35">
@@ -12939,13 +12935,13 @@
         <v>225</v>
       </c>
       <c r="D226" s="17" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E226" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F226" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G226" s="17" t="s">
         <v>186</v>
@@ -12966,7 +12962,7 @@
         <v>140</v>
       </c>
       <c r="M226" s="17" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.35">
@@ -12980,13 +12976,13 @@
         <v>226</v>
       </c>
       <c r="D227" s="17" t="s">
+        <v>705</v>
+      </c>
+      <c r="E227" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F227" t="s">
         <v>706</v>
-      </c>
-      <c r="E227" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F227" t="s">
-        <v>707</v>
       </c>
       <c r="G227" s="17" t="s">
         <v>30</v>
@@ -12998,7 +12994,7 @@
         <v>31</v>
       </c>
       <c r="J227" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K227" s="17" t="s">
         <v>157</v>
@@ -13007,7 +13003,7 @@
         <v>140</v>
       </c>
       <c r="M227" s="17" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.35">
@@ -13021,13 +13017,13 @@
         <v>227</v>
       </c>
       <c r="D228" s="17" t="s">
+        <v>708</v>
+      </c>
+      <c r="E228" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F228" t="s">
         <v>709</v>
-      </c>
-      <c r="E228" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F228" t="s">
-        <v>710</v>
       </c>
       <c r="G228" s="17" t="s">
         <v>186</v>
@@ -13039,7 +13035,7 @@
         <v>31</v>
       </c>
       <c r="J228" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K228" s="17" t="s">
         <v>157</v>
@@ -13048,7 +13044,7 @@
         <v>140</v>
       </c>
       <c r="M228" s="17" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="229" spans="1:13" x14ac:dyDescent="0.35">
@@ -13062,13 +13058,13 @@
         <v>228</v>
       </c>
       <c r="D229" s="17" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E229" s="17" t="s">
         <v>438</v>
       </c>
       <c r="F229" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="G229" s="17" t="s">
         <v>30</v>
@@ -13080,7 +13076,7 @@
         <v>31</v>
       </c>
       <c r="J229" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K229" s="17" t="s">
         <v>157</v>
@@ -13089,7 +13085,7 @@
         <v>248</v>
       </c>
       <c r="M229" s="17" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.35">
@@ -13103,13 +13099,13 @@
         <v>229</v>
       </c>
       <c r="D230" s="17" t="s">
+        <v>714</v>
+      </c>
+      <c r="E230" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F230" t="s">
         <v>715</v>
-      </c>
-      <c r="E230" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F230" t="s">
-        <v>716</v>
       </c>
       <c r="G230" s="17" t="s">
         <v>186</v>
@@ -13130,7 +13126,7 @@
         <v>140</v>
       </c>
       <c r="M230" s="17" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.35">
@@ -13144,13 +13140,13 @@
         <v>230</v>
       </c>
       <c r="D231" s="17" t="s">
+        <v>717</v>
+      </c>
+      <c r="E231" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F231" t="s">
         <v>718</v>
-      </c>
-      <c r="E231" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F231" t="s">
-        <v>719</v>
       </c>
       <c r="G231" s="17" t="s">
         <v>30</v>
@@ -13171,7 +13167,7 @@
         <v>140</v>
       </c>
       <c r="M231" s="17" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="232" spans="1:13" x14ac:dyDescent="0.35">
@@ -13185,13 +13181,13 @@
         <v>231</v>
       </c>
       <c r="D232" s="17" t="s">
+        <v>720</v>
+      </c>
+      <c r="E232" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F232" t="s">
         <v>721</v>
-      </c>
-      <c r="E232" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F232" t="s">
-        <v>722</v>
       </c>
       <c r="G232" s="17" t="s">
         <v>30</v>
@@ -13203,7 +13199,7 @@
         <v>31</v>
       </c>
       <c r="J232" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K232" s="17" t="s">
         <v>157</v>
@@ -13212,7 +13208,7 @@
         <v>140</v>
       </c>
       <c r="M232" s="17" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.35">
@@ -13226,13 +13222,13 @@
         <v>232</v>
       </c>
       <c r="D233" s="17" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E233" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F233" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="G233" s="17" t="s">
         <v>30</v>
@@ -13253,7 +13249,7 @@
         <v>248</v>
       </c>
       <c r="M233" s="17" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.35">
@@ -13267,13 +13263,13 @@
         <v>233</v>
       </c>
       <c r="D234" s="17" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E234" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F234" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="G234" s="17" t="s">
         <v>30</v>
@@ -13294,7 +13290,7 @@
         <v>248</v>
       </c>
       <c r="M234" s="17" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.35">
@@ -13308,13 +13304,13 @@
         <v>234</v>
       </c>
       <c r="D235" s="17" t="s">
+        <v>729</v>
+      </c>
+      <c r="E235" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F235" t="s">
         <v>730</v>
-      </c>
-      <c r="E235" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F235" t="s">
-        <v>731</v>
       </c>
       <c r="G235" s="17" t="s">
         <v>18</v>
@@ -13326,7 +13322,7 @@
         <v>20</v>
       </c>
       <c r="J235" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K235" s="17" t="s">
         <v>157</v>
@@ -13335,7 +13331,7 @@
         <v>248</v>
       </c>
       <c r="M235" s="17" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="236" spans="1:13" x14ac:dyDescent="0.35">
@@ -13349,13 +13345,13 @@
         <v>235</v>
       </c>
       <c r="D236" s="17" t="s">
+        <v>732</v>
+      </c>
+      <c r="E236" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F236" t="s">
         <v>733</v>
-      </c>
-      <c r="E236" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F236" t="s">
-        <v>734</v>
       </c>
       <c r="G236" s="17" t="s">
         <v>30</v>
@@ -13367,7 +13363,7 @@
         <v>138</v>
       </c>
       <c r="J236" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K236" s="17" t="s">
         <v>157</v>
@@ -13376,7 +13372,7 @@
         <v>248</v>
       </c>
       <c r="M236" s="17" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.35">
@@ -13390,13 +13386,13 @@
         <v>236</v>
       </c>
       <c r="D237" s="17" t="s">
+        <v>735</v>
+      </c>
+      <c r="E237" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F237" t="s">
         <v>736</v>
-      </c>
-      <c r="E237" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F237" t="s">
-        <v>737</v>
       </c>
       <c r="G237" s="17" t="s">
         <v>30</v>
@@ -13408,7 +13404,7 @@
         <v>138</v>
       </c>
       <c r="J237" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K237" s="17" t="s">
         <v>157</v>
@@ -13417,7 +13413,7 @@
         <v>248</v>
       </c>
       <c r="M237" s="17" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="238" spans="1:13" x14ac:dyDescent="0.35">
@@ -13431,13 +13427,13 @@
         <v>237</v>
       </c>
       <c r="D238" s="17" t="s">
+        <v>738</v>
+      </c>
+      <c r="E238" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F238" t="s">
         <v>739</v>
-      </c>
-      <c r="E238" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F238" t="s">
-        <v>740</v>
       </c>
       <c r="G238" s="17" t="s">
         <v>30</v>
@@ -13449,7 +13445,7 @@
         <v>138</v>
       </c>
       <c r="J238" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K238" s="17" t="s">
         <v>157</v>
@@ -13458,7 +13454,7 @@
         <v>248</v>
       </c>
       <c r="M238" s="17" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="239" spans="1:13" x14ac:dyDescent="0.35">
@@ -13472,13 +13468,13 @@
         <v>238</v>
       </c>
       <c r="D239" s="17" t="s">
+        <v>741</v>
+      </c>
+      <c r="E239" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F239" t="s">
         <v>742</v>
-      </c>
-      <c r="E239" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F239" t="s">
-        <v>743</v>
       </c>
       <c r="G239" s="17" t="s">
         <v>30</v>
@@ -13490,7 +13486,7 @@
         <v>138</v>
       </c>
       <c r="J239" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K239" s="17" t="s">
         <v>157</v>
@@ -13499,7 +13495,7 @@
         <v>248</v>
       </c>
       <c r="M239" s="17" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.35">
@@ -13513,13 +13509,13 @@
         <v>239</v>
       </c>
       <c r="D240" s="17" t="s">
+        <v>744</v>
+      </c>
+      <c r="E240" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F240" t="s">
         <v>745</v>
-      </c>
-      <c r="E240" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F240" t="s">
-        <v>746</v>
       </c>
       <c r="G240" s="17" t="s">
         <v>30</v>
@@ -13531,7 +13527,7 @@
         <v>138</v>
       </c>
       <c r="J240" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K240" s="17" t="s">
         <v>157</v>
@@ -13540,7 +13536,7 @@
         <v>248</v>
       </c>
       <c r="M240" s="17" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.35">
@@ -13554,13 +13550,13 @@
         <v>240</v>
       </c>
       <c r="D241" s="17" t="s">
+        <v>747</v>
+      </c>
+      <c r="E241" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F241" t="s">
         <v>748</v>
-      </c>
-      <c r="E241" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F241" t="s">
-        <v>749</v>
       </c>
       <c r="G241" s="17" t="s">
         <v>30</v>
@@ -13572,7 +13568,7 @@
         <v>138</v>
       </c>
       <c r="J241" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K241" s="17" t="s">
         <v>157</v>
@@ -13598,10 +13594,10 @@
         <v>142</v>
       </c>
       <c r="E242" s="17" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="F242" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G242" s="17" t="s">
         <v>30</v>
@@ -13613,7 +13609,7 @@
         <v>20</v>
       </c>
       <c r="J242" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K242" s="6" t="s">
         <v>157</v>
@@ -13636,13 +13632,13 @@
         <v>242</v>
       </c>
       <c r="D243" s="32" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E243" s="6" t="s">
         <v>135</v>
       </c>
       <c r="F243" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="G243" t="s">
         <v>30</v>
@@ -13654,7 +13650,7 @@
         <v>31</v>
       </c>
       <c r="J243" s="6" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="K243" s="6" t="s">
         <v>157</v>
@@ -13663,7 +13659,7 @@
         <v>140</v>
       </c>
       <c r="M243" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="244" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -13677,16 +13673,16 @@
         <v>243</v>
       </c>
       <c r="D244" s="32" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E244" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F244" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="G244" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H244" s="6" t="s">
         <v>153</v>
@@ -13695,7 +13691,7 @@
         <v>20</v>
       </c>
       <c r="J244" s="6" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="K244" s="6" t="s">
         <v>157</v>
@@ -13704,7 +13700,7 @@
         <v>140</v>
       </c>
       <c r="M244" s="6" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="245" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -13718,13 +13714,13 @@
         <v>244</v>
       </c>
       <c r="D245" s="32" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E245" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F245" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="G245" t="s">
         <v>30</v>
@@ -13745,7 +13741,7 @@
         <v>140</v>
       </c>
       <c r="M245" s="6" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="246" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -13759,13 +13755,13 @@
         <v>245</v>
       </c>
       <c r="D246" s="32" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E246" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F246" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="G246" t="s">
         <v>30</v>
@@ -13786,7 +13782,7 @@
         <v>140</v>
       </c>
       <c r="M246" s="6" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="247" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -13800,13 +13796,13 @@
         <v>246</v>
       </c>
       <c r="D247" s="32" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E247" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F247" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="G247" t="s">
         <v>30</v>
@@ -13827,7 +13823,7 @@
         <v>140</v>
       </c>
       <c r="M247" s="6" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="248" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -13841,13 +13837,13 @@
         <v>247</v>
       </c>
       <c r="D248" s="32" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E248" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F248" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G248" t="s">
         <v>18</v>
@@ -13868,7 +13864,7 @@
         <v>140</v>
       </c>
       <c r="M248" s="6" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="249" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -13882,13 +13878,13 @@
         <v>248</v>
       </c>
       <c r="D249" s="32" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E249" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F249" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="G249" t="s">
         <v>18</v>
@@ -13909,7 +13905,7 @@
         <v>140</v>
       </c>
       <c r="M249" s="6" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="250" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -13923,19 +13919,19 @@
         <v>249</v>
       </c>
       <c r="D250" s="32" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E250" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F250" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="G250" t="s">
         <v>18</v>
       </c>
       <c r="H250" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="I250" s="6" t="s">
         <v>20</v>
@@ -13950,7 +13946,7 @@
         <v>140</v>
       </c>
       <c r="M250" s="6" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="251" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -13964,13 +13960,13 @@
         <v>250</v>
       </c>
       <c r="D251" s="32" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="E251" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F251" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="G251" t="s">
         <v>30</v>
@@ -13982,7 +13978,7 @@
         <v>31</v>
       </c>
       <c r="J251" s="6" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="K251" s="6" t="s">
         <v>157</v>
@@ -13991,7 +13987,7 @@
         <v>140</v>
       </c>
       <c r="M251" s="6" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="252" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -14005,13 +14001,13 @@
         <v>251</v>
       </c>
       <c r="D252" s="32" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E252" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F252" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="G252" t="s">
         <v>18</v>
@@ -14032,7 +14028,7 @@
         <v>140</v>
       </c>
       <c r="M252" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="253" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -14046,13 +14042,13 @@
         <v>252</v>
       </c>
       <c r="D253" s="32" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E253" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F253" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="G253" t="s">
         <v>30</v>
@@ -14073,7 +14069,7 @@
         <v>140</v>
       </c>
       <c r="M253" s="6" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="254" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -14087,13 +14083,13 @@
         <v>253</v>
       </c>
       <c r="D254" s="32" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="E254" s="6" t="s">
         <v>438</v>
       </c>
       <c r="F254" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G254" t="s">
         <v>18</v>
@@ -14114,7 +14110,7 @@
         <v>140</v>
       </c>
       <c r="M254" s="6" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="255" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -14128,13 +14124,13 @@
         <v>254</v>
       </c>
       <c r="D255" s="32" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E255" s="6" t="s">
         <v>438</v>
       </c>
       <c r="F255" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G255" t="s">
         <v>18</v>
@@ -14155,7 +14151,7 @@
         <v>140</v>
       </c>
       <c r="M255" s="6" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="256" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -14169,13 +14165,13 @@
         <v>255</v>
       </c>
       <c r="D256" s="32" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E256" s="6" t="s">
         <v>438</v>
       </c>
       <c r="F256" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="G256" t="s">
         <v>18</v>
@@ -14196,7 +14192,7 @@
         <v>140</v>
       </c>
       <c r="M256" s="6" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="257" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -14210,13 +14206,13 @@
         <v>256</v>
       </c>
       <c r="D257" s="32" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="E257" s="6" t="s">
         <v>438</v>
       </c>
       <c r="F257" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="G257" t="s">
         <v>18</v>
@@ -14237,7 +14233,7 @@
         <v>140</v>
       </c>
       <c r="M257" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="258" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -14251,19 +14247,19 @@
         <v>257</v>
       </c>
       <c r="D258" s="32" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="E258" s="6" t="s">
         <v>438</v>
       </c>
       <c r="F258" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="G258" t="s">
         <v>18</v>
       </c>
       <c r="H258" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="I258" s="6" t="s">
         <v>20</v>
@@ -14278,7 +14274,7 @@
         <v>140</v>
       </c>
       <c r="M258" s="6" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="259" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -14292,13 +14288,13 @@
         <v>258</v>
       </c>
       <c r="D259" s="32" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="E259" s="6" t="s">
         <v>438</v>
       </c>
       <c r="F259" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="G259" t="s">
         <v>18</v>
@@ -14319,7 +14315,7 @@
         <v>140</v>
       </c>
       <c r="M259" s="32" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="260" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -14333,13 +14329,13 @@
         <v>259</v>
       </c>
       <c r="D260" s="32" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="E260" s="6" t="s">
         <v>438</v>
       </c>
       <c r="F260" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="G260" t="s">
         <v>18</v>
@@ -14360,7 +14356,7 @@
         <v>140</v>
       </c>
       <c r="M260" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="261" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -14374,13 +14370,13 @@
         <v>260</v>
       </c>
       <c r="D261" s="32" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="E261" s="6" t="s">
         <v>438</v>
       </c>
       <c r="F261" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="G261" t="s">
         <v>18</v>
@@ -14401,7 +14397,7 @@
         <v>140</v>
       </c>
       <c r="M261" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="262" spans="1:13" x14ac:dyDescent="0.35">
@@ -14415,13 +14411,13 @@
         <v>261</v>
       </c>
       <c r="D262" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="E262" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F262" s="35" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G262" s="33" t="s">
         <v>18</v>
@@ -14435,14 +14431,14 @@
       <c r="J262" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K262" s="37" t="s">
+      <c r="K262" t="s">
         <v>139</v>
       </c>
       <c r="L262" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M262" s="33" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="263" spans="1:13" x14ac:dyDescent="0.35">
@@ -14456,13 +14452,13 @@
         <v>262</v>
       </c>
       <c r="D263" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="E263" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F263" s="35" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="G263" s="33" t="s">
         <v>18</v>
@@ -14476,14 +14472,14 @@
       <c r="J263" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K263" s="37" t="s">
+      <c r="K263" t="s">
         <v>139</v>
       </c>
       <c r="L263" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M263" s="33" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="264" spans="1:13" x14ac:dyDescent="0.35">
@@ -14497,13 +14493,13 @@
         <v>263</v>
       </c>
       <c r="D264" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E264" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F264" s="35" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G264" s="33" t="s">
         <v>18</v>
@@ -14517,14 +14513,14 @@
       <c r="J264" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K264" s="37" t="s">
+      <c r="K264" t="s">
         <v>139</v>
       </c>
       <c r="L264" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M264" s="33" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="265" spans="1:13" x14ac:dyDescent="0.35">
@@ -14538,13 +14534,13 @@
         <v>264</v>
       </c>
       <c r="D265" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="E265" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F265" s="35" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="G265" s="33" t="s">
         <v>18</v>
@@ -14558,14 +14554,14 @@
       <c r="J265" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K265" s="37" t="s">
+      <c r="K265" t="s">
         <v>139</v>
       </c>
       <c r="L265" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M265" s="33" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="266" spans="1:13" x14ac:dyDescent="0.35">
@@ -14579,13 +14575,13 @@
         <v>265</v>
       </c>
       <c r="D266" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="E266" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F266" s="35" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="G266" s="33" t="s">
         <v>18</v>
@@ -14599,14 +14595,14 @@
       <c r="J266" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K266" s="37" t="s">
+      <c r="K266" t="s">
         <v>139</v>
       </c>
       <c r="L266" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M266" s="33" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="267" spans="1:13" x14ac:dyDescent="0.35">
@@ -14620,13 +14616,13 @@
         <v>266</v>
       </c>
       <c r="D267" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="E267" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F267" s="35" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="G267" s="33" t="s">
         <v>18</v>
@@ -14640,14 +14636,14 @@
       <c r="J267" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K267" s="37" t="s">
+      <c r="K267" t="s">
         <v>139</v>
       </c>
       <c r="L267" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M267" s="33" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="268" spans="1:13" x14ac:dyDescent="0.35">
@@ -14661,13 +14657,13 @@
         <v>267</v>
       </c>
       <c r="D268" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E268" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F268" s="35" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="G268" s="33" t="s">
         <v>18</v>
@@ -14681,14 +14677,14 @@
       <c r="J268" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K268" s="37" t="s">
+      <c r="K268" t="s">
         <v>139</v>
       </c>
       <c r="L268" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M268" s="33" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="269" spans="1:13" x14ac:dyDescent="0.35">
@@ -14702,13 +14698,13 @@
         <v>268</v>
       </c>
       <c r="D269" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="E269" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F269" s="35" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="G269" s="33" t="s">
         <v>18</v>
@@ -14722,14 +14718,14 @@
       <c r="J269" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K269" s="37" t="s">
+      <c r="K269" t="s">
         <v>139</v>
       </c>
       <c r="L269" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M269" s="33" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="270" spans="1:13" x14ac:dyDescent="0.35">
@@ -14743,13 +14739,13 @@
         <v>269</v>
       </c>
       <c r="D270" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="E270" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F270" s="35" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="G270" s="33" t="s">
         <v>18</v>
@@ -14763,14 +14759,14 @@
       <c r="J270" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K270" s="37" t="s">
+      <c r="K270" t="s">
         <v>139</v>
       </c>
       <c r="L270" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M270" s="33" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="271" spans="1:13" x14ac:dyDescent="0.35">
@@ -14784,13 +14780,13 @@
         <v>270</v>
       </c>
       <c r="D271" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="E271" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F271" s="35" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="G271" s="33" t="s">
         <v>18</v>
@@ -14804,14 +14800,14 @@
       <c r="J271" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K271" s="37" t="s">
+      <c r="K271" t="s">
         <v>139</v>
       </c>
       <c r="L271" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M271" s="33" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="272" spans="1:13" x14ac:dyDescent="0.35">
@@ -14825,13 +14821,13 @@
         <v>271</v>
       </c>
       <c r="D272" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E272" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F272" s="35" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="G272" s="33" t="s">
         <v>18</v>
@@ -14845,14 +14841,14 @@
       <c r="J272" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K272" s="37" t="s">
+      <c r="K272" t="s">
         <v>139</v>
       </c>
       <c r="L272" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M272" s="33" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="273" spans="1:13" x14ac:dyDescent="0.35">
@@ -14866,13 +14862,13 @@
         <v>272</v>
       </c>
       <c r="D273" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E273" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F273" s="35" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="G273" s="33" t="s">
         <v>18</v>
@@ -14886,14 +14882,14 @@
       <c r="J273" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K273" s="37" t="s">
+      <c r="K273" t="s">
         <v>139</v>
       </c>
       <c r="L273" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M273" s="33" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="274" spans="1:13" x14ac:dyDescent="0.35">
@@ -14907,13 +14903,13 @@
         <v>273</v>
       </c>
       <c r="D274" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E274" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F274" s="35" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="G274" s="33" t="s">
         <v>18</v>
@@ -14927,14 +14923,14 @@
       <c r="J274" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K274" s="37" t="s">
+      <c r="K274" t="s">
         <v>139</v>
       </c>
       <c r="L274" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M274" s="33" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="275" spans="1:13" x14ac:dyDescent="0.35">
@@ -14948,13 +14944,13 @@
         <v>274</v>
       </c>
       <c r="D275" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E275" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F275" s="35" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="G275" s="33" t="s">
         <v>18</v>
@@ -14968,14 +14964,14 @@
       <c r="J275" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K275" s="37" t="s">
+      <c r="K275" t="s">
         <v>139</v>
       </c>
       <c r="L275" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M275" s="33" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="276" spans="1:13" x14ac:dyDescent="0.35">
@@ -14989,13 +14985,13 @@
         <v>275</v>
       </c>
       <c r="D276" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="E276" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F276" s="35" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G276" s="33" t="s">
         <v>18</v>
@@ -15009,14 +15005,14 @@
       <c r="J276" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K276" s="37" t="s">
+      <c r="K276" t="s">
         <v>139</v>
       </c>
       <c r="L276" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M276" s="33" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="277" spans="1:13" x14ac:dyDescent="0.35">
@@ -15030,13 +15026,13 @@
         <v>276</v>
       </c>
       <c r="D277" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E277" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F277" s="35" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G277" s="33" t="s">
         <v>18</v>
@@ -15050,14 +15046,14 @@
       <c r="J277" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K277" s="37" t="s">
+      <c r="K277" t="s">
         <v>139</v>
       </c>
       <c r="L277" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M277" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="278" spans="1:13" x14ac:dyDescent="0.35">
@@ -15071,13 +15067,13 @@
         <v>277</v>
       </c>
       <c r="D278" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="E278" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F278" s="35" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="G278" s="33" t="s">
         <v>18</v>
@@ -15091,14 +15087,14 @@
       <c r="J278" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K278" s="37" t="s">
+      <c r="K278" t="s">
         <v>139</v>
       </c>
       <c r="L278" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M278" s="33" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="279" spans="1:13" x14ac:dyDescent="0.35">
@@ -15112,13 +15108,13 @@
         <v>278</v>
       </c>
       <c r="D279" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="E279" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F279" s="35" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="G279" s="33" t="s">
         <v>18</v>
@@ -15132,14 +15128,14 @@
       <c r="J279" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K279" s="37" t="s">
+      <c r="K279" t="s">
         <v>139</v>
       </c>
       <c r="L279" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M279" s="33" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="280" spans="1:13" x14ac:dyDescent="0.35">
@@ -15153,13 +15149,13 @@
         <v>279</v>
       </c>
       <c r="D280" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="E280" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F280" s="35" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="G280" s="33" t="s">
         <v>18</v>
@@ -15173,14 +15169,14 @@
       <c r="J280" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K280" s="37" t="s">
+      <c r="K280" t="s">
         <v>139</v>
       </c>
       <c r="L280" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M280" s="33" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="281" spans="1:13" x14ac:dyDescent="0.35">
@@ -15194,13 +15190,13 @@
         <v>280</v>
       </c>
       <c r="D281" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E281" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F281" s="35" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="G281" s="33" t="s">
         <v>18</v>
@@ -15214,14 +15210,14 @@
       <c r="J281" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K281" s="37" t="s">
+      <c r="K281" t="s">
         <v>139</v>
       </c>
       <c r="L281" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M281" s="33" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="282" spans="1:13" x14ac:dyDescent="0.35">
@@ -15235,13 +15231,13 @@
         <v>281</v>
       </c>
       <c r="D282" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="E282" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F282" s="35" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="G282" s="33" t="s">
         <v>18</v>
@@ -15255,14 +15251,14 @@
       <c r="J282" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K282" s="37" t="s">
+      <c r="K282" t="s">
         <v>139</v>
       </c>
       <c r="L282" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M282" s="33" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="283" spans="1:13" x14ac:dyDescent="0.35">
@@ -15276,13 +15272,13 @@
         <v>282</v>
       </c>
       <c r="D283" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="E283" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F283" s="35" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="G283" s="33" t="s">
         <v>18</v>
@@ -15296,14 +15292,14 @@
       <c r="J283" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K283" s="37" t="s">
+      <c r="K283" t="s">
         <v>139</v>
       </c>
       <c r="L283" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M283" s="33" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="284" spans="1:13" x14ac:dyDescent="0.35">
@@ -15317,13 +15313,13 @@
         <v>283</v>
       </c>
       <c r="D284" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="E284" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F284" s="35" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="G284" s="33" t="s">
         <v>18</v>
@@ -15337,14 +15333,14 @@
       <c r="J284" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K284" s="37" t="s">
+      <c r="K284" t="s">
         <v>139</v>
       </c>
       <c r="L284" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M284" s="33" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="285" spans="1:13" x14ac:dyDescent="0.35">
@@ -15358,13 +15354,13 @@
         <v>284</v>
       </c>
       <c r="D285" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E285" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F285" s="35" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="G285" s="33" t="s">
         <v>18</v>
@@ -15378,14 +15374,14 @@
       <c r="J285" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K285" s="37" t="s">
+      <c r="K285" t="s">
         <v>139</v>
       </c>
       <c r="L285" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M285" s="33" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="286" spans="1:13" x14ac:dyDescent="0.35">
@@ -15399,13 +15395,13 @@
         <v>285</v>
       </c>
       <c r="D286" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="E286" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F286" s="35" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="G286" s="33" t="s">
         <v>18</v>
@@ -15419,14 +15415,14 @@
       <c r="J286" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K286" s="37" t="s">
+      <c r="K286" t="s">
         <v>139</v>
       </c>
       <c r="L286" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M286" s="33" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="287" spans="1:13" x14ac:dyDescent="0.35">
@@ -15440,13 +15436,13 @@
         <v>286</v>
       </c>
       <c r="D287" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E287" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F287" s="35" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="G287" s="33" t="s">
         <v>18</v>
@@ -15460,14 +15456,14 @@
       <c r="J287" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K287" s="37" t="s">
+      <c r="K287" t="s">
         <v>139</v>
       </c>
       <c r="L287" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M287" s="33" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="288" spans="1:13" x14ac:dyDescent="0.35">
@@ -15481,13 +15477,13 @@
         <v>287</v>
       </c>
       <c r="D288" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E288" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F288" s="35" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G288" s="33" t="s">
         <v>18</v>
@@ -15501,14 +15497,14 @@
       <c r="J288" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K288" s="37" t="s">
+      <c r="K288" t="s">
         <v>139</v>
       </c>
       <c r="L288" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M288" s="33" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="289" spans="1:13" x14ac:dyDescent="0.35">
@@ -15522,13 +15518,13 @@
         <v>288</v>
       </c>
       <c r="D289" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="E289" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F289" s="35" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="G289" s="33" t="s">
         <v>18</v>
@@ -15542,14 +15538,14 @@
       <c r="J289" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K289" s="37" t="s">
+      <c r="K289" t="s">
         <v>139</v>
       </c>
       <c r="L289" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M289" s="33" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="290" spans="1:13" x14ac:dyDescent="0.35">
@@ -15563,13 +15559,13 @@
         <v>289</v>
       </c>
       <c r="D290" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="E290" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F290" s="35" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="G290" s="33" t="s">
         <v>18</v>
@@ -15583,14 +15579,14 @@
       <c r="J290" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K290" s="37" t="s">
+      <c r="K290" t="s">
         <v>139</v>
       </c>
       <c r="L290" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M290" s="33" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="291" spans="1:13" x14ac:dyDescent="0.35">
@@ -15604,13 +15600,13 @@
         <v>290</v>
       </c>
       <c r="D291" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="E291" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F291" s="35" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G291" s="33" t="s">
         <v>18</v>
@@ -15624,14 +15620,14 @@
       <c r="J291" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K291" s="37" t="s">
+      <c r="K291" t="s">
         <v>139</v>
       </c>
       <c r="L291" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M291" s="33" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="292" spans="1:13" x14ac:dyDescent="0.35">
@@ -15645,13 +15641,13 @@
         <v>300</v>
       </c>
       <c r="D292" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E292" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F292" s="35" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G292" s="33" t="s">
         <v>18</v>
@@ -15665,14 +15661,14 @@
       <c r="J292" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K292" s="37" t="s">
+      <c r="K292" t="s">
         <v>139</v>
       </c>
       <c r="L292" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M292" s="33" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="293" spans="1:13" x14ac:dyDescent="0.35">
@@ -15686,13 +15682,13 @@
         <v>301</v>
       </c>
       <c r="D293" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E293" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F293" s="35" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="G293" s="33" t="s">
         <v>18</v>
@@ -15706,14 +15702,14 @@
       <c r="J293" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K293" s="37" t="s">
+      <c r="K293" t="s">
         <v>139</v>
       </c>
       <c r="L293" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M293" s="33" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="294" spans="1:13" x14ac:dyDescent="0.35">
@@ -15727,13 +15723,13 @@
         <v>302</v>
       </c>
       <c r="D294" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="E294" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F294" s="35" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="G294" s="33" t="s">
         <v>18</v>
@@ -15747,14 +15743,14 @@
       <c r="J294" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K294" s="37" t="s">
+      <c r="K294" t="s">
         <v>139</v>
       </c>
       <c r="L294" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M294" s="33" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="295" spans="1:13" x14ac:dyDescent="0.35">
@@ -15768,13 +15764,13 @@
         <v>303</v>
       </c>
       <c r="D295" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E295" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F295" s="35" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="G295" s="33" t="s">
         <v>18</v>
@@ -15788,14 +15784,14 @@
       <c r="J295" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K295" s="37" t="s">
+      <c r="K295" t="s">
         <v>139</v>
       </c>
       <c r="L295" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M295" s="33" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="296" spans="1:13" x14ac:dyDescent="0.35">
@@ -15809,13 +15805,13 @@
         <v>304</v>
       </c>
       <c r="D296" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E296" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F296" s="35" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="G296" s="33" t="s">
         <v>18</v>
@@ -15829,14 +15825,14 @@
       <c r="J296" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K296" s="37" t="s">
+      <c r="K296" t="s">
         <v>139</v>
       </c>
       <c r="L296" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M296" s="33" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="297" spans="1:13" x14ac:dyDescent="0.35">
@@ -15850,13 +15846,13 @@
         <v>305</v>
       </c>
       <c r="D297" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="E297" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F297" s="35" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G297" s="33" t="s">
         <v>18</v>
@@ -15870,14 +15866,14 @@
       <c r="J297" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K297" s="37" t="s">
+      <c r="K297" t="s">
         <v>139</v>
       </c>
       <c r="L297" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M297" s="33" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="298" spans="1:13" x14ac:dyDescent="0.35">
@@ -15891,13 +15887,13 @@
         <v>306</v>
       </c>
       <c r="D298" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="E298" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F298" s="35" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="G298" s="33" t="s">
         <v>18</v>
@@ -15911,14 +15907,14 @@
       <c r="J298" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K298" s="37" t="s">
+      <c r="K298" t="s">
         <v>139</v>
       </c>
       <c r="L298" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M298" s="33" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="299" spans="1:13" x14ac:dyDescent="0.35">
@@ -15932,13 +15928,13 @@
         <v>307</v>
       </c>
       <c r="D299" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="E299" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F299" s="35" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G299" s="33" t="s">
         <v>18</v>
@@ -15952,14 +15948,14 @@
       <c r="J299" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K299" s="37" t="s">
+      <c r="K299" t="s">
         <v>139</v>
       </c>
       <c r="L299" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M299" s="33" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="300" spans="1:13" x14ac:dyDescent="0.35">
@@ -15973,13 +15969,13 @@
         <v>308</v>
       </c>
       <c r="D300" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="E300" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F300" s="35" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G300" s="33" t="s">
         <v>18</v>
@@ -15993,14 +15989,14 @@
       <c r="J300" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K300" s="37" t="s">
+      <c r="K300" t="s">
         <v>139</v>
       </c>
       <c r="L300" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M300" s="33" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="301" spans="1:13" x14ac:dyDescent="0.35">
@@ -16014,13 +16010,13 @@
         <v>309</v>
       </c>
       <c r="D301" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="E301" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F301" s="35" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="G301" s="33" t="s">
         <v>18</v>
@@ -16034,14 +16030,14 @@
       <c r="J301" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K301" s="37" t="s">
+      <c r="K301" t="s">
         <v>139</v>
       </c>
       <c r="L301" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M301" s="33" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="302" spans="1:13" x14ac:dyDescent="0.35">
@@ -16055,13 +16051,13 @@
         <v>310</v>
       </c>
       <c r="D302" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="E302" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F302" s="35" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="G302" s="33" t="s">
         <v>18</v>
@@ -16075,14 +16071,14 @@
       <c r="J302" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K302" s="37" t="s">
+      <c r="K302" t="s">
         <v>139</v>
       </c>
       <c r="L302" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M302" s="33" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="303" spans="1:13" x14ac:dyDescent="0.35">
@@ -16096,13 +16092,13 @@
         <v>311</v>
       </c>
       <c r="D303" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E303" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F303" s="35" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="G303" s="33" t="s">
         <v>30</v>
@@ -16116,14 +16112,14 @@
       <c r="J303" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K303" s="37" t="s">
+      <c r="K303" t="s">
         <v>139</v>
       </c>
       <c r="L303" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M303" s="33" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="304" spans="1:13" x14ac:dyDescent="0.35">
@@ -16137,13 +16133,13 @@
         <v>312</v>
       </c>
       <c r="D304" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="E304" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F304" s="35" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="G304" s="33" t="s">
         <v>18</v>
@@ -16157,14 +16153,14 @@
       <c r="J304" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K304" s="37" t="s">
+      <c r="K304" t="s">
         <v>139</v>
       </c>
       <c r="L304" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M304" s="33" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="305" spans="1:13" x14ac:dyDescent="0.35">
@@ -16178,13 +16174,13 @@
         <v>313</v>
       </c>
       <c r="D305" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="E305" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F305" s="35" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="G305" s="33" t="s">
         <v>30</v>
@@ -16198,14 +16194,14 @@
       <c r="J305" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K305" s="37" t="s">
+      <c r="K305" t="s">
         <v>139</v>
       </c>
       <c r="L305" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M305" s="33" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="306" spans="1:13" x14ac:dyDescent="0.35">
@@ -16219,13 +16215,13 @@
         <v>314</v>
       </c>
       <c r="D306" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="E306" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F306" s="35" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="G306" s="33" t="s">
         <v>18</v>
@@ -16239,14 +16235,14 @@
       <c r="J306" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K306" s="37" t="s">
+      <c r="K306" t="s">
         <v>139</v>
       </c>
       <c r="L306" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M306" s="33" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="307" spans="1:13" x14ac:dyDescent="0.35">
@@ -16260,13 +16256,13 @@
         <v>315</v>
       </c>
       <c r="D307" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="E307" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F307" s="35" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="G307" s="33" t="s">
         <v>18</v>
@@ -16280,14 +16276,14 @@
       <c r="J307" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K307" s="37" t="s">
+      <c r="K307" t="s">
         <v>139</v>
       </c>
       <c r="L307" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M307" s="33" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="308" spans="1:13" x14ac:dyDescent="0.35">
@@ -16301,13 +16297,13 @@
         <v>316</v>
       </c>
       <c r="D308" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="E308" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F308" s="35" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="G308" s="33" t="s">
         <v>18</v>
@@ -16321,14 +16317,14 @@
       <c r="J308" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K308" s="37" t="s">
+      <c r="K308" t="s">
         <v>139</v>
       </c>
       <c r="L308" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M308" s="33" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="309" spans="1:13" x14ac:dyDescent="0.35">
@@ -16342,13 +16338,13 @@
         <v>317</v>
       </c>
       <c r="D309" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="E309" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F309" s="35" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="G309" s="33" t="s">
         <v>18</v>
@@ -16362,14 +16358,14 @@
       <c r="J309" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K309" s="37" t="s">
+      <c r="K309" t="s">
         <v>139</v>
       </c>
       <c r="L309" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M309" s="33" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="310" spans="1:13" x14ac:dyDescent="0.35">
@@ -16383,13 +16379,13 @@
         <v>318</v>
       </c>
       <c r="D310" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E310" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F310" s="35" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="G310" s="33" t="s">
         <v>18</v>
@@ -16403,14 +16399,14 @@
       <c r="J310" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K310" s="37" t="s">
+      <c r="K310" t="s">
         <v>139</v>
       </c>
       <c r="L310" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M310" s="33" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="311" spans="1:13" x14ac:dyDescent="0.35">
@@ -16424,13 +16420,13 @@
         <v>319</v>
       </c>
       <c r="D311" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="E311" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F311" s="35" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="G311" s="33" t="s">
         <v>30</v>
@@ -16444,14 +16440,14 @@
       <c r="J311" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K311" s="37" t="s">
+      <c r="K311" t="s">
         <v>139</v>
       </c>
       <c r="L311" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M311" s="33" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="312" spans="1:13" x14ac:dyDescent="0.35">
@@ -16465,13 +16461,13 @@
         <v>320</v>
       </c>
       <c r="D312" s="34" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="E312" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F312" s="35" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="G312" s="33" t="s">
         <v>30</v>
@@ -16485,14 +16481,14 @@
       <c r="J312" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K312" s="37" t="s">
+      <c r="K312" t="s">
         <v>139</v>
       </c>
       <c r="L312" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M312" s="33" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="313" spans="1:13" x14ac:dyDescent="0.35">
@@ -16506,13 +16502,13 @@
         <v>321</v>
       </c>
       <c r="D313" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E313" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F313" s="35" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="G313" s="33" t="s">
         <v>30</v>
@@ -16526,14 +16522,14 @@
       <c r="J313" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K313" s="37" t="s">
+      <c r="K313" t="s">
         <v>139</v>
       </c>
       <c r="L313" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M313" s="33" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="314" spans="1:13" x14ac:dyDescent="0.35">
@@ -16547,13 +16543,13 @@
         <v>322</v>
       </c>
       <c r="D314" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="E314" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F314" s="35" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="G314" s="33" t="s">
         <v>18</v>
@@ -16567,14 +16563,14 @@
       <c r="J314" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K314" s="37" t="s">
+      <c r="K314" t="s">
         <v>139</v>
       </c>
       <c r="L314" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M314" s="33" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="315" spans="1:13" x14ac:dyDescent="0.35">
@@ -16588,13 +16584,13 @@
         <v>323</v>
       </c>
       <c r="D315" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E315" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F315" s="35" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="G315" s="33" t="s">
         <v>18</v>
@@ -16608,14 +16604,14 @@
       <c r="J315" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K315" s="37" t="s">
+      <c r="K315" t="s">
         <v>139</v>
       </c>
       <c r="L315" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M315" s="33" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="316" spans="1:13" x14ac:dyDescent="0.35">
@@ -16629,13 +16625,13 @@
         <v>324</v>
       </c>
       <c r="D316" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="E316" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F316" s="35" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="G316" s="33" t="s">
         <v>18</v>
@@ -16649,14 +16645,14 @@
       <c r="J316" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K316" s="37" t="s">
+      <c r="K316" t="s">
         <v>139</v>
       </c>
       <c r="L316" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M316" s="33" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="317" spans="1:13" x14ac:dyDescent="0.35">
@@ -16670,13 +16666,13 @@
         <v>325</v>
       </c>
       <c r="D317" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="E317" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F317" s="35" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="G317" s="33" t="s">
         <v>18</v>
@@ -16690,14 +16686,14 @@
       <c r="J317" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K317" s="37" t="s">
+      <c r="K317" t="s">
         <v>139</v>
       </c>
       <c r="L317" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M317" s="33" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
   </sheetData>
@@ -16802,13 +16798,13 @@
         <v>196</v>
       </c>
       <c r="D2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E2" t="s">
         <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G2" t="s">
         <v>18</v>
@@ -16829,7 +16825,7 @@
         <v>140</v>
       </c>
       <c r="M2" s="19" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -16843,13 +16839,13 @@
         <v>197</v>
       </c>
       <c r="D3" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E3" t="s">
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G3" t="s">
         <v>18</v>
@@ -16870,7 +16866,7 @@
         <v>140</v>
       </c>
       <c r="M3" s="19" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -16884,13 +16880,13 @@
         <v>198</v>
       </c>
       <c r="D4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G4" t="s">
         <v>18</v>
@@ -16911,7 +16907,7 @@
         <v>140</v>
       </c>
       <c r="M4" s="19" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -16925,13 +16921,13 @@
         <v>199</v>
       </c>
       <c r="D5" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E5" t="s">
         <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G5" t="s">
         <v>18</v>
@@ -16952,7 +16948,7 @@
         <v>140</v>
       </c>
       <c r="M5" s="19" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -16966,19 +16962,19 @@
         <v>200</v>
       </c>
       <c r="D6" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E6" t="s">
         <v>16</v>
       </c>
       <c r="F6" t="s">
+        <v>625</v>
+      </c>
+      <c r="G6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" t="s">
         <v>626</v>
-      </c>
-      <c r="G6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" t="s">
-        <v>627</v>
       </c>
       <c r="I6" t="s">
         <v>138</v>
@@ -16993,7 +16989,7 @@
         <v>140</v>
       </c>
       <c r="M6" s="18" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
   </sheetData>
@@ -17071,13 +17067,13 @@
         <v>201</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E2" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G2" s="17" t="s">
         <v>186</v>
@@ -17098,7 +17094,7 @@
         <v>140</v>
       </c>
       <c r="M2" s="17" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -17112,13 +17108,13 @@
         <v>202</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E3" s="17" t="s">
         <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="G3" s="17" t="s">
         <v>30</v>
@@ -17139,7 +17135,7 @@
         <v>140</v>
       </c>
       <c r="M3" s="17" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -17153,13 +17149,13 @@
         <v>203</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E4" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G4" s="17" t="s">
         <v>18</v>
@@ -17180,7 +17176,7 @@
         <v>140</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -17194,13 +17190,13 @@
         <v>204</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G5" s="17" t="s">
         <v>18</v>
@@ -17221,7 +17217,7 @@
         <v>140</v>
       </c>
       <c r="M5" s="17" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -17235,13 +17231,13 @@
         <v>205</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G6" s="17" t="s">
         <v>18</v>
@@ -17262,7 +17258,7 @@
         <v>140</v>
       </c>
       <c r="M6" s="17" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -17276,13 +17272,13 @@
         <v>206</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>438</v>
       </c>
       <c r="F7" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G7" s="17" t="s">
         <v>18</v>
@@ -17303,7 +17299,7 @@
         <v>248</v>
       </c>
       <c r="M7" s="17" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -17317,13 +17313,13 @@
         <v>207</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G8" s="17" t="s">
         <v>18</v>
@@ -17344,7 +17340,7 @@
         <v>140</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -17358,13 +17354,13 @@
         <v>208</v>
       </c>
       <c r="D9" s="17" t="s">
+        <v>649</v>
+      </c>
+      <c r="E9" s="17" t="s">
         <v>650</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="F9" t="s">
         <v>651</v>
-      </c>
-      <c r="F9" t="s">
-        <v>652</v>
       </c>
       <c r="G9" s="17" t="s">
         <v>30</v>
@@ -17376,7 +17372,7 @@
         <v>31</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K9" s="17" t="s">
         <v>157</v>
@@ -17385,7 +17381,7 @@
         <v>140</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
@@ -17399,13 +17395,13 @@
         <v>209</v>
       </c>
       <c r="D10" s="17" t="s">
+        <v>654</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F10" t="s">
         <v>655</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F10" t="s">
-        <v>656</v>
       </c>
       <c r="G10" s="17" t="s">
         <v>30</v>
@@ -17417,7 +17413,7 @@
         <v>20</v>
       </c>
       <c r="J10" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K10" s="17" t="s">
         <v>157</v>
@@ -17426,7 +17422,7 @@
         <v>140</v>
       </c>
       <c r="M10" s="17" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -17440,13 +17436,13 @@
         <v>210</v>
       </c>
       <c r="D11" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F11" t="s">
         <v>658</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F11" t="s">
-        <v>659</v>
       </c>
       <c r="G11" s="17" t="s">
         <v>30</v>
@@ -17458,7 +17454,7 @@
         <v>31</v>
       </c>
       <c r="J11" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K11" s="17" t="s">
         <v>157</v>
@@ -17467,7 +17463,7 @@
         <v>140</v>
       </c>
       <c r="M11" s="17" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -17481,13 +17477,13 @@
         <v>211</v>
       </c>
       <c r="D12" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F12" t="s">
         <v>661</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F12" t="s">
-        <v>662</v>
       </c>
       <c r="G12" s="17" t="s">
         <v>30</v>
@@ -17499,7 +17495,7 @@
         <v>31</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K12" s="17" t="s">
         <v>157</v>
@@ -17508,7 +17504,7 @@
         <v>140</v>
       </c>
       <c r="M12" s="17" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -17522,13 +17518,13 @@
         <v>212</v>
       </c>
       <c r="D13" s="17" t="s">
+        <v>663</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F13" t="s">
         <v>664</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F13" t="s">
-        <v>665</v>
       </c>
       <c r="G13" s="17" t="s">
         <v>30</v>
@@ -17540,7 +17536,7 @@
         <v>31</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K13" s="17" t="s">
         <v>157</v>
@@ -17549,7 +17545,7 @@
         <v>140</v>
       </c>
       <c r="M13" s="17" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -17563,13 +17559,13 @@
         <v>213</v>
       </c>
       <c r="D14" s="17" t="s">
+        <v>666</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F14" t="s">
         <v>667</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F14" t="s">
-        <v>668</v>
       </c>
       <c r="G14" s="17" t="s">
         <v>30</v>
@@ -17581,7 +17577,7 @@
         <v>31</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>157</v>
@@ -17590,7 +17586,7 @@
         <v>140</v>
       </c>
       <c r="M14" s="17" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -17604,13 +17600,13 @@
         <v>214</v>
       </c>
       <c r="D15" s="17" t="s">
+        <v>669</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F15" t="s">
         <v>670</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F15" t="s">
-        <v>671</v>
       </c>
       <c r="G15" s="17" t="s">
         <v>30</v>
@@ -17622,7 +17618,7 @@
         <v>31</v>
       </c>
       <c r="J15" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K15" s="17" t="s">
         <v>157</v>
@@ -17631,7 +17627,7 @@
         <v>140</v>
       </c>
       <c r="M15" s="17" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -17645,13 +17641,13 @@
         <v>215</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G16" s="17" t="s">
         <v>30</v>
@@ -17663,7 +17659,7 @@
         <v>31</v>
       </c>
       <c r="J16" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K16" s="17" t="s">
         <v>157</v>
@@ -17672,7 +17668,7 @@
         <v>140</v>
       </c>
       <c r="M16" s="17" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
@@ -17686,13 +17682,13 @@
         <v>216</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>25</v>
       </c>
       <c r="F17" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="G17" s="17" t="s">
         <v>30</v>
@@ -17704,7 +17700,7 @@
         <v>31</v>
       </c>
       <c r="J17" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K17" s="17" t="s">
         <v>157</v>
@@ -17713,7 +17709,7 @@
         <v>140</v>
       </c>
       <c r="M17" s="17" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
@@ -17727,13 +17723,13 @@
         <v>217</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>25</v>
       </c>
       <c r="F18" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G18" s="17" t="s">
         <v>30</v>
@@ -17745,7 +17741,7 @@
         <v>31</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K18" s="17" t="s">
         <v>157</v>
@@ -17754,7 +17750,7 @@
         <v>140</v>
       </c>
       <c r="M18" s="17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
@@ -17768,13 +17764,13 @@
         <v>218</v>
       </c>
       <c r="D19" s="17" t="s">
+        <v>681</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F19" t="s">
         <v>682</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F19" t="s">
-        <v>683</v>
       </c>
       <c r="G19" s="17" t="s">
         <v>30</v>
@@ -17786,7 +17782,7 @@
         <v>31</v>
       </c>
       <c r="J19" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K19" s="17" t="s">
         <v>157</v>
@@ -17795,7 +17791,7 @@
         <v>140</v>
       </c>
       <c r="M19" s="17" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
@@ -17809,13 +17805,13 @@
         <v>219</v>
       </c>
       <c r="D20" s="17" t="s">
+        <v>684</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F20" t="s">
         <v>685</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F20" t="s">
-        <v>686</v>
       </c>
       <c r="G20" s="17" t="s">
         <v>30</v>
@@ -17827,7 +17823,7 @@
         <v>31</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K20" s="17" t="s">
         <v>157</v>
@@ -17836,7 +17832,7 @@
         <v>140</v>
       </c>
       <c r="M20" s="17" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
@@ -17850,13 +17846,13 @@
         <v>220</v>
       </c>
       <c r="D21" s="17" t="s">
+        <v>687</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F21" t="s">
         <v>688</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F21" t="s">
-        <v>689</v>
       </c>
       <c r="G21" s="17" t="s">
         <v>30</v>
@@ -17868,7 +17864,7 @@
         <v>31</v>
       </c>
       <c r="J21" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K21" s="17" t="s">
         <v>157</v>
@@ -17877,7 +17873,7 @@
         <v>140</v>
       </c>
       <c r="M21" s="17" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
@@ -17891,13 +17887,13 @@
         <v>221</v>
       </c>
       <c r="D22" s="17" t="s">
+        <v>690</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F22" t="s">
         <v>691</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F22" t="s">
-        <v>692</v>
       </c>
       <c r="G22" s="17" t="s">
         <v>30</v>
@@ -17909,7 +17905,7 @@
         <v>20</v>
       </c>
       <c r="J22" s="17" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="K22" s="17" t="s">
         <v>157</v>
@@ -17918,7 +17914,7 @@
         <v>140</v>
       </c>
       <c r="M22" s="17" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
@@ -17932,13 +17928,13 @@
         <v>222</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="F23" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="G23" s="17" t="s">
         <v>30</v>
@@ -17950,7 +17946,7 @@
         <v>31</v>
       </c>
       <c r="J23" s="17" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="K23" s="17" t="s">
         <v>157</v>
@@ -17959,7 +17955,7 @@
         <v>140</v>
       </c>
       <c r="M23" s="17" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
@@ -17973,13 +17969,13 @@
         <v>223</v>
       </c>
       <c r="D24" s="17" t="s">
+        <v>696</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F24" t="s">
         <v>697</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F24" t="s">
-        <v>698</v>
       </c>
       <c r="G24" s="17" t="s">
         <v>30</v>
@@ -17991,7 +17987,7 @@
         <v>31</v>
       </c>
       <c r="J24" s="17" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="K24" s="17" t="s">
         <v>157</v>
@@ -18000,7 +17996,7 @@
         <v>140</v>
       </c>
       <c r="M24" s="17" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
@@ -18014,13 +18010,13 @@
         <v>224</v>
       </c>
       <c r="D25" s="17" t="s">
+        <v>699</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F25" t="s">
         <v>700</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F25" t="s">
-        <v>701</v>
       </c>
       <c r="G25" s="17" t="s">
         <v>30</v>
@@ -18032,7 +18028,7 @@
         <v>31</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="K25" s="17" t="s">
         <v>157</v>
@@ -18041,7 +18037,7 @@
         <v>140</v>
       </c>
       <c r="M25" s="17" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
@@ -18055,13 +18051,13 @@
         <v>225</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E26" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F26" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G26" s="17" t="s">
         <v>186</v>
@@ -18082,7 +18078,7 @@
         <v>140</v>
       </c>
       <c r="M26" s="17" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
@@ -18096,13 +18092,13 @@
         <v>226</v>
       </c>
       <c r="D27" s="17" t="s">
+        <v>705</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F27" t="s">
         <v>706</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F27" t="s">
-        <v>707</v>
       </c>
       <c r="G27" s="17" t="s">
         <v>30</v>
@@ -18114,7 +18110,7 @@
         <v>31</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K27" s="17" t="s">
         <v>157</v>
@@ -18123,7 +18119,7 @@
         <v>140</v>
       </c>
       <c r="M27" s="17" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
@@ -18137,13 +18133,13 @@
         <v>227</v>
       </c>
       <c r="D28" s="17" t="s">
+        <v>708</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F28" t="s">
         <v>709</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F28" t="s">
-        <v>710</v>
       </c>
       <c r="G28" s="17" t="s">
         <v>186</v>
@@ -18155,7 +18151,7 @@
         <v>31</v>
       </c>
       <c r="J28" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K28" s="17" t="s">
         <v>157</v>
@@ -18164,7 +18160,7 @@
         <v>140</v>
       </c>
       <c r="M28" s="17" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
@@ -18178,13 +18174,13 @@
         <v>228</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>438</v>
       </c>
       <c r="F29" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="G29" s="17" t="s">
         <v>30</v>
@@ -18196,7 +18192,7 @@
         <v>31</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K29" s="17" t="s">
         <v>157</v>
@@ -18205,7 +18201,7 @@
         <v>248</v>
       </c>
       <c r="M29" s="17" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.35">
@@ -18219,13 +18215,13 @@
         <v>229</v>
       </c>
       <c r="D30" s="17" t="s">
+        <v>714</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F30" t="s">
         <v>715</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F30" t="s">
-        <v>716</v>
       </c>
       <c r="G30" s="17" t="s">
         <v>186</v>
@@ -18246,7 +18242,7 @@
         <v>140</v>
       </c>
       <c r="M30" s="17" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
@@ -18260,13 +18256,13 @@
         <v>230</v>
       </c>
       <c r="D31" s="17" t="s">
+        <v>717</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F31" t="s">
         <v>718</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F31" t="s">
-        <v>719</v>
       </c>
       <c r="G31" s="17" t="s">
         <v>30</v>
@@ -18287,7 +18283,7 @@
         <v>140</v>
       </c>
       <c r="M31" s="17" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.35">
@@ -18301,13 +18297,13 @@
         <v>231</v>
       </c>
       <c r="D32" s="17" t="s">
+        <v>720</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F32" t="s">
         <v>721</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F32" t="s">
-        <v>722</v>
       </c>
       <c r="G32" s="17" t="s">
         <v>30</v>
@@ -18319,7 +18315,7 @@
         <v>31</v>
       </c>
       <c r="J32" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K32" s="17" t="s">
         <v>157</v>
@@ -18328,7 +18324,7 @@
         <v>140</v>
       </c>
       <c r="M32" s="17" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.35">
@@ -18342,13 +18338,13 @@
         <v>232</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E33" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F33" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="G33" s="17" t="s">
         <v>30</v>
@@ -18369,7 +18365,7 @@
         <v>248</v>
       </c>
       <c r="M33" s="17" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.35">
@@ -18383,13 +18379,13 @@
         <v>233</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E34" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F34" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="G34" s="17" t="s">
         <v>30</v>
@@ -18410,7 +18406,7 @@
         <v>248</v>
       </c>
       <c r="M34" s="17" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.35">
@@ -18424,13 +18420,13 @@
         <v>234</v>
       </c>
       <c r="D35" s="17" t="s">
+        <v>729</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F35" t="s">
         <v>730</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F35" t="s">
-        <v>731</v>
       </c>
       <c r="G35" s="17" t="s">
         <v>18</v>
@@ -18442,7 +18438,7 @@
         <v>20</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K35" s="17" t="s">
         <v>157</v>
@@ -18451,7 +18447,7 @@
         <v>248</v>
       </c>
       <c r="M35" s="17" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.35">
@@ -18465,13 +18461,13 @@
         <v>235</v>
       </c>
       <c r="D36" s="17" t="s">
+        <v>732</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F36" t="s">
         <v>733</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F36" t="s">
-        <v>734</v>
       </c>
       <c r="G36" s="17" t="s">
         <v>30</v>
@@ -18483,7 +18479,7 @@
         <v>138</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K36" s="17" t="s">
         <v>157</v>
@@ -18492,7 +18488,7 @@
         <v>248</v>
       </c>
       <c r="M36" s="17" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.35">
@@ -18506,13 +18502,13 @@
         <v>236</v>
       </c>
       <c r="D37" s="17" t="s">
+        <v>735</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F37" t="s">
         <v>736</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F37" t="s">
-        <v>737</v>
       </c>
       <c r="G37" s="17" t="s">
         <v>30</v>
@@ -18524,7 +18520,7 @@
         <v>138</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K37" s="17" t="s">
         <v>157</v>
@@ -18533,7 +18529,7 @@
         <v>248</v>
       </c>
       <c r="M37" s="17" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.35">
@@ -18547,13 +18543,13 @@
         <v>237</v>
       </c>
       <c r="D38" s="17" t="s">
+        <v>738</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F38" t="s">
         <v>739</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F38" t="s">
-        <v>740</v>
       </c>
       <c r="G38" s="17" t="s">
         <v>30</v>
@@ -18565,7 +18561,7 @@
         <v>138</v>
       </c>
       <c r="J38" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K38" s="17" t="s">
         <v>157</v>
@@ -18574,7 +18570,7 @@
         <v>248</v>
       </c>
       <c r="M38" s="17" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.35">
@@ -18588,13 +18584,13 @@
         <v>238</v>
       </c>
       <c r="D39" s="17" t="s">
+        <v>741</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F39" t="s">
         <v>742</v>
-      </c>
-      <c r="E39" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F39" t="s">
-        <v>743</v>
       </c>
       <c r="G39" s="17" t="s">
         <v>30</v>
@@ -18606,7 +18602,7 @@
         <v>138</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K39" s="17" t="s">
         <v>157</v>
@@ -18615,7 +18611,7 @@
         <v>248</v>
       </c>
       <c r="M39" s="17" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.35">
@@ -18629,13 +18625,13 @@
         <v>239</v>
       </c>
       <c r="D40" s="17" t="s">
+        <v>744</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F40" t="s">
         <v>745</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F40" t="s">
-        <v>746</v>
       </c>
       <c r="G40" s="17" t="s">
         <v>30</v>
@@ -18647,7 +18643,7 @@
         <v>138</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K40" s="17" t="s">
         <v>157</v>
@@ -18656,7 +18652,7 @@
         <v>248</v>
       </c>
       <c r="M40" s="17" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.35">
@@ -18670,13 +18666,13 @@
         <v>240</v>
       </c>
       <c r="D41" s="17" t="s">
+        <v>747</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F41" t="s">
         <v>748</v>
-      </c>
-      <c r="E41" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="F41" t="s">
-        <v>749</v>
       </c>
       <c r="G41" s="17" t="s">
         <v>30</v>
@@ -18688,7 +18684,7 @@
         <v>138</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K41" s="17" t="s">
         <v>157</v>
@@ -18714,10 +18710,10 @@
         <v>142</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="F42" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G42" s="17" t="s">
         <v>30</v>
@@ -18729,7 +18725,7 @@
         <v>20</v>
       </c>
       <c r="J42" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>157</v>
@@ -18816,13 +18812,13 @@
         <v>242</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>135</v>
       </c>
       <c r="F2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="G2" t="s">
         <v>30</v>
@@ -18834,7 +18830,7 @@
         <v>31</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="K2" s="6" t="s">
         <v>157</v>
@@ -18843,7 +18839,7 @@
         <v>140</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -18857,16 +18853,16 @@
         <v>243</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="G3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>153</v>
@@ -18875,7 +18871,7 @@
         <v>20</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>157</v>
@@ -18884,7 +18880,7 @@
         <v>140</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -18898,13 +18894,13 @@
         <v>244</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="G4" t="s">
         <v>30</v>
@@ -18925,7 +18921,7 @@
         <v>140</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -18939,13 +18935,13 @@
         <v>245</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="G5" t="s">
         <v>30</v>
@@ -18966,7 +18962,7 @@
         <v>140</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -18980,13 +18976,13 @@
         <v>246</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="G6" t="s">
         <v>30</v>
@@ -19007,7 +19003,7 @@
         <v>140</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -19021,13 +19017,13 @@
         <v>247</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G7" t="s">
         <v>18</v>
@@ -19048,7 +19044,7 @@
         <v>140</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -19062,13 +19058,13 @@
         <v>248</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="G8" t="s">
         <v>18</v>
@@ -19089,7 +19085,7 @@
         <v>140</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -19103,19 +19099,19 @@
         <v>249</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="G9" t="s">
         <v>18</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>20</v>
@@ -19130,7 +19126,7 @@
         <v>140</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -19144,13 +19140,13 @@
         <v>250</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="G10" t="s">
         <v>30</v>
@@ -19162,7 +19158,7 @@
         <v>31</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>157</v>
@@ -19171,7 +19167,7 @@
         <v>140</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -19185,13 +19181,13 @@
         <v>251</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="G11" t="s">
         <v>18</v>
@@ -19212,7 +19208,7 @@
         <v>140</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -19226,13 +19222,13 @@
         <v>252</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="G12" t="s">
         <v>30</v>
@@ -19253,7 +19249,7 @@
         <v>140</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -19267,13 +19263,13 @@
         <v>253</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>438</v>
       </c>
       <c r="F13" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G13" t="s">
         <v>18</v>
@@ -19294,7 +19290,7 @@
         <v>140</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -19308,13 +19304,13 @@
         <v>254</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>438</v>
       </c>
       <c r="F14" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G14" t="s">
         <v>18</v>
@@ -19335,7 +19331,7 @@
         <v>140</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -19349,13 +19345,13 @@
         <v>255</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>438</v>
       </c>
       <c r="F15" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="G15" t="s">
         <v>18</v>
@@ -19376,7 +19372,7 @@
         <v>140</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -19390,13 +19386,13 @@
         <v>256</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>438</v>
       </c>
       <c r="F16" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="G16" t="s">
         <v>18</v>
@@ -19417,7 +19413,7 @@
         <v>140</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -19431,19 +19427,19 @@
         <v>257</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>438</v>
       </c>
       <c r="F17" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="G17" t="s">
         <v>18</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="I17" s="6" t="s">
         <v>20</v>
@@ -19458,7 +19454,7 @@
         <v>140</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -19472,13 +19468,13 @@
         <v>258</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>438</v>
       </c>
       <c r="F18" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="G18" t="s">
         <v>18</v>
@@ -19499,7 +19495,7 @@
         <v>140</v>
       </c>
       <c r="M18" s="32" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -19513,13 +19509,13 @@
         <v>259</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>438</v>
       </c>
       <c r="F19" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="G19" t="s">
         <v>18</v>
@@ -19540,7 +19536,7 @@
         <v>140</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -19554,13 +19550,13 @@
         <v>260</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>438</v>
       </c>
       <c r="F20" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="G20" t="s">
         <v>18</v>
@@ -19581,7 +19577,7 @@
         <v>140</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
   </sheetData>
@@ -19659,13 +19655,13 @@
         <v>261</v>
       </c>
       <c r="D2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G2" s="33" t="s">
         <v>18</v>
@@ -19679,14 +19675,14 @@
       <c r="J2" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K2" s="37" t="s">
+      <c r="K2" t="s">
         <v>139</v>
       </c>
       <c r="L2" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M2" s="33" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -19700,13 +19696,13 @@
         <v>262</v>
       </c>
       <c r="D3" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="G3" s="33" t="s">
         <v>18</v>
@@ -19720,14 +19716,14 @@
       <c r="J3" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K3" s="37" t="s">
+      <c r="K3" t="s">
         <v>139</v>
       </c>
       <c r="L3" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M3" s="33" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -19741,13 +19737,13 @@
         <v>263</v>
       </c>
       <c r="D4" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G4" s="33" t="s">
         <v>18</v>
@@ -19761,14 +19757,14 @@
       <c r="J4" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K4" s="37" t="s">
+      <c r="K4" t="s">
         <v>139</v>
       </c>
       <c r="L4" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M4" s="33" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -19782,13 +19778,13 @@
         <v>264</v>
       </c>
       <c r="D5" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="G5" s="33" t="s">
         <v>18</v>
@@ -19802,14 +19798,14 @@
       <c r="J5" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K5" s="37" t="s">
+      <c r="K5" t="s">
         <v>139</v>
       </c>
       <c r="L5" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M5" s="33" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -19823,13 +19819,13 @@
         <v>265</v>
       </c>
       <c r="D6" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="G6" s="33" t="s">
         <v>18</v>
@@ -19843,14 +19839,14 @@
       <c r="J6" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K6" s="37" t="s">
+      <c r="K6" t="s">
         <v>139</v>
       </c>
       <c r="L6" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M6" s="33" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -19864,13 +19860,13 @@
         <v>266</v>
       </c>
       <c r="D7" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="G7" s="33" t="s">
         <v>18</v>
@@ -19884,14 +19880,14 @@
       <c r="J7" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K7" s="37" t="s">
+      <c r="K7" t="s">
         <v>139</v>
       </c>
       <c r="L7" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M7" s="33" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -19905,13 +19901,13 @@
         <v>267</v>
       </c>
       <c r="D8" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="G8" s="33" t="s">
         <v>18</v>
@@ -19925,14 +19921,14 @@
       <c r="J8" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K8" s="37" t="s">
+      <c r="K8" t="s">
         <v>139</v>
       </c>
       <c r="L8" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M8" s="33" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -19946,13 +19942,13 @@
         <v>268</v>
       </c>
       <c r="D9" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="G9" s="33" t="s">
         <v>18</v>
@@ -19966,14 +19962,14 @@
       <c r="J9" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K9" s="37" t="s">
+      <c r="K9" t="s">
         <v>139</v>
       </c>
       <c r="L9" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M9" s="33" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
@@ -19987,13 +19983,13 @@
         <v>269</v>
       </c>
       <c r="D10" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="G10" s="33" t="s">
         <v>18</v>
@@ -20007,14 +20003,14 @@
       <c r="J10" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K10" s="37" t="s">
+      <c r="K10" t="s">
         <v>139</v>
       </c>
       <c r="L10" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M10" s="33" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -20028,13 +20024,13 @@
         <v>270</v>
       </c>
       <c r="D11" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="G11" s="33" t="s">
         <v>18</v>
@@ -20048,14 +20044,14 @@
       <c r="J11" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K11" s="37" t="s">
+      <c r="K11" t="s">
         <v>139</v>
       </c>
       <c r="L11" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M11" s="33" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -20069,13 +20065,13 @@
         <v>271</v>
       </c>
       <c r="D12" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="G12" s="33" t="s">
         <v>18</v>
@@ -20089,14 +20085,14 @@
       <c r="J12" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K12" s="37" t="s">
+      <c r="K12" t="s">
         <v>139</v>
       </c>
       <c r="L12" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M12" s="33" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -20110,13 +20106,13 @@
         <v>272</v>
       </c>
       <c r="D13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="G13" s="33" t="s">
         <v>18</v>
@@ -20130,14 +20126,14 @@
       <c r="J13" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K13" s="37" t="s">
+      <c r="K13" t="s">
         <v>139</v>
       </c>
       <c r="L13" s="33" t="s">
         <v>248</v>
       </c>
       <c r="M13" s="33" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -20151,13 +20147,13 @@
         <v>273</v>
       </c>
       <c r="D14" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="G14" s="33" t="s">
         <v>18</v>
@@ -20171,14 +20167,14 @@
       <c r="J14" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K14" s="37" t="s">
+      <c r="K14" t="s">
         <v>139</v>
       </c>
       <c r="L14" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M14" s="33" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -20192,13 +20188,13 @@
         <v>274</v>
       </c>
       <c r="D15" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F15" s="35" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="G15" s="33" t="s">
         <v>18</v>
@@ -20212,14 +20208,14 @@
       <c r="J15" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K15" s="37" t="s">
+      <c r="K15" t="s">
         <v>139</v>
       </c>
       <c r="L15" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M15" s="33" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -20233,13 +20229,13 @@
         <v>275</v>
       </c>
       <c r="D16" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F16" s="35" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G16" s="33" t="s">
         <v>18</v>
@@ -20253,14 +20249,14 @@
       <c r="J16" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K16" s="37" t="s">
+      <c r="K16" t="s">
         <v>139</v>
       </c>
       <c r="L16" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M16" s="33" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
@@ -20274,13 +20270,13 @@
         <v>276</v>
       </c>
       <c r="D17" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F17" s="35" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G17" s="33" t="s">
         <v>18</v>
@@ -20294,14 +20290,14 @@
       <c r="J17" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K17" s="37" t="s">
+      <c r="K17" t="s">
         <v>139</v>
       </c>
       <c r="L17" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M17" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
@@ -20315,13 +20311,13 @@
         <v>277</v>
       </c>
       <c r="D18" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F18" s="35" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="G18" s="33" t="s">
         <v>18</v>
@@ -20335,14 +20331,14 @@
       <c r="J18" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K18" s="37" t="s">
+      <c r="K18" t="s">
         <v>139</v>
       </c>
       <c r="L18" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M18" s="33" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
@@ -20356,13 +20352,13 @@
         <v>278</v>
       </c>
       <c r="D19" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F19" s="35" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="G19" s="33" t="s">
         <v>18</v>
@@ -20376,14 +20372,14 @@
       <c r="J19" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K19" s="37" t="s">
+      <c r="K19" t="s">
         <v>139</v>
       </c>
       <c r="L19" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M19" s="33" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
@@ -20397,13 +20393,13 @@
         <v>279</v>
       </c>
       <c r="D20" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F20" s="35" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="G20" s="33" t="s">
         <v>18</v>
@@ -20417,14 +20413,14 @@
       <c r="J20" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K20" s="37" t="s">
+      <c r="K20" t="s">
         <v>139</v>
       </c>
       <c r="L20" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M20" s="33" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
@@ -20438,13 +20434,13 @@
         <v>280</v>
       </c>
       <c r="D21" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E21" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F21" s="35" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="G21" s="33" t="s">
         <v>18</v>
@@ -20458,14 +20454,14 @@
       <c r="J21" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K21" s="37" t="s">
+      <c r="K21" t="s">
         <v>139</v>
       </c>
       <c r="L21" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M21" s="33" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
@@ -20479,13 +20475,13 @@
         <v>281</v>
       </c>
       <c r="D22" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F22" s="35" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="G22" s="33" t="s">
         <v>18</v>
@@ -20499,14 +20495,14 @@
       <c r="J22" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K22" s="37" t="s">
+      <c r="K22" t="s">
         <v>139</v>
       </c>
       <c r="L22" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M22" s="33" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
@@ -20520,13 +20516,13 @@
         <v>282</v>
       </c>
       <c r="D23" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F23" s="35" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="G23" s="33" t="s">
         <v>18</v>
@@ -20540,14 +20536,14 @@
       <c r="J23" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K23" s="37" t="s">
+      <c r="K23" t="s">
         <v>139</v>
       </c>
       <c r="L23" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M23" s="33" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
@@ -20561,13 +20557,13 @@
         <v>283</v>
       </c>
       <c r="D24" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F24" s="35" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="G24" s="33" t="s">
         <v>18</v>
@@ -20581,14 +20577,14 @@
       <c r="J24" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K24" s="37" t="s">
+      <c r="K24" t="s">
         <v>139</v>
       </c>
       <c r="L24" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M24" s="33" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
@@ -20602,13 +20598,13 @@
         <v>284</v>
       </c>
       <c r="D25" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F25" s="35" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="G25" s="33" t="s">
         <v>18</v>
@@ -20622,14 +20618,14 @@
       <c r="J25" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K25" s="37" t="s">
+      <c r="K25" t="s">
         <v>139</v>
       </c>
       <c r="L25" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M25" s="33" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
@@ -20643,13 +20639,13 @@
         <v>285</v>
       </c>
       <c r="D26" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F26" s="35" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="G26" s="33" t="s">
         <v>18</v>
@@ -20663,14 +20659,14 @@
       <c r="J26" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K26" s="37" t="s">
+      <c r="K26" t="s">
         <v>139</v>
       </c>
       <c r="L26" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M26" s="33" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
@@ -20684,13 +20680,13 @@
         <v>286</v>
       </c>
       <c r="D27" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F27" s="35" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="G27" s="33" t="s">
         <v>18</v>
@@ -20704,14 +20700,14 @@
       <c r="J27" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K27" s="37" t="s">
+      <c r="K27" t="s">
         <v>139</v>
       </c>
       <c r="L27" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M27" s="33" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
@@ -20725,13 +20721,13 @@
         <v>287</v>
       </c>
       <c r="D28" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F28" s="35" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G28" s="33" t="s">
         <v>18</v>
@@ -20745,14 +20741,14 @@
       <c r="J28" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K28" s="37" t="s">
+      <c r="K28" t="s">
         <v>139</v>
       </c>
       <c r="L28" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M28" s="33" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
@@ -20766,13 +20762,13 @@
         <v>288</v>
       </c>
       <c r="D29" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F29" s="35" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="G29" s="33" t="s">
         <v>18</v>
@@ -20786,14 +20782,14 @@
       <c r="J29" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K29" s="37" t="s">
+      <c r="K29" t="s">
         <v>139</v>
       </c>
       <c r="L29" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M29" s="33" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.35">
@@ -20807,13 +20803,13 @@
         <v>289</v>
       </c>
       <c r="D30" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F30" s="35" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="G30" s="33" t="s">
         <v>18</v>
@@ -20827,14 +20823,14 @@
       <c r="J30" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K30" s="37" t="s">
+      <c r="K30" t="s">
         <v>139</v>
       </c>
       <c r="L30" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M30" s="33" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
@@ -20848,13 +20844,13 @@
         <v>290</v>
       </c>
       <c r="D31" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F31" s="35" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G31" s="33" t="s">
         <v>18</v>
@@ -20868,14 +20864,14 @@
       <c r="J31" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K31" s="37" t="s">
+      <c r="K31" t="s">
         <v>139</v>
       </c>
       <c r="L31" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M31" s="33" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.35">
@@ -20889,13 +20885,13 @@
         <v>300</v>
       </c>
       <c r="D32" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F32" s="35" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G32" s="33" t="s">
         <v>18</v>
@@ -20909,14 +20905,14 @@
       <c r="J32" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K32" s="37" t="s">
+      <c r="K32" t="s">
         <v>139</v>
       </c>
       <c r="L32" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M32" s="33" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.35">
@@ -20930,13 +20926,13 @@
         <v>301</v>
       </c>
       <c r="D33" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E33" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F33" s="35" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="G33" s="33" t="s">
         <v>18</v>
@@ -20950,14 +20946,14 @@
       <c r="J33" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K33" s="37" t="s">
+      <c r="K33" t="s">
         <v>139</v>
       </c>
       <c r="L33" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M33" s="33" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.35">
@@ -20971,13 +20967,13 @@
         <v>302</v>
       </c>
       <c r="D34" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="E34" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F34" s="35" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="G34" s="33" t="s">
         <v>18</v>
@@ -20991,14 +20987,14 @@
       <c r="J34" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K34" s="37" t="s">
+      <c r="K34" t="s">
         <v>139</v>
       </c>
       <c r="L34" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M34" s="33" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.35">
@@ -21012,13 +21008,13 @@
         <v>303</v>
       </c>
       <c r="D35" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E35" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F35" s="35" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="G35" s="33" t="s">
         <v>18</v>
@@ -21032,14 +21028,14 @@
       <c r="J35" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K35" s="37" t="s">
+      <c r="K35" t="s">
         <v>139</v>
       </c>
       <c r="L35" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M35" s="33" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.35">
@@ -21053,13 +21049,13 @@
         <v>304</v>
       </c>
       <c r="D36" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E36" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F36" s="35" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="G36" s="33" t="s">
         <v>18</v>
@@ -21073,14 +21069,14 @@
       <c r="J36" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K36" s="37" t="s">
+      <c r="K36" t="s">
         <v>139</v>
       </c>
       <c r="L36" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M36" s="33" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.35">
@@ -21094,13 +21090,13 @@
         <v>305</v>
       </c>
       <c r="D37" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="E37" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F37" s="35" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G37" s="33" t="s">
         <v>18</v>
@@ -21114,14 +21110,14 @@
       <c r="J37" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K37" s="37" t="s">
+      <c r="K37" t="s">
         <v>139</v>
       </c>
       <c r="L37" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M37" s="33" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.35">
@@ -21135,13 +21131,13 @@
         <v>306</v>
       </c>
       <c r="D38" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="E38" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F38" s="35" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="G38" s="33" t="s">
         <v>18</v>
@@ -21155,14 +21151,14 @@
       <c r="J38" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K38" s="37" t="s">
+      <c r="K38" t="s">
         <v>139</v>
       </c>
       <c r="L38" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M38" s="33" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.35">
@@ -21176,13 +21172,13 @@
         <v>307</v>
       </c>
       <c r="D39" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F39" s="35" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G39" s="33" t="s">
         <v>18</v>
@@ -21196,14 +21192,14 @@
       <c r="J39" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K39" s="37" t="s">
+      <c r="K39" t="s">
         <v>139</v>
       </c>
       <c r="L39" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M39" s="33" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.35">
@@ -21217,13 +21213,13 @@
         <v>308</v>
       </c>
       <c r="D40" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F40" s="35" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G40" s="33" t="s">
         <v>18</v>
@@ -21237,14 +21233,14 @@
       <c r="J40" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K40" s="37" t="s">
+      <c r="K40" t="s">
         <v>139</v>
       </c>
       <c r="L40" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M40" s="33" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.35">
@@ -21258,13 +21254,13 @@
         <v>309</v>
       </c>
       <c r="D41" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="E41" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F41" s="35" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="G41" s="33" t="s">
         <v>18</v>
@@ -21278,14 +21274,14 @@
       <c r="J41" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K41" s="37" t="s">
+      <c r="K41" t="s">
         <v>139</v>
       </c>
       <c r="L41" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M41" s="33" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.35">
@@ -21299,13 +21295,13 @@
         <v>310</v>
       </c>
       <c r="D42" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="E42" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F42" s="35" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="G42" s="33" t="s">
         <v>18</v>
@@ -21319,14 +21315,14 @@
       <c r="J42" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K42" s="37" t="s">
+      <c r="K42" t="s">
         <v>139</v>
       </c>
       <c r="L42" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M42" s="33" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.35">
@@ -21340,13 +21336,13 @@
         <v>311</v>
       </c>
       <c r="D43" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E43" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F43" s="35" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="G43" s="33" t="s">
         <v>30</v>
@@ -21360,14 +21356,14 @@
       <c r="J43" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K43" s="37" t="s">
+      <c r="K43" t="s">
         <v>139</v>
       </c>
       <c r="L43" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M43" s="33" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.35">
@@ -21381,13 +21377,13 @@
         <v>312</v>
       </c>
       <c r="D44" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="E44" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F44" s="35" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="G44" s="33" t="s">
         <v>18</v>
@@ -21401,14 +21397,14 @@
       <c r="J44" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K44" s="37" t="s">
+      <c r="K44" t="s">
         <v>139</v>
       </c>
       <c r="L44" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M44" s="33" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.35">
@@ -21422,13 +21418,13 @@
         <v>313</v>
       </c>
       <c r="D45" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="E45" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F45" s="35" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="G45" s="33" t="s">
         <v>30</v>
@@ -21442,14 +21438,14 @@
       <c r="J45" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K45" s="37" t="s">
+      <c r="K45" t="s">
         <v>139</v>
       </c>
       <c r="L45" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M45" s="33" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.35">
@@ -21463,13 +21459,13 @@
         <v>314</v>
       </c>
       <c r="D46" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="E46" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F46" s="35" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="G46" s="33" t="s">
         <v>18</v>
@@ -21483,14 +21479,14 @@
       <c r="J46" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K46" s="37" t="s">
+      <c r="K46" t="s">
         <v>139</v>
       </c>
       <c r="L46" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M46" s="33" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.35">
@@ -21504,13 +21500,13 @@
         <v>315</v>
       </c>
       <c r="D47" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="E47" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F47" s="35" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="G47" s="33" t="s">
         <v>18</v>
@@ -21524,14 +21520,14 @@
       <c r="J47" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K47" s="37" t="s">
+      <c r="K47" t="s">
         <v>139</v>
       </c>
       <c r="L47" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M47" s="33" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.35">
@@ -21545,13 +21541,13 @@
         <v>316</v>
       </c>
       <c r="D48" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F48" s="35" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="G48" s="33" t="s">
         <v>18</v>
@@ -21565,14 +21561,14 @@
       <c r="J48" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K48" s="37" t="s">
+      <c r="K48" t="s">
         <v>139</v>
       </c>
       <c r="L48" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M48" s="33" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.35">
@@ -21586,13 +21582,13 @@
         <v>317</v>
       </c>
       <c r="D49" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="E49" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F49" s="35" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="G49" s="33" t="s">
         <v>18</v>
@@ -21606,14 +21602,14 @@
       <c r="J49" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K49" s="37" t="s">
+      <c r="K49" t="s">
         <v>139</v>
       </c>
       <c r="L49" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M49" s="33" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.35">
@@ -21627,13 +21623,13 @@
         <v>318</v>
       </c>
       <c r="D50" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E50" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F50" s="35" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="G50" s="33" t="s">
         <v>18</v>
@@ -21647,14 +21643,14 @@
       <c r="J50" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K50" s="37" t="s">
+      <c r="K50" t="s">
         <v>139</v>
       </c>
       <c r="L50" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M50" s="33" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.35">
@@ -21668,13 +21664,13 @@
         <v>319</v>
       </c>
       <c r="D51" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="E51" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F51" s="35" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="G51" s="33" t="s">
         <v>30</v>
@@ -21688,14 +21684,14 @@
       <c r="J51" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K51" s="37" t="s">
+      <c r="K51" t="s">
         <v>139</v>
       </c>
       <c r="L51" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M51" s="33" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.35">
@@ -21709,13 +21705,13 @@
         <v>320</v>
       </c>
       <c r="D52" s="34" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="E52" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F52" s="35" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="G52" s="33" t="s">
         <v>30</v>
@@ -21729,14 +21725,14 @@
       <c r="J52" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K52" s="37" t="s">
+      <c r="K52" t="s">
         <v>139</v>
       </c>
       <c r="L52" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M52" s="33" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.35">
@@ -21750,13 +21746,13 @@
         <v>321</v>
       </c>
       <c r="D53" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E53" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F53" s="35" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="G53" s="33" t="s">
         <v>30</v>
@@ -21770,14 +21766,14 @@
       <c r="J53" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K53" s="37" t="s">
+      <c r="K53" t="s">
         <v>139</v>
       </c>
       <c r="L53" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M53" s="33" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.35">
@@ -21791,13 +21787,13 @@
         <v>322</v>
       </c>
       <c r="D54" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="E54" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F54" s="35" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="G54" s="33" t="s">
         <v>18</v>
@@ -21811,14 +21807,14 @@
       <c r="J54" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K54" s="37" t="s">
+      <c r="K54" t="s">
         <v>139</v>
       </c>
       <c r="L54" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M54" s="33" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.35">
@@ -21832,13 +21828,13 @@
         <v>323</v>
       </c>
       <c r="D55" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E55" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F55" s="35" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="G55" s="33" t="s">
         <v>18</v>
@@ -21852,14 +21848,14 @@
       <c r="J55" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K55" s="37" t="s">
+      <c r="K55" t="s">
         <v>139</v>
       </c>
       <c r="L55" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M55" s="33" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.35">
@@ -21873,13 +21869,13 @@
         <v>324</v>
       </c>
       <c r="D56" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="E56" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F56" s="35" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="G56" s="33" t="s">
         <v>18</v>
@@ -21893,14 +21889,14 @@
       <c r="J56" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K56" s="37" t="s">
+      <c r="K56" t="s">
         <v>139</v>
       </c>
       <c r="L56" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M56" s="33" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.35">
@@ -21914,13 +21910,13 @@
         <v>325</v>
       </c>
       <c r="D57" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="E57" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F57" s="35" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="G57" s="33" t="s">
         <v>18</v>
@@ -21934,14 +21930,14 @@
       <c r="J57" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="K57" s="37" t="s">
+      <c r="K57" t="s">
         <v>139</v>
       </c>
       <c r="L57" s="33" t="s">
         <v>140</v>
       </c>
       <c r="M57" s="33" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.35">
@@ -22932,7 +22928,7 @@
         <v>58</v>
       </c>
       <c r="M23" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
@@ -22973,7 +22969,7 @@
         <v>58</v>
       </c>
       <c r="M24" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
@@ -23014,7 +23010,7 @@
         <v>58</v>
       </c>
       <c r="M25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
@@ -23055,7 +23051,7 @@
         <v>58</v>
       </c>
       <c r="M26" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
@@ -23096,7 +23092,7 @@
         <v>58</v>
       </c>
       <c r="M27" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
@@ -23137,7 +23133,7 @@
         <v>58</v>
       </c>
       <c r="M28" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
@@ -24123,7 +24119,7 @@
         <v>159</v>
       </c>
       <c r="F8" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="G8" t="s">
         <v>30</v>
@@ -28512,7 +28508,7 @@
         <v>438</v>
       </c>
       <c r="F15" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="G15" t="s">
         <v>18</v>
@@ -28659,7 +28655,7 @@
         <v>260</v>
       </c>
       <c r="F2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="G2" t="s">
         <v>18</v>
@@ -28700,7 +28696,7 @@
         <v>260</v>
       </c>
       <c r="F3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="G3" t="s">
         <v>18</v>
@@ -28741,7 +28737,7 @@
         <v>260</v>
       </c>
       <c r="F4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="G4" t="s">
         <v>18</v>
@@ -28782,7 +28778,7 @@
         <v>260</v>
       </c>
       <c r="F5" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G5" t="s">
         <v>18</v>
@@ -28823,7 +28819,7 @@
         <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G6" t="s">
         <v>30</v>
@@ -28864,7 +28860,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="G7" t="s">
         <v>30</v>
@@ -28905,7 +28901,7 @@
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G8" t="s">
         <v>30</v>
@@ -28946,7 +28942,7 @@
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="G9" t="s">
         <v>30</v>
@@ -29050,7 +29046,7 @@
         <v>488</v>
       </c>
       <c r="F2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G2" s="18" t="s">
         <v>18</v>
@@ -29091,7 +29087,7 @@
         <v>488</v>
       </c>
       <c r="F3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G3" s="18" t="s">
         <v>18</v>
@@ -29132,7 +29128,7 @@
         <v>488</v>
       </c>
       <c r="F4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G4" s="18" t="s">
         <v>18</v>
@@ -29173,7 +29169,7 @@
         <v>488</v>
       </c>
       <c r="F5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G5" s="18" t="s">
         <v>30</v>
@@ -29214,7 +29210,7 @@
         <v>488</v>
       </c>
       <c r="F6" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>30</v>
@@ -29255,7 +29251,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G7" s="18" t="s">
         <v>18</v>
@@ -29296,7 +29292,7 @@
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G8" s="18" t="s">
         <v>18</v>
@@ -29378,7 +29374,7 @@
         <v>260</v>
       </c>
       <c r="F10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G10" s="18" t="s">
         <v>18</v>
@@ -29419,7 +29415,7 @@
         <v>260</v>
       </c>
       <c r="F11" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G11" s="18" t="s">
         <v>18</v>
@@ -29460,7 +29456,7 @@
         <v>488</v>
       </c>
       <c r="F12" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>30</v>
@@ -29501,7 +29497,7 @@
         <v>488</v>
       </c>
       <c r="F13" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>30</v>
@@ -29542,7 +29538,7 @@
         <v>488</v>
       </c>
       <c r="F14" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>30</v>
@@ -29583,7 +29579,7 @@
         <v>488</v>
       </c>
       <c r="F15" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>30</v>
@@ -29624,7 +29620,7 @@
         <v>488</v>
       </c>
       <c r="F16" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G16" s="18" t="s">
         <v>186</v>
@@ -29723,16 +29719,16 @@
         <v>177</v>
       </c>
       <c r="D2" s="24" t="s">
+        <v>554</v>
+      </c>
+      <c r="E2" t="s">
         <v>555</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>556</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" s="24" t="s">
         <v>557</v>
-      </c>
-      <c r="G2" s="24" t="s">
-        <v>558</v>
       </c>
       <c r="H2" s="24" t="s">
         <v>137</v>
@@ -29741,7 +29737,7 @@
         <v>20</v>
       </c>
       <c r="J2" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K2" s="24" t="s">
         <v>157</v>
@@ -29750,7 +29746,7 @@
         <v>140</v>
       </c>
       <c r="M2" s="27" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -29764,16 +29760,16 @@
         <v>178</v>
       </c>
       <c r="D3" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="E3" t="s">
+        <v>555</v>
+      </c>
+      <c r="F3" t="s">
         <v>561</v>
       </c>
-      <c r="E3" t="s">
-        <v>556</v>
-      </c>
-      <c r="F3" t="s">
-        <v>562</v>
-      </c>
       <c r="G3" s="24" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H3" s="24" t="s">
         <v>153</v>
@@ -29782,7 +29778,7 @@
         <v>20</v>
       </c>
       <c r="J3" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K3" s="24" t="s">
         <v>157</v>
@@ -29791,7 +29787,7 @@
         <v>140</v>
       </c>
       <c r="M3" s="27" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -29805,13 +29801,13 @@
         <v>179</v>
       </c>
       <c r="D4" s="25" t="s">
+        <v>563</v>
+      </c>
+      <c r="E4" t="s">
+        <v>555</v>
+      </c>
+      <c r="F4" t="s">
         <v>564</v>
-      </c>
-      <c r="E4" t="s">
-        <v>556</v>
-      </c>
-      <c r="F4" t="s">
-        <v>565</v>
       </c>
       <c r="G4" s="25" t="s">
         <v>18</v>
@@ -29823,7 +29819,7 @@
         <v>20</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K4" s="24" t="s">
         <v>157</v>
@@ -29832,7 +29828,7 @@
         <v>140</v>
       </c>
       <c r="M4" s="27" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -29846,13 +29842,13 @@
         <v>180</v>
       </c>
       <c r="D5" s="26" t="s">
+        <v>566</v>
+      </c>
+      <c r="E5" t="s">
+        <v>555</v>
+      </c>
+      <c r="F5" t="s">
         <v>567</v>
-      </c>
-      <c r="E5" t="s">
-        <v>556</v>
-      </c>
-      <c r="F5" t="s">
-        <v>568</v>
       </c>
       <c r="G5" s="24" t="s">
         <v>30</v>
@@ -29864,7 +29860,7 @@
         <v>138</v>
       </c>
       <c r="J5" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K5" s="24" t="s">
         <v>157</v>
@@ -29873,7 +29869,7 @@
         <v>140</v>
       </c>
       <c r="M5" s="27" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -29887,13 +29883,13 @@
         <v>181</v>
       </c>
       <c r="D6" s="26" t="s">
+        <v>569</v>
+      </c>
+      <c r="E6" t="s">
+        <v>555</v>
+      </c>
+      <c r="F6" t="s">
         <v>570</v>
-      </c>
-      <c r="E6" t="s">
-        <v>556</v>
-      </c>
-      <c r="F6" t="s">
-        <v>571</v>
       </c>
       <c r="G6" s="24" t="s">
         <v>30</v>
@@ -29905,7 +29901,7 @@
         <v>138</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K6" s="24" t="s">
         <v>157</v>
@@ -29914,7 +29910,7 @@
         <v>140</v>
       </c>
       <c r="M6" s="27" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -29928,13 +29924,13 @@
         <v>182</v>
       </c>
       <c r="D7" s="26" t="s">
+        <v>572</v>
+      </c>
+      <c r="E7" t="s">
+        <v>555</v>
+      </c>
+      <c r="F7" t="s">
         <v>573</v>
-      </c>
-      <c r="E7" t="s">
-        <v>556</v>
-      </c>
-      <c r="F7" t="s">
-        <v>574</v>
       </c>
       <c r="G7" s="25" t="s">
         <v>30</v>
@@ -29946,7 +29942,7 @@
         <v>138</v>
       </c>
       <c r="J7" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K7" s="24" t="s">
         <v>157</v>
@@ -29955,7 +29951,7 @@
         <v>140</v>
       </c>
       <c r="M7" s="27" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -29969,13 +29965,13 @@
         <v>183</v>
       </c>
       <c r="D8" s="25" t="s">
+        <v>575</v>
+      </c>
+      <c r="E8" t="s">
+        <v>555</v>
+      </c>
+      <c r="F8" t="s">
         <v>576</v>
-      </c>
-      <c r="E8" t="s">
-        <v>556</v>
-      </c>
-      <c r="F8" t="s">
-        <v>577</v>
       </c>
       <c r="G8" s="25" t="s">
         <v>30</v>
@@ -29987,7 +29983,7 @@
         <v>138</v>
       </c>
       <c r="J8" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K8" s="24" t="s">
         <v>157</v>
@@ -29996,7 +29992,7 @@
         <v>140</v>
       </c>
       <c r="M8" s="27" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -30010,13 +30006,13 @@
         <v>184</v>
       </c>
       <c r="D9" s="25" t="s">
+        <v>578</v>
+      </c>
+      <c r="E9" t="s">
+        <v>555</v>
+      </c>
+      <c r="F9" t="s">
         <v>579</v>
-      </c>
-      <c r="E9" t="s">
-        <v>556</v>
-      </c>
-      <c r="F9" t="s">
-        <v>580</v>
       </c>
       <c r="G9" s="25" t="s">
         <v>30</v>
@@ -30028,7 +30024,7 @@
         <v>138</v>
       </c>
       <c r="J9" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K9" s="24" t="s">
         <v>157</v>
@@ -30037,7 +30033,7 @@
         <v>140</v>
       </c>
       <c r="M9" s="27" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
@@ -30051,13 +30047,13 @@
         <v>185</v>
       </c>
       <c r="D10" s="25" t="s">
+        <v>581</v>
+      </c>
+      <c r="E10" t="s">
+        <v>555</v>
+      </c>
+      <c r="F10" t="s">
         <v>582</v>
-      </c>
-      <c r="E10" t="s">
-        <v>556</v>
-      </c>
-      <c r="F10" t="s">
-        <v>583</v>
       </c>
       <c r="G10" s="25" t="s">
         <v>30</v>
@@ -30069,7 +30065,7 @@
         <v>138</v>
       </c>
       <c r="J10" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K10" s="24" t="s">
         <v>157</v>
@@ -30078,7 +30074,7 @@
         <v>140</v>
       </c>
       <c r="M10" s="27" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -30092,13 +30088,13 @@
         <v>186</v>
       </c>
       <c r="D11" s="25" t="s">
+        <v>584</v>
+      </c>
+      <c r="E11" t="s">
+        <v>555</v>
+      </c>
+      <c r="F11" t="s">
         <v>585</v>
-      </c>
-      <c r="E11" t="s">
-        <v>556</v>
-      </c>
-      <c r="F11" t="s">
-        <v>586</v>
       </c>
       <c r="G11" s="25" t="s">
         <v>30</v>
@@ -30110,7 +30106,7 @@
         <v>138</v>
       </c>
       <c r="J11" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K11" s="24" t="s">
         <v>157</v>
@@ -30119,7 +30115,7 @@
         <v>140</v>
       </c>
       <c r="M11" s="27" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -30133,13 +30129,13 @@
         <v>187</v>
       </c>
       <c r="D12" s="25" t="s">
+        <v>587</v>
+      </c>
+      <c r="E12" t="s">
+        <v>555</v>
+      </c>
+      <c r="F12" t="s">
         <v>588</v>
-      </c>
-      <c r="E12" t="s">
-        <v>556</v>
-      </c>
-      <c r="F12" t="s">
-        <v>589</v>
       </c>
       <c r="G12" s="25" t="s">
         <v>30</v>
@@ -30151,7 +30147,7 @@
         <v>138</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K12" s="24" t="s">
         <v>157</v>
@@ -30160,7 +30156,7 @@
         <v>140</v>
       </c>
       <c r="M12" s="27" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -30174,13 +30170,13 @@
         <v>188</v>
       </c>
       <c r="D13" s="25" t="s">
+        <v>590</v>
+      </c>
+      <c r="E13" t="s">
+        <v>555</v>
+      </c>
+      <c r="F13" t="s">
         <v>591</v>
-      </c>
-      <c r="E13" t="s">
-        <v>556</v>
-      </c>
-      <c r="F13" t="s">
-        <v>592</v>
       </c>
       <c r="G13" s="25" t="s">
         <v>30</v>
@@ -30192,7 +30188,7 @@
         <v>138</v>
       </c>
       <c r="J13" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K13" s="24" t="s">
         <v>157</v>
@@ -30201,7 +30197,7 @@
         <v>140</v>
       </c>
       <c r="M13" s="27" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -30215,25 +30211,25 @@
         <v>189</v>
       </c>
       <c r="D14" s="25" t="s">
+        <v>593</v>
+      </c>
+      <c r="E14" t="s">
+        <v>555</v>
+      </c>
+      <c r="F14" t="s">
         <v>594</v>
       </c>
-      <c r="E14" t="s">
-        <v>556</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="G14" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="24" t="s">
         <v>595</v>
-      </c>
-      <c r="G14" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>596</v>
       </c>
       <c r="I14" s="24" t="s">
         <v>138</v>
       </c>
       <c r="J14" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K14" s="24" t="s">
         <v>157</v>
@@ -30242,7 +30238,7 @@
         <v>140</v>
       </c>
       <c r="M14" s="27" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -30256,13 +30252,13 @@
         <v>190</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E15" s="24" t="s">
+        <v>597</v>
+      </c>
+      <c r="F15" t="s">
         <v>598</v>
-      </c>
-      <c r="F15" t="s">
-        <v>599</v>
       </c>
       <c r="G15" s="24" t="s">
         <v>18</v>
@@ -30274,7 +30270,7 @@
         <v>20</v>
       </c>
       <c r="J15" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K15" s="24" t="s">
         <v>157</v>
@@ -30283,7 +30279,7 @@
         <v>140</v>
       </c>
       <c r="M15" s="27" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
@@ -30297,13 +30293,13 @@
         <v>191</v>
       </c>
       <c r="D16" s="26" t="s">
+        <v>599</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>597</v>
+      </c>
+      <c r="F16" t="s">
         <v>600</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>598</v>
-      </c>
-      <c r="F16" t="s">
-        <v>601</v>
       </c>
       <c r="G16" s="24" t="s">
         <v>30</v>
@@ -30315,7 +30311,7 @@
         <v>138</v>
       </c>
       <c r="J16" s="24" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K16" s="24" t="s">
         <v>157</v>
@@ -30324,7 +30320,7 @@
         <v>140</v>
       </c>
       <c r="M16" s="27" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
@@ -30338,13 +30334,13 @@
         <v>192</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F17" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G17" s="24" t="s">
         <v>30</v>
@@ -30356,7 +30352,7 @@
         <v>138</v>
       </c>
       <c r="J17" s="24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K17" s="24" t="s">
         <v>157</v>
@@ -30365,7 +30361,7 @@
         <v>140</v>
       </c>
       <c r="M17" s="27" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
@@ -30379,13 +30375,13 @@
         <v>193</v>
       </c>
       <c r="D18" s="24" t="s">
+        <v>604</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>597</v>
+      </c>
+      <c r="F18" t="s">
         <v>605</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>598</v>
-      </c>
-      <c r="F18" t="s">
-        <v>606</v>
       </c>
       <c r="G18" s="24" t="s">
         <v>30</v>
@@ -30397,7 +30393,7 @@
         <v>138</v>
       </c>
       <c r="J18" s="24" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K18" s="24" t="s">
         <v>157</v>
@@ -30406,7 +30402,7 @@
         <v>140</v>
       </c>
       <c r="M18" s="27" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
@@ -30420,13 +30416,13 @@
         <v>194</v>
       </c>
       <c r="D19" s="24" t="s">
+        <v>607</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>597</v>
+      </c>
+      <c r="F19" t="s">
         <v>608</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>598</v>
-      </c>
-      <c r="F19" t="s">
-        <v>609</v>
       </c>
       <c r="G19" s="24" t="s">
         <v>30</v>
@@ -30438,7 +30434,7 @@
         <v>138</v>
       </c>
       <c r="J19" s="24" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K19" s="24" t="s">
         <v>157</v>
@@ -30447,7 +30443,7 @@
         <v>140</v>
       </c>
       <c r="M19" s="27" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
@@ -30461,25 +30457,25 @@
         <v>195</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F20" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G20" s="24" t="s">
         <v>30</v>
       </c>
       <c r="H20" s="24" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I20" s="24" t="s">
         <v>138</v>
       </c>
       <c r="J20" s="24" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K20" s="24" t="s">
         <v>157</v>
@@ -30488,7 +30484,7 @@
         <v>140</v>
       </c>
       <c r="M20" s="27" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
   </sheetData>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/Round 2 Pods for Testing/Fast Track Pods/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="473" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39F6345D-2B03-42F2-B361-04542480C060}"/>
+  <xr:revisionPtr revIDLastSave="524" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF0A7575-0103-4AD1-8408-9E30C6623EFC}"/>
   <bookViews>
-    <workbookView xWindow="-180" yWindow="760" windowWidth="19380" windowHeight="10570" firstSheet="12" activeTab="13" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView xWindow="-28215" yWindow="420" windowWidth="27150" windowHeight="14985" firstSheet="10" activeTab="14" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7098" uniqueCount="1020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7129" uniqueCount="1020">
   <si>
     <t>schema</t>
   </si>
@@ -2968,12 +2968,6 @@
     <t>verification_quantity_uom</t>
   </si>
   <si>
-    <t>verification_body_name</t>
-  </si>
-  <si>
-    <t>verification_body_id</t>
-  </si>
-  <si>
     <t>verification_applied_standard</t>
   </si>
   <si>
@@ -3040,12 +3034,6 @@
     <t>The Unit of Measure for the verified quantity (e.g., tCO2e, m3_biogas).</t>
   </si>
   <si>
-    <t>The official name of the third-party auditing entity/VVB.</t>
-  </si>
-  <si>
-    <t>The decentralized identifier (DID) or registry ID of the verification body.</t>
-  </si>
-  <si>
     <t>The overarching registry framework (e.g., Verra_VCS_v4.5, Gold_Standard).</t>
   </si>
   <si>
@@ -3085,18 +3073,6 @@
     <t>verification</t>
   </si>
   <si>
-    <t>verification.identification[].verification_id</t>
-  </si>
-  <si>
-    <t>verification.identification[].verification_claim_type</t>
-  </si>
-  <si>
-    <t>verification.identification[].verification_project_id</t>
-  </si>
-  <si>
-    <t>verification.identification[].verification_description</t>
-  </si>
-  <si>
     <t>verification.reporting[].verification_reporting_period_start</t>
   </si>
   <si>
@@ -3112,12 +3088,6 @@
     <t>verification.quantity[].verification_quantity_uom</t>
   </si>
   <si>
-    <t>verification.body[].verification_body_name</t>
-  </si>
-  <si>
-    <t>verification.body[].verification_body_id</t>
-  </si>
-  <si>
     <t>verification.standard[].verification_applied_standard</t>
   </si>
   <si>
@@ -3136,25 +3106,55 @@
     <t>verification.verification_digital_signature_payload</t>
   </si>
   <si>
-    <t>verification.leakage[].verification_leakage_risk_mitigation</t>
-  </si>
-  <si>
-    <t>verification.leakage[].verification_leakage_risk_mitigation_strategy</t>
-  </si>
-  <si>
-    <t>verification.leakage[].verification_leakage_deduction_quantity</t>
-  </si>
-  <si>
-    <t>verification.verification_uncertainty_deduction_margin</t>
-  </si>
-  <si>
-    <t>verification.verification_buffer_pool_deduction_quantity</t>
-  </si>
-  <si>
-    <t>verification.verification_audit_checkpoint_status</t>
-  </si>
-  <si>
     <t>validation.validation_event[].validation_id</t>
+  </si>
+  <si>
+    <t>verification.verification_id</t>
+  </si>
+  <si>
+    <t>verification.verification_project_id</t>
+  </si>
+  <si>
+    <t>verification.details[].verification_claim_type</t>
+  </si>
+  <si>
+    <t>verification.details[].verification_description</t>
+  </si>
+  <si>
+    <t>verification_vvb_id</t>
+  </si>
+  <si>
+    <t>verification.verification_vvb_id</t>
+  </si>
+  <si>
+    <t>A globally unique identifier for a validation or verification body (vvb).</t>
+  </si>
+  <si>
+    <t>verification.status[].verification_audit_checkpoint_status</t>
+  </si>
+  <si>
+    <t>verification_audit_checkpoint_status_reason</t>
+  </si>
+  <si>
+    <t>verification.status[].verification_audit_checkpoint_status_reason</t>
+  </si>
+  <si>
+    <t>verification.status[].is_current</t>
+  </si>
+  <si>
+    <t>verification.deductions[].verification_leakage_risk_mitigation</t>
+  </si>
+  <si>
+    <t>verification.deductions[].verification_leakage_risk_mitigation_strategy</t>
+  </si>
+  <si>
+    <t>verification.deductions[].verification_leakage_deduction_quantity</t>
+  </si>
+  <si>
+    <t>verification.deductions[].verification_uncertainty_deduction_margin</t>
+  </si>
+  <si>
+    <t>verification.deductions[].verification_buffer_pool_deduction_quantity</t>
   </si>
 </sst>
 </file>
@@ -18490,7 +18490,7 @@
         <v>266</v>
       </c>
       <c r="F18" t="s">
-        <v>1019</v>
+        <v>1003</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>18</v>
@@ -19240,7 +19240,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7A22D2F-6AFE-4D3D-A8D1-BBD797E61616}">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="37.90625" customWidth="1"/>
@@ -19297,6 +19297,9 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
       <c r="C2">
         <v>307</v>
       </c>
@@ -19304,10 +19307,10 @@
         <v>948</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="F2" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
       <c r="G2" s="36" t="s">
         <v>18</v>
@@ -19319,579 +19322,680 @@
         <v>20</v>
       </c>
       <c r="M2" s="34" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
       <c r="C3">
         <v>308</v>
       </c>
-      <c r="D3" s="35" t="s">
-        <v>949</v>
-      </c>
-      <c r="E3" s="38" t="s">
-        <v>995</v>
+      <c r="D3" s="34" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>991</v>
       </c>
       <c r="F3" t="s">
-        <v>997</v>
-      </c>
-      <c r="G3" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="I3" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" s="35" t="s">
-        <v>973</v>
+        <v>1009</v>
+      </c>
+      <c r="G3" s="36" t="s">
+        <v>192</v>
+      </c>
+      <c r="H3" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I3" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M3" s="34" t="s">
+        <v>1010</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
       <c r="C4">
         <v>309</v>
       </c>
-      <c r="D4" s="34" t="s">
-        <v>950</v>
-      </c>
-      <c r="E4" s="36" t="s">
-        <v>995</v>
+      <c r="D4" s="35" t="s">
+        <v>949</v>
+      </c>
+      <c r="E4" s="38" t="s">
+        <v>991</v>
       </c>
       <c r="F4" t="s">
-        <v>998</v>
-      </c>
-      <c r="G4" s="36" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G4" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="I4" s="36" t="s">
+      <c r="H4" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="I4" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="M4" s="34" t="s">
-        <v>974</v>
+      <c r="M4" s="35" t="s">
+        <v>971</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
       <c r="C5">
         <v>310</v>
       </c>
-      <c r="D5" s="35" t="s">
-        <v>951</v>
-      </c>
-      <c r="E5" s="38" t="s">
-        <v>995</v>
+      <c r="D5" s="34" t="s">
+        <v>950</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>991</v>
       </c>
       <c r="F5" t="s">
-        <v>999</v>
-      </c>
-      <c r="G5" s="38" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G5" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="39" t="s">
+      <c r="H5" s="37" t="s">
         <v>215</v>
       </c>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="M5" s="35" t="s">
-        <v>975</v>
+      <c r="M5" s="34" t="s">
+        <v>972</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
       <c r="C6">
         <v>311</v>
       </c>
-      <c r="D6" s="34" t="s">
-        <v>952</v>
-      </c>
-      <c r="E6" s="36" t="s">
-        <v>995</v>
+      <c r="D6" s="35" t="s">
+        <v>951</v>
+      </c>
+      <c r="E6" s="38" t="s">
+        <v>991</v>
       </c>
       <c r="F6" t="s">
-        <v>1000</v>
-      </c>
-      <c r="G6" s="36" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G6" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="37" t="s">
-        <v>219</v>
-      </c>
-      <c r="I6" s="36" t="s">
+      <c r="H6" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I6" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="M6" s="34" t="s">
-        <v>976</v>
+      <c r="M6" s="35" t="s">
+        <v>973</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
       <c r="C7">
         <v>312</v>
       </c>
-      <c r="D7" s="35" t="s">
-        <v>953</v>
-      </c>
-      <c r="E7" s="38" t="s">
-        <v>995</v>
+      <c r="D7" s="34" t="s">
+        <v>952</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>991</v>
       </c>
       <c r="F7" t="s">
-        <v>1001</v>
-      </c>
-      <c r="G7" s="38" t="s">
+        <v>992</v>
+      </c>
+      <c r="G7" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="39" t="s">
+      <c r="H7" s="37" t="s">
         <v>219</v>
       </c>
-      <c r="I7" s="38" t="s">
+      <c r="I7" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="M7" s="35" t="s">
-        <v>977</v>
+      <c r="M7" s="34" t="s">
+        <v>974</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
       <c r="C8">
         <v>313</v>
       </c>
-      <c r="D8" s="34" t="s">
-        <v>954</v>
-      </c>
-      <c r="E8" s="36" t="s">
-        <v>995</v>
+      <c r="D8" s="35" t="s">
+        <v>953</v>
+      </c>
+      <c r="E8" s="38" t="s">
+        <v>991</v>
       </c>
       <c r="F8" t="s">
-        <v>1002</v>
-      </c>
-      <c r="G8" s="36" t="s">
+        <v>993</v>
+      </c>
+      <c r="G8" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="37" t="s">
+      <c r="H8" s="39" t="s">
         <v>219</v>
       </c>
-      <c r="I8" s="36" t="s">
+      <c r="I8" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="M8" s="34" t="s">
-        <v>978</v>
+      <c r="M8" s="35" t="s">
+        <v>975</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
       <c r="C9">
         <v>314</v>
       </c>
-      <c r="D9" s="35" t="s">
-        <v>955</v>
-      </c>
-      <c r="E9" s="38" t="s">
-        <v>995</v>
+      <c r="D9" s="34" t="s">
+        <v>954</v>
+      </c>
+      <c r="E9" s="36" t="s">
+        <v>991</v>
       </c>
       <c r="F9" t="s">
-        <v>1003</v>
-      </c>
-      <c r="G9" s="38" t="s">
+        <v>994</v>
+      </c>
+      <c r="G9" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="I9" s="38" t="s">
+      <c r="H9" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I9" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="M9" s="35" t="s">
-        <v>979</v>
+      <c r="M9" s="34" t="s">
+        <v>976</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
       <c r="C10">
         <v>315</v>
       </c>
-      <c r="D10" s="34" t="s">
-        <v>956</v>
-      </c>
-      <c r="E10" s="36" t="s">
+      <c r="D10" s="35" t="s">
+        <v>955</v>
+      </c>
+      <c r="E10" s="38" t="s">
+        <v>991</v>
+      </c>
+      <c r="F10" t="s">
         <v>995</v>
       </c>
-      <c r="F10" t="s">
-        <v>1004</v>
-      </c>
-      <c r="G10" s="36" t="s">
+      <c r="G10" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H10" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="I10" s="36" t="s">
+      <c r="H10" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="I10" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="M10" s="34" t="s">
-        <v>980</v>
+      <c r="M10" s="35" t="s">
+        <v>977</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
       <c r="C11">
         <v>316</v>
       </c>
-      <c r="D11" s="35" t="s">
-        <v>957</v>
-      </c>
-      <c r="E11" s="38" t="s">
-        <v>995</v>
+      <c r="D11" s="34" t="s">
+        <v>956</v>
+      </c>
+      <c r="E11" s="36" t="s">
+        <v>991</v>
       </c>
       <c r="F11" t="s">
-        <v>1005</v>
-      </c>
-      <c r="G11" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="G11" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="I11" s="38" t="s">
+      <c r="H11" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="I11" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="M11" s="35" t="s">
-        <v>981</v>
+      <c r="M11" s="34" t="s">
+        <v>978</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
       <c r="C12">
         <v>317</v>
       </c>
-      <c r="D12" s="34" t="s">
-        <v>958</v>
-      </c>
-      <c r="E12" s="36" t="s">
-        <v>995</v>
+      <c r="D12" s="35" t="s">
+        <v>957</v>
+      </c>
+      <c r="E12" s="38" t="s">
+        <v>991</v>
       </c>
       <c r="F12" t="s">
-        <v>1006</v>
-      </c>
-      <c r="G12" s="36" t="s">
+        <v>997</v>
+      </c>
+      <c r="G12" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="37" t="s">
+      <c r="H12" s="39" t="s">
         <v>215</v>
       </c>
-      <c r="I12" s="36" t="s">
+      <c r="I12" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="M12" s="34" t="s">
-        <v>982</v>
+      <c r="M12" s="35" t="s">
+        <v>979</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
       <c r="C13">
         <v>318</v>
       </c>
-      <c r="D13" s="35" t="s">
-        <v>959</v>
-      </c>
-      <c r="E13" s="38" t="s">
-        <v>995</v>
+      <c r="D13" s="34" t="s">
+        <v>958</v>
+      </c>
+      <c r="E13" s="36" t="s">
+        <v>991</v>
       </c>
       <c r="F13" t="s">
-        <v>1007</v>
-      </c>
-      <c r="G13" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="39" t="s">
+        <v>998</v>
+      </c>
+      <c r="G13" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="37" t="s">
         <v>215</v>
       </c>
-      <c r="I13" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M13" s="35" t="s">
-        <v>983</v>
+      <c r="I13" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M13" s="34" t="s">
+        <v>980</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
       <c r="C14">
         <v>319</v>
       </c>
-      <c r="D14" s="34" t="s">
-        <v>960</v>
-      </c>
-      <c r="E14" s="36" t="s">
-        <v>995</v>
+      <c r="D14" s="35" t="s">
+        <v>288</v>
+      </c>
+      <c r="E14" s="38" t="s">
+        <v>991</v>
       </c>
       <c r="F14" t="s">
-        <v>1008</v>
-      </c>
-      <c r="G14" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="I14" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="M14" s="34" t="s">
-        <v>984</v>
+        <v>999</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>564</v>
+      </c>
+      <c r="H14" s="39" t="s">
+        <v>968</v>
+      </c>
+      <c r="I14" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M14" s="35" t="s">
+        <v>981</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
       <c r="C15">
         <v>320</v>
       </c>
-      <c r="D15" s="35" t="s">
-        <v>288</v>
-      </c>
-      <c r="E15" s="38" t="s">
-        <v>995</v>
+      <c r="D15" s="34" t="s">
+        <v>959</v>
+      </c>
+      <c r="E15" s="36" t="s">
+        <v>991</v>
       </c>
       <c r="F15" t="s">
-        <v>1009</v>
-      </c>
-      <c r="G15" s="38" t="s">
-        <v>564</v>
-      </c>
-      <c r="H15" s="39" t="s">
-        <v>970</v>
-      </c>
-      <c r="I15" s="38" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G15" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I15" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="M15" s="35" t="s">
-        <v>985</v>
+      <c r="M15" s="34" t="s">
+        <v>982</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
       <c r="C16">
         <v>321</v>
       </c>
-      <c r="D16" s="34" t="s">
-        <v>961</v>
-      </c>
-      <c r="E16" s="36" t="s">
-        <v>995</v>
+      <c r="D16" s="35" t="s">
+        <v>960</v>
+      </c>
+      <c r="E16" s="38" t="s">
+        <v>991</v>
       </c>
       <c r="F16" t="s">
-        <v>1010</v>
-      </c>
-      <c r="G16" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="H16" s="37" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="39" t="s">
         <v>215</v>
       </c>
-      <c r="I16" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="M16" s="34" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="I16" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="M16" s="35" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
       <c r="C17">
         <v>322</v>
       </c>
-      <c r="D17" s="35" t="s">
-        <v>962</v>
-      </c>
-      <c r="E17" s="38" t="s">
-        <v>995</v>
+      <c r="D17" s="34" t="s">
+        <v>961</v>
+      </c>
+      <c r="E17" s="36" t="s">
+        <v>991</v>
       </c>
       <c r="F17" t="s">
-        <v>1011</v>
+        <v>1002</v>
       </c>
       <c r="G17" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H17" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="I17" s="38" t="s">
+      <c r="H17" s="37" t="s">
+        <v>969</v>
+      </c>
+      <c r="I17" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="M17" s="35" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="M17" s="34" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
       <c r="C18">
         <v>323</v>
       </c>
-      <c r="D18" s="34" t="s">
-        <v>963</v>
-      </c>
-      <c r="E18" s="36" t="s">
-        <v>995</v>
+      <c r="D18" s="35" t="s">
+        <v>962</v>
+      </c>
+      <c r="E18" s="38" t="s">
+        <v>991</v>
       </c>
       <c r="F18" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="G18" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H18" s="37" t="s">
-        <v>971</v>
-      </c>
-      <c r="I18" s="36" t="s">
+      <c r="H18" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="I18" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="M18" s="34" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="M18" s="35" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
       <c r="C19">
         <v>324</v>
       </c>
-      <c r="D19" s="35" t="s">
-        <v>964</v>
-      </c>
-      <c r="E19" s="38" t="s">
-        <v>995</v>
+      <c r="D19" s="34" t="s">
+        <v>963</v>
+      </c>
+      <c r="E19" s="36" t="s">
+        <v>991</v>
       </c>
       <c r="F19" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="G19" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H19" s="39" t="s">
-        <v>150</v>
-      </c>
-      <c r="I19" s="38" t="s">
+      <c r="H19" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I19" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="M19" s="35" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="M19" s="34" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
       <c r="C20">
         <v>325</v>
       </c>
-      <c r="D20" s="34" t="s">
-        <v>965</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>995</v>
+      <c r="D20" s="35" t="s">
+        <v>964</v>
+      </c>
+      <c r="E20" s="38" t="s">
+        <v>991</v>
       </c>
       <c r="F20" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="G20" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H20" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="I20" s="36" t="s">
+      <c r="H20" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="I20" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="M20" s="34" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="M20" s="35" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
       <c r="C21">
         <v>326</v>
       </c>
-      <c r="D21" s="35" t="s">
-        <v>966</v>
-      </c>
-      <c r="E21" s="38" t="s">
-        <v>995</v>
+      <c r="D21" s="34" t="s">
+        <v>965</v>
+      </c>
+      <c r="E21" s="36" t="s">
+        <v>991</v>
       </c>
       <c r="F21" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="G21" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="39" t="s">
+      <c r="H21" s="37" t="s">
         <v>316</v>
       </c>
-      <c r="I21" s="38" t="s">
+      <c r="I21" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="M21" s="35" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="M21" s="34" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
       <c r="C22">
         <v>327</v>
       </c>
-      <c r="D22" s="34" t="s">
-        <v>967</v>
-      </c>
-      <c r="E22" s="36" t="s">
-        <v>995</v>
+      <c r="D22" s="35" t="s">
+        <v>966</v>
+      </c>
+      <c r="E22" s="38" t="s">
+        <v>991</v>
       </c>
       <c r="F22" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="G22" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H22" s="37" t="s">
+      <c r="H22" s="39" t="s">
         <v>316</v>
       </c>
-      <c r="I22" s="36" t="s">
+      <c r="I22" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="M22" s="34" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="M22" s="35" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
       <c r="C23">
         <v>328</v>
       </c>
-      <c r="D23" s="35" t="s">
-        <v>968</v>
-      </c>
-      <c r="E23" s="38" t="s">
-        <v>995</v>
+      <c r="D23" s="34" t="s">
+        <v>967</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>991</v>
       </c>
       <c r="F23" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="G23" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H23" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="I23" s="38" t="s">
+      <c r="H23" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="I23" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="M23" s="35" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="M23" s="34" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
       <c r="C24">
         <v>329</v>
       </c>
       <c r="D24" s="34" t="s">
-        <v>969</v>
+        <v>1012</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="F24" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G24" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H24" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="I24" s="36" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="I24" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="M24" s="34" t="s">
-        <v>994</v>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="30" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25">
+        <v>330</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>991</v>
+      </c>
+      <c r="F25" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G25" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6" t="s">
+        <v>527</v>
       </c>
     </row>
   </sheetData>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/Round 2 Pods for Testing/Fast Track Pods/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="524" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF0A7575-0103-4AD1-8408-9E30C6623EFC}"/>
+  <xr:revisionPtr revIDLastSave="527" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A8E844A-1D58-4DFC-9D20-5AF2A91A062C}"/>
   <bookViews>
-    <workbookView xWindow="-28215" yWindow="420" windowWidth="27150" windowHeight="14985" firstSheet="10" activeTab="14" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView xWindow="-27315" yWindow="525" windowWidth="26085" windowHeight="12255" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7129" uniqueCount="1020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7825" uniqueCount="1020">
   <si>
     <t>schema</t>
   </si>
@@ -3784,7 +3784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{752D3095-90A4-45FF-BD20-0492A3C6EFAC}">
-  <dimension ref="A1:M261"/>
+  <dimension ref="A1:M331"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="21.1796875" bestFit="1" customWidth="1"/>
@@ -14498,6 +14498,2450 @@
       </c>
       <c r="M261" s="6" t="s">
         <v>803</v>
+      </c>
+    </row>
+    <row r="262" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A262" t="s">
+        <v>13</v>
+      </c>
+      <c r="B262" t="s">
+        <v>275</v>
+      </c>
+      <c r="C262">
+        <v>261</v>
+      </c>
+      <c r="D262" s="25" t="s">
+        <v>828</v>
+      </c>
+      <c r="E262" t="s">
+        <v>116</v>
+      </c>
+      <c r="F262" t="s">
+        <v>841</v>
+      </c>
+      <c r="G262" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H262" s="25" t="s">
+        <v>392</v>
+      </c>
+      <c r="I262" t="s">
+        <v>226</v>
+      </c>
+      <c r="J262" t="s">
+        <v>116</v>
+      </c>
+      <c r="L262" t="s">
+        <v>146</v>
+      </c>
+      <c r="M262" s="18" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="263" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A263" t="s">
+        <v>13</v>
+      </c>
+      <c r="B263" t="s">
+        <v>275</v>
+      </c>
+      <c r="C263">
+        <v>262</v>
+      </c>
+      <c r="D263" s="25" t="s">
+        <v>829</v>
+      </c>
+      <c r="E263" t="s">
+        <v>116</v>
+      </c>
+      <c r="F263" t="s">
+        <v>842</v>
+      </c>
+      <c r="G263" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H263" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="I263" t="s">
+        <v>226</v>
+      </c>
+      <c r="J263" t="s">
+        <v>116</v>
+      </c>
+      <c r="L263" t="s">
+        <v>146</v>
+      </c>
+      <c r="M263" s="18" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="264" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A264" t="s">
+        <v>13</v>
+      </c>
+      <c r="B264" t="s">
+        <v>275</v>
+      </c>
+      <c r="C264">
+        <v>263</v>
+      </c>
+      <c r="D264" s="25" t="s">
+        <v>830</v>
+      </c>
+      <c r="E264" t="s">
+        <v>116</v>
+      </c>
+      <c r="F264" t="s">
+        <v>843</v>
+      </c>
+      <c r="G264" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H264" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="I264" t="s">
+        <v>226</v>
+      </c>
+      <c r="J264" t="s">
+        <v>116</v>
+      </c>
+      <c r="L264" t="s">
+        <v>146</v>
+      </c>
+      <c r="M264" s="18" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="265" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A265" t="s">
+        <v>13</v>
+      </c>
+      <c r="B265" t="s">
+        <v>275</v>
+      </c>
+      <c r="C265">
+        <v>264</v>
+      </c>
+      <c r="D265" s="25" t="s">
+        <v>831</v>
+      </c>
+      <c r="E265" t="s">
+        <v>116</v>
+      </c>
+      <c r="F265" t="s">
+        <v>844</v>
+      </c>
+      <c r="G265" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H265" s="25" t="s">
+        <v>392</v>
+      </c>
+      <c r="I265" t="s">
+        <v>226</v>
+      </c>
+      <c r="J265" t="s">
+        <v>116</v>
+      </c>
+      <c r="L265" t="s">
+        <v>146</v>
+      </c>
+      <c r="M265" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="266" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A266" t="s">
+        <v>13</v>
+      </c>
+      <c r="B266" t="s">
+        <v>275</v>
+      </c>
+      <c r="C266">
+        <v>265</v>
+      </c>
+      <c r="D266" s="25" t="s">
+        <v>832</v>
+      </c>
+      <c r="E266" t="s">
+        <v>116</v>
+      </c>
+      <c r="F266" t="s">
+        <v>845</v>
+      </c>
+      <c r="G266" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H266" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="I266" t="s">
+        <v>226</v>
+      </c>
+      <c r="J266" t="s">
+        <v>116</v>
+      </c>
+      <c r="L266" t="s">
+        <v>146</v>
+      </c>
+      <c r="M266" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="267" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A267" t="s">
+        <v>13</v>
+      </c>
+      <c r="B267" t="s">
+        <v>275</v>
+      </c>
+      <c r="C267">
+        <v>266</v>
+      </c>
+      <c r="D267" s="25" t="s">
+        <v>833</v>
+      </c>
+      <c r="E267" t="s">
+        <v>116</v>
+      </c>
+      <c r="F267" t="s">
+        <v>846</v>
+      </c>
+      <c r="G267" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H267" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="I267" t="s">
+        <v>226</v>
+      </c>
+      <c r="J267" t="s">
+        <v>116</v>
+      </c>
+      <c r="L267" t="s">
+        <v>146</v>
+      </c>
+      <c r="M267" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="268" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A268" t="s">
+        <v>13</v>
+      </c>
+      <c r="B268" t="s">
+        <v>275</v>
+      </c>
+      <c r="C268">
+        <v>267</v>
+      </c>
+      <c r="D268" s="25" t="s">
+        <v>834</v>
+      </c>
+      <c r="E268" t="s">
+        <v>116</v>
+      </c>
+      <c r="F268" t="s">
+        <v>847</v>
+      </c>
+      <c r="G268" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H268" s="25" t="s">
+        <v>392</v>
+      </c>
+      <c r="I268" t="s">
+        <v>226</v>
+      </c>
+      <c r="J268" t="s">
+        <v>823</v>
+      </c>
+      <c r="L268" t="s">
+        <v>146</v>
+      </c>
+      <c r="M268" s="18" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="269" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A269" t="s">
+        <v>13</v>
+      </c>
+      <c r="B269" t="s">
+        <v>275</v>
+      </c>
+      <c r="C269">
+        <v>268</v>
+      </c>
+      <c r="D269" s="25" t="s">
+        <v>835</v>
+      </c>
+      <c r="E269" t="s">
+        <v>116</v>
+      </c>
+      <c r="F269" t="s">
+        <v>848</v>
+      </c>
+      <c r="G269" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H269" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="I269" t="s">
+        <v>226</v>
+      </c>
+      <c r="J269" t="s">
+        <v>823</v>
+      </c>
+      <c r="L269" t="s">
+        <v>146</v>
+      </c>
+      <c r="M269" s="18" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="270" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A270" t="s">
+        <v>13</v>
+      </c>
+      <c r="B270" t="s">
+        <v>275</v>
+      </c>
+      <c r="C270">
+        <v>269</v>
+      </c>
+      <c r="D270" s="25" t="s">
+        <v>836</v>
+      </c>
+      <c r="E270" t="s">
+        <v>116</v>
+      </c>
+      <c r="F270" t="s">
+        <v>839</v>
+      </c>
+      <c r="G270" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H270" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="I270" t="s">
+        <v>226</v>
+      </c>
+      <c r="L270" t="s">
+        <v>146</v>
+      </c>
+      <c r="M270" s="18" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="271" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A271" t="s">
+        <v>13</v>
+      </c>
+      <c r="B271" t="s">
+        <v>275</v>
+      </c>
+      <c r="C271">
+        <v>270</v>
+      </c>
+      <c r="D271" s="25" t="s">
+        <v>837</v>
+      </c>
+      <c r="E271" t="s">
+        <v>116</v>
+      </c>
+      <c r="F271" t="s">
+        <v>840</v>
+      </c>
+      <c r="G271" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="H271" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="I271" t="s">
+        <v>31</v>
+      </c>
+      <c r="L271" t="s">
+        <v>146</v>
+      </c>
+      <c r="M271" s="18" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="272" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A272" t="s">
+        <v>13</v>
+      </c>
+      <c r="B272" t="s">
+        <v>275</v>
+      </c>
+      <c r="C272">
+        <v>271</v>
+      </c>
+      <c r="D272" s="33" t="s">
+        <v>481</v>
+      </c>
+      <c r="E272" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F272" t="s">
+        <v>913</v>
+      </c>
+      <c r="G272" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H272" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="I272" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J272" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L272" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M272" s="6" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="273" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A273" t="s">
+        <v>13</v>
+      </c>
+      <c r="B273" t="s">
+        <v>275</v>
+      </c>
+      <c r="C273">
+        <v>272</v>
+      </c>
+      <c r="D273" s="33" t="s">
+        <v>483</v>
+      </c>
+      <c r="E273" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F273" t="s">
+        <v>916</v>
+      </c>
+      <c r="G273" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H273" s="33" t="s">
+        <v>392</v>
+      </c>
+      <c r="I273" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J273" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L273" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M273" s="6" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="274" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="A274" t="s">
+        <v>13</v>
+      </c>
+      <c r="B274" t="s">
+        <v>275</v>
+      </c>
+      <c r="C274">
+        <v>273</v>
+      </c>
+      <c r="D274" s="33" t="s">
+        <v>479</v>
+      </c>
+      <c r="E274" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F274" t="s">
+        <v>918</v>
+      </c>
+      <c r="G274" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H274" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="I274" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J274" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L274" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M274" s="6" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="275" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
+        <v>13</v>
+      </c>
+      <c r="B275" t="s">
+        <v>275</v>
+      </c>
+      <c r="C275">
+        <v>274</v>
+      </c>
+      <c r="D275" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="E275" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F275" t="s">
+        <v>914</v>
+      </c>
+      <c r="G275" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H275" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I275" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J275" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L275" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M275" s="6" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="276" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>13</v>
+      </c>
+      <c r="B276" t="s">
+        <v>275</v>
+      </c>
+      <c r="C276">
+        <v>275</v>
+      </c>
+      <c r="D276" s="6" t="s">
+        <v>850</v>
+      </c>
+      <c r="E276" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F276" t="s">
+        <v>917</v>
+      </c>
+      <c r="G276" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H276" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I276" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J276" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L276" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M276" s="6" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="277" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
+        <v>13</v>
+      </c>
+      <c r="B277" t="s">
+        <v>275</v>
+      </c>
+      <c r="C277">
+        <v>276</v>
+      </c>
+      <c r="D277" s="6" t="s">
+        <v>851</v>
+      </c>
+      <c r="E277" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F277" t="s">
+        <v>919</v>
+      </c>
+      <c r="G277" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H277" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I277" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J277" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L277" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M277" s="6" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="278" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
+        <v>13</v>
+      </c>
+      <c r="B278" t="s">
+        <v>275</v>
+      </c>
+      <c r="C278">
+        <v>277</v>
+      </c>
+      <c r="D278" s="6" t="s">
+        <v>852</v>
+      </c>
+      <c r="E278" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F278" t="s">
+        <v>920</v>
+      </c>
+      <c r="G278" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H278" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I278" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J278" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L278" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M278" s="6" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="279" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A279" t="s">
+        <v>13</v>
+      </c>
+      <c r="B279" t="s">
+        <v>275</v>
+      </c>
+      <c r="C279">
+        <v>278</v>
+      </c>
+      <c r="D279" s="6" t="s">
+        <v>853</v>
+      </c>
+      <c r="E279" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F279" t="s">
+        <v>921</v>
+      </c>
+      <c r="G279" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H279" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I279" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J279" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L279" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M279" s="6" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="280" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A280" t="s">
+        <v>13</v>
+      </c>
+      <c r="B280" t="s">
+        <v>275</v>
+      </c>
+      <c r="C280">
+        <v>279</v>
+      </c>
+      <c r="D280" s="6" t="s">
+        <v>854</v>
+      </c>
+      <c r="E280" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F280" t="s">
+        <v>922</v>
+      </c>
+      <c r="G280" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H280" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I280" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J280" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L280" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M280" s="6" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="281" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
+        <v>13</v>
+      </c>
+      <c r="B281" t="s">
+        <v>275</v>
+      </c>
+      <c r="C281">
+        <v>280</v>
+      </c>
+      <c r="D281" s="6" t="s">
+        <v>905</v>
+      </c>
+      <c r="E281" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F281" t="s">
+        <v>923</v>
+      </c>
+      <c r="G281" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H281" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I281" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J281" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L281" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M281" s="6" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="282" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>13</v>
+      </c>
+      <c r="B282" t="s">
+        <v>275</v>
+      </c>
+      <c r="C282">
+        <v>281</v>
+      </c>
+      <c r="D282" s="6" t="s">
+        <v>906</v>
+      </c>
+      <c r="E282" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F282" t="s">
+        <v>924</v>
+      </c>
+      <c r="G282" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H282" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I282" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J282" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L282" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M282" s="6" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="283" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>13</v>
+      </c>
+      <c r="B283" t="s">
+        <v>275</v>
+      </c>
+      <c r="C283">
+        <v>282</v>
+      </c>
+      <c r="D283" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="E283" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F283" t="s">
+        <v>925</v>
+      </c>
+      <c r="G283" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H283" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I283" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J283" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L283" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M283" s="6" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="284" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>13</v>
+      </c>
+      <c r="B284" t="s">
+        <v>275</v>
+      </c>
+      <c r="C284">
+        <v>283</v>
+      </c>
+      <c r="D284" s="6" t="s">
+        <v>908</v>
+      </c>
+      <c r="E284" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F284" t="s">
+        <v>926</v>
+      </c>
+      <c r="G284" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H284" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I284" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J284" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L284" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M284" s="6" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="285" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>13</v>
+      </c>
+      <c r="B285" t="s">
+        <v>275</v>
+      </c>
+      <c r="C285">
+        <v>284</v>
+      </c>
+      <c r="D285" s="6" t="s">
+        <v>909</v>
+      </c>
+      <c r="E285" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F285" t="s">
+        <v>927</v>
+      </c>
+      <c r="G285" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H285" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I285" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J285" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L285" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M285" s="6" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="286" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>13</v>
+      </c>
+      <c r="B286" t="s">
+        <v>275</v>
+      </c>
+      <c r="C286">
+        <v>285</v>
+      </c>
+      <c r="D286" s="6" t="s">
+        <v>910</v>
+      </c>
+      <c r="E286" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F286" t="s">
+        <v>928</v>
+      </c>
+      <c r="G286" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H286" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I286" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J286" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L286" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M286" s="6" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="287" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>13</v>
+      </c>
+      <c r="B287" t="s">
+        <v>275</v>
+      </c>
+      <c r="C287">
+        <v>286</v>
+      </c>
+      <c r="D287" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="E287" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F287" t="s">
+        <v>929</v>
+      </c>
+      <c r="G287" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H287" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I287" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J287" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L287" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M287" s="6" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="288" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>13</v>
+      </c>
+      <c r="B288" t="s">
+        <v>275</v>
+      </c>
+      <c r="C288">
+        <v>287</v>
+      </c>
+      <c r="D288" s="33" t="s">
+        <v>477</v>
+      </c>
+      <c r="E288" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F288" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G288" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H288" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="I288" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J288" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L288" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M288" s="6" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="289" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>13</v>
+      </c>
+      <c r="B289" t="s">
+        <v>275</v>
+      </c>
+      <c r="C289">
+        <v>288</v>
+      </c>
+      <c r="D289" s="30" t="s">
+        <v>511</v>
+      </c>
+      <c r="E289" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F289" t="s">
+        <v>930</v>
+      </c>
+      <c r="G289" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H289" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I289" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J289" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L289" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M289" s="6" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="290" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>13</v>
+      </c>
+      <c r="B290" t="s">
+        <v>275</v>
+      </c>
+      <c r="C290">
+        <v>289</v>
+      </c>
+      <c r="D290" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="E290" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="F290" t="s">
+        <v>941</v>
+      </c>
+      <c r="G290" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H290" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I290" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J290" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L290" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M290" s="6" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="291" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>13</v>
+      </c>
+      <c r="B291" t="s">
+        <v>275</v>
+      </c>
+      <c r="C291">
+        <v>290</v>
+      </c>
+      <c r="D291" s="17" t="s">
+        <v>856</v>
+      </c>
+      <c r="E291" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="F291" t="s">
+        <v>942</v>
+      </c>
+      <c r="G291" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H291" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I291" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J291" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L291" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M291" s="6" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="292" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>13</v>
+      </c>
+      <c r="B292" t="s">
+        <v>275</v>
+      </c>
+      <c r="C292">
+        <v>291</v>
+      </c>
+      <c r="D292" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="E292" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="F292" t="s">
+        <v>943</v>
+      </c>
+      <c r="G292" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H292" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I292" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J292" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L292" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M292" s="6" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="293" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
+        <v>13</v>
+      </c>
+      <c r="B293" t="s">
+        <v>275</v>
+      </c>
+      <c r="C293">
+        <v>292</v>
+      </c>
+      <c r="D293" s="17" t="s">
+        <v>857</v>
+      </c>
+      <c r="E293" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="F293" t="s">
+        <v>944</v>
+      </c>
+      <c r="G293" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H293" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I293" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J293" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L293" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M293" s="6" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="294" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A294" t="s">
+        <v>13</v>
+      </c>
+      <c r="B294" t="s">
+        <v>275</v>
+      </c>
+      <c r="C294">
+        <v>293</v>
+      </c>
+      <c r="D294" s="6" t="s">
+        <v>858</v>
+      </c>
+      <c r="E294" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="F294" t="s">
+        <v>945</v>
+      </c>
+      <c r="G294" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="H294" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I294" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J294" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L294" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M294" s="6" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="295" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A295" t="s">
+        <v>13</v>
+      </c>
+      <c r="B295" t="s">
+        <v>275</v>
+      </c>
+      <c r="C295">
+        <v>294</v>
+      </c>
+      <c r="D295" s="6" t="s">
+        <v>859</v>
+      </c>
+      <c r="E295" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="F295" t="s">
+        <v>946</v>
+      </c>
+      <c r="G295" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H295" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I295" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J295" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L295" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M295" s="6" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="296" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A296" t="s">
+        <v>13</v>
+      </c>
+      <c r="B296" t="s">
+        <v>275</v>
+      </c>
+      <c r="C296">
+        <v>295</v>
+      </c>
+      <c r="D296" s="6" t="s">
+        <v>860</v>
+      </c>
+      <c r="E296" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="F296" t="s">
+        <v>947</v>
+      </c>
+      <c r="G296" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H296" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I296" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J296" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L296" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M296" s="6" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="297" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A297" t="s">
+        <v>13</v>
+      </c>
+      <c r="B297" t="s">
+        <v>275</v>
+      </c>
+      <c r="C297">
+        <v>296</v>
+      </c>
+      <c r="D297" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="E297" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F297" t="s">
+        <v>931</v>
+      </c>
+      <c r="G297" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H297" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I297" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J297" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L297" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M297" s="6" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="298" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A298" t="s">
+        <v>13</v>
+      </c>
+      <c r="B298" t="s">
+        <v>275</v>
+      </c>
+      <c r="C298">
+        <v>297</v>
+      </c>
+      <c r="D298" s="6" t="s">
+        <v>861</v>
+      </c>
+      <c r="E298" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F298" t="s">
+        <v>932</v>
+      </c>
+      <c r="G298" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H298" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I298" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J298" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L298" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M298" s="6" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="299" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
+        <v>13</v>
+      </c>
+      <c r="B299" t="s">
+        <v>275</v>
+      </c>
+      <c r="C299">
+        <v>298</v>
+      </c>
+      <c r="D299" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="E299" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F299" t="s">
+        <v>933</v>
+      </c>
+      <c r="G299" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H299" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I299" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J299" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L299" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M299" s="6" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="300" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A300" t="s">
+        <v>13</v>
+      </c>
+      <c r="B300" t="s">
+        <v>275</v>
+      </c>
+      <c r="C300">
+        <v>299</v>
+      </c>
+      <c r="D300" s="6" t="s">
+        <v>863</v>
+      </c>
+      <c r="E300" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F300" t="s">
+        <v>934</v>
+      </c>
+      <c r="G300" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H300" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I300" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J300" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L300" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M300" s="6" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="301" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A301" t="s">
+        <v>13</v>
+      </c>
+      <c r="B301" t="s">
+        <v>275</v>
+      </c>
+      <c r="C301">
+        <v>300</v>
+      </c>
+      <c r="D301" s="17" t="s">
+        <v>864</v>
+      </c>
+      <c r="E301" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F301" t="s">
+        <v>935</v>
+      </c>
+      <c r="G301" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H301" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="I301" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J301" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L301" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M301" s="17" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="302" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A302" t="s">
+        <v>13</v>
+      </c>
+      <c r="B302" t="s">
+        <v>275</v>
+      </c>
+      <c r="C302">
+        <v>301</v>
+      </c>
+      <c r="D302" s="6" t="s">
+        <v>865</v>
+      </c>
+      <c r="E302" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F302" t="s">
+        <v>937</v>
+      </c>
+      <c r="G302" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H302" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="I302" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J302" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L302" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M302" s="6" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="303" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>13</v>
+      </c>
+      <c r="B303" t="s">
+        <v>275</v>
+      </c>
+      <c r="C303">
+        <v>302</v>
+      </c>
+      <c r="D303" s="6" t="s">
+        <v>866</v>
+      </c>
+      <c r="E303" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F303" t="s">
+        <v>938</v>
+      </c>
+      <c r="G303" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H303" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="I303" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J303" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L303" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M303" s="6" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="304" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>13</v>
+      </c>
+      <c r="B304" t="s">
+        <v>275</v>
+      </c>
+      <c r="C304">
+        <v>303</v>
+      </c>
+      <c r="D304" s="6" t="s">
+        <v>867</v>
+      </c>
+      <c r="E304" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F304" t="s">
+        <v>915</v>
+      </c>
+      <c r="G304" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H304" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="I304" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J304" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L304" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M304" s="6" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="305" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
+        <v>13</v>
+      </c>
+      <c r="B305" t="s">
+        <v>275</v>
+      </c>
+      <c r="C305">
+        <v>304</v>
+      </c>
+      <c r="D305" s="6" t="s">
+        <v>868</v>
+      </c>
+      <c r="E305" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F305" t="s">
+        <v>939</v>
+      </c>
+      <c r="G305" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="H305" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I305" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J305" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L305" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M305" s="6" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="306" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A306" t="s">
+        <v>13</v>
+      </c>
+      <c r="B306" t="s">
+        <v>275</v>
+      </c>
+      <c r="C306">
+        <v>305</v>
+      </c>
+      <c r="D306" s="6" t="s">
+        <v>869</v>
+      </c>
+      <c r="E306" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F306" t="s">
+        <v>936</v>
+      </c>
+      <c r="G306" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H306" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I306" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J306" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L306" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M306" s="6" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="307" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A307" t="s">
+        <v>13</v>
+      </c>
+      <c r="B307" t="s">
+        <v>275</v>
+      </c>
+      <c r="C307">
+        <v>306</v>
+      </c>
+      <c r="D307" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="E307" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F307" t="s">
+        <v>940</v>
+      </c>
+      <c r="G307" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H307" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I307" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J307" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L307" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M307" s="6" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="308" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A308" t="s">
+        <v>13</v>
+      </c>
+      <c r="C308">
+        <v>307</v>
+      </c>
+      <c r="D308" s="34" t="s">
+        <v>948</v>
+      </c>
+      <c r="E308" s="36" t="s">
+        <v>991</v>
+      </c>
+      <c r="F308" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G308" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H308" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I308" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M308" s="34" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="309" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>13</v>
+      </c>
+      <c r="C309">
+        <v>308</v>
+      </c>
+      <c r="D309" s="34" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E309" s="36" t="s">
+        <v>991</v>
+      </c>
+      <c r="F309" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G309" s="36" t="s">
+        <v>192</v>
+      </c>
+      <c r="H309" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I309" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M309" s="34" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="310" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>13</v>
+      </c>
+      <c r="C310">
+        <v>309</v>
+      </c>
+      <c r="D310" s="35" t="s">
+        <v>949</v>
+      </c>
+      <c r="E310" s="38" t="s">
+        <v>991</v>
+      </c>
+      <c r="F310" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G310" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H310" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="I310" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M310" s="35" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="311" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>13</v>
+      </c>
+      <c r="C311">
+        <v>310</v>
+      </c>
+      <c r="D311" s="34" t="s">
+        <v>950</v>
+      </c>
+      <c r="E311" s="36" t="s">
+        <v>991</v>
+      </c>
+      <c r="F311" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G311" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H311" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I311" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M311" s="34" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="312" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>13</v>
+      </c>
+      <c r="C312">
+        <v>311</v>
+      </c>
+      <c r="D312" s="35" t="s">
+        <v>951</v>
+      </c>
+      <c r="E312" s="38" t="s">
+        <v>991</v>
+      </c>
+      <c r="F312" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G312" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H312" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I312" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M312" s="35" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="313" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A313" t="s">
+        <v>13</v>
+      </c>
+      <c r="C313">
+        <v>312</v>
+      </c>
+      <c r="D313" s="34" t="s">
+        <v>952</v>
+      </c>
+      <c r="E313" s="36" t="s">
+        <v>991</v>
+      </c>
+      <c r="F313" t="s">
+        <v>992</v>
+      </c>
+      <c r="G313" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H313" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I313" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M313" s="34" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="314" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>13</v>
+      </c>
+      <c r="C314">
+        <v>313</v>
+      </c>
+      <c r="D314" s="35" t="s">
+        <v>953</v>
+      </c>
+      <c r="E314" s="38" t="s">
+        <v>991</v>
+      </c>
+      <c r="F314" t="s">
+        <v>993</v>
+      </c>
+      <c r="G314" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H314" s="39" t="s">
+        <v>219</v>
+      </c>
+      <c r="I314" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M314" s="35" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="315" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>13</v>
+      </c>
+      <c r="C315">
+        <v>314</v>
+      </c>
+      <c r="D315" s="34" t="s">
+        <v>954</v>
+      </c>
+      <c r="E315" s="36" t="s">
+        <v>991</v>
+      </c>
+      <c r="F315" t="s">
+        <v>994</v>
+      </c>
+      <c r="G315" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H315" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I315" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M315" s="34" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="316" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
+        <v>13</v>
+      </c>
+      <c r="C316">
+        <v>315</v>
+      </c>
+      <c r="D316" s="35" t="s">
+        <v>955</v>
+      </c>
+      <c r="E316" s="38" t="s">
+        <v>991</v>
+      </c>
+      <c r="F316" t="s">
+        <v>995</v>
+      </c>
+      <c r="G316" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H316" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="I316" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M316" s="35" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="317" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
+        <v>13</v>
+      </c>
+      <c r="C317">
+        <v>316</v>
+      </c>
+      <c r="D317" s="34" t="s">
+        <v>956</v>
+      </c>
+      <c r="E317" s="36" t="s">
+        <v>991</v>
+      </c>
+      <c r="F317" t="s">
+        <v>996</v>
+      </c>
+      <c r="G317" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H317" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="I317" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M317" s="34" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="318" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A318" t="s">
+        <v>13</v>
+      </c>
+      <c r="C318">
+        <v>317</v>
+      </c>
+      <c r="D318" s="35" t="s">
+        <v>957</v>
+      </c>
+      <c r="E318" s="38" t="s">
+        <v>991</v>
+      </c>
+      <c r="F318" t="s">
+        <v>997</v>
+      </c>
+      <c r="G318" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H318" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I318" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M318" s="35" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="319" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A319" t="s">
+        <v>13</v>
+      </c>
+      <c r="C319">
+        <v>318</v>
+      </c>
+      <c r="D319" s="34" t="s">
+        <v>958</v>
+      </c>
+      <c r="E319" s="36" t="s">
+        <v>991</v>
+      </c>
+      <c r="F319" t="s">
+        <v>998</v>
+      </c>
+      <c r="G319" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="H319" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I319" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M319" s="34" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="320" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A320" t="s">
+        <v>13</v>
+      </c>
+      <c r="C320">
+        <v>319</v>
+      </c>
+      <c r="D320" s="35" t="s">
+        <v>288</v>
+      </c>
+      <c r="E320" s="38" t="s">
+        <v>991</v>
+      </c>
+      <c r="F320" t="s">
+        <v>999</v>
+      </c>
+      <c r="G320" s="38" t="s">
+        <v>564</v>
+      </c>
+      <c r="H320" s="39" t="s">
+        <v>968</v>
+      </c>
+      <c r="I320" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M320" s="35" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="321" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>13</v>
+      </c>
+      <c r="C321">
+        <v>320</v>
+      </c>
+      <c r="D321" s="34" t="s">
+        <v>959</v>
+      </c>
+      <c r="E321" s="36" t="s">
+        <v>991</v>
+      </c>
+      <c r="F321" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G321" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H321" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I321" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M321" s="34" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="322" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
+        <v>13</v>
+      </c>
+      <c r="C322">
+        <v>321</v>
+      </c>
+      <c r="D322" s="35" t="s">
+        <v>960</v>
+      </c>
+      <c r="E322" s="38" t="s">
+        <v>991</v>
+      </c>
+      <c r="F322" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G322" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H322" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I322" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="M322" s="35" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="323" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
+        <v>13</v>
+      </c>
+      <c r="C323">
+        <v>322</v>
+      </c>
+      <c r="D323" s="34" t="s">
+        <v>961</v>
+      </c>
+      <c r="E323" s="36" t="s">
+        <v>991</v>
+      </c>
+      <c r="F323" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G323" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H323" s="37" t="s">
+        <v>969</v>
+      </c>
+      <c r="I323" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M323" s="34" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="324" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>13</v>
+      </c>
+      <c r="C324">
+        <v>323</v>
+      </c>
+      <c r="D324" s="35" t="s">
+        <v>962</v>
+      </c>
+      <c r="E324" s="38" t="s">
+        <v>991</v>
+      </c>
+      <c r="F324" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G324" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H324" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="I324" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="M324" s="35" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="325" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
+        <v>13</v>
+      </c>
+      <c r="C325">
+        <v>324</v>
+      </c>
+      <c r="D325" s="34" t="s">
+        <v>963</v>
+      </c>
+      <c r="E325" s="36" t="s">
+        <v>991</v>
+      </c>
+      <c r="F325" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G325" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H325" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I325" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M325" s="34" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="326" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A326" t="s">
+        <v>13</v>
+      </c>
+      <c r="C326">
+        <v>325</v>
+      </c>
+      <c r="D326" s="35" t="s">
+        <v>964</v>
+      </c>
+      <c r="E326" s="38" t="s">
+        <v>991</v>
+      </c>
+      <c r="F326" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G326" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H326" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="I326" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="M326" s="35" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="327" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A327" t="s">
+        <v>13</v>
+      </c>
+      <c r="C327">
+        <v>326</v>
+      </c>
+      <c r="D327" s="34" t="s">
+        <v>965</v>
+      </c>
+      <c r="E327" s="36" t="s">
+        <v>991</v>
+      </c>
+      <c r="F327" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G327" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H327" s="37" t="s">
+        <v>316</v>
+      </c>
+      <c r="I327" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M327" s="34" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="328" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A328" t="s">
+        <v>13</v>
+      </c>
+      <c r="C328">
+        <v>327</v>
+      </c>
+      <c r="D328" s="35" t="s">
+        <v>966</v>
+      </c>
+      <c r="E328" s="38" t="s">
+        <v>991</v>
+      </c>
+      <c r="F328" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G328" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H328" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="I328" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="M328" s="35" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="329" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A329" t="s">
+        <v>13</v>
+      </c>
+      <c r="C329">
+        <v>328</v>
+      </c>
+      <c r="D329" s="34" t="s">
+        <v>967</v>
+      </c>
+      <c r="E329" s="36" t="s">
+        <v>991</v>
+      </c>
+      <c r="F329" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G329" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H329" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="I329" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M329" s="34" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="330" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A330" t="s">
+        <v>13</v>
+      </c>
+      <c r="C330">
+        <v>329</v>
+      </c>
+      <c r="D330" s="34" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E330" s="36" t="s">
+        <v>991</v>
+      </c>
+      <c r="F330" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G330" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H330" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="I330" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J330" s="6"/>
+      <c r="K330" s="6"/>
+      <c r="L330" s="6"/>
+      <c r="M330" s="30" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="331" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A331" t="s">
+        <v>13</v>
+      </c>
+      <c r="C331">
+        <v>330</v>
+      </c>
+      <c r="D331" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E331" s="36" t="s">
+        <v>991</v>
+      </c>
+      <c r="F331" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G331" t="s">
+        <v>30</v>
+      </c>
+      <c r="H331" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I331" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J331" s="6"/>
+      <c r="K331" s="6"/>
+      <c r="L331" s="6"/>
+      <c r="M331" s="6" t="s">
+        <v>527</v>
       </c>
     </row>
   </sheetData>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/Round 2 Pods for Testing/Fast Track Pods/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Verification Metadata/CDOP_SCHEMAs for Testing/VerificationAE_no arrays/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="527" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A8E844A-1D58-4DFC-9D20-5AF2A91A062C}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{43812F2F-CE42-471E-B59C-F29A7962070A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F90AA9B7-3DCB-465F-BB58-71E6EC1D840A}"/>
   <bookViews>
-    <workbookView xWindow="-27315" yWindow="525" windowWidth="26085" windowHeight="12255" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView xWindow="-28080" yWindow="315" windowWidth="27450" windowHeight="14490" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7825" uniqueCount="1020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7825" uniqueCount="1019">
   <si>
     <t>schema</t>
   </si>
@@ -1671,9 +1671,6 @@
   </si>
   <si>
     <t>unit.credit_block[].block_end</t>
-  </si>
-  <si>
-    <t>unit.credit_block[]block_start</t>
   </si>
   <si>
     <t>validation.validation[].validation_id</t>
@@ -3073,27 +3070,6 @@
     <t>verification</t>
   </si>
   <si>
-    <t>verification.reporting[].verification_reporting_period_start</t>
-  </si>
-  <si>
-    <t>verification.reporting[].verification_reporting_period_end</t>
-  </si>
-  <si>
-    <t>verification.reporting[].verification_date</t>
-  </si>
-  <si>
-    <t>verification.quantity[].verified_quantity</t>
-  </si>
-  <si>
-    <t>verification.quantity[].verification_quantity_uom</t>
-  </si>
-  <si>
-    <t>verification.standard[].verification_applied_standard</t>
-  </si>
-  <si>
-    <t>verification.standard[].verification_applied_methodology_protocol</t>
-  </si>
-  <si>
     <t>verification.verification_report_url</t>
   </si>
   <si>
@@ -3115,12 +3091,6 @@
     <t>verification.verification_project_id</t>
   </si>
   <si>
-    <t>verification.details[].verification_claim_type</t>
-  </si>
-  <si>
-    <t>verification.details[].verification_description</t>
-  </si>
-  <si>
     <t>verification_vvb_id</t>
   </si>
   <si>
@@ -3130,31 +3100,58 @@
     <t>A globally unique identifier for a validation or verification body (vvb).</t>
   </si>
   <si>
-    <t>verification.status[].verification_audit_checkpoint_status</t>
-  </si>
-  <si>
     <t>verification_audit_checkpoint_status_reason</t>
   </si>
   <si>
-    <t>verification.status[].verification_audit_checkpoint_status_reason</t>
-  </si>
-  <si>
-    <t>verification.status[].is_current</t>
-  </si>
-  <si>
-    <t>verification.deductions[].verification_leakage_risk_mitigation</t>
-  </si>
-  <si>
-    <t>verification.deductions[].verification_leakage_risk_mitigation_strategy</t>
-  </si>
-  <si>
-    <t>verification.deductions[].verification_leakage_deduction_quantity</t>
-  </si>
-  <si>
-    <t>verification.deductions[].verification_uncertainty_deduction_margin</t>
-  </si>
-  <si>
-    <t>verification.deductions[].verification_buffer_pool_deduction_quantity</t>
+    <t>verification.verification_claim_type</t>
+  </si>
+  <si>
+    <t>verification.verification_description</t>
+  </si>
+  <si>
+    <t>verification.verification_reporting_period_start</t>
+  </si>
+  <si>
+    <t>verification.verification_reporting_period_end</t>
+  </si>
+  <si>
+    <t>verification.verification_date</t>
+  </si>
+  <si>
+    <t>verification.verified_quantity</t>
+  </si>
+  <si>
+    <t>verification.verification_quantity_uom</t>
+  </si>
+  <si>
+    <t>verification.verification_applied_standard</t>
+  </si>
+  <si>
+    <t>verification.verification_applied_methodology_protocol</t>
+  </si>
+  <si>
+    <t>verification.verification_leakage_risk_mitigation</t>
+  </si>
+  <si>
+    <t>verification.verification_leakage_risk_mitigation_strategy</t>
+  </si>
+  <si>
+    <t>verification.verification_leakage_deduction_quantity</t>
+  </si>
+  <si>
+    <t>verification.verification_uncertainty_deduction_margin</t>
+  </si>
+  <si>
+    <t>verification.verification_buffer_pool_deduction_quantity</t>
+  </si>
+  <si>
+    <t>verification.verification_audit_checkpoint_status</t>
+  </si>
+  <si>
+    <t>verification.verification_audit_checkpoint_status_reason</t>
+  </si>
+  <si>
+    <t>verification.is_current</t>
   </si>
 </sst>
 </file>
@@ -5868,7 +5865,7 @@
         <v>165</v>
       </c>
       <c r="F51" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="G51" t="s">
         <v>30</v>
@@ -10048,7 +10045,7 @@
         <v>444</v>
       </c>
       <c r="F153" t="s">
-        <v>539</v>
+        <v>759</v>
       </c>
       <c r="G153" t="s">
         <v>18</v>
@@ -10130,7 +10127,7 @@
         <v>266</v>
       </c>
       <c r="F155" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G155" t="s">
         <v>18</v>
@@ -10145,7 +10142,7 @@
         <v>445</v>
       </c>
       <c r="K155" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="L155" t="s">
         <v>146</v>
@@ -10171,7 +10168,7 @@
         <v>266</v>
       </c>
       <c r="F156" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G156" t="s">
         <v>18</v>
@@ -10212,7 +10209,7 @@
         <v>266</v>
       </c>
       <c r="F157" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G157" t="s">
         <v>18</v>
@@ -10253,7 +10250,7 @@
         <v>266</v>
       </c>
       <c r="F158" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G158" t="s">
         <v>18</v>
@@ -10294,7 +10291,7 @@
         <v>16</v>
       </c>
       <c r="F159" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G159" t="s">
         <v>30</v>
@@ -10335,7 +10332,7 @@
         <v>16</v>
       </c>
       <c r="F160" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G160" t="s">
         <v>30</v>
@@ -10376,7 +10373,7 @@
         <v>16</v>
       </c>
       <c r="F161" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G161" t="s">
         <v>30</v>
@@ -10417,7 +10414,7 @@
         <v>16</v>
       </c>
       <c r="F162" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G162" t="s">
         <v>30</v>
@@ -10458,7 +10455,7 @@
         <v>494</v>
       </c>
       <c r="F163" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G163" s="18" t="s">
         <v>18</v>
@@ -10499,7 +10496,7 @@
         <v>494</v>
       </c>
       <c r="F164" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G164" s="18" t="s">
         <v>18</v>
@@ -10540,7 +10537,7 @@
         <v>494</v>
       </c>
       <c r="F165" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G165" s="18" t="s">
         <v>18</v>
@@ -10581,7 +10578,7 @@
         <v>494</v>
       </c>
       <c r="F166" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G166" s="18" t="s">
         <v>30</v>
@@ -10622,7 +10619,7 @@
         <v>494</v>
       </c>
       <c r="F167" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G167" s="6" t="s">
         <v>30</v>
@@ -10663,7 +10660,7 @@
         <v>16</v>
       </c>
       <c r="F168" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G168" s="18" t="s">
         <v>18</v>
@@ -10704,7 +10701,7 @@
         <v>16</v>
       </c>
       <c r="F169" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G169" s="18" t="s">
         <v>18</v>
@@ -10786,7 +10783,7 @@
         <v>266</v>
       </c>
       <c r="F171" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G171" s="18" t="s">
         <v>18</v>
@@ -10827,7 +10824,7 @@
         <v>266</v>
       </c>
       <c r="F172" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G172" s="18" t="s">
         <v>18</v>
@@ -10868,7 +10865,7 @@
         <v>494</v>
       </c>
       <c r="F173" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G173" s="6" t="s">
         <v>30</v>
@@ -10909,7 +10906,7 @@
         <v>494</v>
       </c>
       <c r="F174" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G174" s="6" t="s">
         <v>30</v>
@@ -10950,7 +10947,7 @@
         <v>494</v>
       </c>
       <c r="F175" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G175" s="6" t="s">
         <v>30</v>
@@ -10991,7 +10988,7 @@
         <v>494</v>
       </c>
       <c r="F176" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G176" s="6" t="s">
         <v>30</v>
@@ -11032,7 +11029,7 @@
         <v>494</v>
       </c>
       <c r="F177" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G177" s="18" t="s">
         <v>192</v>
@@ -11067,16 +11064,16 @@
         <v>177</v>
       </c>
       <c r="D178" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="E178" t="s">
         <v>561</v>
       </c>
-      <c r="E178" t="s">
+      <c r="F178" t="s">
         <v>562</v>
       </c>
-      <c r="F178" t="s">
+      <c r="G178" s="24" t="s">
         <v>563</v>
-      </c>
-      <c r="G178" s="24" t="s">
-        <v>564</v>
       </c>
       <c r="H178" s="24" t="s">
         <v>143</v>
@@ -11085,7 +11082,7 @@
         <v>20</v>
       </c>
       <c r="J178" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K178" s="24" t="s">
         <v>163</v>
@@ -11094,7 +11091,7 @@
         <v>146</v>
       </c>
       <c r="M178" s="27" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="179" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -11108,16 +11105,16 @@
         <v>178</v>
       </c>
       <c r="D179" s="24" t="s">
+        <v>566</v>
+      </c>
+      <c r="E179" t="s">
+        <v>561</v>
+      </c>
+      <c r="F179" t="s">
         <v>567</v>
       </c>
-      <c r="E179" t="s">
-        <v>562</v>
-      </c>
-      <c r="F179" t="s">
-        <v>568</v>
-      </c>
       <c r="G179" s="24" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H179" s="24" t="s">
         <v>159</v>
@@ -11126,7 +11123,7 @@
         <v>20</v>
       </c>
       <c r="J179" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K179" s="24" t="s">
         <v>163</v>
@@ -11135,7 +11132,7 @@
         <v>146</v>
       </c>
       <c r="M179" s="27" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.35">
@@ -11149,13 +11146,13 @@
         <v>179</v>
       </c>
       <c r="D180" s="25" t="s">
+        <v>569</v>
+      </c>
+      <c r="E180" t="s">
+        <v>561</v>
+      </c>
+      <c r="F180" t="s">
         <v>570</v>
-      </c>
-      <c r="E180" t="s">
-        <v>562</v>
-      </c>
-      <c r="F180" t="s">
-        <v>571</v>
       </c>
       <c r="G180" s="25" t="s">
         <v>18</v>
@@ -11167,7 +11164,7 @@
         <v>20</v>
       </c>
       <c r="J180" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K180" s="24" t="s">
         <v>163</v>
@@ -11176,7 +11173,7 @@
         <v>146</v>
       </c>
       <c r="M180" s="27" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.35">
@@ -11190,13 +11187,13 @@
         <v>180</v>
       </c>
       <c r="D181" s="26" t="s">
+        <v>572</v>
+      </c>
+      <c r="E181" t="s">
+        <v>561</v>
+      </c>
+      <c r="F181" t="s">
         <v>573</v>
-      </c>
-      <c r="E181" t="s">
-        <v>562</v>
-      </c>
-      <c r="F181" t="s">
-        <v>574</v>
       </c>
       <c r="G181" s="24" t="s">
         <v>30</v>
@@ -11208,7 +11205,7 @@
         <v>144</v>
       </c>
       <c r="J181" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K181" s="24" t="s">
         <v>163</v>
@@ -11217,7 +11214,7 @@
         <v>146</v>
       </c>
       <c r="M181" s="27" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="182" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -11231,13 +11228,13 @@
         <v>181</v>
       </c>
       <c r="D182" s="26" t="s">
+        <v>575</v>
+      </c>
+      <c r="E182" t="s">
+        <v>561</v>
+      </c>
+      <c r="F182" t="s">
         <v>576</v>
-      </c>
-      <c r="E182" t="s">
-        <v>562</v>
-      </c>
-      <c r="F182" t="s">
-        <v>577</v>
       </c>
       <c r="G182" s="24" t="s">
         <v>30</v>
@@ -11249,7 +11246,7 @@
         <v>144</v>
       </c>
       <c r="J182" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K182" s="24" t="s">
         <v>163</v>
@@ -11258,7 +11255,7 @@
         <v>146</v>
       </c>
       <c r="M182" s="27" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.35">
@@ -11272,13 +11269,13 @@
         <v>182</v>
       </c>
       <c r="D183" s="26" t="s">
+        <v>578</v>
+      </c>
+      <c r="E183" t="s">
+        <v>561</v>
+      </c>
+      <c r="F183" t="s">
         <v>579</v>
-      </c>
-      <c r="E183" t="s">
-        <v>562</v>
-      </c>
-      <c r="F183" t="s">
-        <v>580</v>
       </c>
       <c r="G183" s="25" t="s">
         <v>30</v>
@@ -11290,7 +11287,7 @@
         <v>144</v>
       </c>
       <c r="J183" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K183" s="24" t="s">
         <v>163</v>
@@ -11299,7 +11296,7 @@
         <v>146</v>
       </c>
       <c r="M183" s="27" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.35">
@@ -11313,13 +11310,13 @@
         <v>183</v>
       </c>
       <c r="D184" s="25" t="s">
+        <v>581</v>
+      </c>
+      <c r="E184" t="s">
+        <v>561</v>
+      </c>
+      <c r="F184" t="s">
         <v>582</v>
-      </c>
-      <c r="E184" t="s">
-        <v>562</v>
-      </c>
-      <c r="F184" t="s">
-        <v>583</v>
       </c>
       <c r="G184" s="25" t="s">
         <v>30</v>
@@ -11331,7 +11328,7 @@
         <v>144</v>
       </c>
       <c r="J184" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K184" s="24" t="s">
         <v>163</v>
@@ -11340,7 +11337,7 @@
         <v>146</v>
       </c>
       <c r="M184" s="27" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.35">
@@ -11354,13 +11351,13 @@
         <v>184</v>
       </c>
       <c r="D185" s="25" t="s">
+        <v>584</v>
+      </c>
+      <c r="E185" t="s">
+        <v>561</v>
+      </c>
+      <c r="F185" t="s">
         <v>585</v>
-      </c>
-      <c r="E185" t="s">
-        <v>562</v>
-      </c>
-      <c r="F185" t="s">
-        <v>586</v>
       </c>
       <c r="G185" s="25" t="s">
         <v>30</v>
@@ -11372,7 +11369,7 @@
         <v>144</v>
       </c>
       <c r="J185" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K185" s="24" t="s">
         <v>163</v>
@@ -11381,7 +11378,7 @@
         <v>146</v>
       </c>
       <c r="M185" s="27" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.35">
@@ -11395,13 +11392,13 @@
         <v>185</v>
       </c>
       <c r="D186" s="25" t="s">
+        <v>587</v>
+      </c>
+      <c r="E186" t="s">
+        <v>561</v>
+      </c>
+      <c r="F186" t="s">
         <v>588</v>
-      </c>
-      <c r="E186" t="s">
-        <v>562</v>
-      </c>
-      <c r="F186" t="s">
-        <v>589</v>
       </c>
       <c r="G186" s="25" t="s">
         <v>30</v>
@@ -11413,7 +11410,7 @@
         <v>144</v>
       </c>
       <c r="J186" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K186" s="24" t="s">
         <v>163</v>
@@ -11422,7 +11419,7 @@
         <v>146</v>
       </c>
       <c r="M186" s="27" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.35">
@@ -11436,13 +11433,13 @@
         <v>186</v>
       </c>
       <c r="D187" s="25" t="s">
+        <v>590</v>
+      </c>
+      <c r="E187" t="s">
+        <v>561</v>
+      </c>
+      <c r="F187" t="s">
         <v>591</v>
-      </c>
-      <c r="E187" t="s">
-        <v>562</v>
-      </c>
-      <c r="F187" t="s">
-        <v>592</v>
       </c>
       <c r="G187" s="25" t="s">
         <v>30</v>
@@ -11454,7 +11451,7 @@
         <v>144</v>
       </c>
       <c r="J187" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K187" s="24" t="s">
         <v>163</v>
@@ -11463,7 +11460,7 @@
         <v>146</v>
       </c>
       <c r="M187" s="27" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.35">
@@ -11477,13 +11474,13 @@
         <v>187</v>
       </c>
       <c r="D188" s="25" t="s">
+        <v>593</v>
+      </c>
+      <c r="E188" t="s">
+        <v>561</v>
+      </c>
+      <c r="F188" t="s">
         <v>594</v>
-      </c>
-      <c r="E188" t="s">
-        <v>562</v>
-      </c>
-      <c r="F188" t="s">
-        <v>595</v>
       </c>
       <c r="G188" s="25" t="s">
         <v>30</v>
@@ -11495,7 +11492,7 @@
         <v>144</v>
       </c>
       <c r="J188" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K188" s="24" t="s">
         <v>163</v>
@@ -11504,7 +11501,7 @@
         <v>146</v>
       </c>
       <c r="M188" s="27" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="189" spans="1:13" x14ac:dyDescent="0.35">
@@ -11518,13 +11515,13 @@
         <v>188</v>
       </c>
       <c r="D189" s="25" t="s">
+        <v>596</v>
+      </c>
+      <c r="E189" t="s">
+        <v>561</v>
+      </c>
+      <c r="F189" t="s">
         <v>597</v>
-      </c>
-      <c r="E189" t="s">
-        <v>562</v>
-      </c>
-      <c r="F189" t="s">
-        <v>598</v>
       </c>
       <c r="G189" s="25" t="s">
         <v>30</v>
@@ -11536,7 +11533,7 @@
         <v>144</v>
       </c>
       <c r="J189" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K189" s="24" t="s">
         <v>163</v>
@@ -11545,7 +11542,7 @@
         <v>146</v>
       </c>
       <c r="M189" s="27" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.35">
@@ -11559,25 +11556,25 @@
         <v>189</v>
       </c>
       <c r="D190" s="25" t="s">
+        <v>599</v>
+      </c>
+      <c r="E190" t="s">
+        <v>561</v>
+      </c>
+      <c r="F190" t="s">
         <v>600</v>
       </c>
-      <c r="E190" t="s">
-        <v>562</v>
-      </c>
-      <c r="F190" t="s">
+      <c r="G190" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="H190" s="24" t="s">
         <v>601</v>
-      </c>
-      <c r="G190" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="H190" s="24" t="s">
-        <v>602</v>
       </c>
       <c r="I190" s="24" t="s">
         <v>144</v>
       </c>
       <c r="J190" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K190" s="24" t="s">
         <v>163</v>
@@ -11586,7 +11583,7 @@
         <v>146</v>
       </c>
       <c r="M190" s="27" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.35">
@@ -11600,13 +11597,13 @@
         <v>190</v>
       </c>
       <c r="D191" s="24" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E191" s="24" t="s">
+        <v>603</v>
+      </c>
+      <c r="F191" t="s">
         <v>604</v>
-      </c>
-      <c r="F191" t="s">
-        <v>605</v>
       </c>
       <c r="G191" s="24" t="s">
         <v>18</v>
@@ -11618,7 +11615,7 @@
         <v>20</v>
       </c>
       <c r="J191" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K191" s="24" t="s">
         <v>163</v>
@@ -11627,7 +11624,7 @@
         <v>146</v>
       </c>
       <c r="M191" s="27" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="192" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -11641,13 +11638,13 @@
         <v>191</v>
       </c>
       <c r="D192" s="26" t="s">
+        <v>605</v>
+      </c>
+      <c r="E192" s="24" t="s">
+        <v>603</v>
+      </c>
+      <c r="F192" t="s">
         <v>606</v>
-      </c>
-      <c r="E192" s="24" t="s">
-        <v>604</v>
-      </c>
-      <c r="F192" t="s">
-        <v>607</v>
       </c>
       <c r="G192" s="24" t="s">
         <v>30</v>
@@ -11659,7 +11656,7 @@
         <v>144</v>
       </c>
       <c r="J192" s="24" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K192" s="24" t="s">
         <v>163</v>
@@ -11668,7 +11665,7 @@
         <v>146</v>
       </c>
       <c r="M192" s="27" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.35">
@@ -11682,13 +11679,13 @@
         <v>192</v>
       </c>
       <c r="D193" s="26" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E193" s="24" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F193" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G193" s="24" t="s">
         <v>30</v>
@@ -11700,7 +11697,7 @@
         <v>144</v>
       </c>
       <c r="J193" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K193" s="24" t="s">
         <v>163</v>
@@ -11709,7 +11706,7 @@
         <v>146</v>
       </c>
       <c r="M193" s="27" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="194" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -11723,13 +11720,13 @@
         <v>193</v>
       </c>
       <c r="D194" s="24" t="s">
+        <v>610</v>
+      </c>
+      <c r="E194" s="24" t="s">
+        <v>603</v>
+      </c>
+      <c r="F194" t="s">
         <v>611</v>
-      </c>
-      <c r="E194" s="24" t="s">
-        <v>604</v>
-      </c>
-      <c r="F194" t="s">
-        <v>612</v>
       </c>
       <c r="G194" s="24" t="s">
         <v>30</v>
@@ -11741,7 +11738,7 @@
         <v>144</v>
       </c>
       <c r="J194" s="24" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K194" s="24" t="s">
         <v>163</v>
@@ -11750,7 +11747,7 @@
         <v>146</v>
       </c>
       <c r="M194" s="27" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="195" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -11764,13 +11761,13 @@
         <v>194</v>
       </c>
       <c r="D195" s="24" t="s">
+        <v>613</v>
+      </c>
+      <c r="E195" s="24" t="s">
+        <v>603</v>
+      </c>
+      <c r="F195" t="s">
         <v>614</v>
-      </c>
-      <c r="E195" s="24" t="s">
-        <v>604</v>
-      </c>
-      <c r="F195" t="s">
-        <v>615</v>
       </c>
       <c r="G195" s="24" t="s">
         <v>30</v>
@@ -11782,7 +11779,7 @@
         <v>144</v>
       </c>
       <c r="J195" s="24" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K195" s="24" t="s">
         <v>163</v>
@@ -11791,7 +11788,7 @@
         <v>146</v>
       </c>
       <c r="M195" s="27" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="196" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -11805,25 +11802,25 @@
         <v>195</v>
       </c>
       <c r="D196" s="24" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E196" s="24" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F196" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G196" s="24" t="s">
         <v>30</v>
       </c>
       <c r="H196" s="24" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="I196" s="24" t="s">
         <v>144</v>
       </c>
       <c r="J196" s="24" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K196" s="24" t="s">
         <v>163</v>
@@ -11832,7 +11829,7 @@
         <v>146</v>
       </c>
       <c r="M196" s="27" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.35">
@@ -11846,13 +11843,13 @@
         <v>196</v>
       </c>
       <c r="D197" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E197" t="s">
         <v>16</v>
       </c>
       <c r="F197" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G197" t="s">
         <v>18</v>
@@ -11873,7 +11870,7 @@
         <v>146</v>
       </c>
       <c r="M197" s="19" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.35">
@@ -11887,13 +11884,13 @@
         <v>197</v>
       </c>
       <c r="D198" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E198" t="s">
         <v>16</v>
       </c>
       <c r="F198" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G198" t="s">
         <v>18</v>
@@ -11914,7 +11911,7 @@
         <v>146</v>
       </c>
       <c r="M198" s="19" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.35">
@@ -11928,13 +11925,13 @@
         <v>198</v>
       </c>
       <c r="D199" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E199" t="s">
         <v>16</v>
       </c>
       <c r="F199" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G199" t="s">
         <v>18</v>
@@ -11955,7 +11952,7 @@
         <v>146</v>
       </c>
       <c r="M199" s="19" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.35">
@@ -11969,13 +11966,13 @@
         <v>199</v>
       </c>
       <c r="D200" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E200" t="s">
         <v>16</v>
       </c>
       <c r="F200" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G200" t="s">
         <v>18</v>
@@ -11996,7 +11993,7 @@
         <v>146</v>
       </c>
       <c r="M200" s="19" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.35">
@@ -12010,19 +12007,19 @@
         <v>200</v>
       </c>
       <c r="D201" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E201" t="s">
         <v>16</v>
       </c>
       <c r="F201" t="s">
+        <v>631</v>
+      </c>
+      <c r="G201" t="s">
+        <v>30</v>
+      </c>
+      <c r="H201" t="s">
         <v>632</v>
-      </c>
-      <c r="G201" t="s">
-        <v>30</v>
-      </c>
-      <c r="H201" t="s">
-        <v>633</v>
       </c>
       <c r="I201" t="s">
         <v>144</v>
@@ -12037,7 +12034,7 @@
         <v>146</v>
       </c>
       <c r="M201" s="18" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="202" spans="1:13" x14ac:dyDescent="0.35">
@@ -12051,13 +12048,13 @@
         <v>201</v>
       </c>
       <c r="D202" s="17" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E202" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F202" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G202" s="17" t="s">
         <v>192</v>
@@ -12078,7 +12075,7 @@
         <v>146</v>
       </c>
       <c r="M202" s="17" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="203" spans="1:13" x14ac:dyDescent="0.35">
@@ -12092,13 +12089,13 @@
         <v>202</v>
       </c>
       <c r="D203" s="17" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E203" s="17" t="s">
         <v>25</v>
       </c>
       <c r="F203" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G203" s="17" t="s">
         <v>30</v>
@@ -12119,7 +12116,7 @@
         <v>146</v>
       </c>
       <c r="M203" s="17" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="204" spans="1:13" x14ac:dyDescent="0.35">
@@ -12133,13 +12130,13 @@
         <v>203</v>
       </c>
       <c r="D204" s="17" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E204" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F204" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G204" s="17" t="s">
         <v>18</v>
@@ -12160,7 +12157,7 @@
         <v>146</v>
       </c>
       <c r="M204" s="17" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.35">
@@ -12174,13 +12171,13 @@
         <v>204</v>
       </c>
       <c r="D205" s="17" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E205" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F205" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G205" s="17" t="s">
         <v>18</v>
@@ -12201,7 +12198,7 @@
         <v>146</v>
       </c>
       <c r="M205" s="17" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.35">
@@ -12215,13 +12212,13 @@
         <v>205</v>
       </c>
       <c r="D206" s="17" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E206" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F206" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G206" s="17" t="s">
         <v>18</v>
@@ -12242,7 +12239,7 @@
         <v>146</v>
       </c>
       <c r="M206" s="17" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="207" spans="1:13" x14ac:dyDescent="0.35">
@@ -12256,13 +12253,13 @@
         <v>206</v>
       </c>
       <c r="D207" s="17" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E207" s="17" t="s">
         <v>444</v>
       </c>
       <c r="F207" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G207" s="17" t="s">
         <v>18</v>
@@ -12283,7 +12280,7 @@
         <v>254</v>
       </c>
       <c r="M207" s="17" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="208" spans="1:13" x14ac:dyDescent="0.35">
@@ -12297,13 +12294,13 @@
         <v>207</v>
       </c>
       <c r="D208" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E208" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F208" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G208" s="17" t="s">
         <v>18</v>
@@ -12324,7 +12321,7 @@
         <v>146</v>
       </c>
       <c r="M208" s="17" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="209" spans="1:13" x14ac:dyDescent="0.35">
@@ -12338,13 +12335,13 @@
         <v>208</v>
       </c>
       <c r="D209" s="17" t="s">
+        <v>655</v>
+      </c>
+      <c r="E209" s="17" t="s">
         <v>656</v>
       </c>
-      <c r="E209" s="17" t="s">
+      <c r="F209" t="s">
         <v>657</v>
-      </c>
-      <c r="F209" t="s">
-        <v>658</v>
       </c>
       <c r="G209" s="17" t="s">
         <v>30</v>
@@ -12356,7 +12353,7 @@
         <v>31</v>
       </c>
       <c r="J209" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K209" s="17" t="s">
         <v>163</v>
@@ -12365,7 +12362,7 @@
         <v>146</v>
       </c>
       <c r="M209" s="17" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="210" spans="1:13" x14ac:dyDescent="0.35">
@@ -12379,13 +12376,13 @@
         <v>209</v>
       </c>
       <c r="D210" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="E210" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F210" t="s">
         <v>661</v>
-      </c>
-      <c r="E210" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F210" t="s">
-        <v>662</v>
       </c>
       <c r="G210" s="17" t="s">
         <v>30</v>
@@ -12397,7 +12394,7 @@
         <v>20</v>
       </c>
       <c r="J210" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K210" s="17" t="s">
         <v>163</v>
@@ -12406,7 +12403,7 @@
         <v>146</v>
       </c>
       <c r="M210" s="17" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="211" spans="1:13" x14ac:dyDescent="0.35">
@@ -12420,13 +12417,13 @@
         <v>210</v>
       </c>
       <c r="D211" s="17" t="s">
+        <v>663</v>
+      </c>
+      <c r="E211" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F211" t="s">
         <v>664</v>
-      </c>
-      <c r="E211" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F211" t="s">
-        <v>665</v>
       </c>
       <c r="G211" s="17" t="s">
         <v>30</v>
@@ -12438,7 +12435,7 @@
         <v>31</v>
       </c>
       <c r="J211" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K211" s="17" t="s">
         <v>163</v>
@@ -12447,7 +12444,7 @@
         <v>146</v>
       </c>
       <c r="M211" s="17" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="212" spans="1:13" x14ac:dyDescent="0.35">
@@ -12461,13 +12458,13 @@
         <v>211</v>
       </c>
       <c r="D212" s="17" t="s">
+        <v>666</v>
+      </c>
+      <c r="E212" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F212" t="s">
         <v>667</v>
-      </c>
-      <c r="E212" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F212" t="s">
-        <v>668</v>
       </c>
       <c r="G212" s="17" t="s">
         <v>30</v>
@@ -12479,7 +12476,7 @@
         <v>31</v>
       </c>
       <c r="J212" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K212" s="17" t="s">
         <v>163</v>
@@ -12488,7 +12485,7 @@
         <v>146</v>
       </c>
       <c r="M212" s="17" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.35">
@@ -12502,13 +12499,13 @@
         <v>212</v>
       </c>
       <c r="D213" s="17" t="s">
+        <v>669</v>
+      </c>
+      <c r="E213" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F213" t="s">
         <v>670</v>
-      </c>
-      <c r="E213" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F213" t="s">
-        <v>671</v>
       </c>
       <c r="G213" s="17" t="s">
         <v>30</v>
@@ -12520,7 +12517,7 @@
         <v>31</v>
       </c>
       <c r="J213" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K213" s="17" t="s">
         <v>163</v>
@@ -12529,7 +12526,7 @@
         <v>146</v>
       </c>
       <c r="M213" s="17" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="214" spans="1:13" x14ac:dyDescent="0.35">
@@ -12543,13 +12540,13 @@
         <v>213</v>
       </c>
       <c r="D214" s="17" t="s">
+        <v>672</v>
+      </c>
+      <c r="E214" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F214" t="s">
         <v>673</v>
-      </c>
-      <c r="E214" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F214" t="s">
-        <v>674</v>
       </c>
       <c r="G214" s="17" t="s">
         <v>30</v>
@@ -12561,7 +12558,7 @@
         <v>31</v>
       </c>
       <c r="J214" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K214" s="17" t="s">
         <v>163</v>
@@ -12570,7 +12567,7 @@
         <v>146</v>
       </c>
       <c r="M214" s="17" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="215" spans="1:13" x14ac:dyDescent="0.35">
@@ -12584,13 +12581,13 @@
         <v>214</v>
       </c>
       <c r="D215" s="17" t="s">
+        <v>675</v>
+      </c>
+      <c r="E215" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F215" t="s">
         <v>676</v>
-      </c>
-      <c r="E215" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F215" t="s">
-        <v>677</v>
       </c>
       <c r="G215" s="17" t="s">
         <v>30</v>
@@ -12602,7 +12599,7 @@
         <v>31</v>
       </c>
       <c r="J215" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K215" s="17" t="s">
         <v>163</v>
@@ -12611,7 +12608,7 @@
         <v>146</v>
       </c>
       <c r="M215" s="17" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="216" spans="1:13" x14ac:dyDescent="0.35">
@@ -12625,13 +12622,13 @@
         <v>215</v>
       </c>
       <c r="D216" s="17" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E216" s="17" t="s">
         <v>25</v>
       </c>
       <c r="F216" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G216" s="17" t="s">
         <v>30</v>
@@ -12643,7 +12640,7 @@
         <v>31</v>
       </c>
       <c r="J216" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K216" s="17" t="s">
         <v>163</v>
@@ -12652,7 +12649,7 @@
         <v>146</v>
       </c>
       <c r="M216" s="17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="217" spans="1:13" x14ac:dyDescent="0.35">
@@ -12666,13 +12663,13 @@
         <v>216</v>
       </c>
       <c r="D217" s="17" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E217" s="17" t="s">
         <v>25</v>
       </c>
       <c r="F217" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="G217" s="17" t="s">
         <v>30</v>
@@ -12684,7 +12681,7 @@
         <v>31</v>
       </c>
       <c r="J217" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K217" s="17" t="s">
         <v>163</v>
@@ -12693,7 +12690,7 @@
         <v>146</v>
       </c>
       <c r="M217" s="17" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="218" spans="1:13" x14ac:dyDescent="0.35">
@@ -12707,13 +12704,13 @@
         <v>217</v>
       </c>
       <c r="D218" s="17" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E218" s="17" t="s">
         <v>25</v>
       </c>
       <c r="F218" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="G218" s="17" t="s">
         <v>30</v>
@@ -12725,7 +12722,7 @@
         <v>31</v>
       </c>
       <c r="J218" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K218" s="17" t="s">
         <v>163</v>
@@ -12734,7 +12731,7 @@
         <v>146</v>
       </c>
       <c r="M218" s="17" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="219" spans="1:13" x14ac:dyDescent="0.35">
@@ -12748,13 +12745,13 @@
         <v>218</v>
       </c>
       <c r="D219" s="17" t="s">
+        <v>687</v>
+      </c>
+      <c r="E219" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F219" t="s">
         <v>688</v>
-      </c>
-      <c r="E219" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F219" t="s">
-        <v>689</v>
       </c>
       <c r="G219" s="17" t="s">
         <v>30</v>
@@ -12766,7 +12763,7 @@
         <v>31</v>
       </c>
       <c r="J219" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K219" s="17" t="s">
         <v>163</v>
@@ -12775,7 +12772,7 @@
         <v>146</v>
       </c>
       <c r="M219" s="17" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="220" spans="1:13" x14ac:dyDescent="0.35">
@@ -12789,13 +12786,13 @@
         <v>219</v>
       </c>
       <c r="D220" s="17" t="s">
+        <v>690</v>
+      </c>
+      <c r="E220" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F220" t="s">
         <v>691</v>
-      </c>
-      <c r="E220" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F220" t="s">
-        <v>692</v>
       </c>
       <c r="G220" s="17" t="s">
         <v>30</v>
@@ -12807,7 +12804,7 @@
         <v>31</v>
       </c>
       <c r="J220" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K220" s="17" t="s">
         <v>163</v>
@@ -12816,7 +12813,7 @@
         <v>146</v>
       </c>
       <c r="M220" s="17" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="221" spans="1:13" x14ac:dyDescent="0.35">
@@ -12830,13 +12827,13 @@
         <v>220</v>
       </c>
       <c r="D221" s="17" t="s">
+        <v>693</v>
+      </c>
+      <c r="E221" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F221" t="s">
         <v>694</v>
-      </c>
-      <c r="E221" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F221" t="s">
-        <v>695</v>
       </c>
       <c r="G221" s="17" t="s">
         <v>30</v>
@@ -12848,7 +12845,7 @@
         <v>31</v>
       </c>
       <c r="J221" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K221" s="17" t="s">
         <v>163</v>
@@ -12857,7 +12854,7 @@
         <v>146</v>
       </c>
       <c r="M221" s="17" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="222" spans="1:13" x14ac:dyDescent="0.35">
@@ -12871,13 +12868,13 @@
         <v>221</v>
       </c>
       <c r="D222" s="17" t="s">
+        <v>696</v>
+      </c>
+      <c r="E222" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F222" t="s">
         <v>697</v>
-      </c>
-      <c r="E222" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F222" t="s">
-        <v>698</v>
       </c>
       <c r="G222" s="17" t="s">
         <v>30</v>
@@ -12889,7 +12886,7 @@
         <v>20</v>
       </c>
       <c r="J222" s="17" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="K222" s="17" t="s">
         <v>163</v>
@@ -12898,7 +12895,7 @@
         <v>146</v>
       </c>
       <c r="M222" s="17" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="223" spans="1:13" x14ac:dyDescent="0.35">
@@ -12912,13 +12909,13 @@
         <v>222</v>
       </c>
       <c r="D223" s="17" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E223" s="17" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="F223" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G223" s="17" t="s">
         <v>30</v>
@@ -12930,7 +12927,7 @@
         <v>31</v>
       </c>
       <c r="J223" s="17" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="K223" s="17" t="s">
         <v>163</v>
@@ -12939,7 +12936,7 @@
         <v>146</v>
       </c>
       <c r="M223" s="17" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="224" spans="1:13" x14ac:dyDescent="0.35">
@@ -12953,13 +12950,13 @@
         <v>223</v>
       </c>
       <c r="D224" s="17" t="s">
+        <v>702</v>
+      </c>
+      <c r="E224" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F224" t="s">
         <v>703</v>
-      </c>
-      <c r="E224" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F224" t="s">
-        <v>704</v>
       </c>
       <c r="G224" s="17" t="s">
         <v>30</v>
@@ -12971,7 +12968,7 @@
         <v>31</v>
       </c>
       <c r="J224" s="17" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="K224" s="17" t="s">
         <v>163</v>
@@ -12980,7 +12977,7 @@
         <v>146</v>
       </c>
       <c r="M224" s="17" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.35">
@@ -12994,13 +12991,13 @@
         <v>224</v>
       </c>
       <c r="D225" s="17" t="s">
+        <v>705</v>
+      </c>
+      <c r="E225" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F225" t="s">
         <v>706</v>
-      </c>
-      <c r="E225" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F225" t="s">
-        <v>707</v>
       </c>
       <c r="G225" s="17" t="s">
         <v>30</v>
@@ -13012,7 +13009,7 @@
         <v>31</v>
       </c>
       <c r="J225" s="17" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="K225" s="17" t="s">
         <v>163</v>
@@ -13021,7 +13018,7 @@
         <v>146</v>
       </c>
       <c r="M225" s="17" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.35">
@@ -13035,13 +13032,13 @@
         <v>225</v>
       </c>
       <c r="D226" s="17" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E226" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F226" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="G226" s="17" t="s">
         <v>192</v>
@@ -13062,7 +13059,7 @@
         <v>146</v>
       </c>
       <c r="M226" s="17" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.35">
@@ -13076,13 +13073,13 @@
         <v>226</v>
       </c>
       <c r="D227" s="17" t="s">
+        <v>711</v>
+      </c>
+      <c r="E227" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F227" t="s">
         <v>712</v>
-      </c>
-      <c r="E227" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F227" t="s">
-        <v>713</v>
       </c>
       <c r="G227" s="17" t="s">
         <v>30</v>
@@ -13094,7 +13091,7 @@
         <v>31</v>
       </c>
       <c r="J227" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K227" s="17" t="s">
         <v>163</v>
@@ -13103,7 +13100,7 @@
         <v>146</v>
       </c>
       <c r="M227" s="17" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.35">
@@ -13117,13 +13114,13 @@
         <v>227</v>
       </c>
       <c r="D228" s="17" t="s">
+        <v>714</v>
+      </c>
+      <c r="E228" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F228" t="s">
         <v>715</v>
-      </c>
-      <c r="E228" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F228" t="s">
-        <v>716</v>
       </c>
       <c r="G228" s="17" t="s">
         <v>192</v>
@@ -13135,7 +13132,7 @@
         <v>31</v>
       </c>
       <c r="J228" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K228" s="17" t="s">
         <v>163</v>
@@ -13144,7 +13141,7 @@
         <v>146</v>
       </c>
       <c r="M228" s="17" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="229" spans="1:13" x14ac:dyDescent="0.35">
@@ -13158,13 +13155,13 @@
         <v>228</v>
       </c>
       <c r="D229" s="17" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E229" s="17" t="s">
         <v>444</v>
       </c>
       <c r="F229" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="G229" s="17" t="s">
         <v>30</v>
@@ -13176,7 +13173,7 @@
         <v>31</v>
       </c>
       <c r="J229" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K229" s="17" t="s">
         <v>163</v>
@@ -13185,7 +13182,7 @@
         <v>254</v>
       </c>
       <c r="M229" s="17" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.35">
@@ -13199,13 +13196,13 @@
         <v>229</v>
       </c>
       <c r="D230" s="17" t="s">
+        <v>720</v>
+      </c>
+      <c r="E230" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F230" t="s">
         <v>721</v>
-      </c>
-      <c r="E230" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F230" t="s">
-        <v>722</v>
       </c>
       <c r="G230" s="17" t="s">
         <v>192</v>
@@ -13226,7 +13223,7 @@
         <v>146</v>
       </c>
       <c r="M230" s="17" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.35">
@@ -13240,13 +13237,13 @@
         <v>230</v>
       </c>
       <c r="D231" s="17" t="s">
+        <v>723</v>
+      </c>
+      <c r="E231" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F231" t="s">
         <v>724</v>
-      </c>
-      <c r="E231" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F231" t="s">
-        <v>725</v>
       </c>
       <c r="G231" s="17" t="s">
         <v>30</v>
@@ -13267,7 +13264,7 @@
         <v>146</v>
       </c>
       <c r="M231" s="17" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="232" spans="1:13" x14ac:dyDescent="0.35">
@@ -13281,13 +13278,13 @@
         <v>231</v>
       </c>
       <c r="D232" s="17" t="s">
+        <v>726</v>
+      </c>
+      <c r="E232" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F232" t="s">
         <v>727</v>
-      </c>
-      <c r="E232" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F232" t="s">
-        <v>728</v>
       </c>
       <c r="G232" s="17" t="s">
         <v>30</v>
@@ -13299,7 +13296,7 @@
         <v>31</v>
       </c>
       <c r="J232" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K232" s="17" t="s">
         <v>163</v>
@@ -13308,7 +13305,7 @@
         <v>146</v>
       </c>
       <c r="M232" s="17" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.35">
@@ -13322,13 +13319,13 @@
         <v>232</v>
       </c>
       <c r="D233" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E233" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F233" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G233" s="17" t="s">
         <v>30</v>
@@ -13349,7 +13346,7 @@
         <v>254</v>
       </c>
       <c r="M233" s="17" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.35">
@@ -13363,13 +13360,13 @@
         <v>233</v>
       </c>
       <c r="D234" s="17" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E234" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F234" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="G234" s="17" t="s">
         <v>30</v>
@@ -13390,7 +13387,7 @@
         <v>254</v>
       </c>
       <c r="M234" s="17" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.35">
@@ -13404,13 +13401,13 @@
         <v>234</v>
       </c>
       <c r="D235" s="17" t="s">
+        <v>735</v>
+      </c>
+      <c r="E235" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F235" t="s">
         <v>736</v>
-      </c>
-      <c r="E235" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F235" t="s">
-        <v>737</v>
       </c>
       <c r="G235" s="17" t="s">
         <v>18</v>
@@ -13422,7 +13419,7 @@
         <v>20</v>
       </c>
       <c r="J235" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K235" s="17" t="s">
         <v>163</v>
@@ -13431,7 +13428,7 @@
         <v>254</v>
       </c>
       <c r="M235" s="17" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="236" spans="1:13" x14ac:dyDescent="0.35">
@@ -13445,13 +13442,13 @@
         <v>235</v>
       </c>
       <c r="D236" s="17" t="s">
+        <v>738</v>
+      </c>
+      <c r="E236" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F236" t="s">
         <v>739</v>
-      </c>
-      <c r="E236" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F236" t="s">
-        <v>740</v>
       </c>
       <c r="G236" s="17" t="s">
         <v>30</v>
@@ -13463,7 +13460,7 @@
         <v>144</v>
       </c>
       <c r="J236" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K236" s="17" t="s">
         <v>163</v>
@@ -13472,7 +13469,7 @@
         <v>254</v>
       </c>
       <c r="M236" s="17" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.35">
@@ -13486,13 +13483,13 @@
         <v>236</v>
       </c>
       <c r="D237" s="17" t="s">
+        <v>741</v>
+      </c>
+      <c r="E237" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F237" t="s">
         <v>742</v>
-      </c>
-      <c r="E237" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F237" t="s">
-        <v>743</v>
       </c>
       <c r="G237" s="17" t="s">
         <v>30</v>
@@ -13504,7 +13501,7 @@
         <v>144</v>
       </c>
       <c r="J237" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K237" s="17" t="s">
         <v>163</v>
@@ -13513,7 +13510,7 @@
         <v>254</v>
       </c>
       <c r="M237" s="17" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="238" spans="1:13" x14ac:dyDescent="0.35">
@@ -13527,13 +13524,13 @@
         <v>237</v>
       </c>
       <c r="D238" s="17" t="s">
+        <v>744</v>
+      </c>
+      <c r="E238" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F238" t="s">
         <v>745</v>
-      </c>
-      <c r="E238" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F238" t="s">
-        <v>746</v>
       </c>
       <c r="G238" s="17" t="s">
         <v>30</v>
@@ -13545,7 +13542,7 @@
         <v>144</v>
       </c>
       <c r="J238" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K238" s="17" t="s">
         <v>163</v>
@@ -13554,7 +13551,7 @@
         <v>254</v>
       </c>
       <c r="M238" s="17" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="239" spans="1:13" x14ac:dyDescent="0.35">
@@ -13568,13 +13565,13 @@
         <v>238</v>
       </c>
       <c r="D239" s="17" t="s">
+        <v>747</v>
+      </c>
+      <c r="E239" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F239" t="s">
         <v>748</v>
-      </c>
-      <c r="E239" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F239" t="s">
-        <v>749</v>
       </c>
       <c r="G239" s="17" t="s">
         <v>30</v>
@@ -13586,7 +13583,7 @@
         <v>144</v>
       </c>
       <c r="J239" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K239" s="17" t="s">
         <v>163</v>
@@ -13595,7 +13592,7 @@
         <v>254</v>
       </c>
       <c r="M239" s="17" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.35">
@@ -13609,13 +13606,13 @@
         <v>239</v>
       </c>
       <c r="D240" s="17" t="s">
+        <v>750</v>
+      </c>
+      <c r="E240" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F240" t="s">
         <v>751</v>
-      </c>
-      <c r="E240" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F240" t="s">
-        <v>752</v>
       </c>
       <c r="G240" s="17" t="s">
         <v>30</v>
@@ -13627,7 +13624,7 @@
         <v>144</v>
       </c>
       <c r="J240" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K240" s="17" t="s">
         <v>163</v>
@@ -13636,7 +13633,7 @@
         <v>254</v>
       </c>
       <c r="M240" s="17" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.35">
@@ -13650,13 +13647,13 @@
         <v>240</v>
       </c>
       <c r="D241" s="17" t="s">
+        <v>753</v>
+      </c>
+      <c r="E241" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F241" t="s">
         <v>754</v>
-      </c>
-      <c r="E241" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F241" t="s">
-        <v>755</v>
       </c>
       <c r="G241" s="17" t="s">
         <v>30</v>
@@ -13668,7 +13665,7 @@
         <v>144</v>
       </c>
       <c r="J241" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K241" s="17" t="s">
         <v>163</v>
@@ -13694,10 +13691,10 @@
         <v>148</v>
       </c>
       <c r="E242" s="17" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="F242" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="G242" s="17" t="s">
         <v>30</v>
@@ -13709,7 +13706,7 @@
         <v>20</v>
       </c>
       <c r="J242" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K242" s="6" t="s">
         <v>163</v>
@@ -13732,13 +13729,13 @@
         <v>242</v>
       </c>
       <c r="D243" s="32" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E243" s="6" t="s">
         <v>141</v>
       </c>
       <c r="F243" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G243" t="s">
         <v>30</v>
@@ -13750,7 +13747,7 @@
         <v>31</v>
       </c>
       <c r="J243" s="6" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="K243" s="6" t="s">
         <v>163</v>
@@ -13759,7 +13756,7 @@
         <v>146</v>
       </c>
       <c r="M243" s="6" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="244" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -13773,16 +13770,16 @@
         <v>243</v>
       </c>
       <c r="D244" s="32" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E244" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F244" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G244" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H244" s="6" t="s">
         <v>159</v>
@@ -13791,7 +13788,7 @@
         <v>20</v>
       </c>
       <c r="J244" s="6" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="K244" s="6" t="s">
         <v>163</v>
@@ -13800,7 +13797,7 @@
         <v>146</v>
       </c>
       <c r="M244" s="6" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="245" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -13814,13 +13811,13 @@
         <v>244</v>
       </c>
       <c r="D245" s="32" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="E245" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F245" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="G245" t="s">
         <v>30</v>
@@ -13841,7 +13838,7 @@
         <v>146</v>
       </c>
       <c r="M245" s="6" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="246" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -13855,13 +13852,13 @@
         <v>245</v>
       </c>
       <c r="D246" s="32" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E246" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F246" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="G246" t="s">
         <v>30</v>
@@ -13882,7 +13879,7 @@
         <v>146</v>
       </c>
       <c r="M246" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="247" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -13896,13 +13893,13 @@
         <v>246</v>
       </c>
       <c r="D247" s="32" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E247" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F247" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="G247" t="s">
         <v>30</v>
@@ -13923,7 +13920,7 @@
         <v>146</v>
       </c>
       <c r="M247" s="6" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="248" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -13937,13 +13934,13 @@
         <v>247</v>
       </c>
       <c r="D248" s="32" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="E248" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F248" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="G248" t="s">
         <v>18</v>
@@ -13964,7 +13961,7 @@
         <v>146</v>
       </c>
       <c r="M248" s="6" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="249" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -13978,13 +13975,13 @@
         <v>248</v>
       </c>
       <c r="D249" s="32" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E249" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F249" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="G249" t="s">
         <v>18</v>
@@ -14005,7 +14002,7 @@
         <v>146</v>
       </c>
       <c r="M249" s="6" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="250" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -14019,19 +14016,19 @@
         <v>249</v>
       </c>
       <c r="D250" s="32" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E250" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F250" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="G250" t="s">
         <v>18</v>
       </c>
       <c r="H250" s="6" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="I250" s="6" t="s">
         <v>20</v>
@@ -14046,7 +14043,7 @@
         <v>146</v>
       </c>
       <c r="M250" s="6" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="251" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -14060,13 +14057,13 @@
         <v>250</v>
       </c>
       <c r="D251" s="32" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="E251" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F251" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="G251" t="s">
         <v>30</v>
@@ -14078,7 +14075,7 @@
         <v>31</v>
       </c>
       <c r="J251" s="6" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="K251" s="6" t="s">
         <v>163</v>
@@ -14087,7 +14084,7 @@
         <v>146</v>
       </c>
       <c r="M251" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="252" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -14101,13 +14098,13 @@
         <v>251</v>
       </c>
       <c r="D252" s="32" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="E252" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F252" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G252" t="s">
         <v>18</v>
@@ -14128,7 +14125,7 @@
         <v>146</v>
       </c>
       <c r="M252" s="6" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="253" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -14142,13 +14139,13 @@
         <v>252</v>
       </c>
       <c r="D253" s="32" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="E253" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F253" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="G253" t="s">
         <v>30</v>
@@ -14169,7 +14166,7 @@
         <v>146</v>
       </c>
       <c r="M253" s="6" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="254" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -14183,13 +14180,13 @@
         <v>253</v>
       </c>
       <c r="D254" s="32" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="E254" s="6" t="s">
         <v>444</v>
       </c>
       <c r="F254" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="G254" t="s">
         <v>18</v>
@@ -14210,7 +14207,7 @@
         <v>146</v>
       </c>
       <c r="M254" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="255" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -14224,13 +14221,13 @@
         <v>254</v>
       </c>
       <c r="D255" s="32" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="E255" s="6" t="s">
         <v>444</v>
       </c>
       <c r="F255" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="G255" t="s">
         <v>18</v>
@@ -14251,7 +14248,7 @@
         <v>146</v>
       </c>
       <c r="M255" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="256" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -14265,13 +14262,13 @@
         <v>255</v>
       </c>
       <c r="D256" s="32" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E256" s="6" t="s">
         <v>444</v>
       </c>
       <c r="F256" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="G256" t="s">
         <v>18</v>
@@ -14292,7 +14289,7 @@
         <v>146</v>
       </c>
       <c r="M256" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="257" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -14306,13 +14303,13 @@
         <v>256</v>
       </c>
       <c r="D257" s="32" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E257" s="6" t="s">
         <v>444</v>
       </c>
       <c r="F257" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="G257" t="s">
         <v>18</v>
@@ -14333,7 +14330,7 @@
         <v>146</v>
       </c>
       <c r="M257" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="258" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -14347,19 +14344,19 @@
         <v>257</v>
       </c>
       <c r="D258" s="32" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E258" s="6" t="s">
         <v>444</v>
       </c>
       <c r="F258" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="G258" t="s">
         <v>18</v>
       </c>
       <c r="H258" s="6" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="I258" s="6" t="s">
         <v>20</v>
@@ -14374,7 +14371,7 @@
         <v>146</v>
       </c>
       <c r="M258" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="259" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -14388,13 +14385,13 @@
         <v>258</v>
       </c>
       <c r="D259" s="32" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="E259" s="6" t="s">
         <v>444</v>
       </c>
       <c r="F259" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="G259" t="s">
         <v>18</v>
@@ -14415,7 +14412,7 @@
         <v>146</v>
       </c>
       <c r="M259" s="32" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="260" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -14429,13 +14426,13 @@
         <v>259</v>
       </c>
       <c r="D260" s="32" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E260" s="6" t="s">
         <v>444</v>
       </c>
       <c r="F260" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="G260" t="s">
         <v>18</v>
@@ -14456,7 +14453,7 @@
         <v>146</v>
       </c>
       <c r="M260" s="6" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="261" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -14470,13 +14467,13 @@
         <v>260</v>
       </c>
       <c r="D261" s="32" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E261" s="6" t="s">
         <v>444</v>
       </c>
       <c r="F261" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="G261" t="s">
         <v>18</v>
@@ -14497,7 +14494,7 @@
         <v>146</v>
       </c>
       <c r="M261" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="262" spans="1:13" x14ac:dyDescent="0.35">
@@ -14511,13 +14508,13 @@
         <v>261</v>
       </c>
       <c r="D262" s="25" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E262" t="s">
         <v>116</v>
       </c>
       <c r="F262" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="G262" s="25" t="s">
         <v>18</v>
@@ -14535,7 +14532,7 @@
         <v>146</v>
       </c>
       <c r="M262" s="18" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="263" spans="1:13" x14ac:dyDescent="0.35">
@@ -14549,13 +14546,13 @@
         <v>262</v>
       </c>
       <c r="D263" s="25" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E263" t="s">
         <v>116</v>
       </c>
       <c r="F263" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="G263" s="25" t="s">
         <v>18</v>
@@ -14573,7 +14570,7 @@
         <v>146</v>
       </c>
       <c r="M263" s="18" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="264" spans="1:13" x14ac:dyDescent="0.35">
@@ -14587,13 +14584,13 @@
         <v>263</v>
       </c>
       <c r="D264" s="25" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E264" t="s">
         <v>116</v>
       </c>
       <c r="F264" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="G264" s="25" t="s">
         <v>18</v>
@@ -14611,7 +14608,7 @@
         <v>146</v>
       </c>
       <c r="M264" s="18" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="265" spans="1:13" x14ac:dyDescent="0.35">
@@ -14625,13 +14622,13 @@
         <v>264</v>
       </c>
       <c r="D265" s="25" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E265" t="s">
         <v>116</v>
       </c>
       <c r="F265" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="G265" s="25" t="s">
         <v>18</v>
@@ -14649,7 +14646,7 @@
         <v>146</v>
       </c>
       <c r="M265" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="266" spans="1:13" x14ac:dyDescent="0.35">
@@ -14663,13 +14660,13 @@
         <v>265</v>
       </c>
       <c r="D266" s="25" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E266" t="s">
         <v>116</v>
       </c>
       <c r="F266" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G266" s="25" t="s">
         <v>18</v>
@@ -14687,7 +14684,7 @@
         <v>146</v>
       </c>
       <c r="M266" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="267" spans="1:13" x14ac:dyDescent="0.35">
@@ -14701,13 +14698,13 @@
         <v>266</v>
       </c>
       <c r="D267" s="25" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E267" t="s">
         <v>116</v>
       </c>
       <c r="F267" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G267" s="25" t="s">
         <v>18</v>
@@ -14725,7 +14722,7 @@
         <v>146</v>
       </c>
       <c r="M267" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="268" spans="1:13" x14ac:dyDescent="0.35">
@@ -14739,13 +14736,13 @@
         <v>267</v>
       </c>
       <c r="D268" s="25" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E268" t="s">
         <v>116</v>
       </c>
       <c r="F268" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="G268" s="25" t="s">
         <v>18</v>
@@ -14757,13 +14754,13 @@
         <v>226</v>
       </c>
       <c r="J268" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="L268" t="s">
         <v>146</v>
       </c>
       <c r="M268" s="18" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="269" spans="1:13" x14ac:dyDescent="0.35">
@@ -14777,13 +14774,13 @@
         <v>268</v>
       </c>
       <c r="D269" s="25" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="E269" t="s">
         <v>116</v>
       </c>
       <c r="F269" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="G269" s="25" t="s">
         <v>18</v>
@@ -14795,13 +14792,13 @@
         <v>226</v>
       </c>
       <c r="J269" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="L269" t="s">
         <v>146</v>
       </c>
       <c r="M269" s="18" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="270" spans="1:13" x14ac:dyDescent="0.35">
@@ -14815,13 +14812,13 @@
         <v>269</v>
       </c>
       <c r="D270" s="25" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="E270" t="s">
         <v>116</v>
       </c>
       <c r="F270" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G270" s="25" t="s">
         <v>18</v>
@@ -14836,7 +14833,7 @@
         <v>146</v>
       </c>
       <c r="M270" s="18" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="271" spans="1:13" x14ac:dyDescent="0.35">
@@ -14850,13 +14847,13 @@
         <v>270</v>
       </c>
       <c r="D271" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E271" t="s">
         <v>116</v>
       </c>
       <c r="F271" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G271" s="25" t="s">
         <v>30</v>
@@ -14871,7 +14868,7 @@
         <v>146</v>
       </c>
       <c r="M271" s="18" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="272" spans="1:13" x14ac:dyDescent="0.35">
@@ -14891,7 +14888,7 @@
         <v>266</v>
       </c>
       <c r="F272" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="G272" s="33" t="s">
         <v>18</v>
@@ -14929,7 +14926,7 @@
         <v>266</v>
       </c>
       <c r="F273" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="G273" s="33" t="s">
         <v>18</v>
@@ -14967,7 +14964,7 @@
         <v>266</v>
       </c>
       <c r="F274" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G274" s="33" t="s">
         <v>18</v>
@@ -14999,13 +14996,13 @@
         <v>274</v>
       </c>
       <c r="D275" s="6" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E275" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F275" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="G275" s="6" t="s">
         <v>18</v>
@@ -15023,7 +15020,7 @@
         <v>146</v>
       </c>
       <c r="M275" s="6" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="276" spans="1:13" x14ac:dyDescent="0.35">
@@ -15037,13 +15034,13 @@
         <v>275</v>
       </c>
       <c r="D276" s="6" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E276" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F276" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="G276" s="6" t="s">
         <v>18</v>
@@ -15061,7 +15058,7 @@
         <v>146</v>
       </c>
       <c r="M276" s="6" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="277" spans="1:13" x14ac:dyDescent="0.35">
@@ -15075,13 +15072,13 @@
         <v>276</v>
       </c>
       <c r="D277" s="6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="E277" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F277" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="G277" s="17" t="s">
         <v>30</v>
@@ -15099,7 +15096,7 @@
         <v>146</v>
       </c>
       <c r="M277" s="6" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="278" spans="1:13" x14ac:dyDescent="0.35">
@@ -15113,13 +15110,13 @@
         <v>277</v>
       </c>
       <c r="D278" s="6" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="E278" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F278" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="G278" s="6" t="s">
         <v>18</v>
@@ -15131,13 +15128,13 @@
         <v>20</v>
       </c>
       <c r="J278" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L278" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M278" s="6" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="279" spans="1:13" x14ac:dyDescent="0.35">
@@ -15151,13 +15148,13 @@
         <v>278</v>
       </c>
       <c r="D279" s="6" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E279" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F279" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="G279" s="6" t="s">
         <v>18</v>
@@ -15169,13 +15166,13 @@
         <v>20</v>
       </c>
       <c r="J279" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L279" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M279" s="6" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="280" spans="1:13" x14ac:dyDescent="0.35">
@@ -15189,13 +15186,13 @@
         <v>279</v>
       </c>
       <c r="D280" s="6" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="E280" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F280" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="G280" s="6" t="s">
         <v>18</v>
@@ -15207,13 +15204,13 @@
         <v>20</v>
       </c>
       <c r="J280" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L280" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M280" s="6" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="281" spans="1:13" x14ac:dyDescent="0.35">
@@ -15227,13 +15224,13 @@
         <v>280</v>
       </c>
       <c r="D281" s="6" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E281" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F281" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="G281" s="17" t="s">
         <v>30</v>
@@ -15245,13 +15242,13 @@
         <v>144</v>
       </c>
       <c r="J281" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L281" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M281" s="6" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="282" spans="1:13" x14ac:dyDescent="0.35">
@@ -15265,13 +15262,13 @@
         <v>281</v>
       </c>
       <c r="D282" s="6" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E282" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F282" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="G282" s="17" t="s">
         <v>30</v>
@@ -15283,13 +15280,13 @@
         <v>144</v>
       </c>
       <c r="J282" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L282" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M282" s="6" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="283" spans="1:13" x14ac:dyDescent="0.35">
@@ -15303,13 +15300,13 @@
         <v>282</v>
       </c>
       <c r="D283" s="6" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="E283" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F283" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="G283" s="17" t="s">
         <v>30</v>
@@ -15321,13 +15318,13 @@
         <v>144</v>
       </c>
       <c r="J283" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L283" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M283" s="6" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="284" spans="1:13" x14ac:dyDescent="0.35">
@@ -15341,13 +15338,13 @@
         <v>283</v>
       </c>
       <c r="D284" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="E284" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F284" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="G284" s="17" t="s">
         <v>30</v>
@@ -15359,13 +15356,13 @@
         <v>144</v>
       </c>
       <c r="J284" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L284" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M284" s="6" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="285" spans="1:13" x14ac:dyDescent="0.35">
@@ -15379,13 +15376,13 @@
         <v>284</v>
       </c>
       <c r="D285" s="6" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="E285" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F285" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="G285" s="17" t="s">
         <v>30</v>
@@ -15397,13 +15394,13 @@
         <v>144</v>
       </c>
       <c r="J285" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L285" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M285" s="6" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="286" spans="1:13" x14ac:dyDescent="0.35">
@@ -15417,13 +15414,13 @@
         <v>285</v>
       </c>
       <c r="D286" s="6" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E286" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F286" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G286" s="17" t="s">
         <v>30</v>
@@ -15435,13 +15432,13 @@
         <v>144</v>
       </c>
       <c r="J286" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L286" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M286" s="6" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="287" spans="1:13" x14ac:dyDescent="0.35">
@@ -15455,13 +15452,13 @@
         <v>286</v>
       </c>
       <c r="D287" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E287" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F287" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="G287" s="17" t="s">
         <v>30</v>
@@ -15473,13 +15470,13 @@
         <v>144</v>
       </c>
       <c r="J287" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L287" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M287" s="6" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="288" spans="1:13" x14ac:dyDescent="0.35">
@@ -15499,7 +15496,7 @@
         <v>266</v>
       </c>
       <c r="F288" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="G288" s="6" t="s">
         <v>18</v>
@@ -15511,13 +15508,13 @@
         <v>20</v>
       </c>
       <c r="J288" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L288" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M288" s="6" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="289" spans="1:13" x14ac:dyDescent="0.35">
@@ -15537,7 +15534,7 @@
         <v>266</v>
       </c>
       <c r="F289" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G289" s="6" t="s">
         <v>18</v>
@@ -15549,13 +15546,13 @@
         <v>20</v>
       </c>
       <c r="J289" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L289" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M289" s="6" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="290" spans="1:13" x14ac:dyDescent="0.35">
@@ -15569,13 +15566,13 @@
         <v>289</v>
       </c>
       <c r="D290" s="6" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="E290" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F290" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="G290" s="17" t="s">
         <v>30</v>
@@ -15587,13 +15584,13 @@
         <v>144</v>
       </c>
       <c r="J290" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L290" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M290" s="6" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="291" spans="1:13" x14ac:dyDescent="0.35">
@@ -15607,13 +15604,13 @@
         <v>290</v>
       </c>
       <c r="D291" s="17" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E291" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F291" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="G291" s="6" t="s">
         <v>18</v>
@@ -15625,13 +15622,13 @@
         <v>20</v>
       </c>
       <c r="J291" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L291" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M291" s="6" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="292" spans="1:13" x14ac:dyDescent="0.35">
@@ -15648,10 +15645,10 @@
         <v>265</v>
       </c>
       <c r="E292" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F292" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="G292" s="6" t="s">
         <v>18</v>
@@ -15663,13 +15660,13 @@
         <v>20</v>
       </c>
       <c r="J292" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L292" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M292" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="293" spans="1:13" x14ac:dyDescent="0.35">
@@ -15683,13 +15680,13 @@
         <v>292</v>
       </c>
       <c r="D293" s="17" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="E293" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F293" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="G293" s="6" t="s">
         <v>18</v>
@@ -15701,13 +15698,13 @@
         <v>20</v>
       </c>
       <c r="J293" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L293" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M293" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="294" spans="1:13" x14ac:dyDescent="0.35">
@@ -15721,16 +15718,16 @@
         <v>293</v>
       </c>
       <c r="D294" s="6" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="E294" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F294" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="G294" s="6" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H294" s="6" t="s">
         <v>143</v>
@@ -15739,13 +15736,13 @@
         <v>20</v>
       </c>
       <c r="J294" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L294" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M294" s="6" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="295" spans="1:13" x14ac:dyDescent="0.35">
@@ -15759,13 +15756,13 @@
         <v>294</v>
       </c>
       <c r="D295" s="6" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="E295" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F295" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="G295" s="6" t="s">
         <v>18</v>
@@ -15777,13 +15774,13 @@
         <v>20</v>
       </c>
       <c r="J295" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L295" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M295" s="6" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="296" spans="1:13" x14ac:dyDescent="0.35">
@@ -15797,13 +15794,13 @@
         <v>295</v>
       </c>
       <c r="D296" s="6" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="E296" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F296" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="G296" s="6" t="s">
         <v>18</v>
@@ -15815,13 +15812,13 @@
         <v>20</v>
       </c>
       <c r="J296" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L296" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M296" s="6" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="297" spans="1:13" x14ac:dyDescent="0.35">
@@ -15841,7 +15838,7 @@
         <v>266</v>
       </c>
       <c r="F297" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="G297" s="6" t="s">
         <v>18</v>
@@ -15853,13 +15850,13 @@
         <v>20</v>
       </c>
       <c r="J297" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L297" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M297" s="6" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="298" spans="1:13" x14ac:dyDescent="0.35">
@@ -15873,13 +15870,13 @@
         <v>297</v>
       </c>
       <c r="D298" s="6" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="E298" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F298" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="G298" s="6" t="s">
         <v>18</v>
@@ -15891,13 +15888,13 @@
         <v>20</v>
       </c>
       <c r="J298" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L298" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M298" s="6" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="299" spans="1:13" x14ac:dyDescent="0.35">
@@ -15911,13 +15908,13 @@
         <v>298</v>
       </c>
       <c r="D299" s="6" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E299" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F299" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="G299" s="6" t="s">
         <v>18</v>
@@ -15929,13 +15926,13 @@
         <v>20</v>
       </c>
       <c r="J299" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L299" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M299" s="6" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="300" spans="1:13" x14ac:dyDescent="0.35">
@@ -15949,13 +15946,13 @@
         <v>299</v>
       </c>
       <c r="D300" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="E300" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F300" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G300" s="6" t="s">
         <v>18</v>
@@ -15967,13 +15964,13 @@
         <v>20</v>
       </c>
       <c r="J300" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L300" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M300" s="6" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="301" spans="1:13" x14ac:dyDescent="0.35">
@@ -15987,13 +15984,13 @@
         <v>300</v>
       </c>
       <c r="D301" s="17" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="E301" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F301" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="G301" s="17" t="s">
         <v>30</v>
@@ -16005,13 +16002,13 @@
         <v>144</v>
       </c>
       <c r="J301" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L301" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M301" s="17" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="302" spans="1:13" x14ac:dyDescent="0.35">
@@ -16025,13 +16022,13 @@
         <v>301</v>
       </c>
       <c r="D302" s="6" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E302" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F302" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G302" s="17" t="s">
         <v>30</v>
@@ -16043,13 +16040,13 @@
         <v>144</v>
       </c>
       <c r="J302" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L302" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M302" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="303" spans="1:13" x14ac:dyDescent="0.35">
@@ -16063,13 +16060,13 @@
         <v>302</v>
       </c>
       <c r="D303" s="6" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="E303" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F303" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="G303" s="17" t="s">
         <v>30</v>
@@ -16081,13 +16078,13 @@
         <v>144</v>
       </c>
       <c r="J303" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L303" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M303" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="304" spans="1:13" x14ac:dyDescent="0.35">
@@ -16101,13 +16098,13 @@
         <v>303</v>
       </c>
       <c r="D304" s="6" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="E304" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F304" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="G304" s="17" t="s">
         <v>30</v>
@@ -16119,13 +16116,13 @@
         <v>144</v>
       </c>
       <c r="J304" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L304" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M304" s="6" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="305" spans="1:13" x14ac:dyDescent="0.35">
@@ -16139,16 +16136,16 @@
         <v>304</v>
       </c>
       <c r="D305" s="6" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="E305" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F305" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G305" s="6" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H305" s="6" t="s">
         <v>143</v>
@@ -16157,13 +16154,13 @@
         <v>20</v>
       </c>
       <c r="J305" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L305" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M305" s="6" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="306" spans="1:13" x14ac:dyDescent="0.35">
@@ -16177,13 +16174,13 @@
         <v>305</v>
       </c>
       <c r="D306" s="6" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="E306" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F306" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="G306" s="6" t="s">
         <v>18</v>
@@ -16201,7 +16198,7 @@
         <v>146</v>
       </c>
       <c r="M306" s="6" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="307" spans="1:13" x14ac:dyDescent="0.35">
@@ -16215,13 +16212,13 @@
         <v>306</v>
       </c>
       <c r="D307" s="6" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E307" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F307" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="G307" s="17" t="s">
         <v>30</v>
@@ -16233,13 +16230,13 @@
         <v>144</v>
       </c>
       <c r="J307" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L307" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M307" s="6" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="308" spans="1:13" x14ac:dyDescent="0.35">
@@ -16250,13 +16247,13 @@
         <v>307</v>
       </c>
       <c r="D308" s="34" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="E308" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F308" t="s">
-        <v>1004</v>
+        <v>996</v>
       </c>
       <c r="G308" s="36" t="s">
         <v>18</v>
@@ -16268,7 +16265,7 @@
         <v>20</v>
       </c>
       <c r="M308" s="34" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="309" spans="1:13" x14ac:dyDescent="0.35">
@@ -16279,13 +16276,13 @@
         <v>308</v>
       </c>
       <c r="D309" s="34" t="s">
-        <v>1008</v>
+        <v>998</v>
       </c>
       <c r="E309" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F309" t="s">
-        <v>1009</v>
+        <v>999</v>
       </c>
       <c r="G309" s="36" t="s">
         <v>192</v>
@@ -16297,7 +16294,7 @@
         <v>144</v>
       </c>
       <c r="M309" s="34" t="s">
-        <v>1010</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="310" spans="1:13" x14ac:dyDescent="0.35">
@@ -16308,13 +16305,13 @@
         <v>309</v>
       </c>
       <c r="D310" s="35" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="E310" s="38" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F310" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="G310" s="38" t="s">
         <v>18</v>
@@ -16326,7 +16323,7 @@
         <v>20</v>
       </c>
       <c r="M310" s="35" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="311" spans="1:13" x14ac:dyDescent="0.35">
@@ -16337,13 +16334,13 @@
         <v>310</v>
       </c>
       <c r="D311" s="34" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="E311" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F311" t="s">
-        <v>1005</v>
+        <v>997</v>
       </c>
       <c r="G311" s="36" t="s">
         <v>18</v>
@@ -16355,7 +16352,7 @@
         <v>20</v>
       </c>
       <c r="M311" s="34" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="312" spans="1:13" x14ac:dyDescent="0.35">
@@ -16366,13 +16363,13 @@
         <v>311</v>
       </c>
       <c r="D312" s="35" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="E312" s="38" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F312" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="G312" s="38" t="s">
         <v>18</v>
@@ -16384,7 +16381,7 @@
         <v>20</v>
       </c>
       <c r="M312" s="35" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="313" spans="1:13" x14ac:dyDescent="0.35">
@@ -16395,13 +16392,13 @@
         <v>312</v>
       </c>
       <c r="D313" s="34" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E313" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F313" t="s">
-        <v>992</v>
+        <v>1004</v>
       </c>
       <c r="G313" s="36" t="s">
         <v>18</v>
@@ -16413,7 +16410,7 @@
         <v>20</v>
       </c>
       <c r="M313" s="34" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="314" spans="1:13" x14ac:dyDescent="0.35">
@@ -16424,13 +16421,13 @@
         <v>313</v>
       </c>
       <c r="D314" s="35" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E314" s="38" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F314" t="s">
-        <v>993</v>
+        <v>1005</v>
       </c>
       <c r="G314" s="38" t="s">
         <v>18</v>
@@ -16442,7 +16439,7 @@
         <v>20</v>
       </c>
       <c r="M314" s="35" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="315" spans="1:13" x14ac:dyDescent="0.35">
@@ -16453,13 +16450,13 @@
         <v>314</v>
       </c>
       <c r="D315" s="34" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E315" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F315" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
       <c r="G315" s="36" t="s">
         <v>18</v>
@@ -16471,7 +16468,7 @@
         <v>20</v>
       </c>
       <c r="M315" s="34" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="316" spans="1:13" x14ac:dyDescent="0.35">
@@ -16482,13 +16479,13 @@
         <v>315</v>
       </c>
       <c r="D316" s="35" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E316" s="38" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F316" t="s">
-        <v>995</v>
+        <v>1007</v>
       </c>
       <c r="G316" s="38" t="s">
         <v>18</v>
@@ -16500,7 +16497,7 @@
         <v>20</v>
       </c>
       <c r="M316" s="35" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="317" spans="1:13" x14ac:dyDescent="0.35">
@@ -16511,13 +16508,13 @@
         <v>316</v>
       </c>
       <c r="D317" s="34" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E317" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F317" t="s">
-        <v>996</v>
+        <v>1008</v>
       </c>
       <c r="G317" s="36" t="s">
         <v>18</v>
@@ -16529,7 +16526,7 @@
         <v>20</v>
       </c>
       <c r="M317" s="34" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="318" spans="1:13" x14ac:dyDescent="0.35">
@@ -16540,13 +16537,13 @@
         <v>317</v>
       </c>
       <c r="D318" s="35" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E318" s="38" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F318" t="s">
-        <v>997</v>
+        <v>1009</v>
       </c>
       <c r="G318" s="38" t="s">
         <v>18</v>
@@ -16558,7 +16555,7 @@
         <v>20</v>
       </c>
       <c r="M318" s="35" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="319" spans="1:13" x14ac:dyDescent="0.35">
@@ -16569,13 +16566,13 @@
         <v>318</v>
       </c>
       <c r="D319" s="34" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="E319" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F319" t="s">
-        <v>998</v>
+        <v>1010</v>
       </c>
       <c r="G319" s="36" t="s">
         <v>30</v>
@@ -16587,7 +16584,7 @@
         <v>144</v>
       </c>
       <c r="M319" s="34" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="320" spans="1:13" x14ac:dyDescent="0.35">
@@ -16601,22 +16598,22 @@
         <v>288</v>
       </c>
       <c r="E320" s="38" t="s">
+        <v>990</v>
+      </c>
+      <c r="F320" t="s">
         <v>991</v>
       </c>
-      <c r="F320" t="s">
-        <v>999</v>
-      </c>
       <c r="G320" s="38" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H320" s="39" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="I320" s="38" t="s">
         <v>20</v>
       </c>
       <c r="M320" s="35" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="321" spans="1:13" x14ac:dyDescent="0.35">
@@ -16627,13 +16624,13 @@
         <v>320</v>
       </c>
       <c r="D321" s="34" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E321" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F321" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
       <c r="G321" s="36" t="s">
         <v>18</v>
@@ -16645,7 +16642,7 @@
         <v>20</v>
       </c>
       <c r="M321" s="34" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="322" spans="1:13" x14ac:dyDescent="0.35">
@@ -16656,13 +16653,13 @@
         <v>321</v>
       </c>
       <c r="D322" s="35" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E322" s="38" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F322" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="G322" s="38" t="s">
         <v>30</v>
@@ -16674,7 +16671,7 @@
         <v>144</v>
       </c>
       <c r="M322" s="35" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="323" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -16685,25 +16682,25 @@
         <v>322</v>
       </c>
       <c r="D323" s="34" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="E323" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F323" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="G323" s="38" t="s">
         <v>30</v>
       </c>
       <c r="H323" s="37" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="I323" s="36" t="s">
         <v>144</v>
       </c>
       <c r="M323" s="34" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="324" spans="1:13" x14ac:dyDescent="0.35">
@@ -16714,13 +16711,13 @@
         <v>323</v>
       </c>
       <c r="D324" s="35" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E324" s="38" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F324" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="G324" s="38" t="s">
         <v>30</v>
@@ -16732,7 +16729,7 @@
         <v>144</v>
       </c>
       <c r="M324" s="35" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="325" spans="1:13" x14ac:dyDescent="0.35">
@@ -16743,13 +16740,13 @@
         <v>324</v>
       </c>
       <c r="D325" s="34" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="E325" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F325" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="G325" s="38" t="s">
         <v>30</v>
@@ -16761,7 +16758,7 @@
         <v>144</v>
       </c>
       <c r="M325" s="34" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="326" spans="1:13" x14ac:dyDescent="0.35">
@@ -16772,13 +16769,13 @@
         <v>325</v>
       </c>
       <c r="D326" s="35" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E326" s="38" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F326" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="G326" s="38" t="s">
         <v>30</v>
@@ -16790,7 +16787,7 @@
         <v>144</v>
       </c>
       <c r="M326" s="35" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="327" spans="1:13" x14ac:dyDescent="0.35">
@@ -16801,13 +16798,13 @@
         <v>326</v>
       </c>
       <c r="D327" s="34" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E327" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F327" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="G327" s="38" t="s">
         <v>30</v>
@@ -16819,7 +16816,7 @@
         <v>144</v>
       </c>
       <c r="M327" s="34" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="328" spans="1:13" x14ac:dyDescent="0.35">
@@ -16830,13 +16827,13 @@
         <v>327</v>
       </c>
       <c r="D328" s="35" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E328" s="38" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F328" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="G328" s="38" t="s">
         <v>30</v>
@@ -16848,7 +16845,7 @@
         <v>144</v>
       </c>
       <c r="M328" s="35" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="329" spans="1:13" x14ac:dyDescent="0.35">
@@ -16859,13 +16856,13 @@
         <v>328</v>
       </c>
       <c r="D329" s="34" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E329" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F329" t="s">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="G329" s="38" t="s">
         <v>30</v>
@@ -16877,7 +16874,7 @@
         <v>144</v>
       </c>
       <c r="M329" s="34" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="330" spans="1:13" x14ac:dyDescent="0.35">
@@ -16888,13 +16885,13 @@
         <v>329</v>
       </c>
       <c r="D330" s="34" t="s">
-        <v>1012</v>
+        <v>1001</v>
       </c>
       <c r="E330" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F330" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="G330" s="6" t="s">
         <v>30</v>
@@ -16923,10 +16920,10 @@
         <v>148</v>
       </c>
       <c r="E331" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F331" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="G331" t="s">
         <v>30</v>
@@ -17025,13 +17022,13 @@
         <v>196</v>
       </c>
       <c r="D2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E2" t="s">
         <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G2" t="s">
         <v>18</v>
@@ -17052,7 +17049,7 @@
         <v>146</v>
       </c>
       <c r="M2" s="19" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -17066,13 +17063,13 @@
         <v>197</v>
       </c>
       <c r="D3" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E3" t="s">
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G3" t="s">
         <v>18</v>
@@ -17093,7 +17090,7 @@
         <v>146</v>
       </c>
       <c r="M3" s="19" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -17107,13 +17104,13 @@
         <v>198</v>
       </c>
       <c r="D4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G4" t="s">
         <v>18</v>
@@ -17134,7 +17131,7 @@
         <v>146</v>
       </c>
       <c r="M4" s="19" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -17148,13 +17145,13 @@
         <v>199</v>
       </c>
       <c r="D5" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E5" t="s">
         <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G5" t="s">
         <v>18</v>
@@ -17175,7 +17172,7 @@
         <v>146</v>
       </c>
       <c r="M5" s="19" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -17189,19 +17186,19 @@
         <v>200</v>
       </c>
       <c r="D6" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E6" t="s">
         <v>16</v>
       </c>
       <c r="F6" t="s">
+        <v>631</v>
+      </c>
+      <c r="G6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" t="s">
         <v>632</v>
-      </c>
-      <c r="G6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" t="s">
-        <v>633</v>
       </c>
       <c r="I6" t="s">
         <v>144</v>
@@ -17216,7 +17213,7 @@
         <v>146</v>
       </c>
       <c r="M6" s="18" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
   </sheetData>
@@ -17294,13 +17291,13 @@
         <v>201</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E2" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G2" s="17" t="s">
         <v>192</v>
@@ -17321,7 +17318,7 @@
         <v>146</v>
       </c>
       <c r="M2" s="17" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -17335,13 +17332,13 @@
         <v>202</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E3" s="17" t="s">
         <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G3" s="17" t="s">
         <v>30</v>
@@ -17362,7 +17359,7 @@
         <v>146</v>
       </c>
       <c r="M3" s="17" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -17376,13 +17373,13 @@
         <v>203</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E4" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G4" s="17" t="s">
         <v>18</v>
@@ -17403,7 +17400,7 @@
         <v>146</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -17417,13 +17414,13 @@
         <v>204</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G5" s="17" t="s">
         <v>18</v>
@@ -17444,7 +17441,7 @@
         <v>146</v>
       </c>
       <c r="M5" s="17" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -17458,13 +17455,13 @@
         <v>205</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G6" s="17" t="s">
         <v>18</v>
@@ -17485,7 +17482,7 @@
         <v>146</v>
       </c>
       <c r="M6" s="17" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -17499,13 +17496,13 @@
         <v>206</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>444</v>
       </c>
       <c r="F7" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G7" s="17" t="s">
         <v>18</v>
@@ -17526,7 +17523,7 @@
         <v>254</v>
       </c>
       <c r="M7" s="17" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -17540,13 +17537,13 @@
         <v>207</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G8" s="17" t="s">
         <v>18</v>
@@ -17567,7 +17564,7 @@
         <v>146</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -17581,13 +17578,13 @@
         <v>208</v>
       </c>
       <c r="D9" s="17" t="s">
+        <v>655</v>
+      </c>
+      <c r="E9" s="17" t="s">
         <v>656</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="F9" t="s">
         <v>657</v>
-      </c>
-      <c r="F9" t="s">
-        <v>658</v>
       </c>
       <c r="G9" s="17" t="s">
         <v>30</v>
@@ -17599,7 +17596,7 @@
         <v>31</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K9" s="17" t="s">
         <v>163</v>
@@ -17608,7 +17605,7 @@
         <v>146</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
@@ -17622,13 +17619,13 @@
         <v>209</v>
       </c>
       <c r="D10" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F10" t="s">
         <v>661</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F10" t="s">
-        <v>662</v>
       </c>
       <c r="G10" s="17" t="s">
         <v>30</v>
@@ -17640,7 +17637,7 @@
         <v>20</v>
       </c>
       <c r="J10" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K10" s="17" t="s">
         <v>163</v>
@@ -17649,7 +17646,7 @@
         <v>146</v>
       </c>
       <c r="M10" s="17" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -17663,13 +17660,13 @@
         <v>210</v>
       </c>
       <c r="D11" s="17" t="s">
+        <v>663</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F11" t="s">
         <v>664</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F11" t="s">
-        <v>665</v>
       </c>
       <c r="G11" s="17" t="s">
         <v>30</v>
@@ -17681,7 +17678,7 @@
         <v>31</v>
       </c>
       <c r="J11" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K11" s="17" t="s">
         <v>163</v>
@@ -17690,7 +17687,7 @@
         <v>146</v>
       </c>
       <c r="M11" s="17" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -17704,13 +17701,13 @@
         <v>211</v>
       </c>
       <c r="D12" s="17" t="s">
+        <v>666</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F12" t="s">
         <v>667</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F12" t="s">
-        <v>668</v>
       </c>
       <c r="G12" s="17" t="s">
         <v>30</v>
@@ -17722,7 +17719,7 @@
         <v>31</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K12" s="17" t="s">
         <v>163</v>
@@ -17731,7 +17728,7 @@
         <v>146</v>
       </c>
       <c r="M12" s="17" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -17745,13 +17742,13 @@
         <v>212</v>
       </c>
       <c r="D13" s="17" t="s">
+        <v>669</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F13" t="s">
         <v>670</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F13" t="s">
-        <v>671</v>
       </c>
       <c r="G13" s="17" t="s">
         <v>30</v>
@@ -17763,7 +17760,7 @@
         <v>31</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K13" s="17" t="s">
         <v>163</v>
@@ -17772,7 +17769,7 @@
         <v>146</v>
       </c>
       <c r="M13" s="17" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -17786,13 +17783,13 @@
         <v>213</v>
       </c>
       <c r="D14" s="17" t="s">
+        <v>672</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F14" t="s">
         <v>673</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F14" t="s">
-        <v>674</v>
       </c>
       <c r="G14" s="17" t="s">
         <v>30</v>
@@ -17804,7 +17801,7 @@
         <v>31</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>163</v>
@@ -17813,7 +17810,7 @@
         <v>146</v>
       </c>
       <c r="M14" s="17" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -17827,13 +17824,13 @@
         <v>214</v>
       </c>
       <c r="D15" s="17" t="s">
+        <v>675</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F15" t="s">
         <v>676</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F15" t="s">
-        <v>677</v>
       </c>
       <c r="G15" s="17" t="s">
         <v>30</v>
@@ -17845,7 +17842,7 @@
         <v>31</v>
       </c>
       <c r="J15" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K15" s="17" t="s">
         <v>163</v>
@@ -17854,7 +17851,7 @@
         <v>146</v>
       </c>
       <c r="M15" s="17" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -17868,13 +17865,13 @@
         <v>215</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G16" s="17" t="s">
         <v>30</v>
@@ -17886,7 +17883,7 @@
         <v>31</v>
       </c>
       <c r="J16" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K16" s="17" t="s">
         <v>163</v>
@@ -17895,7 +17892,7 @@
         <v>146</v>
       </c>
       <c r="M16" s="17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
@@ -17909,13 +17906,13 @@
         <v>216</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>25</v>
       </c>
       <c r="F17" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="G17" s="17" t="s">
         <v>30</v>
@@ -17927,7 +17924,7 @@
         <v>31</v>
       </c>
       <c r="J17" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K17" s="17" t="s">
         <v>163</v>
@@ -17936,7 +17933,7 @@
         <v>146</v>
       </c>
       <c r="M17" s="17" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
@@ -17950,13 +17947,13 @@
         <v>217</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>25</v>
       </c>
       <c r="F18" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="G18" s="17" t="s">
         <v>30</v>
@@ -17968,7 +17965,7 @@
         <v>31</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K18" s="17" t="s">
         <v>163</v>
@@ -17977,7 +17974,7 @@
         <v>146</v>
       </c>
       <c r="M18" s="17" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
@@ -17991,13 +17988,13 @@
         <v>218</v>
       </c>
       <c r="D19" s="17" t="s">
+        <v>687</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F19" t="s">
         <v>688</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F19" t="s">
-        <v>689</v>
       </c>
       <c r="G19" s="17" t="s">
         <v>30</v>
@@ -18009,7 +18006,7 @@
         <v>31</v>
       </c>
       <c r="J19" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K19" s="17" t="s">
         <v>163</v>
@@ -18018,7 +18015,7 @@
         <v>146</v>
       </c>
       <c r="M19" s="17" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
@@ -18032,13 +18029,13 @@
         <v>219</v>
       </c>
       <c r="D20" s="17" t="s">
+        <v>690</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F20" t="s">
         <v>691</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F20" t="s">
-        <v>692</v>
       </c>
       <c r="G20" s="17" t="s">
         <v>30</v>
@@ -18050,7 +18047,7 @@
         <v>31</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K20" s="17" t="s">
         <v>163</v>
@@ -18059,7 +18056,7 @@
         <v>146</v>
       </c>
       <c r="M20" s="17" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
@@ -18073,13 +18070,13 @@
         <v>220</v>
       </c>
       <c r="D21" s="17" t="s">
+        <v>693</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F21" t="s">
         <v>694</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F21" t="s">
-        <v>695</v>
       </c>
       <c r="G21" s="17" t="s">
         <v>30</v>
@@ -18091,7 +18088,7 @@
         <v>31</v>
       </c>
       <c r="J21" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K21" s="17" t="s">
         <v>163</v>
@@ -18100,7 +18097,7 @@
         <v>146</v>
       </c>
       <c r="M21" s="17" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
@@ -18114,13 +18111,13 @@
         <v>221</v>
       </c>
       <c r="D22" s="17" t="s">
+        <v>696</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F22" t="s">
         <v>697</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F22" t="s">
-        <v>698</v>
       </c>
       <c r="G22" s="17" t="s">
         <v>30</v>
@@ -18132,7 +18129,7 @@
         <v>20</v>
       </c>
       <c r="J22" s="17" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="K22" s="17" t="s">
         <v>163</v>
@@ -18141,7 +18138,7 @@
         <v>146</v>
       </c>
       <c r="M22" s="17" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
@@ -18155,13 +18152,13 @@
         <v>222</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="F23" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G23" s="17" t="s">
         <v>30</v>
@@ -18173,7 +18170,7 @@
         <v>31</v>
       </c>
       <c r="J23" s="17" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="K23" s="17" t="s">
         <v>163</v>
@@ -18182,7 +18179,7 @@
         <v>146</v>
       </c>
       <c r="M23" s="17" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
@@ -18196,13 +18193,13 @@
         <v>223</v>
       </c>
       <c r="D24" s="17" t="s">
+        <v>702</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F24" t="s">
         <v>703</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F24" t="s">
-        <v>704</v>
       </c>
       <c r="G24" s="17" t="s">
         <v>30</v>
@@ -18214,7 +18211,7 @@
         <v>31</v>
       </c>
       <c r="J24" s="17" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="K24" s="17" t="s">
         <v>163</v>
@@ -18223,7 +18220,7 @@
         <v>146</v>
       </c>
       <c r="M24" s="17" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
@@ -18237,13 +18234,13 @@
         <v>224</v>
       </c>
       <c r="D25" s="17" t="s">
+        <v>705</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F25" t="s">
         <v>706</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F25" t="s">
-        <v>707</v>
       </c>
       <c r="G25" s="17" t="s">
         <v>30</v>
@@ -18255,7 +18252,7 @@
         <v>31</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="K25" s="17" t="s">
         <v>163</v>
@@ -18264,7 +18261,7 @@
         <v>146</v>
       </c>
       <c r="M25" s="17" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
@@ -18278,13 +18275,13 @@
         <v>225</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E26" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F26" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="G26" s="17" t="s">
         <v>192</v>
@@ -18305,7 +18302,7 @@
         <v>146</v>
       </c>
       <c r="M26" s="17" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
@@ -18319,13 +18316,13 @@
         <v>226</v>
       </c>
       <c r="D27" s="17" t="s">
+        <v>711</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F27" t="s">
         <v>712</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F27" t="s">
-        <v>713</v>
       </c>
       <c r="G27" s="17" t="s">
         <v>30</v>
@@ -18337,7 +18334,7 @@
         <v>31</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K27" s="17" t="s">
         <v>163</v>
@@ -18346,7 +18343,7 @@
         <v>146</v>
       </c>
       <c r="M27" s="17" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
@@ -18360,13 +18357,13 @@
         <v>227</v>
       </c>
       <c r="D28" s="17" t="s">
+        <v>714</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F28" t="s">
         <v>715</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F28" t="s">
-        <v>716</v>
       </c>
       <c r="G28" s="17" t="s">
         <v>192</v>
@@ -18378,7 +18375,7 @@
         <v>31</v>
       </c>
       <c r="J28" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K28" s="17" t="s">
         <v>163</v>
@@ -18387,7 +18384,7 @@
         <v>146</v>
       </c>
       <c r="M28" s="17" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
@@ -18401,13 +18398,13 @@
         <v>228</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>444</v>
       </c>
       <c r="F29" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="G29" s="17" t="s">
         <v>30</v>
@@ -18419,7 +18416,7 @@
         <v>31</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K29" s="17" t="s">
         <v>163</v>
@@ -18428,7 +18425,7 @@
         <v>254</v>
       </c>
       <c r="M29" s="17" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.35">
@@ -18442,13 +18439,13 @@
         <v>229</v>
       </c>
       <c r="D30" s="17" t="s">
+        <v>720</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F30" t="s">
         <v>721</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F30" t="s">
-        <v>722</v>
       </c>
       <c r="G30" s="17" t="s">
         <v>192</v>
@@ -18469,7 +18466,7 @@
         <v>146</v>
       </c>
       <c r="M30" s="17" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
@@ -18483,13 +18480,13 @@
         <v>230</v>
       </c>
       <c r="D31" s="17" t="s">
+        <v>723</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F31" t="s">
         <v>724</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F31" t="s">
-        <v>725</v>
       </c>
       <c r="G31" s="17" t="s">
         <v>30</v>
@@ -18510,7 +18507,7 @@
         <v>146</v>
       </c>
       <c r="M31" s="17" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.35">
@@ -18524,13 +18521,13 @@
         <v>231</v>
       </c>
       <c r="D32" s="17" t="s">
+        <v>726</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F32" t="s">
         <v>727</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F32" t="s">
-        <v>728</v>
       </c>
       <c r="G32" s="17" t="s">
         <v>30</v>
@@ -18542,7 +18539,7 @@
         <v>31</v>
       </c>
       <c r="J32" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K32" s="17" t="s">
         <v>163</v>
@@ -18551,7 +18548,7 @@
         <v>146</v>
       </c>
       <c r="M32" s="17" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.35">
@@ -18565,13 +18562,13 @@
         <v>232</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E33" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F33" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G33" s="17" t="s">
         <v>30</v>
@@ -18592,7 +18589,7 @@
         <v>254</v>
       </c>
       <c r="M33" s="17" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.35">
@@ -18606,13 +18603,13 @@
         <v>233</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E34" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F34" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="G34" s="17" t="s">
         <v>30</v>
@@ -18633,7 +18630,7 @@
         <v>254</v>
       </c>
       <c r="M34" s="17" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.35">
@@ -18647,13 +18644,13 @@
         <v>234</v>
       </c>
       <c r="D35" s="17" t="s">
+        <v>735</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F35" t="s">
         <v>736</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F35" t="s">
-        <v>737</v>
       </c>
       <c r="G35" s="17" t="s">
         <v>18</v>
@@ -18665,7 +18662,7 @@
         <v>20</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K35" s="17" t="s">
         <v>163</v>
@@ -18674,7 +18671,7 @@
         <v>254</v>
       </c>
       <c r="M35" s="17" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.35">
@@ -18688,13 +18685,13 @@
         <v>235</v>
       </c>
       <c r="D36" s="17" t="s">
+        <v>738</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F36" t="s">
         <v>739</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F36" t="s">
-        <v>740</v>
       </c>
       <c r="G36" s="17" t="s">
         <v>30</v>
@@ -18706,7 +18703,7 @@
         <v>144</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K36" s="17" t="s">
         <v>163</v>
@@ -18715,7 +18712,7 @@
         <v>254</v>
       </c>
       <c r="M36" s="17" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.35">
@@ -18729,13 +18726,13 @@
         <v>236</v>
       </c>
       <c r="D37" s="17" t="s">
+        <v>741</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F37" t="s">
         <v>742</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F37" t="s">
-        <v>743</v>
       </c>
       <c r="G37" s="17" t="s">
         <v>30</v>
@@ -18747,7 +18744,7 @@
         <v>144</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K37" s="17" t="s">
         <v>163</v>
@@ -18756,7 +18753,7 @@
         <v>254</v>
       </c>
       <c r="M37" s="17" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.35">
@@ -18770,13 +18767,13 @@
         <v>237</v>
       </c>
       <c r="D38" s="17" t="s">
+        <v>744</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F38" t="s">
         <v>745</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F38" t="s">
-        <v>746</v>
       </c>
       <c r="G38" s="17" t="s">
         <v>30</v>
@@ -18788,7 +18785,7 @@
         <v>144</v>
       </c>
       <c r="J38" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K38" s="17" t="s">
         <v>163</v>
@@ -18797,7 +18794,7 @@
         <v>254</v>
       </c>
       <c r="M38" s="17" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.35">
@@ -18811,13 +18808,13 @@
         <v>238</v>
       </c>
       <c r="D39" s="17" t="s">
+        <v>747</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F39" t="s">
         <v>748</v>
-      </c>
-      <c r="E39" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F39" t="s">
-        <v>749</v>
       </c>
       <c r="G39" s="17" t="s">
         <v>30</v>
@@ -18829,7 +18826,7 @@
         <v>144</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K39" s="17" t="s">
         <v>163</v>
@@ -18838,7 +18835,7 @@
         <v>254</v>
       </c>
       <c r="M39" s="17" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.35">
@@ -18852,13 +18849,13 @@
         <v>239</v>
       </c>
       <c r="D40" s="17" t="s">
+        <v>750</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F40" t="s">
         <v>751</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F40" t="s">
-        <v>752</v>
       </c>
       <c r="G40" s="17" t="s">
         <v>30</v>
@@ -18870,7 +18867,7 @@
         <v>144</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K40" s="17" t="s">
         <v>163</v>
@@ -18879,7 +18876,7 @@
         <v>254</v>
       </c>
       <c r="M40" s="17" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.35">
@@ -18893,13 +18890,13 @@
         <v>240</v>
       </c>
       <c r="D41" s="17" t="s">
+        <v>753</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="F41" t="s">
         <v>754</v>
-      </c>
-      <c r="E41" s="17" t="s">
-        <v>657</v>
-      </c>
-      <c r="F41" t="s">
-        <v>755</v>
       </c>
       <c r="G41" s="17" t="s">
         <v>30</v>
@@ -18911,7 +18908,7 @@
         <v>144</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K41" s="17" t="s">
         <v>163</v>
@@ -18937,10 +18934,10 @@
         <v>148</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="F42" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="G42" s="17" t="s">
         <v>30</v>
@@ -18952,7 +18949,7 @@
         <v>20</v>
       </c>
       <c r="J42" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>163</v>
@@ -19039,13 +19036,13 @@
         <v>242</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>141</v>
       </c>
       <c r="F2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G2" t="s">
         <v>30</v>
@@ -19057,7 +19054,7 @@
         <v>31</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="K2" s="6" t="s">
         <v>163</v>
@@ -19066,7 +19063,7 @@
         <v>146</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -19080,16 +19077,16 @@
         <v>243</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>159</v>
@@ -19098,7 +19095,7 @@
         <v>20</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>163</v>
@@ -19107,7 +19104,7 @@
         <v>146</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -19121,13 +19118,13 @@
         <v>244</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="G4" t="s">
         <v>30</v>
@@ -19148,7 +19145,7 @@
         <v>146</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -19162,13 +19159,13 @@
         <v>245</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="G5" t="s">
         <v>30</v>
@@ -19189,7 +19186,7 @@
         <v>146</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -19203,13 +19200,13 @@
         <v>246</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="G6" t="s">
         <v>30</v>
@@ -19230,7 +19227,7 @@
         <v>146</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -19244,13 +19241,13 @@
         <v>247</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="G7" t="s">
         <v>18</v>
@@ -19271,7 +19268,7 @@
         <v>146</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -19285,13 +19282,13 @@
         <v>248</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="G8" t="s">
         <v>18</v>
@@ -19312,7 +19309,7 @@
         <v>146</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -19326,19 +19323,19 @@
         <v>249</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="G9" t="s">
         <v>18</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>20</v>
@@ -19353,7 +19350,7 @@
         <v>146</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
@@ -19367,13 +19364,13 @@
         <v>250</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="G10" t="s">
         <v>30</v>
@@ -19385,7 +19382,7 @@
         <v>31</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>163</v>
@@ -19394,7 +19391,7 @@
         <v>146</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -19408,13 +19405,13 @@
         <v>251</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G11" t="s">
         <v>18</v>
@@ -19435,7 +19432,7 @@
         <v>146</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -19449,13 +19446,13 @@
         <v>252</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="G12" t="s">
         <v>30</v>
@@ -19476,7 +19473,7 @@
         <v>146</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -19490,13 +19487,13 @@
         <v>253</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>444</v>
       </c>
       <c r="F13" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="G13" t="s">
         <v>18</v>
@@ -19517,7 +19514,7 @@
         <v>146</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -19531,13 +19528,13 @@
         <v>254</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>444</v>
       </c>
       <c r="F14" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="G14" t="s">
         <v>18</v>
@@ -19558,7 +19555,7 @@
         <v>146</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -19572,13 +19569,13 @@
         <v>255</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>444</v>
       </c>
       <c r="F15" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="G15" t="s">
         <v>18</v>
@@ -19599,7 +19596,7 @@
         <v>146</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -19613,13 +19610,13 @@
         <v>256</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>444</v>
       </c>
       <c r="F16" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="G16" t="s">
         <v>18</v>
@@ -19640,7 +19637,7 @@
         <v>146</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
@@ -19654,19 +19651,19 @@
         <v>257</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>444</v>
       </c>
       <c r="F17" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="G17" t="s">
         <v>18</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="I17" s="6" t="s">
         <v>20</v>
@@ -19681,7 +19678,7 @@
         <v>146</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="16" x14ac:dyDescent="0.4">
@@ -19695,13 +19692,13 @@
         <v>258</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>444</v>
       </c>
       <c r="F18" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="G18" t="s">
         <v>18</v>
@@ -19722,7 +19719,7 @@
         <v>146</v>
       </c>
       <c r="M18" s="32" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
@@ -19736,13 +19733,13 @@
         <v>259</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>444</v>
       </c>
       <c r="F19" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="G19" t="s">
         <v>18</v>
@@ -19763,7 +19760,7 @@
         <v>146</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
@@ -19777,13 +19774,13 @@
         <v>260</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>444</v>
       </c>
       <c r="F20" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="G20" t="s">
         <v>18</v>
@@ -19804,7 +19801,7 @@
         <v>146</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -19883,13 +19880,13 @@
         <v>261</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E2" t="s">
         <v>116</v>
       </c>
       <c r="F2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>18</v>
@@ -19907,7 +19904,7 @@
         <v>146</v>
       </c>
       <c r="M2" s="18" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -19921,13 +19918,13 @@
         <v>262</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E3" t="s">
         <v>116</v>
       </c>
       <c r="F3" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="G3" s="25" t="s">
         <v>18</v>
@@ -19945,7 +19942,7 @@
         <v>146</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -19959,13 +19956,13 @@
         <v>263</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E4" t="s">
         <v>116</v>
       </c>
       <c r="F4" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="G4" s="25" t="s">
         <v>18</v>
@@ -19983,7 +19980,7 @@
         <v>146</v>
       </c>
       <c r="M4" s="18" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -19997,13 +19994,13 @@
         <v>264</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E5" t="s">
         <v>116</v>
       </c>
       <c r="F5" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="G5" s="25" t="s">
         <v>18</v>
@@ -20021,7 +20018,7 @@
         <v>146</v>
       </c>
       <c r="M5" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -20035,13 +20032,13 @@
         <v>265</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E6" t="s">
         <v>116</v>
       </c>
       <c r="F6" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G6" s="25" t="s">
         <v>18</v>
@@ -20059,7 +20056,7 @@
         <v>146</v>
       </c>
       <c r="M6" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -20073,13 +20070,13 @@
         <v>266</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E7" t="s">
         <v>116</v>
       </c>
       <c r="F7" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G7" s="25" t="s">
         <v>18</v>
@@ -20097,7 +20094,7 @@
         <v>146</v>
       </c>
       <c r="M7" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -20111,13 +20108,13 @@
         <v>267</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E8" t="s">
         <v>116</v>
       </c>
       <c r="F8" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="G8" s="25" t="s">
         <v>18</v>
@@ -20129,13 +20126,13 @@
         <v>226</v>
       </c>
       <c r="J8" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="L8" t="s">
         <v>146</v>
       </c>
       <c r="M8" s="18" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -20149,13 +20146,13 @@
         <v>268</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="E9" t="s">
         <v>116</v>
       </c>
       <c r="F9" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="G9" s="25" t="s">
         <v>18</v>
@@ -20167,13 +20164,13 @@
         <v>226</v>
       </c>
       <c r="J9" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="L9" t="s">
         <v>146</v>
       </c>
       <c r="M9" s="18" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
@@ -20187,13 +20184,13 @@
         <v>269</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="E10" t="s">
         <v>116</v>
       </c>
       <c r="F10" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G10" s="25" t="s">
         <v>18</v>
@@ -20208,7 +20205,7 @@
         <v>146</v>
       </c>
       <c r="M10" s="18" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -20222,13 +20219,13 @@
         <v>270</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E11" t="s">
         <v>116</v>
       </c>
       <c r="F11" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G11" s="25" t="s">
         <v>30</v>
@@ -20243,7 +20240,7 @@
         <v>146</v>
       </c>
       <c r="M11" s="18" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
   </sheetData>
@@ -20326,7 +20323,7 @@
         <v>266</v>
       </c>
       <c r="F2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="G2" s="33" t="s">
         <v>18</v>
@@ -20364,7 +20361,7 @@
         <v>266</v>
       </c>
       <c r="F3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="G3" s="33" t="s">
         <v>18</v>
@@ -20402,7 +20399,7 @@
         <v>266</v>
       </c>
       <c r="F4" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G4" s="33" t="s">
         <v>18</v>
@@ -20434,13 +20431,13 @@
         <v>274</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>18</v>
@@ -20458,7 +20455,7 @@
         <v>146</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -20472,13 +20469,13 @@
         <v>275</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>18</v>
@@ -20496,7 +20493,7 @@
         <v>146</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -20510,13 +20507,13 @@
         <v>276</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="G7" s="17" t="s">
         <v>30</v>
@@ -20534,7 +20531,7 @@
         <v>146</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -20548,13 +20545,13 @@
         <v>277</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="E8" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F8" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>18</v>
@@ -20566,13 +20563,13 @@
         <v>20</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -20586,13 +20583,13 @@
         <v>278</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E9" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F9" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>18</v>
@@ -20604,13 +20601,13 @@
         <v>20</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
@@ -20624,13 +20621,13 @@
         <v>279</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="E10" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F10" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>18</v>
@@ -20642,13 +20639,13 @@
         <v>20</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -20662,13 +20659,13 @@
         <v>280</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E11" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F11" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="G11" s="17" t="s">
         <v>30</v>
@@ -20680,13 +20677,13 @@
         <v>144</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -20700,13 +20697,13 @@
         <v>281</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E12" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F12" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="G12" s="17" t="s">
         <v>30</v>
@@ -20718,13 +20715,13 @@
         <v>144</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -20738,13 +20735,13 @@
         <v>282</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="E13" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F13" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="G13" s="17" t="s">
         <v>30</v>
@@ -20756,13 +20753,13 @@
         <v>144</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -20776,13 +20773,13 @@
         <v>283</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="E14" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F14" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="G14" s="17" t="s">
         <v>30</v>
@@ -20794,13 +20791,13 @@
         <v>144</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -20814,13 +20811,13 @@
         <v>284</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="E15" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F15" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="G15" s="17" t="s">
         <v>30</v>
@@ -20832,13 +20829,13 @@
         <v>144</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -20852,13 +20849,13 @@
         <v>285</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E16" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F16" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G16" s="17" t="s">
         <v>30</v>
@@ -20870,13 +20867,13 @@
         <v>144</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
@@ -20890,13 +20887,13 @@
         <v>286</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E17" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F17" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="G17" s="17" t="s">
         <v>30</v>
@@ -20908,13 +20905,13 @@
         <v>144</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
@@ -20934,7 +20931,7 @@
         <v>266</v>
       </c>
       <c r="F18" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>18</v>
@@ -20946,13 +20943,13 @@
         <v>20</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L18" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
@@ -20972,7 +20969,7 @@
         <v>266</v>
       </c>
       <c r="F19" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>18</v>
@@ -20984,13 +20981,13 @@
         <v>20</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
@@ -21004,13 +21001,13 @@
         <v>289</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F20" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="G20" s="17" t="s">
         <v>30</v>
@@ -21022,13 +21019,13 @@
         <v>144</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
@@ -21042,13 +21039,13 @@
         <v>290</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F21" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>18</v>
@@ -21060,13 +21057,13 @@
         <v>20</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
@@ -21083,10 +21080,10 @@
         <v>265</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F22" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>18</v>
@@ -21098,13 +21095,13 @@
         <v>20</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
@@ -21118,13 +21115,13 @@
         <v>292</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F23" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>18</v>
@@ -21136,13 +21133,13 @@
         <v>20</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L23" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
@@ -21156,16 +21153,16 @@
         <v>293</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F24" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>143</v>
@@ -21174,13 +21171,13 @@
         <v>20</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L24" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
@@ -21194,13 +21191,13 @@
         <v>294</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F25" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>18</v>
@@ -21212,13 +21209,13 @@
         <v>20</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L25" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
@@ -21232,13 +21229,13 @@
         <v>295</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F26" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>18</v>
@@ -21250,13 +21247,13 @@
         <v>20</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
@@ -21276,7 +21273,7 @@
         <v>266</v>
       </c>
       <c r="F27" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>18</v>
@@ -21288,13 +21285,13 @@
         <v>20</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L27" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
@@ -21308,13 +21305,13 @@
         <v>297</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="E28" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F28" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>18</v>
@@ -21326,13 +21323,13 @@
         <v>20</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
@@ -21346,13 +21343,13 @@
         <v>298</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E29" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F29" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>18</v>
@@ -21364,13 +21361,13 @@
         <v>20</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L29" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.35">
@@ -21384,13 +21381,13 @@
         <v>299</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="E30" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F30" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>18</v>
@@ -21402,13 +21399,13 @@
         <v>20</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L30" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
@@ -21422,13 +21419,13 @@
         <v>300</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="E31" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F31" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="G31" s="17" t="s">
         <v>30</v>
@@ -21440,13 +21437,13 @@
         <v>144</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L31" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M31" s="17" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.35">
@@ -21460,13 +21457,13 @@
         <v>301</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E32" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F32" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G32" s="17" t="s">
         <v>30</v>
@@ -21478,13 +21475,13 @@
         <v>144</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L32" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.35">
@@ -21498,13 +21495,13 @@
         <v>302</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="E33" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F33" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="G33" s="17" t="s">
         <v>30</v>
@@ -21516,13 +21513,13 @@
         <v>144</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L33" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.35">
@@ -21536,13 +21533,13 @@
         <v>303</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="E34" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F34" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="G34" s="17" t="s">
         <v>30</v>
@@ -21554,13 +21551,13 @@
         <v>144</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L34" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.35">
@@ -21574,16 +21571,16 @@
         <v>304</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="E35" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F35" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>143</v>
@@ -21592,13 +21589,13 @@
         <v>20</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L35" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.35">
@@ -21612,13 +21609,13 @@
         <v>305</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F36" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>18</v>
@@ -21636,7 +21633,7 @@
         <v>146</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.35">
@@ -21650,13 +21647,13 @@
         <v>306</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E37" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F37" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="G37" s="17" t="s">
         <v>30</v>
@@ -21668,13 +21665,13 @@
         <v>144</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L37" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
   </sheetData>
@@ -21748,13 +21745,13 @@
         <v>307</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F2" t="s">
-        <v>1004</v>
+        <v>996</v>
       </c>
       <c r="G2" s="36" t="s">
         <v>18</v>
@@ -21766,7 +21763,7 @@
         <v>20</v>
       </c>
       <c r="M2" s="34" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -21777,13 +21774,13 @@
         <v>308</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>1008</v>
+        <v>998</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F3" t="s">
-        <v>1009</v>
+        <v>999</v>
       </c>
       <c r="G3" s="36" t="s">
         <v>192</v>
@@ -21795,7 +21792,7 @@
         <v>144</v>
       </c>
       <c r="M3" s="34" t="s">
-        <v>1010</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -21806,13 +21803,13 @@
         <v>309</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="E4" s="38" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F4" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="G4" s="38" t="s">
         <v>18</v>
@@ -21824,7 +21821,7 @@
         <v>20</v>
       </c>
       <c r="M4" s="35" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -21835,13 +21832,13 @@
         <v>310</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F5" t="s">
-        <v>1005</v>
+        <v>997</v>
       </c>
       <c r="G5" s="36" t="s">
         <v>18</v>
@@ -21853,7 +21850,7 @@
         <v>20</v>
       </c>
       <c r="M5" s="34" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -21864,13 +21861,13 @@
         <v>311</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F6" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="G6" s="38" t="s">
         <v>18</v>
@@ -21882,7 +21879,7 @@
         <v>20</v>
       </c>
       <c r="M6" s="35" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -21893,13 +21890,13 @@
         <v>312</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F7" t="s">
-        <v>992</v>
+        <v>1004</v>
       </c>
       <c r="G7" s="36" t="s">
         <v>18</v>
@@ -21911,7 +21908,7 @@
         <v>20</v>
       </c>
       <c r="M7" s="34" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -21922,13 +21919,13 @@
         <v>313</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E8" s="38" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F8" t="s">
-        <v>993</v>
+        <v>1005</v>
       </c>
       <c r="G8" s="38" t="s">
         <v>18</v>
@@ -21940,7 +21937,7 @@
         <v>20</v>
       </c>
       <c r="M8" s="35" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -21951,13 +21948,13 @@
         <v>314</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F9" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
       <c r="G9" s="36" t="s">
         <v>18</v>
@@ -21969,7 +21966,7 @@
         <v>20</v>
       </c>
       <c r="M9" s="34" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
@@ -21980,13 +21977,13 @@
         <v>315</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F10" t="s">
-        <v>995</v>
+        <v>1007</v>
       </c>
       <c r="G10" s="38" t="s">
         <v>18</v>
@@ -21998,7 +21995,7 @@
         <v>20</v>
       </c>
       <c r="M10" s="35" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -22009,13 +22006,13 @@
         <v>316</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F11" t="s">
-        <v>996</v>
+        <v>1008</v>
       </c>
       <c r="G11" s="36" t="s">
         <v>18</v>
@@ -22027,7 +22024,7 @@
         <v>20</v>
       </c>
       <c r="M11" s="34" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -22038,13 +22035,13 @@
         <v>317</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F12" t="s">
-        <v>997</v>
+        <v>1009</v>
       </c>
       <c r="G12" s="38" t="s">
         <v>18</v>
@@ -22056,7 +22053,7 @@
         <v>20</v>
       </c>
       <c r="M12" s="35" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -22067,13 +22064,13 @@
         <v>318</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F13" t="s">
-        <v>998</v>
+        <v>1010</v>
       </c>
       <c r="G13" s="36" t="s">
         <v>30</v>
@@ -22085,7 +22082,7 @@
         <v>144</v>
       </c>
       <c r="M13" s="34" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -22099,22 +22096,22 @@
         <v>288</v>
       </c>
       <c r="E14" s="38" t="s">
+        <v>990</v>
+      </c>
+      <c r="F14" t="s">
         <v>991</v>
       </c>
-      <c r="F14" t="s">
-        <v>999</v>
-      </c>
       <c r="G14" s="38" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H14" s="39" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="I14" s="38" t="s">
         <v>20</v>
       </c>
       <c r="M14" s="35" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -22125,13 +22122,13 @@
         <v>320</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F15" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
       <c r="G15" s="36" t="s">
         <v>18</v>
@@ -22143,7 +22140,7 @@
         <v>20</v>
       </c>
       <c r="M15" s="34" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -22154,13 +22151,13 @@
         <v>321</v>
       </c>
       <c r="D16" s="35" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F16" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="G16" s="38" t="s">
         <v>30</v>
@@ -22172,7 +22169,7 @@
         <v>144</v>
       </c>
       <c r="M16" s="35" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
@@ -22183,25 +22180,25 @@
         <v>322</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F17" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="G17" s="38" t="s">
         <v>30</v>
       </c>
       <c r="H17" s="37" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="I17" s="36" t="s">
         <v>144</v>
       </c>
       <c r="M17" s="34" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
@@ -22212,13 +22209,13 @@
         <v>323</v>
       </c>
       <c r="D18" s="35" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E18" s="38" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F18" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="G18" s="38" t="s">
         <v>30</v>
@@ -22230,7 +22227,7 @@
         <v>144</v>
       </c>
       <c r="M18" s="35" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
@@ -22241,13 +22238,13 @@
         <v>324</v>
       </c>
       <c r="D19" s="34" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F19" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="G19" s="38" t="s">
         <v>30</v>
@@ -22259,7 +22256,7 @@
         <v>144</v>
       </c>
       <c r="M19" s="34" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
@@ -22270,13 +22267,13 @@
         <v>325</v>
       </c>
       <c r="D20" s="35" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E20" s="38" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F20" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="G20" s="38" t="s">
         <v>30</v>
@@ -22288,7 +22285,7 @@
         <v>144</v>
       </c>
       <c r="M20" s="35" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
@@ -22299,13 +22296,13 @@
         <v>326</v>
       </c>
       <c r="D21" s="34" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E21" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F21" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="G21" s="38" t="s">
         <v>30</v>
@@ -22317,7 +22314,7 @@
         <v>144</v>
       </c>
       <c r="M21" s="34" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
@@ -22328,13 +22325,13 @@
         <v>327</v>
       </c>
       <c r="D22" s="35" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F22" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="G22" s="38" t="s">
         <v>30</v>
@@ -22346,7 +22343,7 @@
         <v>144</v>
       </c>
       <c r="M22" s="35" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
@@ -22357,13 +22354,13 @@
         <v>328</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F23" t="s">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="G23" s="38" t="s">
         <v>30</v>
@@ -22375,7 +22372,7 @@
         <v>144</v>
       </c>
       <c r="M23" s="34" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
@@ -22386,13 +22383,13 @@
         <v>329</v>
       </c>
       <c r="D24" s="34" t="s">
-        <v>1012</v>
+        <v>1001</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F24" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>30</v>
@@ -22421,10 +22418,10 @@
         <v>148</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F25" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="G25" t="s">
         <v>30</v>
@@ -24597,7 +24594,7 @@
         <v>165</v>
       </c>
       <c r="F8" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="G8" t="s">
         <v>30</v>
@@ -28986,7 +28983,7 @@
         <v>444</v>
       </c>
       <c r="F15" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G15" t="s">
         <v>18</v>
@@ -29133,7 +29130,7 @@
         <v>266</v>
       </c>
       <c r="F2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G2" t="s">
         <v>18</v>
@@ -29174,7 +29171,7 @@
         <v>266</v>
       </c>
       <c r="F3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G3" t="s">
         <v>18</v>
@@ -29215,7 +29212,7 @@
         <v>266</v>
       </c>
       <c r="F4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G4" t="s">
         <v>18</v>
@@ -29256,7 +29253,7 @@
         <v>266</v>
       </c>
       <c r="F5" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G5" t="s">
         <v>18</v>
@@ -29297,7 +29294,7 @@
         <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G6" t="s">
         <v>30</v>
@@ -29338,7 +29335,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G7" t="s">
         <v>30</v>
@@ -29379,7 +29376,7 @@
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G8" t="s">
         <v>30</v>
@@ -29420,7 +29417,7 @@
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="G9" t="s">
         <v>30</v>
@@ -29524,7 +29521,7 @@
         <v>494</v>
       </c>
       <c r="F2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G2" s="18" t="s">
         <v>18</v>
@@ -29565,7 +29562,7 @@
         <v>494</v>
       </c>
       <c r="F3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G3" s="18" t="s">
         <v>18</v>
@@ -29606,7 +29603,7 @@
         <v>494</v>
       </c>
       <c r="F4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G4" s="18" t="s">
         <v>18</v>
@@ -29647,7 +29644,7 @@
         <v>494</v>
       </c>
       <c r="F5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G5" s="18" t="s">
         <v>30</v>
@@ -29688,7 +29685,7 @@
         <v>494</v>
       </c>
       <c r="F6" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>30</v>
@@ -29729,7 +29726,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G7" s="18" t="s">
         <v>18</v>
@@ -29770,7 +29767,7 @@
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G8" s="18" t="s">
         <v>18</v>
@@ -29852,7 +29849,7 @@
         <v>266</v>
       </c>
       <c r="F10" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G10" s="18" t="s">
         <v>18</v>
@@ -29893,7 +29890,7 @@
         <v>266</v>
       </c>
       <c r="F11" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G11" s="18" t="s">
         <v>18</v>
@@ -29934,7 +29931,7 @@
         <v>494</v>
       </c>
       <c r="F12" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>30</v>
@@ -29975,7 +29972,7 @@
         <v>494</v>
       </c>
       <c r="F13" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>30</v>
@@ -30016,7 +30013,7 @@
         <v>494</v>
       </c>
       <c r="F14" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>30</v>
@@ -30057,7 +30054,7 @@
         <v>494</v>
       </c>
       <c r="F15" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>30</v>
@@ -30098,7 +30095,7 @@
         <v>494</v>
       </c>
       <c r="F16" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G16" s="18" t="s">
         <v>192</v>
@@ -30197,16 +30194,16 @@
         <v>177</v>
       </c>
       <c r="D2" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="E2" t="s">
         <v>561</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>562</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" s="24" t="s">
         <v>563</v>
-      </c>
-      <c r="G2" s="24" t="s">
-        <v>564</v>
       </c>
       <c r="H2" s="24" t="s">
         <v>143</v>
@@ -30215,7 +30212,7 @@
         <v>20</v>
       </c>
       <c r="J2" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K2" s="24" t="s">
         <v>163</v>
@@ -30224,7 +30221,7 @@
         <v>146</v>
       </c>
       <c r="M2" s="27" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -30238,16 +30235,16 @@
         <v>178</v>
       </c>
       <c r="D3" s="24" t="s">
+        <v>566</v>
+      </c>
+      <c r="E3" t="s">
+        <v>561</v>
+      </c>
+      <c r="F3" t="s">
         <v>567</v>
       </c>
-      <c r="E3" t="s">
-        <v>562</v>
-      </c>
-      <c r="F3" t="s">
-        <v>568</v>
-      </c>
       <c r="G3" s="24" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H3" s="24" t="s">
         <v>159</v>
@@ -30256,7 +30253,7 @@
         <v>20</v>
       </c>
       <c r="J3" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K3" s="24" t="s">
         <v>163</v>
@@ -30265,7 +30262,7 @@
         <v>146</v>
       </c>
       <c r="M3" s="27" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -30279,13 +30276,13 @@
         <v>179</v>
       </c>
       <c r="D4" s="25" t="s">
+        <v>569</v>
+      </c>
+      <c r="E4" t="s">
+        <v>561</v>
+      </c>
+      <c r="F4" t="s">
         <v>570</v>
-      </c>
-      <c r="E4" t="s">
-        <v>562</v>
-      </c>
-      <c r="F4" t="s">
-        <v>571</v>
       </c>
       <c r="G4" s="25" t="s">
         <v>18</v>
@@ -30297,7 +30294,7 @@
         <v>20</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K4" s="24" t="s">
         <v>163</v>
@@ -30306,7 +30303,7 @@
         <v>146</v>
       </c>
       <c r="M4" s="27" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -30320,13 +30317,13 @@
         <v>180</v>
       </c>
       <c r="D5" s="26" t="s">
+        <v>572</v>
+      </c>
+      <c r="E5" t="s">
+        <v>561</v>
+      </c>
+      <c r="F5" t="s">
         <v>573</v>
-      </c>
-      <c r="E5" t="s">
-        <v>562</v>
-      </c>
-      <c r="F5" t="s">
-        <v>574</v>
       </c>
       <c r="G5" s="24" t="s">
         <v>30</v>
@@ -30338,7 +30335,7 @@
         <v>144</v>
       </c>
       <c r="J5" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K5" s="24" t="s">
         <v>163</v>
@@ -30347,7 +30344,7 @@
         <v>146</v>
       </c>
       <c r="M5" s="27" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -30361,13 +30358,13 @@
         <v>181</v>
       </c>
       <c r="D6" s="26" t="s">
+        <v>575</v>
+      </c>
+      <c r="E6" t="s">
+        <v>561</v>
+      </c>
+      <c r="F6" t="s">
         <v>576</v>
-      </c>
-      <c r="E6" t="s">
-        <v>562</v>
-      </c>
-      <c r="F6" t="s">
-        <v>577</v>
       </c>
       <c r="G6" s="24" t="s">
         <v>30</v>
@@ -30379,7 +30376,7 @@
         <v>144</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K6" s="24" t="s">
         <v>163</v>
@@ -30388,7 +30385,7 @@
         <v>146</v>
       </c>
       <c r="M6" s="27" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -30402,13 +30399,13 @@
         <v>182</v>
       </c>
       <c r="D7" s="26" t="s">
+        <v>578</v>
+      </c>
+      <c r="E7" t="s">
+        <v>561</v>
+      </c>
+      <c r="F7" t="s">
         <v>579</v>
-      </c>
-      <c r="E7" t="s">
-        <v>562</v>
-      </c>
-      <c r="F7" t="s">
-        <v>580</v>
       </c>
       <c r="G7" s="25" t="s">
         <v>30</v>
@@ -30420,7 +30417,7 @@
         <v>144</v>
       </c>
       <c r="J7" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K7" s="24" t="s">
         <v>163</v>
@@ -30429,7 +30426,7 @@
         <v>146</v>
       </c>
       <c r="M7" s="27" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -30443,13 +30440,13 @@
         <v>183</v>
       </c>
       <c r="D8" s="25" t="s">
+        <v>581</v>
+      </c>
+      <c r="E8" t="s">
+        <v>561</v>
+      </c>
+      <c r="F8" t="s">
         <v>582</v>
-      </c>
-      <c r="E8" t="s">
-        <v>562</v>
-      </c>
-      <c r="F8" t="s">
-        <v>583</v>
       </c>
       <c r="G8" s="25" t="s">
         <v>30</v>
@@ -30461,7 +30458,7 @@
         <v>144</v>
       </c>
       <c r="J8" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K8" s="24" t="s">
         <v>163</v>
@@ -30470,7 +30467,7 @@
         <v>146</v>
       </c>
       <c r="M8" s="27" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -30484,13 +30481,13 @@
         <v>184</v>
       </c>
       <c r="D9" s="25" t="s">
+        <v>584</v>
+      </c>
+      <c r="E9" t="s">
+        <v>561</v>
+      </c>
+      <c r="F9" t="s">
         <v>585</v>
-      </c>
-      <c r="E9" t="s">
-        <v>562</v>
-      </c>
-      <c r="F9" t="s">
-        <v>586</v>
       </c>
       <c r="G9" s="25" t="s">
         <v>30</v>
@@ -30502,7 +30499,7 @@
         <v>144</v>
       </c>
       <c r="J9" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K9" s="24" t="s">
         <v>163</v>
@@ -30511,7 +30508,7 @@
         <v>146</v>
       </c>
       <c r="M9" s="27" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
@@ -30525,13 +30522,13 @@
         <v>185</v>
       </c>
       <c r="D10" s="25" t="s">
+        <v>587</v>
+      </c>
+      <c r="E10" t="s">
+        <v>561</v>
+      </c>
+      <c r="F10" t="s">
         <v>588</v>
-      </c>
-      <c r="E10" t="s">
-        <v>562</v>
-      </c>
-      <c r="F10" t="s">
-        <v>589</v>
       </c>
       <c r="G10" s="25" t="s">
         <v>30</v>
@@ -30543,7 +30540,7 @@
         <v>144</v>
       </c>
       <c r="J10" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K10" s="24" t="s">
         <v>163</v>
@@ -30552,7 +30549,7 @@
         <v>146</v>
       </c>
       <c r="M10" s="27" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -30566,13 +30563,13 @@
         <v>186</v>
       </c>
       <c r="D11" s="25" t="s">
+        <v>590</v>
+      </c>
+      <c r="E11" t="s">
+        <v>561</v>
+      </c>
+      <c r="F11" t="s">
         <v>591</v>
-      </c>
-      <c r="E11" t="s">
-        <v>562</v>
-      </c>
-      <c r="F11" t="s">
-        <v>592</v>
       </c>
       <c r="G11" s="25" t="s">
         <v>30</v>
@@ -30584,7 +30581,7 @@
         <v>144</v>
       </c>
       <c r="J11" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K11" s="24" t="s">
         <v>163</v>
@@ -30593,7 +30590,7 @@
         <v>146</v>
       </c>
       <c r="M11" s="27" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -30607,13 +30604,13 @@
         <v>187</v>
       </c>
       <c r="D12" s="25" t="s">
+        <v>593</v>
+      </c>
+      <c r="E12" t="s">
+        <v>561</v>
+      </c>
+      <c r="F12" t="s">
         <v>594</v>
-      </c>
-      <c r="E12" t="s">
-        <v>562</v>
-      </c>
-      <c r="F12" t="s">
-        <v>595</v>
       </c>
       <c r="G12" s="25" t="s">
         <v>30</v>
@@ -30625,7 +30622,7 @@
         <v>144</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K12" s="24" t="s">
         <v>163</v>
@@ -30634,7 +30631,7 @@
         <v>146</v>
       </c>
       <c r="M12" s="27" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -30648,13 +30645,13 @@
         <v>188</v>
       </c>
       <c r="D13" s="25" t="s">
+        <v>596</v>
+      </c>
+      <c r="E13" t="s">
+        <v>561</v>
+      </c>
+      <c r="F13" t="s">
         <v>597</v>
-      </c>
-      <c r="E13" t="s">
-        <v>562</v>
-      </c>
-      <c r="F13" t="s">
-        <v>598</v>
       </c>
       <c r="G13" s="25" t="s">
         <v>30</v>
@@ -30666,7 +30663,7 @@
         <v>144</v>
       </c>
       <c r="J13" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K13" s="24" t="s">
         <v>163</v>
@@ -30675,7 +30672,7 @@
         <v>146</v>
       </c>
       <c r="M13" s="27" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -30689,25 +30686,25 @@
         <v>189</v>
       </c>
       <c r="D14" s="25" t="s">
+        <v>599</v>
+      </c>
+      <c r="E14" t="s">
+        <v>561</v>
+      </c>
+      <c r="F14" t="s">
         <v>600</v>
       </c>
-      <c r="E14" t="s">
-        <v>562</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="G14" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="24" t="s">
         <v>601</v>
-      </c>
-      <c r="G14" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>602</v>
       </c>
       <c r="I14" s="24" t="s">
         <v>144</v>
       </c>
       <c r="J14" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K14" s="24" t="s">
         <v>163</v>
@@ -30716,7 +30713,7 @@
         <v>146</v>
       </c>
       <c r="M14" s="27" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -30730,13 +30727,13 @@
         <v>190</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E15" s="24" t="s">
+        <v>603</v>
+      </c>
+      <c r="F15" t="s">
         <v>604</v>
-      </c>
-      <c r="F15" t="s">
-        <v>605</v>
       </c>
       <c r="G15" s="24" t="s">
         <v>18</v>
@@ -30748,7 +30745,7 @@
         <v>20</v>
       </c>
       <c r="J15" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K15" s="24" t="s">
         <v>163</v>
@@ -30757,7 +30754,7 @@
         <v>146</v>
       </c>
       <c r="M15" s="27" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
@@ -30771,13 +30768,13 @@
         <v>191</v>
       </c>
       <c r="D16" s="26" t="s">
+        <v>605</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>603</v>
+      </c>
+      <c r="F16" t="s">
         <v>606</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>604</v>
-      </c>
-      <c r="F16" t="s">
-        <v>607</v>
       </c>
       <c r="G16" s="24" t="s">
         <v>30</v>
@@ -30789,7 +30786,7 @@
         <v>144</v>
       </c>
       <c r="J16" s="24" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K16" s="24" t="s">
         <v>163</v>
@@ -30798,7 +30795,7 @@
         <v>146</v>
       </c>
       <c r="M16" s="27" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
@@ -30812,13 +30809,13 @@
         <v>192</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G17" s="24" t="s">
         <v>30</v>
@@ -30830,7 +30827,7 @@
         <v>144</v>
       </c>
       <c r="J17" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K17" s="24" t="s">
         <v>163</v>
@@ -30839,7 +30836,7 @@
         <v>146</v>
       </c>
       <c r="M17" s="27" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
@@ -30853,13 +30850,13 @@
         <v>193</v>
       </c>
       <c r="D18" s="24" t="s">
+        <v>610</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>603</v>
+      </c>
+      <c r="F18" t="s">
         <v>611</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>604</v>
-      </c>
-      <c r="F18" t="s">
-        <v>612</v>
       </c>
       <c r="G18" s="24" t="s">
         <v>30</v>
@@ -30871,7 +30868,7 @@
         <v>144</v>
       </c>
       <c r="J18" s="24" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K18" s="24" t="s">
         <v>163</v>
@@ -30880,7 +30877,7 @@
         <v>146</v>
       </c>
       <c r="M18" s="27" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
@@ -30894,13 +30891,13 @@
         <v>194</v>
       </c>
       <c r="D19" s="24" t="s">
+        <v>613</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>603</v>
+      </c>
+      <c r="F19" t="s">
         <v>614</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>604</v>
-      </c>
-      <c r="F19" t="s">
-        <v>615</v>
       </c>
       <c r="G19" s="24" t="s">
         <v>30</v>
@@ -30912,7 +30909,7 @@
         <v>144</v>
       </c>
       <c r="J19" s="24" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K19" s="24" t="s">
         <v>163</v>
@@ -30921,7 +30918,7 @@
         <v>146</v>
       </c>
       <c r="M19" s="27" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
@@ -30935,25 +30932,25 @@
         <v>195</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F20" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G20" s="24" t="s">
         <v>30</v>
       </c>
       <c r="H20" s="24" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="I20" s="24" t="s">
         <v>144</v>
       </c>
       <c r="J20" s="24" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K20" s="24" t="s">
         <v>163</v>
@@ -30962,7 +30959,7 @@
         <v>146</v>
       </c>
       <c r="M20" s="27" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
   </sheetData>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Verification Metadata/CDOP_SCHEMAs for Testing/VerificationAE_no arrays/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Verification Metadata/CDOP_SCHEMAs for Testing/ProjectAE_verification array/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{43812F2F-CE42-471E-B59C-F29A7962070A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F90AA9B7-3DCB-465F-BB58-71E6EC1D840A}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{062F5E8A-D75B-41E8-9959-007D39D00B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B8A3C65-9A9C-4703-BC11-6D52140AC2B9}"/>
   <bookViews>
     <workbookView xWindow="-28080" yWindow="315" windowWidth="27450" windowHeight="14490" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7825" uniqueCount="1019">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7825" uniqueCount="1018">
   <si>
     <t>schema</t>
   </si>
@@ -3067,91 +3067,88 @@
     <t>Summary result of the checklist (e.g., PASS, PASS_WITH_RESERVATIONS, FAIL).</t>
   </si>
   <si>
-    <t>verification</t>
-  </si>
-  <si>
-    <t>verification.verification_report_url</t>
-  </si>
-  <si>
-    <t>verification.verification_credential_issuer_id</t>
-  </si>
-  <si>
-    <t>verification.verification_cryptographic_proof_type</t>
-  </si>
-  <si>
-    <t>verification.verification_digital_signature_payload</t>
-  </si>
-  <si>
     <t>validation.validation_event[].validation_id</t>
   </si>
   <si>
-    <t>verification.verification_id</t>
-  </si>
-  <si>
-    <t>verification.verification_project_id</t>
-  </si>
-  <si>
     <t>verification_vvb_id</t>
   </si>
   <si>
-    <t>verification.verification_vvb_id</t>
-  </si>
-  <si>
     <t>A globally unique identifier for a validation or verification body (vvb).</t>
   </si>
   <si>
     <t>verification_audit_checkpoint_status_reason</t>
   </si>
   <si>
-    <t>verification.verification_claim_type</t>
-  </si>
-  <si>
-    <t>verification.verification_description</t>
-  </si>
-  <si>
-    <t>verification.verification_reporting_period_start</t>
-  </si>
-  <si>
-    <t>verification.verification_reporting_period_end</t>
-  </si>
-  <si>
-    <t>verification.verification_date</t>
-  </si>
-  <si>
-    <t>verification.verified_quantity</t>
-  </si>
-  <si>
-    <t>verification.verification_quantity_uom</t>
-  </si>
-  <si>
-    <t>verification.verification_applied_standard</t>
-  </si>
-  <si>
-    <t>verification.verification_applied_methodology_protocol</t>
-  </si>
-  <si>
-    <t>verification.verification_leakage_risk_mitigation</t>
-  </si>
-  <si>
-    <t>verification.verification_leakage_risk_mitigation_strategy</t>
-  </si>
-  <si>
-    <t>verification.verification_leakage_deduction_quantity</t>
-  </si>
-  <si>
-    <t>verification.verification_uncertainty_deduction_margin</t>
-  </si>
-  <si>
-    <t>verification.verification_buffer_pool_deduction_quantity</t>
-  </si>
-  <si>
-    <t>verification.verification_audit_checkpoint_status</t>
-  </si>
-  <si>
-    <t>verification.verification_audit_checkpoint_status_reason</t>
-  </si>
-  <si>
-    <t>verification.is_current</t>
+    <t>project.verification[].verification_id</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_vvb_id</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_claim_type</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_project_id</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_description</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_reporting_period_start</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_reporting_period_end</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_date</t>
+  </si>
+  <si>
+    <t>project.verification[].verified_quantity</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_quantity_uom</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_applied_standard</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_applied_methodology_protocol</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_report_url</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_credential_issuer_id</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_cryptographic_proof_type</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_digital_signature_payload</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_leakage_risk_mitigation</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_leakage_risk_mitigation_strategy</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_leakage_deduction_quantity</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_uncertainty_deduction_margin</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_buffer_pool_deduction_quantity</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_audit_checkpoint_status</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_audit_checkpoint_status_reason</t>
+  </si>
+  <si>
+    <t>project.verification[].is_current</t>
   </si>
 </sst>
 </file>
@@ -15496,7 +15493,7 @@
         <v>266</v>
       </c>
       <c r="F288" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="G288" s="6" t="s">
         <v>18</v>
@@ -16250,10 +16247,10 @@
         <v>947</v>
       </c>
       <c r="E308" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F308" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="G308" s="36" t="s">
         <v>18</v>
@@ -16276,13 +16273,13 @@
         <v>308</v>
       </c>
       <c r="D309" s="34" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="E309" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F309" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="G309" s="36" t="s">
         <v>192</v>
@@ -16294,7 +16291,7 @@
         <v>144</v>
       </c>
       <c r="M309" s="34" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
     </row>
     <row r="310" spans="1:13" x14ac:dyDescent="0.35">
@@ -16307,11 +16304,11 @@
       <c r="D310" s="35" t="s">
         <v>948</v>
       </c>
-      <c r="E310" s="38" t="s">
-        <v>990</v>
+      <c r="E310" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F310" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="G310" s="38" t="s">
         <v>18</v>
@@ -16337,7 +16334,7 @@
         <v>949</v>
       </c>
       <c r="E311" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F311" t="s">
         <v>997</v>
@@ -16365,11 +16362,11 @@
       <c r="D312" s="35" t="s">
         <v>950</v>
       </c>
-      <c r="E312" s="38" t="s">
-        <v>990</v>
+      <c r="E312" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F312" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="G312" s="38" t="s">
         <v>18</v>
@@ -16395,10 +16392,10 @@
         <v>951</v>
       </c>
       <c r="E313" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F313" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="G313" s="36" t="s">
         <v>18</v>
@@ -16423,11 +16420,11 @@
       <c r="D314" s="35" t="s">
         <v>952</v>
       </c>
-      <c r="E314" s="38" t="s">
-        <v>990</v>
+      <c r="E314" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F314" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="G314" s="38" t="s">
         <v>18</v>
@@ -16453,10 +16450,10 @@
         <v>953</v>
       </c>
       <c r="E315" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F315" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="G315" s="36" t="s">
         <v>18</v>
@@ -16481,11 +16478,11 @@
       <c r="D316" s="35" t="s">
         <v>954</v>
       </c>
-      <c r="E316" s="38" t="s">
-        <v>990</v>
+      <c r="E316" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F316" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="G316" s="38" t="s">
         <v>18</v>
@@ -16511,10 +16508,10 @@
         <v>955</v>
       </c>
       <c r="E317" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F317" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="G317" s="36" t="s">
         <v>18</v>
@@ -16539,11 +16536,11 @@
       <c r="D318" s="35" t="s">
         <v>956</v>
       </c>
-      <c r="E318" s="38" t="s">
-        <v>990</v>
+      <c r="E318" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F318" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="G318" s="38" t="s">
         <v>18</v>
@@ -16569,10 +16566,10 @@
         <v>957</v>
       </c>
       <c r="E319" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F319" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="G319" s="36" t="s">
         <v>30</v>
@@ -16597,11 +16594,11 @@
       <c r="D320" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="E320" s="38" t="s">
-        <v>990</v>
+      <c r="E320" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F320" t="s">
-        <v>991</v>
+        <v>1006</v>
       </c>
       <c r="G320" s="38" t="s">
         <v>563</v>
@@ -16627,10 +16624,10 @@
         <v>958</v>
       </c>
       <c r="E321" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F321" t="s">
-        <v>992</v>
+        <v>1007</v>
       </c>
       <c r="G321" s="36" t="s">
         <v>18</v>
@@ -16655,11 +16652,11 @@
       <c r="D322" s="35" t="s">
         <v>959</v>
       </c>
-      <c r="E322" s="38" t="s">
-        <v>990</v>
+      <c r="E322" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F322" t="s">
-        <v>993</v>
+        <v>1008</v>
       </c>
       <c r="G322" s="38" t="s">
         <v>30</v>
@@ -16685,10 +16682,10 @@
         <v>960</v>
       </c>
       <c r="E323" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F323" t="s">
-        <v>994</v>
+        <v>1009</v>
       </c>
       <c r="G323" s="38" t="s">
         <v>30</v>
@@ -16713,11 +16710,11 @@
       <c r="D324" s="35" t="s">
         <v>961</v>
       </c>
-      <c r="E324" s="38" t="s">
-        <v>990</v>
+      <c r="E324" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F324" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="G324" s="38" t="s">
         <v>30</v>
@@ -16743,10 +16740,10 @@
         <v>962</v>
       </c>
       <c r="E325" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F325" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="G325" s="38" t="s">
         <v>30</v>
@@ -16771,11 +16768,11 @@
       <c r="D326" s="35" t="s">
         <v>963</v>
       </c>
-      <c r="E326" s="38" t="s">
-        <v>990</v>
+      <c r="E326" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F326" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="G326" s="38" t="s">
         <v>30</v>
@@ -16801,10 +16798,10 @@
         <v>964</v>
       </c>
       <c r="E327" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F327" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="G327" s="38" t="s">
         <v>30</v>
@@ -16829,11 +16826,11 @@
       <c r="D328" s="35" t="s">
         <v>965</v>
       </c>
-      <c r="E328" s="38" t="s">
-        <v>990</v>
+      <c r="E328" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F328" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="G328" s="38" t="s">
         <v>30</v>
@@ -16859,10 +16856,10 @@
         <v>966</v>
       </c>
       <c r="E329" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F329" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="G329" s="38" t="s">
         <v>30</v>
@@ -16885,13 +16882,13 @@
         <v>329</v>
       </c>
       <c r="D330" s="34" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="E330" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F330" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="G330" s="6" t="s">
         <v>30</v>
@@ -16920,10 +16917,10 @@
         <v>148</v>
       </c>
       <c r="E331" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F331" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="G331" t="s">
         <v>30</v>
@@ -20931,7 +20928,7 @@
         <v>266</v>
       </c>
       <c r="F18" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>18</v>
@@ -21748,10 +21745,10 @@
         <v>947</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="G2" s="36" t="s">
         <v>18</v>
@@ -21774,13 +21771,13 @@
         <v>308</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="G3" s="36" t="s">
         <v>192</v>
@@ -21792,7 +21789,7 @@
         <v>144</v>
       </c>
       <c r="M3" s="34" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -21805,11 +21802,11 @@
       <c r="D4" s="35" t="s">
         <v>948</v>
       </c>
-      <c r="E4" s="38" t="s">
-        <v>990</v>
+      <c r="E4" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="G4" s="38" t="s">
         <v>18</v>
@@ -21835,7 +21832,7 @@
         <v>949</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
         <v>997</v>
@@ -21863,11 +21860,11 @@
       <c r="D6" s="35" t="s">
         <v>950</v>
       </c>
-      <c r="E6" s="38" t="s">
-        <v>990</v>
+      <c r="E6" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="G6" s="38" t="s">
         <v>18</v>
@@ -21893,10 +21890,10 @@
         <v>951</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="G7" s="36" t="s">
         <v>18</v>
@@ -21921,11 +21918,11 @@
       <c r="D8" s="35" t="s">
         <v>952</v>
       </c>
-      <c r="E8" s="38" t="s">
-        <v>990</v>
+      <c r="E8" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="G8" s="38" t="s">
         <v>18</v>
@@ -21951,10 +21948,10 @@
         <v>953</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="G9" s="36" t="s">
         <v>18</v>
@@ -21979,11 +21976,11 @@
       <c r="D10" s="35" t="s">
         <v>954</v>
       </c>
-      <c r="E10" s="38" t="s">
-        <v>990</v>
+      <c r="E10" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="G10" s="38" t="s">
         <v>18</v>
@@ -22009,10 +22006,10 @@
         <v>955</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="G11" s="36" t="s">
         <v>18</v>
@@ -22037,11 +22034,11 @@
       <c r="D12" s="35" t="s">
         <v>956</v>
       </c>
-      <c r="E12" s="38" t="s">
-        <v>990</v>
+      <c r="E12" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="G12" s="38" t="s">
         <v>18</v>
@@ -22067,10 +22064,10 @@
         <v>957</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="G13" s="36" t="s">
         <v>30</v>
@@ -22095,11 +22092,11 @@
       <c r="D14" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="E14" s="38" t="s">
-        <v>990</v>
+      <c r="E14" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>991</v>
+        <v>1006</v>
       </c>
       <c r="G14" s="38" t="s">
         <v>563</v>
@@ -22125,10 +22122,10 @@
         <v>958</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>992</v>
+        <v>1007</v>
       </c>
       <c r="G15" s="36" t="s">
         <v>18</v>
@@ -22153,11 +22150,11 @@
       <c r="D16" s="35" t="s">
         <v>959</v>
       </c>
-      <c r="E16" s="38" t="s">
-        <v>990</v>
+      <c r="E16" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>993</v>
+        <v>1008</v>
       </c>
       <c r="G16" s="38" t="s">
         <v>30</v>
@@ -22183,10 +22180,10 @@
         <v>960</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>994</v>
+        <v>1009</v>
       </c>
       <c r="G17" s="38" t="s">
         <v>30</v>
@@ -22211,11 +22208,11 @@
       <c r="D18" s="35" t="s">
         <v>961</v>
       </c>
-      <c r="E18" s="38" t="s">
-        <v>990</v>
+      <c r="E18" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F18" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="G18" s="38" t="s">
         <v>30</v>
@@ -22241,10 +22238,10 @@
         <v>962</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F19" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="G19" s="38" t="s">
         <v>30</v>
@@ -22269,11 +22266,11 @@
       <c r="D20" s="35" t="s">
         <v>963</v>
       </c>
-      <c r="E20" s="38" t="s">
-        <v>990</v>
+      <c r="E20" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F20" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="G20" s="38" t="s">
         <v>30</v>
@@ -22299,10 +22296,10 @@
         <v>964</v>
       </c>
       <c r="E21" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F21" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="G21" s="38" t="s">
         <v>30</v>
@@ -22327,11 +22324,11 @@
       <c r="D22" s="35" t="s">
         <v>965</v>
       </c>
-      <c r="E22" s="38" t="s">
-        <v>990</v>
+      <c r="E22" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F22" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="G22" s="38" t="s">
         <v>30</v>
@@ -22357,10 +22354,10 @@
         <v>966</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F23" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="G23" s="38" t="s">
         <v>30</v>
@@ -22383,13 +22380,13 @@
         <v>329</v>
       </c>
       <c r="D24" s="34" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F24" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>30</v>
@@ -22418,10 +22415,10 @@
         <v>148</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F25" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="G25" t="s">
         <v>30</v>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Verification Metadata/CDOP_SCHEMAs for Testing/ProjectAE_verification array/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Verification Metadata/CDOP_SCHEMAs for Testing/ProjectAE_no arrays/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{062F5E8A-D75B-41E8-9959-007D39D00B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B8A3C65-9A9C-4703-BC11-6D52140AC2B9}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{1670AFD3-BEFF-4646-88E5-BBA60F7840BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0DD8EDC-265D-4BA3-BC23-E00BF31BE66F}"/>
   <bookViews>
     <workbookView xWindow="-28080" yWindow="315" windowWidth="27450" windowHeight="14490" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
@@ -3079,76 +3079,76 @@
     <t>verification_audit_checkpoint_status_reason</t>
   </si>
   <si>
-    <t>project.verification[].verification_id</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_vvb_id</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_claim_type</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_project_id</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_description</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_reporting_period_start</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_reporting_period_end</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_date</t>
-  </si>
-  <si>
-    <t>project.verification[].verified_quantity</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_quantity_uom</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_applied_standard</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_applied_methodology_protocol</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_report_url</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_credential_issuer_id</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_cryptographic_proof_type</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_digital_signature_payload</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_leakage_risk_mitigation</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_leakage_risk_mitigation_strategy</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_leakage_deduction_quantity</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_uncertainty_deduction_margin</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_buffer_pool_deduction_quantity</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_audit_checkpoint_status</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_audit_checkpoint_status_reason</t>
-  </si>
-  <si>
-    <t>project.verification[].is_current</t>
+    <t>project.verification_id</t>
+  </si>
+  <si>
+    <t>project.verification_vvb_id</t>
+  </si>
+  <si>
+    <t>project.verification_claim_type</t>
+  </si>
+  <si>
+    <t>project.verification_project_id</t>
+  </si>
+  <si>
+    <t>project.verification_description</t>
+  </si>
+  <si>
+    <t>project.verification_reporting_period_start</t>
+  </si>
+  <si>
+    <t>project.verification_reporting_period_end</t>
+  </si>
+  <si>
+    <t>project.verification_date</t>
+  </si>
+  <si>
+    <t>project.verified_quantity</t>
+  </si>
+  <si>
+    <t>project.verification_quantity_uom</t>
+  </si>
+  <si>
+    <t>project.verification_applied_standard</t>
+  </si>
+  <si>
+    <t>project.verification_applied_methodology_protocol</t>
+  </si>
+  <si>
+    <t>project.verification_report_url</t>
+  </si>
+  <si>
+    <t>project.verification_credential_issuer_id</t>
+  </si>
+  <si>
+    <t>project.verification_cryptographic_proof_type</t>
+  </si>
+  <si>
+    <t>project.verification_digital_signature_payload</t>
+  </si>
+  <si>
+    <t>project.verification_leakage_risk_mitigation</t>
+  </si>
+  <si>
+    <t>project.verification_leakage_risk_mitigation_strategy</t>
+  </si>
+  <si>
+    <t>project.verification_leakage_deduction_quantity</t>
+  </si>
+  <si>
+    <t>project.verification_uncertainty_deduction_margin</t>
+  </si>
+  <si>
+    <t>project.verification_buffer_pool_deduction_quantity</t>
+  </si>
+  <si>
+    <t>project.verification_audit_checkpoint_status</t>
+  </si>
+  <si>
+    <t>project.verification_audit_checkpoint_status_reason</t>
+  </si>
+  <si>
+    <t>project.is_current</t>
   </si>
 </sst>
 </file>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Verification Metadata/CDOP_SCHEMAs for Testing/ProjectAE_no arrays/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/Round 2 Pods for Testing/Fast Track Pods/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{1670AFD3-BEFF-4646-88E5-BBA60F7840BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0DD8EDC-265D-4BA3-BC23-E00BF31BE66F}"/>
+  <xr:revisionPtr revIDLastSave="528" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44576A22-C94D-406E-9A93-DB0211AEB78A}"/>
   <bookViews>
-    <workbookView xWindow="-28080" yWindow="315" windowWidth="27450" windowHeight="14490" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7825" uniqueCount="1018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7825" uniqueCount="1019">
   <si>
     <t>schema</t>
   </si>
@@ -3067,88 +3067,91 @@
     <t>Summary result of the checklist (e.g., PASS, PASS_WITH_RESERVATIONS, FAIL).</t>
   </si>
   <si>
+    <t>verification</t>
+  </si>
+  <si>
+    <t>verification.reporting[].verification_reporting_period_start</t>
+  </si>
+  <si>
+    <t>verification.reporting[].verification_reporting_period_end</t>
+  </si>
+  <si>
+    <t>verification.reporting[].verification_date</t>
+  </si>
+  <si>
+    <t>verification.quantity[].verified_quantity</t>
+  </si>
+  <si>
+    <t>verification.quantity[].verification_quantity_uom</t>
+  </si>
+  <si>
+    <t>verification.standard[].verification_applied_standard</t>
+  </si>
+  <si>
+    <t>verification.standard[].verification_applied_methodology_protocol</t>
+  </si>
+  <si>
+    <t>verification.verification_report_url</t>
+  </si>
+  <si>
+    <t>verification.verification_credential_issuer_id</t>
+  </si>
+  <si>
+    <t>verification.verification_cryptographic_proof_type</t>
+  </si>
+  <si>
+    <t>verification.verification_digital_signature_payload</t>
+  </si>
+  <si>
     <t>validation.validation_event[].validation_id</t>
   </si>
   <si>
+    <t>verification.verification_id</t>
+  </si>
+  <si>
+    <t>verification.verification_project_id</t>
+  </si>
+  <si>
+    <t>verification.details[].verification_claim_type</t>
+  </si>
+  <si>
+    <t>verification.details[].verification_description</t>
+  </si>
+  <si>
     <t>verification_vvb_id</t>
   </si>
   <si>
+    <t>verification.verification_vvb_id</t>
+  </si>
+  <si>
     <t>A globally unique identifier for a validation or verification body (vvb).</t>
   </si>
   <si>
+    <t>verification.status[].verification_audit_checkpoint_status</t>
+  </si>
+  <si>
     <t>verification_audit_checkpoint_status_reason</t>
   </si>
   <si>
-    <t>project.verification_id</t>
-  </si>
-  <si>
-    <t>project.verification_vvb_id</t>
-  </si>
-  <si>
-    <t>project.verification_claim_type</t>
-  </si>
-  <si>
-    <t>project.verification_project_id</t>
-  </si>
-  <si>
-    <t>project.verification_description</t>
-  </si>
-  <si>
-    <t>project.verification_reporting_period_start</t>
-  </si>
-  <si>
-    <t>project.verification_reporting_period_end</t>
-  </si>
-  <si>
-    <t>project.verification_date</t>
-  </si>
-  <si>
-    <t>project.verified_quantity</t>
-  </si>
-  <si>
-    <t>project.verification_quantity_uom</t>
-  </si>
-  <si>
-    <t>project.verification_applied_standard</t>
-  </si>
-  <si>
-    <t>project.verification_applied_methodology_protocol</t>
-  </si>
-  <si>
-    <t>project.verification_report_url</t>
-  </si>
-  <si>
-    <t>project.verification_credential_issuer_id</t>
-  </si>
-  <si>
-    <t>project.verification_cryptographic_proof_type</t>
-  </si>
-  <si>
-    <t>project.verification_digital_signature_payload</t>
-  </si>
-  <si>
-    <t>project.verification_leakage_risk_mitigation</t>
-  </si>
-  <si>
-    <t>project.verification_leakage_risk_mitigation_strategy</t>
-  </si>
-  <si>
-    <t>project.verification_leakage_deduction_quantity</t>
-  </si>
-  <si>
-    <t>project.verification_uncertainty_deduction_margin</t>
-  </si>
-  <si>
-    <t>project.verification_buffer_pool_deduction_quantity</t>
-  </si>
-  <si>
-    <t>project.verification_audit_checkpoint_status</t>
-  </si>
-  <si>
-    <t>project.verification_audit_checkpoint_status_reason</t>
-  </si>
-  <si>
-    <t>project.is_current</t>
+    <t>verification.status[].verification_audit_checkpoint_status_reason</t>
+  </si>
+  <si>
+    <t>verification.status[].is_current</t>
+  </si>
+  <si>
+    <t>verification.deductions[].verification_leakage_risk_mitigation</t>
+  </si>
+  <si>
+    <t>verification.deductions[].verification_leakage_risk_mitigation_strategy</t>
+  </si>
+  <si>
+    <t>verification.deductions[].verification_leakage_deduction_quantity</t>
+  </si>
+  <si>
+    <t>verification.deductions[].verification_uncertainty_deduction_margin</t>
+  </si>
+  <si>
+    <t>verification.deductions[].verification_buffer_pool_deduction_quantity</t>
   </si>
 </sst>
 </file>
@@ -15493,7 +15496,7 @@
         <v>266</v>
       </c>
       <c r="F288" t="s">
-        <v>990</v>
+        <v>1002</v>
       </c>
       <c r="G288" s="6" t="s">
         <v>18</v>
@@ -16247,10 +16250,10 @@
         <v>947</v>
       </c>
       <c r="E308" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F308" t="s">
-        <v>994</v>
+        <v>1003</v>
       </c>
       <c r="G308" s="36" t="s">
         <v>18</v>
@@ -16273,13 +16276,13 @@
         <v>308</v>
       </c>
       <c r="D309" s="34" t="s">
-        <v>991</v>
+        <v>1007</v>
       </c>
       <c r="E309" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F309" t="s">
-        <v>995</v>
+        <v>1008</v>
       </c>
       <c r="G309" s="36" t="s">
         <v>192</v>
@@ -16291,7 +16294,7 @@
         <v>144</v>
       </c>
       <c r="M309" s="34" t="s">
-        <v>992</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="310" spans="1:13" x14ac:dyDescent="0.35">
@@ -16304,11 +16307,11 @@
       <c r="D310" s="35" t="s">
         <v>948</v>
       </c>
-      <c r="E310" s="36" t="s">
-        <v>16</v>
+      <c r="E310" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F310" t="s">
-        <v>996</v>
+        <v>1005</v>
       </c>
       <c r="G310" s="38" t="s">
         <v>18</v>
@@ -16334,10 +16337,10 @@
         <v>949</v>
       </c>
       <c r="E311" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F311" t="s">
-        <v>997</v>
+        <v>1004</v>
       </c>
       <c r="G311" s="36" t="s">
         <v>18</v>
@@ -16362,11 +16365,11 @@
       <c r="D312" s="35" t="s">
         <v>950</v>
       </c>
-      <c r="E312" s="36" t="s">
-        <v>16</v>
+      <c r="E312" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F312" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="G312" s="38" t="s">
         <v>18</v>
@@ -16392,10 +16395,10 @@
         <v>951</v>
       </c>
       <c r="E313" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F313" t="s">
-        <v>999</v>
+        <v>991</v>
       </c>
       <c r="G313" s="36" t="s">
         <v>18</v>
@@ -16420,11 +16423,11 @@
       <c r="D314" s="35" t="s">
         <v>952</v>
       </c>
-      <c r="E314" s="36" t="s">
-        <v>16</v>
+      <c r="E314" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F314" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
       <c r="G314" s="38" t="s">
         <v>18</v>
@@ -16450,10 +16453,10 @@
         <v>953</v>
       </c>
       <c r="E315" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F315" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="G315" s="36" t="s">
         <v>18</v>
@@ -16478,11 +16481,11 @@
       <c r="D316" s="35" t="s">
         <v>954</v>
       </c>
-      <c r="E316" s="36" t="s">
-        <v>16</v>
+      <c r="E316" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F316" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="G316" s="38" t="s">
         <v>18</v>
@@ -16508,10 +16511,10 @@
         <v>955</v>
       </c>
       <c r="E317" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F317" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="G317" s="36" t="s">
         <v>18</v>
@@ -16536,11 +16539,11 @@
       <c r="D318" s="35" t="s">
         <v>956</v>
       </c>
-      <c r="E318" s="36" t="s">
-        <v>16</v>
+      <c r="E318" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F318" t="s">
-        <v>1004</v>
+        <v>996</v>
       </c>
       <c r="G318" s="38" t="s">
         <v>18</v>
@@ -16566,10 +16569,10 @@
         <v>957</v>
       </c>
       <c r="E319" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F319" t="s">
-        <v>1005</v>
+        <v>997</v>
       </c>
       <c r="G319" s="36" t="s">
         <v>30</v>
@@ -16594,11 +16597,11 @@
       <c r="D320" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="E320" s="36" t="s">
-        <v>16</v>
+      <c r="E320" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F320" t="s">
-        <v>1006</v>
+        <v>998</v>
       </c>
       <c r="G320" s="38" t="s">
         <v>563</v>
@@ -16624,10 +16627,10 @@
         <v>958</v>
       </c>
       <c r="E321" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F321" t="s">
-        <v>1007</v>
+        <v>999</v>
       </c>
       <c r="G321" s="36" t="s">
         <v>18</v>
@@ -16652,11 +16655,11 @@
       <c r="D322" s="35" t="s">
         <v>959</v>
       </c>
-      <c r="E322" s="36" t="s">
-        <v>16</v>
+      <c r="E322" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F322" t="s">
-        <v>1008</v>
+        <v>1000</v>
       </c>
       <c r="G322" s="38" t="s">
         <v>30</v>
@@ -16682,10 +16685,10 @@
         <v>960</v>
       </c>
       <c r="E323" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F323" t="s">
-        <v>1009</v>
+        <v>1001</v>
       </c>
       <c r="G323" s="38" t="s">
         <v>30</v>
@@ -16710,11 +16713,11 @@
       <c r="D324" s="35" t="s">
         <v>961</v>
       </c>
-      <c r="E324" s="36" t="s">
-        <v>16</v>
+      <c r="E324" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F324" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="G324" s="38" t="s">
         <v>30</v>
@@ -16740,10 +16743,10 @@
         <v>962</v>
       </c>
       <c r="E325" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F325" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="G325" s="38" t="s">
         <v>30</v>
@@ -16768,11 +16771,11 @@
       <c r="D326" s="35" t="s">
         <v>963</v>
       </c>
-      <c r="E326" s="36" t="s">
-        <v>16</v>
+      <c r="E326" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F326" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="G326" s="38" t="s">
         <v>30</v>
@@ -16798,10 +16801,10 @@
         <v>964</v>
       </c>
       <c r="E327" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F327" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="G327" s="38" t="s">
         <v>30</v>
@@ -16826,11 +16829,11 @@
       <c r="D328" s="35" t="s">
         <v>965</v>
       </c>
-      <c r="E328" s="36" t="s">
-        <v>16</v>
+      <c r="E328" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F328" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="G328" s="38" t="s">
         <v>30</v>
@@ -16856,10 +16859,10 @@
         <v>966</v>
       </c>
       <c r="E329" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F329" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="G329" s="38" t="s">
         <v>30</v>
@@ -16882,13 +16885,13 @@
         <v>329</v>
       </c>
       <c r="D330" s="34" t="s">
-        <v>993</v>
+        <v>1011</v>
       </c>
       <c r="E330" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F330" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="G330" s="6" t="s">
         <v>30</v>
@@ -16917,10 +16920,10 @@
         <v>148</v>
       </c>
       <c r="E331" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F331" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="G331" t="s">
         <v>30</v>
@@ -20928,7 +20931,7 @@
         <v>266</v>
       </c>
       <c r="F18" t="s">
-        <v>990</v>
+        <v>1002</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>18</v>
@@ -21745,10 +21748,10 @@
         <v>947</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F2" t="s">
-        <v>994</v>
+        <v>1003</v>
       </c>
       <c r="G2" s="36" t="s">
         <v>18</v>
@@ -21771,13 +21774,13 @@
         <v>308</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>991</v>
+        <v>1007</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F3" t="s">
-        <v>995</v>
+        <v>1008</v>
       </c>
       <c r="G3" s="36" t="s">
         <v>192</v>
@@ -21789,7 +21792,7 @@
         <v>144</v>
       </c>
       <c r="M3" s="34" t="s">
-        <v>992</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -21802,11 +21805,11 @@
       <c r="D4" s="35" t="s">
         <v>948</v>
       </c>
-      <c r="E4" s="36" t="s">
-        <v>16</v>
+      <c r="E4" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F4" t="s">
-        <v>996</v>
+        <v>1005</v>
       </c>
       <c r="G4" s="38" t="s">
         <v>18</v>
@@ -21832,10 +21835,10 @@
         <v>949</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F5" t="s">
-        <v>997</v>
+        <v>1004</v>
       </c>
       <c r="G5" s="36" t="s">
         <v>18</v>
@@ -21860,11 +21863,11 @@
       <c r="D6" s="35" t="s">
         <v>950</v>
       </c>
-      <c r="E6" s="36" t="s">
-        <v>16</v>
+      <c r="E6" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F6" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="G6" s="38" t="s">
         <v>18</v>
@@ -21890,10 +21893,10 @@
         <v>951</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F7" t="s">
-        <v>999</v>
+        <v>991</v>
       </c>
       <c r="G7" s="36" t="s">
         <v>18</v>
@@ -21918,11 +21921,11 @@
       <c r="D8" s="35" t="s">
         <v>952</v>
       </c>
-      <c r="E8" s="36" t="s">
-        <v>16</v>
+      <c r="E8" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F8" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
       <c r="G8" s="38" t="s">
         <v>18</v>
@@ -21948,10 +21951,10 @@
         <v>953</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F9" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="G9" s="36" t="s">
         <v>18</v>
@@ -21976,11 +21979,11 @@
       <c r="D10" s="35" t="s">
         <v>954</v>
       </c>
-      <c r="E10" s="36" t="s">
-        <v>16</v>
+      <c r="E10" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F10" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="G10" s="38" t="s">
         <v>18</v>
@@ -22006,10 +22009,10 @@
         <v>955</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F11" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="G11" s="36" t="s">
         <v>18</v>
@@ -22034,11 +22037,11 @@
       <c r="D12" s="35" t="s">
         <v>956</v>
       </c>
-      <c r="E12" s="36" t="s">
-        <v>16</v>
+      <c r="E12" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F12" t="s">
-        <v>1004</v>
+        <v>996</v>
       </c>
       <c r="G12" s="38" t="s">
         <v>18</v>
@@ -22064,10 +22067,10 @@
         <v>957</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F13" t="s">
-        <v>1005</v>
+        <v>997</v>
       </c>
       <c r="G13" s="36" t="s">
         <v>30</v>
@@ -22092,11 +22095,11 @@
       <c r="D14" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="E14" s="36" t="s">
-        <v>16</v>
+      <c r="E14" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F14" t="s">
-        <v>1006</v>
+        <v>998</v>
       </c>
       <c r="G14" s="38" t="s">
         <v>563</v>
@@ -22122,10 +22125,10 @@
         <v>958</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F15" t="s">
-        <v>1007</v>
+        <v>999</v>
       </c>
       <c r="G15" s="36" t="s">
         <v>18</v>
@@ -22150,11 +22153,11 @@
       <c r="D16" s="35" t="s">
         <v>959</v>
       </c>
-      <c r="E16" s="36" t="s">
-        <v>16</v>
+      <c r="E16" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F16" t="s">
-        <v>1008</v>
+        <v>1000</v>
       </c>
       <c r="G16" s="38" t="s">
         <v>30</v>
@@ -22180,10 +22183,10 @@
         <v>960</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F17" t="s">
-        <v>1009</v>
+        <v>1001</v>
       </c>
       <c r="G17" s="38" t="s">
         <v>30</v>
@@ -22208,11 +22211,11 @@
       <c r="D18" s="35" t="s">
         <v>961</v>
       </c>
-      <c r="E18" s="36" t="s">
-        <v>16</v>
+      <c r="E18" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F18" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="G18" s="38" t="s">
         <v>30</v>
@@ -22238,10 +22241,10 @@
         <v>962</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F19" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="G19" s="38" t="s">
         <v>30</v>
@@ -22266,11 +22269,11 @@
       <c r="D20" s="35" t="s">
         <v>963</v>
       </c>
-      <c r="E20" s="36" t="s">
-        <v>16</v>
+      <c r="E20" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F20" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="G20" s="38" t="s">
         <v>30</v>
@@ -22296,10 +22299,10 @@
         <v>964</v>
       </c>
       <c r="E21" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F21" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="G21" s="38" t="s">
         <v>30</v>
@@ -22324,11 +22327,11 @@
       <c r="D22" s="35" t="s">
         <v>965</v>
       </c>
-      <c r="E22" s="36" t="s">
-        <v>16</v>
+      <c r="E22" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F22" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="G22" s="38" t="s">
         <v>30</v>
@@ -22354,10 +22357,10 @@
         <v>966</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F23" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="G23" s="38" t="s">
         <v>30</v>
@@ -22380,13 +22383,13 @@
         <v>329</v>
       </c>
       <c r="D24" s="34" t="s">
-        <v>993</v>
+        <v>1011</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F24" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>30</v>
@@ -22415,10 +22418,10 @@
         <v>148</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F25" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="G25" t="s">
         <v>30</v>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/Round 2 Pods for Testing/Fast Track Pods/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Verification Metadata/CDOP_SCHEMAs w_JSONS for Testing/ProjectAE_verification array/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="528" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44576A22-C94D-406E-9A93-DB0211AEB78A}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="8_{062F5E8A-D75B-41E8-9959-007D39D00B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2754F05-772A-4992-9B92-65A9381D4220}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="12" activeTab="14" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7825" uniqueCount="1019">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7825" uniqueCount="1018">
   <si>
     <t>schema</t>
   </si>
@@ -3067,91 +3067,88 @@
     <t>Summary result of the checklist (e.g., PASS, PASS_WITH_RESERVATIONS, FAIL).</t>
   </si>
   <si>
-    <t>verification</t>
-  </si>
-  <si>
-    <t>verification.reporting[].verification_reporting_period_start</t>
-  </si>
-  <si>
-    <t>verification.reporting[].verification_reporting_period_end</t>
-  </si>
-  <si>
-    <t>verification.reporting[].verification_date</t>
-  </si>
-  <si>
-    <t>verification.quantity[].verified_quantity</t>
-  </si>
-  <si>
-    <t>verification.quantity[].verification_quantity_uom</t>
-  </si>
-  <si>
-    <t>verification.standard[].verification_applied_standard</t>
-  </si>
-  <si>
-    <t>verification.standard[].verification_applied_methodology_protocol</t>
-  </si>
-  <si>
-    <t>verification.verification_report_url</t>
-  </si>
-  <si>
-    <t>verification.verification_credential_issuer_id</t>
-  </si>
-  <si>
-    <t>verification.verification_cryptographic_proof_type</t>
-  </si>
-  <si>
-    <t>verification.verification_digital_signature_payload</t>
-  </si>
-  <si>
     <t>validation.validation_event[].validation_id</t>
   </si>
   <si>
-    <t>verification.verification_id</t>
-  </si>
-  <si>
-    <t>verification.verification_project_id</t>
-  </si>
-  <si>
-    <t>verification.details[].verification_claim_type</t>
-  </si>
-  <si>
-    <t>verification.details[].verification_description</t>
-  </si>
-  <si>
     <t>verification_vvb_id</t>
   </si>
   <si>
-    <t>verification.verification_vvb_id</t>
-  </si>
-  <si>
     <t>A globally unique identifier for a validation or verification body (vvb).</t>
   </si>
   <si>
-    <t>verification.status[].verification_audit_checkpoint_status</t>
-  </si>
-  <si>
     <t>verification_audit_checkpoint_status_reason</t>
   </si>
   <si>
-    <t>verification.status[].verification_audit_checkpoint_status_reason</t>
-  </si>
-  <si>
-    <t>verification.status[].is_current</t>
-  </si>
-  <si>
-    <t>verification.deductions[].verification_leakage_risk_mitigation</t>
-  </si>
-  <si>
-    <t>verification.deductions[].verification_leakage_risk_mitigation_strategy</t>
-  </si>
-  <si>
-    <t>verification.deductions[].verification_leakage_deduction_quantity</t>
-  </si>
-  <si>
-    <t>verification.deductions[].verification_uncertainty_deduction_margin</t>
-  </si>
-  <si>
-    <t>verification.deductions[].verification_buffer_pool_deduction_quantity</t>
+    <t>project.verification[].verification_id</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_vvb_id</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_claim_type</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_project_id</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_description</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_reporting_period_start</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_reporting_period_end</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_date</t>
+  </si>
+  <si>
+    <t>project.verification[].verified_quantity</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_quantity_uom</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_applied_standard</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_applied_methodology_protocol</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_report_url</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_credential_issuer_id</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_cryptographic_proof_type</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_digital_signature_payload</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_leakage_risk_mitigation</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_leakage_risk_mitigation_strategy</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_leakage_deduction_quantity</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_uncertainty_deduction_margin</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_buffer_pool_deduction_quantity</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_audit_checkpoint_status</t>
+  </si>
+  <si>
+    <t>project.verification[].verification_audit_checkpoint_status_reason</t>
+  </si>
+  <si>
+    <t>project.verification[].is_current</t>
   </si>
 </sst>
 </file>
@@ -15496,7 +15493,7 @@
         <v>266</v>
       </c>
       <c r="F288" t="s">
-        <v>1002</v>
+        <v>990</v>
       </c>
       <c r="G288" s="6" t="s">
         <v>18</v>
@@ -16250,10 +16247,10 @@
         <v>947</v>
       </c>
       <c r="E308" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F308" t="s">
-        <v>1003</v>
+        <v>994</v>
       </c>
       <c r="G308" s="36" t="s">
         <v>18</v>
@@ -16276,16 +16273,16 @@
         <v>308</v>
       </c>
       <c r="D309" s="34" t="s">
-        <v>1007</v>
+        <v>991</v>
       </c>
       <c r="E309" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F309" t="s">
-        <v>1008</v>
+        <v>995</v>
       </c>
       <c r="G309" s="36" t="s">
-        <v>192</v>
+        <v>30</v>
       </c>
       <c r="H309" s="37" t="s">
         <v>215</v>
@@ -16294,7 +16291,7 @@
         <v>144</v>
       </c>
       <c r="M309" s="34" t="s">
-        <v>1009</v>
+        <v>992</v>
       </c>
     </row>
     <row r="310" spans="1:13" x14ac:dyDescent="0.35">
@@ -16307,11 +16304,11 @@
       <c r="D310" s="35" t="s">
         <v>948</v>
       </c>
-      <c r="E310" s="38" t="s">
-        <v>990</v>
+      <c r="E310" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F310" t="s">
-        <v>1005</v>
+        <v>996</v>
       </c>
       <c r="G310" s="38" t="s">
         <v>18</v>
@@ -16337,10 +16334,10 @@
         <v>949</v>
       </c>
       <c r="E311" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F311" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
       <c r="G311" s="36" t="s">
         <v>18</v>
@@ -16365,11 +16362,11 @@
       <c r="D312" s="35" t="s">
         <v>950</v>
       </c>
-      <c r="E312" s="38" t="s">
-        <v>990</v>
+      <c r="E312" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F312" t="s">
-        <v>1006</v>
+        <v>998</v>
       </c>
       <c r="G312" s="38" t="s">
         <v>18</v>
@@ -16395,10 +16392,10 @@
         <v>951</v>
       </c>
       <c r="E313" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F313" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="G313" s="36" t="s">
         <v>18</v>
@@ -16423,11 +16420,11 @@
       <c r="D314" s="35" t="s">
         <v>952</v>
       </c>
-      <c r="E314" s="38" t="s">
-        <v>990</v>
+      <c r="E314" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F314" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="G314" s="38" t="s">
         <v>18</v>
@@ -16453,10 +16450,10 @@
         <v>953</v>
       </c>
       <c r="E315" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F315" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
       <c r="G315" s="36" t="s">
         <v>18</v>
@@ -16481,11 +16478,11 @@
       <c r="D316" s="35" t="s">
         <v>954</v>
       </c>
-      <c r="E316" s="38" t="s">
-        <v>990</v>
+      <c r="E316" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F316" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
       <c r="G316" s="38" t="s">
         <v>18</v>
@@ -16511,10 +16508,10 @@
         <v>955</v>
       </c>
       <c r="E317" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F317" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
       <c r="G317" s="36" t="s">
         <v>18</v>
@@ -16539,11 +16536,11 @@
       <c r="D318" s="35" t="s">
         <v>956</v>
       </c>
-      <c r="E318" s="38" t="s">
-        <v>990</v>
+      <c r="E318" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F318" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
       <c r="G318" s="38" t="s">
         <v>18</v>
@@ -16569,10 +16566,10 @@
         <v>957</v>
       </c>
       <c r="E319" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F319" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
       <c r="G319" s="36" t="s">
         <v>30</v>
@@ -16597,14 +16594,14 @@
       <c r="D320" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="E320" s="38" t="s">
-        <v>990</v>
+      <c r="E320" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F320" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="G320" s="38" t="s">
-        <v>563</v>
+        <v>18</v>
       </c>
       <c r="H320" s="39" t="s">
         <v>967</v>
@@ -16627,10 +16624,10 @@
         <v>958</v>
       </c>
       <c r="E321" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F321" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
       <c r="G321" s="36" t="s">
         <v>18</v>
@@ -16655,11 +16652,11 @@
       <c r="D322" s="35" t="s">
         <v>959</v>
       </c>
-      <c r="E322" s="38" t="s">
-        <v>990</v>
+      <c r="E322" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F322" t="s">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="G322" s="38" t="s">
         <v>30</v>
@@ -16685,10 +16682,10 @@
         <v>960</v>
       </c>
       <c r="E323" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F323" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
       <c r="G323" s="38" t="s">
         <v>30</v>
@@ -16713,11 +16710,11 @@
       <c r="D324" s="35" t="s">
         <v>961</v>
       </c>
-      <c r="E324" s="38" t="s">
-        <v>990</v>
+      <c r="E324" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F324" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="G324" s="38" t="s">
         <v>30</v>
@@ -16743,10 +16740,10 @@
         <v>962</v>
       </c>
       <c r="E325" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F325" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="G325" s="38" t="s">
         <v>30</v>
@@ -16771,11 +16768,11 @@
       <c r="D326" s="35" t="s">
         <v>963</v>
       </c>
-      <c r="E326" s="38" t="s">
-        <v>990</v>
+      <c r="E326" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F326" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="G326" s="38" t="s">
         <v>30</v>
@@ -16801,10 +16798,10 @@
         <v>964</v>
       </c>
       <c r="E327" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F327" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="G327" s="38" t="s">
         <v>30</v>
@@ -16829,11 +16826,11 @@
       <c r="D328" s="35" t="s">
         <v>965</v>
       </c>
-      <c r="E328" s="38" t="s">
-        <v>990</v>
+      <c r="E328" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F328" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="G328" s="38" t="s">
         <v>30</v>
@@ -16859,10 +16856,10 @@
         <v>966</v>
       </c>
       <c r="E329" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F329" t="s">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="G329" s="38" t="s">
         <v>30</v>
@@ -16885,13 +16882,13 @@
         <v>329</v>
       </c>
       <c r="D330" s="34" t="s">
-        <v>1011</v>
+        <v>993</v>
       </c>
       <c r="E330" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F330" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="G330" s="6" t="s">
         <v>30</v>
@@ -16920,10 +16917,10 @@
         <v>148</v>
       </c>
       <c r="E331" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F331" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="G331" t="s">
         <v>30</v>
@@ -20931,7 +20928,7 @@
         <v>266</v>
       </c>
       <c r="F18" t="s">
-        <v>1002</v>
+        <v>990</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>18</v>
@@ -21748,10 +21745,10 @@
         <v>947</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>1003</v>
+        <v>994</v>
       </c>
       <c r="G2" s="36" t="s">
         <v>18</v>
@@ -21774,16 +21771,16 @@
         <v>308</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>1007</v>
+        <v>991</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>1008</v>
+        <v>995</v>
       </c>
       <c r="G3" s="36" t="s">
-        <v>192</v>
+        <v>30</v>
       </c>
       <c r="H3" s="37" t="s">
         <v>215</v>
@@ -21792,7 +21789,7 @@
         <v>144</v>
       </c>
       <c r="M3" s="34" t="s">
-        <v>1009</v>
+        <v>992</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -21805,11 +21802,11 @@
       <c r="D4" s="35" t="s">
         <v>948</v>
       </c>
-      <c r="E4" s="38" t="s">
-        <v>990</v>
+      <c r="E4" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>1005</v>
+        <v>996</v>
       </c>
       <c r="G4" s="38" t="s">
         <v>18</v>
@@ -21835,10 +21832,10 @@
         <v>949</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
       <c r="G5" s="36" t="s">
         <v>18</v>
@@ -21863,11 +21860,11 @@
       <c r="D6" s="35" t="s">
         <v>950</v>
       </c>
-      <c r="E6" s="38" t="s">
-        <v>990</v>
+      <c r="E6" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>1006</v>
+        <v>998</v>
       </c>
       <c r="G6" s="38" t="s">
         <v>18</v>
@@ -21893,10 +21890,10 @@
         <v>951</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="G7" s="36" t="s">
         <v>18</v>
@@ -21921,11 +21918,11 @@
       <c r="D8" s="35" t="s">
         <v>952</v>
       </c>
-      <c r="E8" s="38" t="s">
-        <v>990</v>
+      <c r="E8" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="G8" s="38" t="s">
         <v>18</v>
@@ -21951,10 +21948,10 @@
         <v>953</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
       <c r="G9" s="36" t="s">
         <v>18</v>
@@ -21979,11 +21976,11 @@
       <c r="D10" s="35" t="s">
         <v>954</v>
       </c>
-      <c r="E10" s="38" t="s">
-        <v>990</v>
+      <c r="E10" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
       <c r="G10" s="38" t="s">
         <v>18</v>
@@ -22009,10 +22006,10 @@
         <v>955</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
       <c r="G11" s="36" t="s">
         <v>18</v>
@@ -22037,11 +22034,11 @@
       <c r="D12" s="35" t="s">
         <v>956</v>
       </c>
-      <c r="E12" s="38" t="s">
-        <v>990</v>
+      <c r="E12" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
       <c r="G12" s="38" t="s">
         <v>18</v>
@@ -22067,10 +22064,10 @@
         <v>957</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
       <c r="G13" s="36" t="s">
         <v>30</v>
@@ -22095,14 +22092,14 @@
       <c r="D14" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="E14" s="38" t="s">
-        <v>990</v>
+      <c r="E14" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>563</v>
+        <v>18</v>
       </c>
       <c r="H14" s="39" t="s">
         <v>967</v>
@@ -22125,10 +22122,10 @@
         <v>958</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
       <c r="G15" s="36" t="s">
         <v>18</v>
@@ -22153,11 +22150,11 @@
       <c r="D16" s="35" t="s">
         <v>959</v>
       </c>
-      <c r="E16" s="38" t="s">
-        <v>990</v>
+      <c r="E16" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="G16" s="38" t="s">
         <v>30</v>
@@ -22183,10 +22180,10 @@
         <v>960</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
       <c r="G17" s="38" t="s">
         <v>30</v>
@@ -22211,11 +22208,11 @@
       <c r="D18" s="35" t="s">
         <v>961</v>
       </c>
-      <c r="E18" s="38" t="s">
-        <v>990</v>
+      <c r="E18" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F18" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="G18" s="38" t="s">
         <v>30</v>
@@ -22241,10 +22238,10 @@
         <v>962</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F19" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="G19" s="38" t="s">
         <v>30</v>
@@ -22269,11 +22266,11 @@
       <c r="D20" s="35" t="s">
         <v>963</v>
       </c>
-      <c r="E20" s="38" t="s">
-        <v>990</v>
+      <c r="E20" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F20" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="G20" s="38" t="s">
         <v>30</v>
@@ -22299,10 +22296,10 @@
         <v>964</v>
       </c>
       <c r="E21" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F21" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="G21" s="38" t="s">
         <v>30</v>
@@ -22327,11 +22324,11 @@
       <c r="D22" s="35" t="s">
         <v>965</v>
       </c>
-      <c r="E22" s="38" t="s">
-        <v>990</v>
+      <c r="E22" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="F22" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="G22" s="38" t="s">
         <v>30</v>
@@ -22357,10 +22354,10 @@
         <v>966</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F23" t="s">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="G23" s="38" t="s">
         <v>30</v>
@@ -22383,13 +22380,13 @@
         <v>329</v>
       </c>
       <c r="D24" s="34" t="s">
-        <v>1011</v>
+        <v>993</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F24" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>30</v>
@@ -22418,10 +22415,10 @@
         <v>148</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="F25" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="G25" t="s">
         <v>30</v>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Verification Metadata/CDOP_SCHEMAs w_JSONS for Testing/ProjectAE_verification array/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/Round 2 Pods for Testing/Fast Track Pods/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{062F5E8A-D75B-41E8-9959-007D39D00B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2754F05-772A-4992-9B92-65A9381D4220}"/>
+  <xr:revisionPtr revIDLastSave="528" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44576A22-C94D-406E-9A93-DB0211AEB78A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="12" activeTab="14" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7825" uniqueCount="1018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7825" uniqueCount="1019">
   <si>
     <t>schema</t>
   </si>
@@ -3067,88 +3067,91 @@
     <t>Summary result of the checklist (e.g., PASS, PASS_WITH_RESERVATIONS, FAIL).</t>
   </si>
   <si>
+    <t>verification</t>
+  </si>
+  <si>
+    <t>verification.reporting[].verification_reporting_period_start</t>
+  </si>
+  <si>
+    <t>verification.reporting[].verification_reporting_period_end</t>
+  </si>
+  <si>
+    <t>verification.reporting[].verification_date</t>
+  </si>
+  <si>
+    <t>verification.quantity[].verified_quantity</t>
+  </si>
+  <si>
+    <t>verification.quantity[].verification_quantity_uom</t>
+  </si>
+  <si>
+    <t>verification.standard[].verification_applied_standard</t>
+  </si>
+  <si>
+    <t>verification.standard[].verification_applied_methodology_protocol</t>
+  </si>
+  <si>
+    <t>verification.verification_report_url</t>
+  </si>
+  <si>
+    <t>verification.verification_credential_issuer_id</t>
+  </si>
+  <si>
+    <t>verification.verification_cryptographic_proof_type</t>
+  </si>
+  <si>
+    <t>verification.verification_digital_signature_payload</t>
+  </si>
+  <si>
     <t>validation.validation_event[].validation_id</t>
   </si>
   <si>
+    <t>verification.verification_id</t>
+  </si>
+  <si>
+    <t>verification.verification_project_id</t>
+  </si>
+  <si>
+    <t>verification.details[].verification_claim_type</t>
+  </si>
+  <si>
+    <t>verification.details[].verification_description</t>
+  </si>
+  <si>
     <t>verification_vvb_id</t>
   </si>
   <si>
+    <t>verification.verification_vvb_id</t>
+  </si>
+  <si>
     <t>A globally unique identifier for a validation or verification body (vvb).</t>
   </si>
   <si>
+    <t>verification.status[].verification_audit_checkpoint_status</t>
+  </si>
+  <si>
     <t>verification_audit_checkpoint_status_reason</t>
   </si>
   <si>
-    <t>project.verification[].verification_id</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_vvb_id</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_claim_type</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_project_id</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_description</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_reporting_period_start</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_reporting_period_end</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_date</t>
-  </si>
-  <si>
-    <t>project.verification[].verified_quantity</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_quantity_uom</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_applied_standard</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_applied_methodology_protocol</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_report_url</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_credential_issuer_id</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_cryptographic_proof_type</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_digital_signature_payload</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_leakage_risk_mitigation</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_leakage_risk_mitigation_strategy</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_leakage_deduction_quantity</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_uncertainty_deduction_margin</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_buffer_pool_deduction_quantity</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_audit_checkpoint_status</t>
-  </si>
-  <si>
-    <t>project.verification[].verification_audit_checkpoint_status_reason</t>
-  </si>
-  <si>
-    <t>project.verification[].is_current</t>
+    <t>verification.status[].verification_audit_checkpoint_status_reason</t>
+  </si>
+  <si>
+    <t>verification.status[].is_current</t>
+  </si>
+  <si>
+    <t>verification.deductions[].verification_leakage_risk_mitigation</t>
+  </si>
+  <si>
+    <t>verification.deductions[].verification_leakage_risk_mitigation_strategy</t>
+  </si>
+  <si>
+    <t>verification.deductions[].verification_leakage_deduction_quantity</t>
+  </si>
+  <si>
+    <t>verification.deductions[].verification_uncertainty_deduction_margin</t>
+  </si>
+  <si>
+    <t>verification.deductions[].verification_buffer_pool_deduction_quantity</t>
   </si>
 </sst>
 </file>
@@ -15493,7 +15496,7 @@
         <v>266</v>
       </c>
       <c r="F288" t="s">
-        <v>990</v>
+        <v>1002</v>
       </c>
       <c r="G288" s="6" t="s">
         <v>18</v>
@@ -16247,10 +16250,10 @@
         <v>947</v>
       </c>
       <c r="E308" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F308" t="s">
-        <v>994</v>
+        <v>1003</v>
       </c>
       <c r="G308" s="36" t="s">
         <v>18</v>
@@ -16273,16 +16276,16 @@
         <v>308</v>
       </c>
       <c r="D309" s="34" t="s">
-        <v>991</v>
+        <v>1007</v>
       </c>
       <c r="E309" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F309" t="s">
-        <v>995</v>
+        <v>1008</v>
       </c>
       <c r="G309" s="36" t="s">
-        <v>30</v>
+        <v>192</v>
       </c>
       <c r="H309" s="37" t="s">
         <v>215</v>
@@ -16291,7 +16294,7 @@
         <v>144</v>
       </c>
       <c r="M309" s="34" t="s">
-        <v>992</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="310" spans="1:13" x14ac:dyDescent="0.35">
@@ -16304,11 +16307,11 @@
       <c r="D310" s="35" t="s">
         <v>948</v>
       </c>
-      <c r="E310" s="36" t="s">
-        <v>16</v>
+      <c r="E310" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F310" t="s">
-        <v>996</v>
+        <v>1005</v>
       </c>
       <c r="G310" s="38" t="s">
         <v>18</v>
@@ -16334,10 +16337,10 @@
         <v>949</v>
       </c>
       <c r="E311" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F311" t="s">
-        <v>997</v>
+        <v>1004</v>
       </c>
       <c r="G311" s="36" t="s">
         <v>18</v>
@@ -16362,11 +16365,11 @@
       <c r="D312" s="35" t="s">
         <v>950</v>
       </c>
-      <c r="E312" s="36" t="s">
-        <v>16</v>
+      <c r="E312" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F312" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="G312" s="38" t="s">
         <v>18</v>
@@ -16392,10 +16395,10 @@
         <v>951</v>
       </c>
       <c r="E313" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F313" t="s">
-        <v>999</v>
+        <v>991</v>
       </c>
       <c r="G313" s="36" t="s">
         <v>18</v>
@@ -16420,11 +16423,11 @@
       <c r="D314" s="35" t="s">
         <v>952</v>
       </c>
-      <c r="E314" s="36" t="s">
-        <v>16</v>
+      <c r="E314" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F314" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
       <c r="G314" s="38" t="s">
         <v>18</v>
@@ -16450,10 +16453,10 @@
         <v>953</v>
       </c>
       <c r="E315" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F315" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="G315" s="36" t="s">
         <v>18</v>
@@ -16478,11 +16481,11 @@
       <c r="D316" s="35" t="s">
         <v>954</v>
       </c>
-      <c r="E316" s="36" t="s">
-        <v>16</v>
+      <c r="E316" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F316" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="G316" s="38" t="s">
         <v>18</v>
@@ -16508,10 +16511,10 @@
         <v>955</v>
       </c>
       <c r="E317" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F317" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="G317" s="36" t="s">
         <v>18</v>
@@ -16536,11 +16539,11 @@
       <c r="D318" s="35" t="s">
         <v>956</v>
       </c>
-      <c r="E318" s="36" t="s">
-        <v>16</v>
+      <c r="E318" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F318" t="s">
-        <v>1004</v>
+        <v>996</v>
       </c>
       <c r="G318" s="38" t="s">
         <v>18</v>
@@ -16566,10 +16569,10 @@
         <v>957</v>
       </c>
       <c r="E319" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F319" t="s">
-        <v>1005</v>
+        <v>997</v>
       </c>
       <c r="G319" s="36" t="s">
         <v>30</v>
@@ -16594,14 +16597,14 @@
       <c r="D320" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="E320" s="36" t="s">
-        <v>16</v>
+      <c r="E320" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F320" t="s">
-        <v>1006</v>
+        <v>998</v>
       </c>
       <c r="G320" s="38" t="s">
-        <v>18</v>
+        <v>563</v>
       </c>
       <c r="H320" s="39" t="s">
         <v>967</v>
@@ -16624,10 +16627,10 @@
         <v>958</v>
       </c>
       <c r="E321" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F321" t="s">
-        <v>1007</v>
+        <v>999</v>
       </c>
       <c r="G321" s="36" t="s">
         <v>18</v>
@@ -16652,11 +16655,11 @@
       <c r="D322" s="35" t="s">
         <v>959</v>
       </c>
-      <c r="E322" s="36" t="s">
-        <v>16</v>
+      <c r="E322" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F322" t="s">
-        <v>1008</v>
+        <v>1000</v>
       </c>
       <c r="G322" s="38" t="s">
         <v>30</v>
@@ -16682,10 +16685,10 @@
         <v>960</v>
       </c>
       <c r="E323" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F323" t="s">
-        <v>1009</v>
+        <v>1001</v>
       </c>
       <c r="G323" s="38" t="s">
         <v>30</v>
@@ -16710,11 +16713,11 @@
       <c r="D324" s="35" t="s">
         <v>961</v>
       </c>
-      <c r="E324" s="36" t="s">
-        <v>16</v>
+      <c r="E324" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F324" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="G324" s="38" t="s">
         <v>30</v>
@@ -16740,10 +16743,10 @@
         <v>962</v>
       </c>
       <c r="E325" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F325" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="G325" s="38" t="s">
         <v>30</v>
@@ -16768,11 +16771,11 @@
       <c r="D326" s="35" t="s">
         <v>963</v>
       </c>
-      <c r="E326" s="36" t="s">
-        <v>16</v>
+      <c r="E326" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F326" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="G326" s="38" t="s">
         <v>30</v>
@@ -16798,10 +16801,10 @@
         <v>964</v>
       </c>
       <c r="E327" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F327" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="G327" s="38" t="s">
         <v>30</v>
@@ -16826,11 +16829,11 @@
       <c r="D328" s="35" t="s">
         <v>965</v>
       </c>
-      <c r="E328" s="36" t="s">
-        <v>16</v>
+      <c r="E328" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F328" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="G328" s="38" t="s">
         <v>30</v>
@@ -16856,10 +16859,10 @@
         <v>966</v>
       </c>
       <c r="E329" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F329" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="G329" s="38" t="s">
         <v>30</v>
@@ -16882,13 +16885,13 @@
         <v>329</v>
       </c>
       <c r="D330" s="34" t="s">
-        <v>993</v>
+        <v>1011</v>
       </c>
       <c r="E330" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F330" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="G330" s="6" t="s">
         <v>30</v>
@@ -16917,10 +16920,10 @@
         <v>148</v>
       </c>
       <c r="E331" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F331" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="G331" t="s">
         <v>30</v>
@@ -20928,7 +20931,7 @@
         <v>266</v>
       </c>
       <c r="F18" t="s">
-        <v>990</v>
+        <v>1002</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>18</v>
@@ -21745,10 +21748,10 @@
         <v>947</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F2" t="s">
-        <v>994</v>
+        <v>1003</v>
       </c>
       <c r="G2" s="36" t="s">
         <v>18</v>
@@ -21771,16 +21774,16 @@
         <v>308</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>991</v>
+        <v>1007</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F3" t="s">
-        <v>995</v>
+        <v>1008</v>
       </c>
       <c r="G3" s="36" t="s">
-        <v>30</v>
+        <v>192</v>
       </c>
       <c r="H3" s="37" t="s">
         <v>215</v>
@@ -21789,7 +21792,7 @@
         <v>144</v>
       </c>
       <c r="M3" s="34" t="s">
-        <v>992</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -21802,11 +21805,11 @@
       <c r="D4" s="35" t="s">
         <v>948</v>
       </c>
-      <c r="E4" s="36" t="s">
-        <v>16</v>
+      <c r="E4" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F4" t="s">
-        <v>996</v>
+        <v>1005</v>
       </c>
       <c r="G4" s="38" t="s">
         <v>18</v>
@@ -21832,10 +21835,10 @@
         <v>949</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F5" t="s">
-        <v>997</v>
+        <v>1004</v>
       </c>
       <c r="G5" s="36" t="s">
         <v>18</v>
@@ -21860,11 +21863,11 @@
       <c r="D6" s="35" t="s">
         <v>950</v>
       </c>
-      <c r="E6" s="36" t="s">
-        <v>16</v>
+      <c r="E6" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F6" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="G6" s="38" t="s">
         <v>18</v>
@@ -21890,10 +21893,10 @@
         <v>951</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F7" t="s">
-        <v>999</v>
+        <v>991</v>
       </c>
       <c r="G7" s="36" t="s">
         <v>18</v>
@@ -21918,11 +21921,11 @@
       <c r="D8" s="35" t="s">
         <v>952</v>
       </c>
-      <c r="E8" s="36" t="s">
-        <v>16</v>
+      <c r="E8" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F8" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
       <c r="G8" s="38" t="s">
         <v>18</v>
@@ -21948,10 +21951,10 @@
         <v>953</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F9" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="G9" s="36" t="s">
         <v>18</v>
@@ -21976,11 +21979,11 @@
       <c r="D10" s="35" t="s">
         <v>954</v>
       </c>
-      <c r="E10" s="36" t="s">
-        <v>16</v>
+      <c r="E10" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F10" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="G10" s="38" t="s">
         <v>18</v>
@@ -22006,10 +22009,10 @@
         <v>955</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F11" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="G11" s="36" t="s">
         <v>18</v>
@@ -22034,11 +22037,11 @@
       <c r="D12" s="35" t="s">
         <v>956</v>
       </c>
-      <c r="E12" s="36" t="s">
-        <v>16</v>
+      <c r="E12" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F12" t="s">
-        <v>1004</v>
+        <v>996</v>
       </c>
       <c r="G12" s="38" t="s">
         <v>18</v>
@@ -22064,10 +22067,10 @@
         <v>957</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F13" t="s">
-        <v>1005</v>
+        <v>997</v>
       </c>
       <c r="G13" s="36" t="s">
         <v>30</v>
@@ -22092,14 +22095,14 @@
       <c r="D14" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="E14" s="36" t="s">
-        <v>16</v>
+      <c r="E14" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F14" t="s">
-        <v>1006</v>
+        <v>998</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>18</v>
+        <v>563</v>
       </c>
       <c r="H14" s="39" t="s">
         <v>967</v>
@@ -22122,10 +22125,10 @@
         <v>958</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F15" t="s">
-        <v>1007</v>
+        <v>999</v>
       </c>
       <c r="G15" s="36" t="s">
         <v>18</v>
@@ -22150,11 +22153,11 @@
       <c r="D16" s="35" t="s">
         <v>959</v>
       </c>
-      <c r="E16" s="36" t="s">
-        <v>16</v>
+      <c r="E16" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F16" t="s">
-        <v>1008</v>
+        <v>1000</v>
       </c>
       <c r="G16" s="38" t="s">
         <v>30</v>
@@ -22180,10 +22183,10 @@
         <v>960</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F17" t="s">
-        <v>1009</v>
+        <v>1001</v>
       </c>
       <c r="G17" s="38" t="s">
         <v>30</v>
@@ -22208,11 +22211,11 @@
       <c r="D18" s="35" t="s">
         <v>961</v>
       </c>
-      <c r="E18" s="36" t="s">
-        <v>16</v>
+      <c r="E18" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F18" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="G18" s="38" t="s">
         <v>30</v>
@@ -22238,10 +22241,10 @@
         <v>962</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F19" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="G19" s="38" t="s">
         <v>30</v>
@@ -22266,11 +22269,11 @@
       <c r="D20" s="35" t="s">
         <v>963</v>
       </c>
-      <c r="E20" s="36" t="s">
-        <v>16</v>
+      <c r="E20" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F20" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="G20" s="38" t="s">
         <v>30</v>
@@ -22296,10 +22299,10 @@
         <v>964</v>
       </c>
       <c r="E21" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F21" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="G21" s="38" t="s">
         <v>30</v>
@@ -22324,11 +22327,11 @@
       <c r="D22" s="35" t="s">
         <v>965</v>
       </c>
-      <c r="E22" s="36" t="s">
-        <v>16</v>
+      <c r="E22" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="F22" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="G22" s="38" t="s">
         <v>30</v>
@@ -22354,10 +22357,10 @@
         <v>966</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F23" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="G23" s="38" t="s">
         <v>30</v>
@@ -22380,13 +22383,13 @@
         <v>329</v>
       </c>
       <c r="D24" s="34" t="s">
-        <v>993</v>
+        <v>1011</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F24" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>30</v>
@@ -22415,10 +22418,10 @@
         <v>148</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="F25" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="G25" t="s">
         <v>30</v>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/Round 2 Pods for Testing/Fast Track Pods/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="528" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44576A22-C94D-406E-9A93-DB0211AEB78A}"/>
+  <xr:revisionPtr revIDLastSave="574" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{732AFFD1-6DEC-4C9D-926E-65D04E509589}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView xWindow="-28155" yWindow="405" windowWidth="27570" windowHeight="14985" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <sheet name="Registry_Metadata" sheetId="13" r:id="rId13"/>
     <sheet name="Validation_Metadata" sheetId="14" r:id="rId14"/>
     <sheet name="Verification_Metadata" sheetId="15" r:id="rId15"/>
+    <sheet name="VVB" sheetId="16" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Full List'!$A$1:$M$174</definedName>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7825" uniqueCount="1019">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8174" uniqueCount="1047">
   <si>
     <t>schema</t>
   </si>
@@ -2566,87 +2567,18 @@
     <t>crediting program</t>
   </si>
   <si>
-    <t>Describes the current registry, that contains the information about the project, and units</t>
-  </si>
-  <si>
-    <t>Describes the first registry, where the project was registered</t>
-  </si>
-  <si>
-    <t>Describes the Crediting Program that the proejct is following for the implementationunits</t>
-  </si>
-  <si>
-    <t>Date of the last update</t>
-  </si>
-  <si>
     <t>registry_identifier</t>
   </si>
   <si>
     <t>registry_name</t>
   </si>
   <si>
-    <t>registry_link</t>
-  </si>
-  <si>
-    <t>original_registry_identifier</t>
-  </si>
-  <si>
-    <t>original_registry_name</t>
-  </si>
-  <si>
-    <t>original_registry_link</t>
-  </si>
-  <si>
     <t>program_identifier</t>
   </si>
   <si>
     <t>program_name</t>
   </si>
   <si>
-    <t>creation_date</t>
-  </si>
-  <si>
-    <t>update_date</t>
-  </si>
-  <si>
-    <t>Date that the project was first registered</t>
-  </si>
-  <si>
-    <t>registry.creation_date</t>
-  </si>
-  <si>
-    <t>registry.update_date</t>
-  </si>
-  <si>
-    <t>registry.identification[].registry_identifier</t>
-  </si>
-  <si>
-    <t>registry.identification[].registry_name</t>
-  </si>
-  <si>
-    <t>registry.identification[].registry_link</t>
-  </si>
-  <si>
-    <t>registry.original[].original_registry_identifier</t>
-  </si>
-  <si>
-    <t>registry.original[].original_registry_name</t>
-  </si>
-  <si>
-    <t>registry.original[].original_registry_link</t>
-  </si>
-  <si>
-    <t>registry.program[].program_identifier</t>
-  </si>
-  <si>
-    <t>registry.program[].program_name</t>
-  </si>
-  <si>
-    <t>current_validation_stage</t>
-  </si>
-  <si>
-    <t>current_validation_stage_status</t>
-  </si>
-  <si>
     <t>date_previous_validation</t>
   </si>
   <si>
@@ -2659,24 +2591,6 @@
     <t>date_validation_requested</t>
   </si>
   <si>
-    <t>validation_body_accreditation</t>
-  </si>
-  <si>
-    <t>validation_body_id</t>
-  </si>
-  <si>
-    <t>validator_name</t>
-  </si>
-  <si>
-    <t>validation_body_sectoral_scopes</t>
-  </si>
-  <si>
-    <t>validation_body_selection</t>
-  </si>
-  <si>
-    <t>validation_body_team_members_and_roles</t>
-  </si>
-  <si>
     <t>validation_is_planned</t>
   </si>
   <si>
@@ -2710,12 +2624,6 @@
     <t>Validation and Verification Body (VVB)/ Certification Bodies/ Third Party Auditors</t>
   </si>
   <si>
-    <t>Name of the current validation step</t>
-  </si>
-  <si>
-    <t>Status of the current validation step</t>
-  </si>
-  <si>
     <t>Date of the previous validation event</t>
   </si>
   <si>
@@ -2758,15 +2666,9 @@
     <t>List any accreditations of the validation body</t>
   </si>
   <si>
-    <t>Identification number of the validation body</t>
-  </si>
-  <si>
     <t>Name of the validation body</t>
   </si>
   <si>
-    <t>Name(s) of the validator(s)</t>
-  </si>
-  <si>
     <t>List the sectoral scopes the validation body is accredited to validate</t>
   </si>
   <si>
@@ -2776,9 +2678,6 @@
     <t>List the names of any other validation body team members and their roles (FIRST NAME - LAST NAME, ROLE)</t>
   </si>
   <si>
-    <t>Date of validation event</t>
-  </si>
-  <si>
     <t>Indicate whether the valiation event is planned.</t>
   </si>
   <si>
@@ -2800,9 +2699,6 @@
     <t>Link (URL) to the document that contains the description and details of the validation event stages</t>
   </si>
   <si>
-    <t>Select all validation event stages</t>
-  </si>
-  <si>
     <t>Indicate whether the project has been validated.</t>
   </si>
   <si>
@@ -2830,39 +2726,6 @@
     <t>lca_system_boundary_overview</t>
   </si>
   <si>
-    <t>validation_body</t>
-  </si>
-  <si>
-    <t>validation.crediting_period[].current_crediting_period_end_date</t>
-  </si>
-  <si>
-    <t>project.validation_stage[].current_validation_stage</t>
-  </si>
-  <si>
-    <t>validation.stage[].validation_stage_document_link</t>
-  </si>
-  <si>
-    <t>validation.crediting_period[].current_crediting_period_number</t>
-  </si>
-  <si>
-    <t>project.validation_stage[].current_validation_stage_status</t>
-  </si>
-  <si>
-    <t>validation.crediting_period[].current_crediting_period_start_date</t>
-  </si>
-  <si>
-    <t>project.date[].date_previous_validation</t>
-  </si>
-  <si>
-    <t>validation.date[].date_validation_expiration</t>
-  </si>
-  <si>
-    <t>validation.date[].date_validation_planned</t>
-  </si>
-  <si>
-    <t>validation.date[].date_validation_requested</t>
-  </si>
-  <si>
     <t>validation.lca[].lca_completed</t>
   </si>
   <si>
@@ -2884,60 +2747,6 @@
     <t>validation.lca[].lca_system_boundary_overview</t>
   </si>
   <si>
-    <t>validation.validation_event[].validation_type</t>
-  </si>
-  <si>
-    <t>validation.validation_event[].validation_date</t>
-  </si>
-  <si>
-    <t>validation.validation_event[].validation_is_planned</t>
-  </si>
-  <si>
-    <t>validation.validation_event[].validation_period_end_date</t>
-  </si>
-  <si>
-    <t>validation.validation_event[].validation_period_start_date</t>
-  </si>
-  <si>
-    <t>validation.report[].validation_report_link</t>
-  </si>
-  <si>
-    <t>project.validation_status</t>
-  </si>
-  <si>
-    <t>validation.report[].validation_report_summary</t>
-  </si>
-  <si>
-    <t>validation.stage[].validation_stage_description</t>
-  </si>
-  <si>
-    <t>validation.stage[].validation_stages</t>
-  </si>
-  <si>
-    <t>validation.report[].validation_report_version</t>
-  </si>
-  <si>
-    <t>validation_body.details[].validation_body_accreditation</t>
-  </si>
-  <si>
-    <t>validation_body.details[].validation_body_id</t>
-  </si>
-  <si>
-    <t>validation_body.details[].validation_body_name</t>
-  </si>
-  <si>
-    <t>validation_body.details[].validator_name</t>
-  </si>
-  <si>
-    <t>validation_body.details[].validation_body_sectoral_scopes</t>
-  </si>
-  <si>
-    <t>validation_body.details[].validation_body_selection</t>
-  </si>
-  <si>
-    <t>validation_body.details[].validation_body_team_members_and_roles</t>
-  </si>
-  <si>
     <t>verification_id</t>
   </si>
   <si>
@@ -3103,9 +2912,6 @@
     <t>verification.verification_digital_signature_payload</t>
   </si>
   <si>
-    <t>validation.validation_event[].validation_id</t>
-  </si>
-  <si>
     <t>verification.verification_id</t>
   </si>
   <si>
@@ -3152,13 +2958,292 @@
   </si>
   <si>
     <t>verification.deductions[].verification_buffer_pool_deduction_quantity</t>
+  </si>
+  <si>
+    <t>validation.current_crediting_period_end_date</t>
+  </si>
+  <si>
+    <t>validation.current_crediting_period_number</t>
+  </si>
+  <si>
+    <t>validation.current_crediting_period_start_date</t>
+  </si>
+  <si>
+    <t>validation.date_previous_validation</t>
+  </si>
+  <si>
+    <t>validation.date_validation_expiration</t>
+  </si>
+  <si>
+    <t>validation.date_validation_planned</t>
+  </si>
+  <si>
+    <t>validation.date_validation_requested</t>
+  </si>
+  <si>
+    <t>validation_project_id</t>
+  </si>
+  <si>
+    <t>validation.validation_project_id</t>
+  </si>
+  <si>
+    <t>validation.validation_id</t>
+  </si>
+  <si>
+    <t>validation.validation_type</t>
+  </si>
+  <si>
+    <t>validation.validation_is_planned</t>
+  </si>
+  <si>
+    <t>validation.validation_period_end_date</t>
+  </si>
+  <si>
+    <t>validation.validation_period_start_date</t>
+  </si>
+  <si>
+    <t>validation.validation_report_link</t>
+  </si>
+  <si>
+    <t>validation.validation_report_summary</t>
+  </si>
+  <si>
+    <t>validation.validation_report_version</t>
+  </si>
+  <si>
+    <t>validation.validation_stage_description</t>
+  </si>
+  <si>
+    <t>validation.validation_stage_document_link</t>
+  </si>
+  <si>
+    <t>validation.validation_stages</t>
+  </si>
+  <si>
+    <t>Select all validation event stages planned for the project.</t>
+  </si>
+  <si>
+    <t>validation.status[].validation_status</t>
+  </si>
+  <si>
+    <t>validation_status_reason</t>
+  </si>
+  <si>
+    <t>validation.status[].validation_status_reason</t>
+  </si>
+  <si>
+    <t>The reason for updating the validation status</t>
+  </si>
+  <si>
+    <t>validation.status[].is_current</t>
+  </si>
+  <si>
+    <t>vvb_id</t>
+  </si>
+  <si>
+    <t>vvb</t>
+  </si>
+  <si>
+    <t>vvb.vvb_id</t>
+  </si>
+  <si>
+    <t>The identifier of the VVB</t>
+  </si>
+  <si>
+    <t>vvb_type</t>
+  </si>
+  <si>
+    <t>vvb.vvb_type</t>
+  </si>
+  <si>
+    <t>Indicate whether the VVB is acting as a validation body or a verification body.</t>
+  </si>
+  <si>
+    <t>accreditation</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>sectoral_scopes</t>
+  </si>
+  <si>
+    <t>selection</t>
+  </si>
+  <si>
+    <t>team_members_and_roles</t>
+  </si>
+  <si>
+    <t>vvb.accreditation</t>
+  </si>
+  <si>
+    <t>vvb.name</t>
+  </si>
+  <si>
+    <t>vvb.sectoral_scopes</t>
+  </si>
+  <si>
+    <t>vvb.selection</t>
+  </si>
+  <si>
+    <t>vvb.team_members_and_roles</t>
+  </si>
+  <si>
+    <t>project_registry_history</t>
+  </si>
+  <si>
+    <t>project_registry_history.project_identifier</t>
+  </si>
+  <si>
+    <t>CDOP project identifier of the project this registry history describes. Join key to the Project entity (same value as project.project_identifier).</t>
+  </si>
+  <si>
+    <t>last_updated_at</t>
+  </si>
+  <si>
+    <t>project_registry_history.last_updated_at</t>
+  </si>
+  <si>
+    <t>DateTime</t>
+  </si>
+  <si>
+    <t>Timestamp of the last modification of the source registry record for this project (not of the CDOP payload). Intended to be usable as a synchronisation watermark for incremental (delta) exports.</t>
+  </si>
+  <si>
+    <t>project_registry_history.registrations[].registry_identifier</t>
+  </si>
+  <si>
+    <t>Identifier of the registry on which the project is / was registered, taken from the CDOP registry list. References registry.registry_identifier. Unique across CDOP.</t>
+  </si>
+  <si>
+    <t>project_registry_history.registrations[].registry_name</t>
+  </si>
+  <si>
+    <t>Name of the registry on which the project is / was registered, from the CDOP controlled registry list.</t>
+  </si>
+  <si>
+    <t>registry_project_identifier</t>
+  </si>
+  <si>
+    <t>project_registry_history.registrations[].registry_project_identifier</t>
+  </si>
+  <si>
+    <t>Identifier assigned to the project by this registry (e.g. "VCS-1234"). Unique within the registry identified by registry_identifier.</t>
+  </si>
+  <si>
+    <t>registry_project_link</t>
+  </si>
+  <si>
+    <t>project_registry_history.registrations[].registry_project_link</t>
+  </si>
+  <si>
+    <t>URL of the project's public page on this registry (deep link to the project record, not the registry homepage).</t>
+  </si>
+  <si>
+    <t>registration_date</t>
+  </si>
+  <si>
+    <t>project_registry_history.registrations[].registration_date</t>
+  </si>
+  <si>
+    <t>Date on which the project was registered on this registry (effective start date of this registration). The earliest registration_date across registrations[] is the original registration.</t>
+  </si>
+  <si>
+    <t>registry_exit_date</t>
+  </si>
+  <si>
+    <t>project_registry_history.registrations[].registry_exit_date</t>
+  </si>
+  <si>
+    <t>Date on which the project left this registry (transfer out, withdrawal or rejection). Empty while the registration is active.</t>
+  </si>
+  <si>
+    <t>project_registry_history.registrations[].is_current</t>
+  </si>
+  <si>
+    <t>True for the registry that currently holds the project; False for previous registrations.</t>
+  </si>
+  <si>
+    <t>registration_status</t>
+  </si>
+  <si>
+    <t>project_registry_history.status[].registration_status</t>
+  </si>
+  <si>
+    <t>Status of the project on this registry. Registries map their internal workflow states into this short normalised list.</t>
+  </si>
+  <si>
+    <t>project_registry_history.status[].status_reason</t>
+  </si>
+  <si>
+    <t>Reason for a transfer, withdrawal or rejection on this registry.</t>
+  </si>
+  <si>
+    <t>project_registry_history.status[].is_current</t>
+  </si>
+  <si>
+    <t>project_registry_history.registrations[].program_identifier</t>
+  </si>
+  <si>
+    <t>Identifier of the crediting program under which the project is / was registered on this registry. References crediting_program.program_identifier.</t>
+  </si>
+  <si>
+    <t>registry_account_identifier</t>
+  </si>
+  <si>
+    <t>project_registry_history.registrations[].registry_account_identifier</t>
+  </si>
+  <si>
+    <t>Identifier of the registry account (e.g. project developer / proponent account) that holds the project on this registry.</t>
+  </si>
+  <si>
+    <t>registry_account_name</t>
+  </si>
+  <si>
+    <t>project_registry_history.registrations[].registry_account_name</t>
+  </si>
+  <si>
+    <t>Name of the registry account holder for the project on this registry.</t>
+  </si>
+  <si>
+    <t>crediting_program.program_identifier</t>
+  </si>
+  <si>
+    <t>Unique identifier of the crediting program (the rules / standard under which credits are issued). Distinct from the registry, which is the system that records projects and units.</t>
+  </si>
+  <si>
+    <t>crediting_program.program_name</t>
+  </si>
+  <si>
+    <t>Name of the crediting program, from the CDOP controlled crediting program list.</t>
+  </si>
+  <si>
+    <t>registry.registry_identifier</t>
+  </si>
+  <si>
+    <t>Unique identifier of the registry organisation / system in the CDOP registry list.</t>
+  </si>
+  <si>
+    <t>registry.registry_name</t>
+  </si>
+  <si>
+    <t>Official name of the registry organisation / system.</t>
+  </si>
+  <si>
+    <t>registry_website</t>
+  </si>
+  <si>
+    <t>registry.registry_website</t>
+  </si>
+  <si>
+    <t>Homepage URL of the registry organisation (as opposed to registry_project_link, the project's page).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3260,6 +3345,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -3317,7 +3407,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -3360,11 +3450,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3446,6 +3551,12 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3781,7 +3892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{752D3095-90A4-45FF-BD20-0492A3C6EFAC}">
-  <dimension ref="A1:M331"/>
+  <dimension ref="A1:M341"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="21.1796875" bestFit="1" customWidth="1"/>
@@ -14507,32 +14618,35 @@
       <c r="C262">
         <v>261</v>
       </c>
-      <c r="D262" s="25" t="s">
-        <v>827</v>
-      </c>
-      <c r="E262" t="s">
+      <c r="D262" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="E262" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F262" s="41" t="s">
+        <v>998</v>
+      </c>
+      <c r="G262" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H262" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="I262" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J262" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="F262" t="s">
-        <v>840</v>
-      </c>
-      <c r="G262" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H262" s="25" t="s">
-        <v>392</v>
-      </c>
-      <c r="I262" t="s">
-        <v>226</v>
-      </c>
-      <c r="J262" t="s">
-        <v>116</v>
-      </c>
-      <c r="L262" t="s">
-        <v>146</v>
-      </c>
-      <c r="M262" s="18" t="s">
-        <v>823</v>
+      <c r="K262" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="L262" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M262" s="41" t="s">
+        <v>999</v>
       </c>
     </row>
     <row r="263" spans="1:13" x14ac:dyDescent="0.35">
@@ -14545,32 +14659,35 @@
       <c r="C263">
         <v>262</v>
       </c>
-      <c r="D263" s="25" t="s">
-        <v>828</v>
-      </c>
-      <c r="E263" t="s">
+      <c r="D263" s="41" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E263" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F263" s="41" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G263" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H263" s="41" t="s">
+        <v>1002</v>
+      </c>
+      <c r="I263" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="J263" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="F263" t="s">
-        <v>841</v>
-      </c>
-      <c r="G263" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H263" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="I263" t="s">
-        <v>226</v>
-      </c>
-      <c r="J263" t="s">
-        <v>116</v>
-      </c>
-      <c r="L263" t="s">
-        <v>146</v>
-      </c>
-      <c r="M263" s="18" t="s">
-        <v>823</v>
+      <c r="K263" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L263" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M263" s="41" t="s">
+        <v>1003</v>
       </c>
     </row>
     <row r="264" spans="1:13" x14ac:dyDescent="0.35">
@@ -14583,32 +14700,35 @@
       <c r="C264">
         <v>263</v>
       </c>
-      <c r="D264" s="25" t="s">
-        <v>829</v>
-      </c>
-      <c r="E264" t="s">
+      <c r="D264" s="41" t="s">
+        <v>823</v>
+      </c>
+      <c r="E264" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F264" s="41" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G264" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H264" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="I264" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J264" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="F264" t="s">
-        <v>842</v>
-      </c>
-      <c r="G264" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H264" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="I264" t="s">
-        <v>226</v>
-      </c>
-      <c r="J264" t="s">
-        <v>116</v>
-      </c>
-      <c r="L264" t="s">
-        <v>146</v>
-      </c>
-      <c r="M264" s="18" t="s">
-        <v>823</v>
+      <c r="K264" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="L264" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M264" s="41" t="s">
+        <v>1005</v>
       </c>
     </row>
     <row r="265" spans="1:13" x14ac:dyDescent="0.35">
@@ -14621,32 +14741,35 @@
       <c r="C265">
         <v>264</v>
       </c>
-      <c r="D265" s="25" t="s">
-        <v>830</v>
-      </c>
-      <c r="E265" t="s">
+      <c r="D265" s="41" t="s">
+        <v>824</v>
+      </c>
+      <c r="E265" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F265" s="41" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G265" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H265" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="I265" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J265" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="F265" t="s">
-        <v>843</v>
-      </c>
-      <c r="G265" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H265" s="25" t="s">
-        <v>392</v>
-      </c>
-      <c r="I265" t="s">
-        <v>226</v>
-      </c>
-      <c r="J265" t="s">
-        <v>116</v>
-      </c>
-      <c r="L265" t="s">
-        <v>146</v>
-      </c>
-      <c r="M265" t="s">
-        <v>824</v>
+      <c r="K265" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="L265" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M265" s="41" t="s">
+        <v>1007</v>
       </c>
     </row>
     <row r="266" spans="1:13" x14ac:dyDescent="0.35">
@@ -14659,32 +14782,35 @@
       <c r="C266">
         <v>265</v>
       </c>
-      <c r="D266" s="25" t="s">
-        <v>831</v>
-      </c>
-      <c r="E266" t="s">
+      <c r="D266" s="41" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E266" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F266" s="41" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G266" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H266" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="I266" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J266" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="F266" t="s">
-        <v>844</v>
-      </c>
-      <c r="G266" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H266" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="I266" t="s">
-        <v>226</v>
-      </c>
-      <c r="J266" t="s">
-        <v>116</v>
-      </c>
-      <c r="L266" t="s">
-        <v>146</v>
-      </c>
-      <c r="M266" t="s">
-        <v>824</v>
+      <c r="K266" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="L266" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M266" s="41" t="s">
+        <v>1010</v>
       </c>
     </row>
     <row r="267" spans="1:13" x14ac:dyDescent="0.35">
@@ -14697,32 +14823,35 @@
       <c r="C267">
         <v>266</v>
       </c>
-      <c r="D267" s="25" t="s">
-        <v>832</v>
-      </c>
-      <c r="E267" t="s">
+      <c r="D267" s="41" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E267" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F267" s="41" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G267" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H267" s="41" t="s">
+        <v>903</v>
+      </c>
+      <c r="I267" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J267" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="F267" t="s">
-        <v>845</v>
-      </c>
-      <c r="G267" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H267" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="I267" t="s">
-        <v>226</v>
-      </c>
-      <c r="J267" t="s">
-        <v>116</v>
-      </c>
-      <c r="L267" t="s">
-        <v>146</v>
-      </c>
-      <c r="M267" t="s">
-        <v>824</v>
+      <c r="K267" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L267" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M267" s="41" t="s">
+        <v>1013</v>
       </c>
     </row>
     <row r="268" spans="1:13" x14ac:dyDescent="0.35">
@@ -14735,32 +14864,35 @@
       <c r="C268">
         <v>267</v>
       </c>
-      <c r="D268" s="25" t="s">
-        <v>833</v>
-      </c>
-      <c r="E268" t="s">
+      <c r="D268" s="41" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E268" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F268" s="41" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G268" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H268" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="I268" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J268" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="F268" t="s">
-        <v>846</v>
-      </c>
-      <c r="G268" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H268" s="25" t="s">
-        <v>392</v>
-      </c>
-      <c r="I268" t="s">
-        <v>226</v>
-      </c>
-      <c r="J268" t="s">
-        <v>822</v>
-      </c>
-      <c r="L268" t="s">
-        <v>146</v>
-      </c>
-      <c r="M268" s="18" t="s">
-        <v>825</v>
+      <c r="K268" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="L268" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M268" s="41" t="s">
+        <v>1016</v>
       </c>
     </row>
     <row r="269" spans="1:13" x14ac:dyDescent="0.35">
@@ -14773,32 +14905,35 @@
       <c r="C269">
         <v>268</v>
       </c>
-      <c r="D269" s="25" t="s">
-        <v>834</v>
-      </c>
-      <c r="E269" t="s">
+      <c r="D269" s="41" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E269" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F269" s="41" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G269" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H269" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="I269" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="J269" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="F269" t="s">
-        <v>847</v>
-      </c>
-      <c r="G269" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H269" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="I269" t="s">
-        <v>226</v>
-      </c>
-      <c r="J269" t="s">
-        <v>822</v>
-      </c>
-      <c r="L269" t="s">
-        <v>146</v>
-      </c>
-      <c r="M269" s="18" t="s">
-        <v>825</v>
+      <c r="K269" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L269" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M269" s="41" t="s">
+        <v>1019</v>
       </c>
     </row>
     <row r="270" spans="1:13" x14ac:dyDescent="0.35">
@@ -14811,29 +14946,35 @@
       <c r="C270">
         <v>269</v>
       </c>
-      <c r="D270" s="25" t="s">
-        <v>835</v>
-      </c>
-      <c r="E270" t="s">
+      <c r="D270" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="E270" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F270" s="41" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G270" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H270" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="I270" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J270" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="F270" t="s">
-        <v>838</v>
-      </c>
-      <c r="G270" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H270" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="I270" t="s">
-        <v>226</v>
-      </c>
-      <c r="L270" t="s">
-        <v>146</v>
-      </c>
-      <c r="M270" s="18" t="s">
-        <v>837</v>
+      <c r="K270" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L270" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M270" s="41" t="s">
+        <v>1021</v>
       </c>
     </row>
     <row r="271" spans="1:13" x14ac:dyDescent="0.35">
@@ -14846,29 +14987,35 @@
       <c r="C271">
         <v>270</v>
       </c>
-      <c r="D271" s="25" t="s">
-        <v>836</v>
-      </c>
-      <c r="E271" t="s">
+      <c r="D271" s="41" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E271" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F271" s="41" t="s">
+        <v>1023</v>
+      </c>
+      <c r="G271" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H271" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="I271" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="J271" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="F271" t="s">
-        <v>839</v>
-      </c>
-      <c r="G271" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="H271" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="I271" t="s">
-        <v>31</v>
-      </c>
-      <c r="L271" t="s">
-        <v>146</v>
-      </c>
-      <c r="M271" s="18" t="s">
-        <v>826</v>
+      <c r="K271" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L271" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M271" s="41" t="s">
+        <v>1024</v>
       </c>
     </row>
     <row r="272" spans="1:13" x14ac:dyDescent="0.35">
@@ -14881,32 +15028,35 @@
       <c r="C272">
         <v>271</v>
       </c>
-      <c r="D272" s="33" t="s">
-        <v>481</v>
-      </c>
-      <c r="E272" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F272" t="s">
-        <v>912</v>
-      </c>
-      <c r="G272" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="H272" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="I272" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="J272" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L272" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M272" s="6" t="s">
-        <v>482</v>
+      <c r="D272" s="41" t="s">
+        <v>462</v>
+      </c>
+      <c r="E272" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F272" s="41" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G272" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H272" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="I272" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="J272" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="K272" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L272" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M272" s="41" t="s">
+        <v>1026</v>
       </c>
     </row>
     <row r="273" spans="1:13" x14ac:dyDescent="0.35">
@@ -14919,35 +15069,38 @@
       <c r="C273">
         <v>272</v>
       </c>
-      <c r="D273" s="33" t="s">
-        <v>483</v>
-      </c>
-      <c r="E273" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F273" t="s">
-        <v>915</v>
-      </c>
-      <c r="G273" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="H273" s="33" t="s">
-        <v>392</v>
-      </c>
-      <c r="I273" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="J273" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L273" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M273" s="6" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="274" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="D273" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="E273" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F273" s="41" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G273" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H273" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="I273" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="J273" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="K273" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L273" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M273" s="41" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="274" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>13</v>
       </c>
@@ -14957,32 +15110,35 @@
       <c r="C274">
         <v>273</v>
       </c>
-      <c r="D274" s="33" t="s">
-        <v>479</v>
-      </c>
-      <c r="E274" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F274" t="s">
-        <v>917</v>
-      </c>
-      <c r="G274" s="33" t="s">
+      <c r="D274" s="41" t="s">
+        <v>825</v>
+      </c>
+      <c r="E274" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F274" s="41" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G274" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="H274" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="I274" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="J274" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L274" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M274" s="6" t="s">
-        <v>480</v>
+      <c r="H274" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="I274" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J274" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="K274" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L274" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M274" s="41" t="s">
+        <v>1029</v>
       </c>
     </row>
     <row r="275" spans="1:13" x14ac:dyDescent="0.35">
@@ -14995,32 +15151,35 @@
       <c r="C275">
         <v>274</v>
       </c>
-      <c r="D275" s="6" t="s">
-        <v>848</v>
-      </c>
-      <c r="E275" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F275" t="s">
-        <v>913</v>
-      </c>
-      <c r="G275" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H275" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="I275" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J275" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L275" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M275" s="6" t="s">
-        <v>871</v>
+      <c r="D275" s="41" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E275" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F275" s="41" t="s">
+        <v>1031</v>
+      </c>
+      <c r="G275" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H275" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="I275" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="J275" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="K275" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L275" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M275" s="41" t="s">
+        <v>1032</v>
       </c>
     </row>
     <row r="276" spans="1:13" x14ac:dyDescent="0.35">
@@ -15033,32 +15192,35 @@
       <c r="C276">
         <v>275</v>
       </c>
-      <c r="D276" s="6" t="s">
-        <v>849</v>
-      </c>
-      <c r="E276" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F276" t="s">
-        <v>916</v>
-      </c>
-      <c r="G276" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H276" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="I276" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J276" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L276" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M276" s="6" t="s">
-        <v>872</v>
+      <c r="D276" s="41" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E276" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F276" s="41" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G276" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H276" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="I276" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="J276" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="K276" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L276" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M276" s="41" t="s">
+        <v>1035</v>
       </c>
     </row>
     <row r="277" spans="1:13" x14ac:dyDescent="0.35">
@@ -15071,32 +15233,35 @@
       <c r="C277">
         <v>276</v>
       </c>
-      <c r="D277" s="6" t="s">
-        <v>850</v>
-      </c>
-      <c r="E277" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F277" t="s">
-        <v>918</v>
-      </c>
-      <c r="G277" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H277" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="I277" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J277" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L277" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M277" s="6" t="s">
-        <v>873</v>
+      <c r="D277" s="41" t="s">
+        <v>825</v>
+      </c>
+      <c r="E277" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="F277" s="41" t="s">
+        <v>1036</v>
+      </c>
+      <c r="G277" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H277" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="I277" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J277" s="41" t="s">
+        <v>822</v>
+      </c>
+      <c r="K277" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="L277" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M277" s="41" t="s">
+        <v>1037</v>
       </c>
     </row>
     <row r="278" spans="1:13" x14ac:dyDescent="0.35">
@@ -15109,32 +15274,35 @@
       <c r="C278">
         <v>277</v>
       </c>
-      <c r="D278" s="6" t="s">
-        <v>851</v>
-      </c>
-      <c r="E278" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F278" t="s">
-        <v>919</v>
-      </c>
-      <c r="G278" s="6" t="s">
+      <c r="D278" s="41" t="s">
+        <v>826</v>
+      </c>
+      <c r="E278" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="F278" s="41" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G278" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="H278" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="I278" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J278" s="6" t="s">
-        <v>870</v>
-      </c>
-      <c r="L278" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M278" s="6" t="s">
-        <v>874</v>
+      <c r="H278" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="I278" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J278" s="41" t="s">
+        <v>822</v>
+      </c>
+      <c r="K278" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="L278" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M278" s="41" t="s">
+        <v>1039</v>
       </c>
     </row>
     <row r="279" spans="1:13" x14ac:dyDescent="0.35">
@@ -15147,32 +15315,35 @@
       <c r="C279">
         <v>278</v>
       </c>
-      <c r="D279" s="6" t="s">
-        <v>852</v>
-      </c>
-      <c r="E279" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F279" t="s">
-        <v>920</v>
-      </c>
-      <c r="G279" s="6" t="s">
+      <c r="D279" s="41" t="s">
+        <v>823</v>
+      </c>
+      <c r="E279" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="F279" s="41" t="s">
+        <v>1040</v>
+      </c>
+      <c r="G279" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="H279" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="I279" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J279" s="6" t="s">
-        <v>870</v>
-      </c>
-      <c r="L279" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M279" s="6" t="s">
-        <v>875</v>
+      <c r="H279" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="I279" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J279" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="K279" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="L279" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M279" s="41" t="s">
+        <v>1041</v>
       </c>
     </row>
     <row r="280" spans="1:13" x14ac:dyDescent="0.35">
@@ -15185,32 +15356,35 @@
       <c r="C280">
         <v>279</v>
       </c>
-      <c r="D280" s="6" t="s">
-        <v>853</v>
-      </c>
-      <c r="E280" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F280" t="s">
-        <v>921</v>
-      </c>
-      <c r="G280" s="6" t="s">
+      <c r="D280" s="41" t="s">
+        <v>824</v>
+      </c>
+      <c r="E280" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="F280" s="41" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G280" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="H280" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="I280" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J280" s="6" t="s">
-        <v>870</v>
-      </c>
-      <c r="L280" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M280" s="6" t="s">
-        <v>876</v>
+      <c r="H280" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="I280" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J280" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="K280" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L280" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M280" s="41" t="s">
+        <v>1043</v>
       </c>
     </row>
     <row r="281" spans="1:13" x14ac:dyDescent="0.35">
@@ -15223,32 +15397,35 @@
       <c r="C281">
         <v>280</v>
       </c>
-      <c r="D281" s="6" t="s">
-        <v>904</v>
-      </c>
-      <c r="E281" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F281" t="s">
-        <v>922</v>
-      </c>
-      <c r="G281" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H281" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="I281" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J281" s="6" t="s">
-        <v>870</v>
-      </c>
-      <c r="L281" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M281" s="6" t="s">
-        <v>877</v>
+      <c r="D281" s="41" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E281" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="F281" s="41" t="s">
+        <v>1045</v>
+      </c>
+      <c r="G281" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H281" s="41" t="s">
+        <v>903</v>
+      </c>
+      <c r="I281" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="J281" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="K281" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L281" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M281" s="41" t="s">
+        <v>1046</v>
       </c>
     </row>
     <row r="282" spans="1:13" x14ac:dyDescent="0.35">
@@ -15261,32 +15438,35 @@
       <c r="C282">
         <v>281</v>
       </c>
-      <c r="D282" s="6" t="s">
-        <v>905</v>
+      <c r="D282" s="33" t="s">
+        <v>481</v>
       </c>
       <c r="E282" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F282" t="s">
-        <v>923</v>
-      </c>
-      <c r="G282" s="17" t="s">
-        <v>30</v>
+        <v>954</v>
+      </c>
+      <c r="G282" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="H282" s="6" t="s">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="I282" s="6" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="J282" s="6" t="s">
-        <v>870</v>
+        <v>445</v>
+      </c>
+      <c r="K282" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L282" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M282" s="6" t="s">
-        <v>878</v>
+        <v>482</v>
       </c>
     </row>
     <row r="283" spans="1:13" x14ac:dyDescent="0.35">
@@ -15299,35 +15479,38 @@
       <c r="C283">
         <v>282</v>
       </c>
-      <c r="D283" s="6" t="s">
-        <v>906</v>
+      <c r="D283" s="33" t="s">
+        <v>483</v>
       </c>
       <c r="E283" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F283" t="s">
-        <v>924</v>
-      </c>
-      <c r="G283" s="17" t="s">
-        <v>30</v>
+        <v>955</v>
+      </c>
+      <c r="G283" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="H283" s="6" t="s">
-        <v>159</v>
+        <v>392</v>
       </c>
       <c r="I283" s="6" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="J283" s="6" t="s">
-        <v>870</v>
+        <v>445</v>
+      </c>
+      <c r="K283" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L283" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M283" s="6" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.35">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="284" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>13</v>
       </c>
@@ -15337,32 +15520,35 @@
       <c r="C284">
         <v>283</v>
       </c>
-      <c r="D284" s="6" t="s">
-        <v>907</v>
+      <c r="D284" s="33" t="s">
+        <v>479</v>
       </c>
       <c r="E284" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F284" t="s">
-        <v>925</v>
-      </c>
-      <c r="G284" s="17" t="s">
-        <v>30</v>
+        <v>956</v>
+      </c>
+      <c r="G284" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="H284" s="6" t="s">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="I284" s="6" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="J284" s="6" t="s">
-        <v>870</v>
+        <v>445</v>
+      </c>
+      <c r="K284" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L284" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M284" s="6" t="s">
-        <v>880</v>
+        <v>480</v>
       </c>
     </row>
     <row r="285" spans="1:13" x14ac:dyDescent="0.35">
@@ -15376,31 +15562,34 @@
         <v>284</v>
       </c>
       <c r="D285" s="6" t="s">
-        <v>908</v>
+        <v>827</v>
       </c>
       <c r="E285" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F285" t="s">
-        <v>926</v>
+        <v>957</v>
       </c>
       <c r="G285" s="17" t="s">
         <v>30</v>
       </c>
       <c r="H285" s="6" t="s">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="I285" s="6" t="s">
         <v>144</v>
       </c>
       <c r="J285" s="6" t="s">
-        <v>870</v>
+        <v>445</v>
+      </c>
+      <c r="K285" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L285" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M285" s="6" t="s">
-        <v>881</v>
+        <v>842</v>
       </c>
     </row>
     <row r="286" spans="1:13" x14ac:dyDescent="0.35">
@@ -15414,31 +15603,34 @@
         <v>285</v>
       </c>
       <c r="D286" s="6" t="s">
-        <v>909</v>
+        <v>828</v>
       </c>
       <c r="E286" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F286" t="s">
-        <v>927</v>
-      </c>
-      <c r="G286" s="17" t="s">
-        <v>30</v>
+        <v>958</v>
+      </c>
+      <c r="G286" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="H286" s="6" t="s">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="I286" s="6" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="J286" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K286" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L286" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M286" s="6" t="s">
-        <v>882</v>
+        <v>843</v>
       </c>
     </row>
     <row r="287" spans="1:13" x14ac:dyDescent="0.35">
@@ -15452,31 +15644,34 @@
         <v>286</v>
       </c>
       <c r="D287" s="6" t="s">
-        <v>910</v>
+        <v>829</v>
       </c>
       <c r="E287" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F287" t="s">
-        <v>928</v>
-      </c>
-      <c r="G287" s="17" t="s">
-        <v>30</v>
+        <v>959</v>
+      </c>
+      <c r="G287" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="H287" s="6" t="s">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="I287" s="6" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="J287" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K287" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L287" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M287" s="6" t="s">
-        <v>883</v>
+        <v>844</v>
       </c>
     </row>
     <row r="288" spans="1:13" x14ac:dyDescent="0.35">
@@ -15487,34 +15682,37 @@
         <v>275</v>
       </c>
       <c r="C288">
-        <v>287</v>
-      </c>
-      <c r="D288" s="33" t="s">
-        <v>477</v>
+        <v>294</v>
+      </c>
+      <c r="D288" s="6" t="s">
+        <v>830</v>
       </c>
       <c r="E288" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F288" t="s">
-        <v>1002</v>
+        <v>960</v>
       </c>
       <c r="G288" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H288" s="6" t="s">
-        <v>392</v>
+        <v>219</v>
       </c>
       <c r="I288" s="6" t="s">
         <v>20</v>
       </c>
       <c r="J288" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K288" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L288" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M288" s="6" t="s">
-        <v>884</v>
+        <v>845</v>
       </c>
     </row>
     <row r="289" spans="1:13" x14ac:dyDescent="0.35">
@@ -15525,34 +15723,37 @@
         <v>275</v>
       </c>
       <c r="C289">
-        <v>288</v>
-      </c>
-      <c r="D289" s="30" t="s">
-        <v>511</v>
+        <v>295</v>
+      </c>
+      <c r="D289" s="6" t="s">
+        <v>869</v>
       </c>
       <c r="E289" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F289" t="s">
-        <v>929</v>
-      </c>
-      <c r="G289" s="6" t="s">
-        <v>18</v>
+        <v>876</v>
+      </c>
+      <c r="G289" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="H289" s="6" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="I289" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J289" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K289" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L289" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M289" s="6" t="s">
-        <v>885</v>
+        <v>846</v>
       </c>
     </row>
     <row r="290" spans="1:13" x14ac:dyDescent="0.35">
@@ -15563,34 +15764,37 @@
         <v>275</v>
       </c>
       <c r="C290">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="D290" s="6" t="s">
-        <v>854</v>
-      </c>
-      <c r="E290" s="6" t="s">
-        <v>911</v>
+        <v>870</v>
+      </c>
+      <c r="E290" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F290" t="s">
-        <v>940</v>
+        <v>877</v>
       </c>
       <c r="G290" s="17" t="s">
         <v>30</v>
       </c>
       <c r="H290" s="6" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="I290" s="6" t="s">
         <v>144</v>
       </c>
       <c r="J290" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K290" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L290" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M290" s="6" t="s">
-        <v>886</v>
+        <v>847</v>
       </c>
     </row>
     <row r="291" spans="1:13" x14ac:dyDescent="0.35">
@@ -15601,34 +15805,37 @@
         <v>275</v>
       </c>
       <c r="C291">
-        <v>290</v>
-      </c>
-      <c r="D291" s="17" t="s">
-        <v>855</v>
-      </c>
-      <c r="E291" s="6" t="s">
-        <v>911</v>
+        <v>297</v>
+      </c>
+      <c r="D291" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="E291" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F291" t="s">
-        <v>941</v>
-      </c>
-      <c r="G291" s="6" t="s">
-        <v>18</v>
+        <v>878</v>
+      </c>
+      <c r="G291" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="H291" s="6" t="s">
         <v>159</v>
       </c>
       <c r="I291" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J291" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K291" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L291" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M291" s="6" t="s">
-        <v>887</v>
+        <v>848</v>
       </c>
     </row>
     <row r="292" spans="1:13" x14ac:dyDescent="0.35">
@@ -15639,34 +15846,37 @@
         <v>275</v>
       </c>
       <c r="C292">
-        <v>291</v>
-      </c>
-      <c r="D292" s="17" t="s">
-        <v>265</v>
-      </c>
-      <c r="E292" s="6" t="s">
-        <v>911</v>
+        <v>298</v>
+      </c>
+      <c r="D292" s="6" t="s">
+        <v>872</v>
+      </c>
+      <c r="E292" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F292" t="s">
-        <v>942</v>
-      </c>
-      <c r="G292" s="6" t="s">
-        <v>18</v>
+        <v>879</v>
+      </c>
+      <c r="G292" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="H292" s="6" t="s">
         <v>159</v>
       </c>
       <c r="I292" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J292" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K292" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L292" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M292" s="6" t="s">
-        <v>888</v>
+        <v>849</v>
       </c>
     </row>
     <row r="293" spans="1:13" x14ac:dyDescent="0.35">
@@ -15677,34 +15887,37 @@
         <v>275</v>
       </c>
       <c r="C293">
-        <v>292</v>
-      </c>
-      <c r="D293" s="17" t="s">
-        <v>856</v>
-      </c>
-      <c r="E293" s="6" t="s">
-        <v>911</v>
+        <v>299</v>
+      </c>
+      <c r="D293" s="6" t="s">
+        <v>873</v>
+      </c>
+      <c r="E293" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F293" t="s">
-        <v>943</v>
-      </c>
-      <c r="G293" s="6" t="s">
-        <v>18</v>
+        <v>880</v>
+      </c>
+      <c r="G293" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="H293" s="6" t="s">
         <v>159</v>
       </c>
       <c r="I293" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J293" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K293" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L293" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M293" s="6" t="s">
-        <v>889</v>
+        <v>850</v>
       </c>
     </row>
     <row r="294" spans="1:13" x14ac:dyDescent="0.35">
@@ -15715,34 +15928,37 @@
         <v>275</v>
       </c>
       <c r="C294">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="D294" s="6" t="s">
-        <v>857</v>
-      </c>
-      <c r="E294" s="6" t="s">
-        <v>911</v>
+        <v>874</v>
+      </c>
+      <c r="E294" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F294" t="s">
-        <v>944</v>
-      </c>
-      <c r="G294" s="6" t="s">
-        <v>563</v>
+        <v>881</v>
+      </c>
+      <c r="G294" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="H294" s="6" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="I294" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J294" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K294" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L294" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M294" s="6" t="s">
-        <v>890</v>
+        <v>851</v>
       </c>
     </row>
     <row r="295" spans="1:13" x14ac:dyDescent="0.35">
@@ -15753,34 +15969,37 @@
         <v>275</v>
       </c>
       <c r="C295">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="D295" s="6" t="s">
-        <v>858</v>
-      </c>
-      <c r="E295" s="6" t="s">
-        <v>911</v>
+        <v>875</v>
+      </c>
+      <c r="E295" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F295" t="s">
-        <v>945</v>
-      </c>
-      <c r="G295" s="6" t="s">
-        <v>18</v>
+        <v>882</v>
+      </c>
+      <c r="G295" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="H295" s="6" t="s">
         <v>159</v>
       </c>
       <c r="I295" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J295" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K295" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L295" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M295" s="6" t="s">
-        <v>891</v>
+        <v>852</v>
       </c>
     </row>
     <row r="296" spans="1:13" x14ac:dyDescent="0.35">
@@ -15791,34 +16010,37 @@
         <v>275</v>
       </c>
       <c r="C296">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="D296" s="6" t="s">
-        <v>859</v>
-      </c>
-      <c r="E296" s="6" t="s">
-        <v>911</v>
+        <v>961</v>
+      </c>
+      <c r="E296" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F296" t="s">
-        <v>946</v>
-      </c>
-      <c r="G296" s="6" t="s">
-        <v>18</v>
+        <v>962</v>
+      </c>
+      <c r="G296" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="H296" s="6" t="s">
         <v>159</v>
       </c>
       <c r="I296" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J296" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K296" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L296" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M296" s="6" t="s">
-        <v>892</v>
+        <v>853</v>
       </c>
     </row>
     <row r="297" spans="1:13" x14ac:dyDescent="0.35">
@@ -15829,34 +16051,37 @@
         <v>275</v>
       </c>
       <c r="C297">
-        <v>296</v>
-      </c>
-      <c r="D297" s="17" t="s">
-        <v>269</v>
+        <v>303</v>
+      </c>
+      <c r="D297" s="33" t="s">
+        <v>477</v>
       </c>
       <c r="E297" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F297" t="s">
-        <v>930</v>
+        <v>963</v>
       </c>
       <c r="G297" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H297" s="6" t="s">
-        <v>219</v>
+        <v>392</v>
       </c>
       <c r="I297" s="6" t="s">
         <v>20</v>
       </c>
       <c r="J297" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K297" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L297" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M297" s="6" t="s">
-        <v>893</v>
+        <v>854</v>
       </c>
     </row>
     <row r="298" spans="1:13" x14ac:dyDescent="0.35">
@@ -15867,34 +16092,37 @@
         <v>275</v>
       </c>
       <c r="C298">
-        <v>297</v>
-      </c>
-      <c r="D298" s="6" t="s">
-        <v>860</v>
+        <v>304</v>
+      </c>
+      <c r="D298" s="30" t="s">
+        <v>511</v>
       </c>
       <c r="E298" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F298" t="s">
-        <v>931</v>
+        <v>964</v>
       </c>
       <c r="G298" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H298" s="6" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="I298" s="6" t="s">
         <v>20</v>
       </c>
       <c r="J298" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K298" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L298" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M298" s="6" t="s">
-        <v>894</v>
+        <v>852</v>
       </c>
     </row>
     <row r="299" spans="1:13" x14ac:dyDescent="0.35">
@@ -15905,34 +16133,37 @@
         <v>275</v>
       </c>
       <c r="C299">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D299" s="6" t="s">
-        <v>861</v>
+        <v>831</v>
       </c>
       <c r="E299" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F299" t="s">
-        <v>932</v>
+        <v>965</v>
       </c>
       <c r="G299" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H299" s="6" t="s">
-        <v>219</v>
+        <v>150</v>
       </c>
       <c r="I299" s="6" t="s">
         <v>20</v>
       </c>
       <c r="J299" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K299" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L299" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M299" s="6" t="s">
-        <v>895</v>
+        <v>860</v>
       </c>
     </row>
     <row r="300" spans="1:13" x14ac:dyDescent="0.35">
@@ -15943,16 +16174,16 @@
         <v>275</v>
       </c>
       <c r="C300">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="D300" s="6" t="s">
-        <v>862</v>
+        <v>832</v>
       </c>
       <c r="E300" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F300" t="s">
-        <v>933</v>
+        <v>966</v>
       </c>
       <c r="G300" s="6" t="s">
         <v>18</v>
@@ -15964,13 +16195,16 @@
         <v>20</v>
       </c>
       <c r="J300" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K300" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L300" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M300" s="6" t="s">
-        <v>896</v>
+        <v>861</v>
       </c>
     </row>
     <row r="301" spans="1:13" x14ac:dyDescent="0.35">
@@ -15981,34 +16215,37 @@
         <v>275</v>
       </c>
       <c r="C301">
-        <v>300</v>
-      </c>
-      <c r="D301" s="17" t="s">
-        <v>863</v>
+        <v>307</v>
+      </c>
+      <c r="D301" s="6" t="s">
+        <v>833</v>
       </c>
       <c r="E301" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F301" t="s">
-        <v>934</v>
-      </c>
-      <c r="G301" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H301" s="17" t="s">
-        <v>159</v>
+        <v>967</v>
+      </c>
+      <c r="G301" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H301" s="6" t="s">
+        <v>219</v>
       </c>
       <c r="I301" s="6" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="J301" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K301" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L301" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M301" s="17" t="s">
-        <v>897</v>
+      <c r="M301" s="6" t="s">
+        <v>862</v>
       </c>
     </row>
     <row r="302" spans="1:13" x14ac:dyDescent="0.35">
@@ -16019,16 +16256,16 @@
         <v>275</v>
       </c>
       <c r="C302">
-        <v>301</v>
-      </c>
-      <c r="D302" s="6" t="s">
-        <v>864</v>
+        <v>308</v>
+      </c>
+      <c r="D302" s="17" t="s">
+        <v>834</v>
       </c>
       <c r="E302" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F302" t="s">
-        <v>936</v>
+        <v>968</v>
       </c>
       <c r="G302" s="17" t="s">
         <v>30</v>
@@ -16040,13 +16277,16 @@
         <v>144</v>
       </c>
       <c r="J302" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K302" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L302" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M302" s="6" t="s">
-        <v>898</v>
+      <c r="M302" s="17" t="s">
+        <v>863</v>
       </c>
     </row>
     <row r="303" spans="1:13" x14ac:dyDescent="0.35">
@@ -16057,16 +16297,16 @@
         <v>275</v>
       </c>
       <c r="C303">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="D303" s="6" t="s">
-        <v>865</v>
+        <v>835</v>
       </c>
       <c r="E303" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F303" t="s">
-        <v>937</v>
+        <v>969</v>
       </c>
       <c r="G303" s="17" t="s">
         <v>30</v>
@@ -16078,13 +16318,16 @@
         <v>144</v>
       </c>
       <c r="J303" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K303" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L303" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M303" s="6" t="s">
-        <v>899</v>
+        <v>864</v>
       </c>
     </row>
     <row r="304" spans="1:13" x14ac:dyDescent="0.35">
@@ -16095,34 +16338,37 @@
         <v>275</v>
       </c>
       <c r="C304">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="D304" s="6" t="s">
-        <v>866</v>
+        <v>840</v>
       </c>
       <c r="E304" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F304" t="s">
-        <v>914</v>
+        <v>970</v>
       </c>
       <c r="G304" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="H304" s="17" t="s">
+      <c r="H304" s="6" t="s">
         <v>159</v>
       </c>
       <c r="I304" s="6" t="s">
         <v>144</v>
       </c>
       <c r="J304" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K304" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L304" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M304" s="6" t="s">
-        <v>900</v>
+        <v>868</v>
       </c>
     </row>
     <row r="305" spans="1:13" x14ac:dyDescent="0.35">
@@ -16133,34 +16379,37 @@
         <v>275</v>
       </c>
       <c r="C305">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="D305" s="6" t="s">
-        <v>867</v>
+        <v>836</v>
       </c>
       <c r="E305" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F305" t="s">
-        <v>938</v>
-      </c>
-      <c r="G305" s="6" t="s">
-        <v>563</v>
-      </c>
-      <c r="H305" s="6" t="s">
-        <v>143</v>
+        <v>971</v>
+      </c>
+      <c r="G305" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H305" s="17" t="s">
+        <v>159</v>
       </c>
       <c r="I305" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J305" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K305" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L305" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M305" s="6" t="s">
-        <v>901</v>
+        <v>865</v>
       </c>
     </row>
     <row r="306" spans="1:13" x14ac:dyDescent="0.35">
@@ -16171,34 +16420,37 @@
         <v>275</v>
       </c>
       <c r="C306">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="D306" s="6" t="s">
-        <v>868</v>
-      </c>
-      <c r="E306" s="6" t="s">
-        <v>16</v>
+        <v>837</v>
+      </c>
+      <c r="E306" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F306" t="s">
-        <v>935</v>
-      </c>
-      <c r="G306" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H306" s="6" t="s">
-        <v>150</v>
+        <v>972</v>
+      </c>
+      <c r="G306" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H306" s="17" t="s">
+        <v>159</v>
       </c>
       <c r="I306" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J306" s="6" t="s">
-        <v>445</v>
+        <v>841</v>
+      </c>
+      <c r="K306" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L306" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M306" s="6" t="s">
-        <v>902</v>
+        <v>866</v>
       </c>
     </row>
     <row r="307" spans="1:13" x14ac:dyDescent="0.35">
@@ -16209,121 +16461,160 @@
         <v>275</v>
       </c>
       <c r="C307">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="D307" s="6" t="s">
-        <v>869</v>
+        <v>838</v>
       </c>
       <c r="E307" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F307" t="s">
-        <v>939</v>
-      </c>
-      <c r="G307" s="17" t="s">
-        <v>30</v>
+        <v>973</v>
+      </c>
+      <c r="G307" s="6" t="s">
+        <v>563</v>
       </c>
       <c r="H307" s="6" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="I307" s="6" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="J307" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K307" s="6" t="s">
+        <v>163</v>
       </c>
       <c r="L307" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M307" s="6" t="s">
-        <v>903</v>
+        <v>974</v>
       </c>
     </row>
     <row r="308" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>13</v>
       </c>
+      <c r="B308" t="s">
+        <v>275</v>
+      </c>
       <c r="C308">
-        <v>307</v>
-      </c>
-      <c r="D308" s="34" t="s">
-        <v>947</v>
-      </c>
-      <c r="E308" s="36" t="s">
-        <v>990</v>
+        <v>314</v>
+      </c>
+      <c r="D308" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="E308" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F308" t="s">
-        <v>1003</v>
-      </c>
-      <c r="G308" s="36" t="s">
+        <v>975</v>
+      </c>
+      <c r="G308" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H308" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="I308" s="36" t="s">
+      <c r="H308" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I308" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M308" s="34" t="s">
-        <v>969</v>
+      <c r="J308" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="K308" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="L308" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M308" s="6" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="309" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>13</v>
       </c>
+      <c r="B309" t="s">
+        <v>275</v>
+      </c>
       <c r="C309">
-        <v>308</v>
-      </c>
-      <c r="D309" s="34" t="s">
-        <v>1007</v>
-      </c>
-      <c r="E309" s="36" t="s">
-        <v>990</v>
+        <v>315</v>
+      </c>
+      <c r="D309" s="6" t="s">
+        <v>976</v>
+      </c>
+      <c r="E309" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F309" t="s">
-        <v>1008</v>
-      </c>
-      <c r="G309" s="36" t="s">
-        <v>192</v>
-      </c>
-      <c r="H309" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="I309" s="36" t="s">
+        <v>977</v>
+      </c>
+      <c r="G309" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H309" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I309" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="M309" s="34" t="s">
-        <v>1009</v>
+      <c r="J309" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="K309" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="L309" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M309" t="s">
+        <v>978</v>
       </c>
     </row>
     <row r="310" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>13</v>
       </c>
+      <c r="B310" t="s">
+        <v>275</v>
+      </c>
       <c r="C310">
-        <v>309</v>
-      </c>
-      <c r="D310" s="35" t="s">
-        <v>948</v>
-      </c>
-      <c r="E310" s="38" t="s">
-        <v>990</v>
+        <v>316</v>
+      </c>
+      <c r="D310" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E310" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F310" t="s">
-        <v>1005</v>
-      </c>
-      <c r="G310" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="H310" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="I310" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M310" s="35" t="s">
-        <v>970</v>
+        <v>979</v>
+      </c>
+      <c r="G310" t="s">
+        <v>30</v>
+      </c>
+      <c r="H310" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I310" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J310" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="K310" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="L310" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M310" s="6" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="311" spans="1:13" x14ac:dyDescent="0.35">
@@ -16331,16 +16622,16 @@
         <v>13</v>
       </c>
       <c r="C311">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="D311" s="34" t="s">
-        <v>949</v>
+        <v>883</v>
       </c>
       <c r="E311" s="36" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F311" t="s">
-        <v>1004</v>
+        <v>938</v>
       </c>
       <c r="G311" s="36" t="s">
         <v>18</v>
@@ -16352,7 +16643,7 @@
         <v>20</v>
       </c>
       <c r="M311" s="34" t="s">
-        <v>971</v>
+        <v>905</v>
       </c>
     </row>
     <row r="312" spans="1:13" x14ac:dyDescent="0.35">
@@ -16360,28 +16651,28 @@
         <v>13</v>
       </c>
       <c r="C312">
-        <v>311</v>
-      </c>
-      <c r="D312" s="35" t="s">
-        <v>950</v>
-      </c>
-      <c r="E312" s="38" t="s">
-        <v>990</v>
+        <v>318</v>
+      </c>
+      <c r="D312" s="34" t="s">
+        <v>942</v>
+      </c>
+      <c r="E312" s="36" t="s">
+        <v>926</v>
       </c>
       <c r="F312" t="s">
-        <v>1006</v>
-      </c>
-      <c r="G312" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="H312" s="39" t="s">
+        <v>943</v>
+      </c>
+      <c r="G312" s="36" t="s">
+        <v>192</v>
+      </c>
+      <c r="H312" s="37" t="s">
         <v>215</v>
       </c>
-      <c r="I312" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M312" s="35" t="s">
-        <v>972</v>
+      <c r="I312" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M312" s="34" t="s">
+        <v>944</v>
       </c>
     </row>
     <row r="313" spans="1:13" x14ac:dyDescent="0.35">
@@ -16389,28 +16680,28 @@
         <v>13</v>
       </c>
       <c r="C313">
-        <v>312</v>
-      </c>
-      <c r="D313" s="34" t="s">
-        <v>951</v>
-      </c>
-      <c r="E313" s="36" t="s">
-        <v>990</v>
+        <v>319</v>
+      </c>
+      <c r="D313" s="35" t="s">
+        <v>884</v>
+      </c>
+      <c r="E313" s="38" t="s">
+        <v>926</v>
       </c>
       <c r="F313" t="s">
-        <v>991</v>
-      </c>
-      <c r="G313" s="36" t="s">
+        <v>940</v>
+      </c>
+      <c r="G313" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H313" s="37" t="s">
-        <v>219</v>
-      </c>
-      <c r="I313" s="36" t="s">
+      <c r="H313" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="I313" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="M313" s="34" t="s">
-        <v>973</v>
+      <c r="M313" s="35" t="s">
+        <v>906</v>
       </c>
     </row>
     <row r="314" spans="1:13" x14ac:dyDescent="0.35">
@@ -16418,28 +16709,28 @@
         <v>13</v>
       </c>
       <c r="C314">
-        <v>313</v>
-      </c>
-      <c r="D314" s="35" t="s">
-        <v>952</v>
-      </c>
-      <c r="E314" s="38" t="s">
-        <v>990</v>
+        <v>320</v>
+      </c>
+      <c r="D314" s="34" t="s">
+        <v>885</v>
+      </c>
+      <c r="E314" s="36" t="s">
+        <v>926</v>
       </c>
       <c r="F314" t="s">
-        <v>992</v>
-      </c>
-      <c r="G314" s="38" t="s">
+        <v>939</v>
+      </c>
+      <c r="G314" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="H314" s="39" t="s">
-        <v>219</v>
-      </c>
-      <c r="I314" s="38" t="s">
+      <c r="H314" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I314" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="M314" s="35" t="s">
-        <v>974</v>
+      <c r="M314" s="34" t="s">
+        <v>907</v>
       </c>
     </row>
     <row r="315" spans="1:13" x14ac:dyDescent="0.35">
@@ -16447,28 +16738,28 @@
         <v>13</v>
       </c>
       <c r="C315">
-        <v>314</v>
-      </c>
-      <c r="D315" s="34" t="s">
-        <v>953</v>
-      </c>
-      <c r="E315" s="36" t="s">
-        <v>990</v>
+        <v>321</v>
+      </c>
+      <c r="D315" s="35" t="s">
+        <v>886</v>
+      </c>
+      <c r="E315" s="38" t="s">
+        <v>926</v>
       </c>
       <c r="F315" t="s">
-        <v>993</v>
-      </c>
-      <c r="G315" s="36" t="s">
+        <v>941</v>
+      </c>
+      <c r="G315" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H315" s="37" t="s">
-        <v>219</v>
-      </c>
-      <c r="I315" s="36" t="s">
+      <c r="H315" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I315" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="M315" s="34" t="s">
-        <v>975</v>
+      <c r="M315" s="35" t="s">
+        <v>908</v>
       </c>
     </row>
     <row r="316" spans="1:13" x14ac:dyDescent="0.35">
@@ -16476,28 +16767,28 @@
         <v>13</v>
       </c>
       <c r="C316">
-        <v>315</v>
-      </c>
-      <c r="D316" s="35" t="s">
-        <v>954</v>
-      </c>
-      <c r="E316" s="38" t="s">
-        <v>990</v>
+        <v>322</v>
+      </c>
+      <c r="D316" s="34" t="s">
+        <v>887</v>
+      </c>
+      <c r="E316" s="36" t="s">
+        <v>926</v>
       </c>
       <c r="F316" t="s">
-        <v>994</v>
-      </c>
-      <c r="G316" s="38" t="s">
+        <v>927</v>
+      </c>
+      <c r="G316" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="H316" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="I316" s="38" t="s">
+      <c r="H316" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I316" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="M316" s="35" t="s">
-        <v>976</v>
+      <c r="M316" s="34" t="s">
+        <v>909</v>
       </c>
     </row>
     <row r="317" spans="1:13" x14ac:dyDescent="0.35">
@@ -16505,28 +16796,28 @@
         <v>13</v>
       </c>
       <c r="C317">
-        <v>316</v>
-      </c>
-      <c r="D317" s="34" t="s">
-        <v>955</v>
-      </c>
-      <c r="E317" s="36" t="s">
-        <v>990</v>
+        <v>323</v>
+      </c>
+      <c r="D317" s="35" t="s">
+        <v>888</v>
+      </c>
+      <c r="E317" s="38" t="s">
+        <v>926</v>
       </c>
       <c r="F317" t="s">
-        <v>995</v>
-      </c>
-      <c r="G317" s="36" t="s">
+        <v>928</v>
+      </c>
+      <c r="G317" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H317" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="I317" s="36" t="s">
+      <c r="H317" s="39" t="s">
+        <v>219</v>
+      </c>
+      <c r="I317" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="M317" s="34" t="s">
-        <v>977</v>
+      <c r="M317" s="35" t="s">
+        <v>910</v>
       </c>
     </row>
     <row r="318" spans="1:13" x14ac:dyDescent="0.35">
@@ -16534,28 +16825,28 @@
         <v>13</v>
       </c>
       <c r="C318">
-        <v>317</v>
-      </c>
-      <c r="D318" s="35" t="s">
-        <v>956</v>
-      </c>
-      <c r="E318" s="38" t="s">
-        <v>990</v>
+        <v>324</v>
+      </c>
+      <c r="D318" s="34" t="s">
+        <v>889</v>
+      </c>
+      <c r="E318" s="36" t="s">
+        <v>926</v>
       </c>
       <c r="F318" t="s">
-        <v>996</v>
-      </c>
-      <c r="G318" s="38" t="s">
+        <v>929</v>
+      </c>
+      <c r="G318" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="H318" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="I318" s="38" t="s">
+      <c r="H318" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I318" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="M318" s="35" t="s">
-        <v>978</v>
+      <c r="M318" s="34" t="s">
+        <v>911</v>
       </c>
     </row>
     <row r="319" spans="1:13" x14ac:dyDescent="0.35">
@@ -16563,28 +16854,28 @@
         <v>13</v>
       </c>
       <c r="C319">
-        <v>318</v>
-      </c>
-      <c r="D319" s="34" t="s">
-        <v>957</v>
-      </c>
-      <c r="E319" s="36" t="s">
-        <v>990</v>
+        <v>325</v>
+      </c>
+      <c r="D319" s="35" t="s">
+        <v>890</v>
+      </c>
+      <c r="E319" s="38" t="s">
+        <v>926</v>
       </c>
       <c r="F319" t="s">
-        <v>997</v>
-      </c>
-      <c r="G319" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="H319" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="I319" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="M319" s="34" t="s">
-        <v>979</v>
+        <v>930</v>
+      </c>
+      <c r="G319" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H319" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="I319" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M319" s="35" t="s">
+        <v>912</v>
       </c>
     </row>
     <row r="320" spans="1:13" x14ac:dyDescent="0.35">
@@ -16592,28 +16883,28 @@
         <v>13</v>
       </c>
       <c r="C320">
-        <v>319</v>
-      </c>
-      <c r="D320" s="35" t="s">
-        <v>288</v>
-      </c>
-      <c r="E320" s="38" t="s">
-        <v>990</v>
+        <v>326</v>
+      </c>
+      <c r="D320" s="34" t="s">
+        <v>891</v>
+      </c>
+      <c r="E320" s="36" t="s">
+        <v>926</v>
       </c>
       <c r="F320" t="s">
-        <v>998</v>
-      </c>
-      <c r="G320" s="38" t="s">
-        <v>563</v>
-      </c>
-      <c r="H320" s="39" t="s">
-        <v>967</v>
-      </c>
-      <c r="I320" s="38" t="s">
+        <v>931</v>
+      </c>
+      <c r="G320" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H320" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="I320" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="M320" s="35" t="s">
-        <v>980</v>
+      <c r="M320" s="34" t="s">
+        <v>913</v>
       </c>
     </row>
     <row r="321" spans="1:13" x14ac:dyDescent="0.35">
@@ -16621,28 +16912,28 @@
         <v>13</v>
       </c>
       <c r="C321">
-        <v>320</v>
-      </c>
-      <c r="D321" s="34" t="s">
-        <v>958</v>
-      </c>
-      <c r="E321" s="36" t="s">
-        <v>990</v>
+        <v>327</v>
+      </c>
+      <c r="D321" s="35" t="s">
+        <v>892</v>
+      </c>
+      <c r="E321" s="38" t="s">
+        <v>926</v>
       </c>
       <c r="F321" t="s">
-        <v>999</v>
-      </c>
-      <c r="G321" s="36" t="s">
+        <v>932</v>
+      </c>
+      <c r="G321" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H321" s="37" t="s">
+      <c r="H321" s="39" t="s">
         <v>215</v>
       </c>
-      <c r="I321" s="36" t="s">
+      <c r="I321" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="M321" s="34" t="s">
-        <v>981</v>
+      <c r="M321" s="35" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="322" spans="1:13" x14ac:dyDescent="0.35">
@@ -16650,57 +16941,57 @@
         <v>13</v>
       </c>
       <c r="C322">
-        <v>321</v>
-      </c>
-      <c r="D322" s="35" t="s">
-        <v>959</v>
-      </c>
-      <c r="E322" s="38" t="s">
-        <v>990</v>
+        <v>328</v>
+      </c>
+      <c r="D322" s="34" t="s">
+        <v>893</v>
+      </c>
+      <c r="E322" s="36" t="s">
+        <v>926</v>
       </c>
       <c r="F322" t="s">
-        <v>1000</v>
-      </c>
-      <c r="G322" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H322" s="39" t="s">
+        <v>933</v>
+      </c>
+      <c r="G322" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="H322" s="37" t="s">
         <v>215</v>
       </c>
-      <c r="I322" s="38" t="s">
+      <c r="I322" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="M322" s="35" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="323" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="M322" s="34" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="323" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>13</v>
       </c>
       <c r="C323">
-        <v>322</v>
-      </c>
-      <c r="D323" s="34" t="s">
-        <v>960</v>
-      </c>
-      <c r="E323" s="36" t="s">
-        <v>990</v>
+        <v>329</v>
+      </c>
+      <c r="D323" s="35" t="s">
+        <v>288</v>
+      </c>
+      <c r="E323" s="38" t="s">
+        <v>926</v>
       </c>
       <c r="F323" t="s">
-        <v>1001</v>
+        <v>934</v>
       </c>
       <c r="G323" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H323" s="37" t="s">
-        <v>968</v>
-      </c>
-      <c r="I323" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="M323" s="34" t="s">
-        <v>983</v>
+        <v>563</v>
+      </c>
+      <c r="H323" s="39" t="s">
+        <v>903</v>
+      </c>
+      <c r="I323" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M323" s="35" t="s">
+        <v>916</v>
       </c>
     </row>
     <row r="324" spans="1:13" x14ac:dyDescent="0.35">
@@ -16708,28 +16999,28 @@
         <v>13</v>
       </c>
       <c r="C324">
-        <v>323</v>
-      </c>
-      <c r="D324" s="35" t="s">
-        <v>961</v>
-      </c>
-      <c r="E324" s="38" t="s">
-        <v>990</v>
+        <v>330</v>
+      </c>
+      <c r="D324" s="34" t="s">
+        <v>894</v>
+      </c>
+      <c r="E324" s="36" t="s">
+        <v>926</v>
       </c>
       <c r="F324" t="s">
-        <v>1014</v>
-      </c>
-      <c r="G324" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H324" s="39" t="s">
-        <v>150</v>
-      </c>
-      <c r="I324" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="M324" s="35" t="s">
-        <v>984</v>
+        <v>935</v>
+      </c>
+      <c r="G324" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H324" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I324" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M324" s="34" t="s">
+        <v>917</v>
       </c>
     </row>
     <row r="325" spans="1:13" x14ac:dyDescent="0.35">
@@ -16737,57 +17028,57 @@
         <v>13</v>
       </c>
       <c r="C325">
-        <v>324</v>
-      </c>
-      <c r="D325" s="34" t="s">
-        <v>962</v>
-      </c>
-      <c r="E325" s="36" t="s">
-        <v>990</v>
+        <v>331</v>
+      </c>
+      <c r="D325" s="35" t="s">
+        <v>895</v>
+      </c>
+      <c r="E325" s="38" t="s">
+        <v>926</v>
       </c>
       <c r="F325" t="s">
-        <v>1015</v>
+        <v>936</v>
       </c>
       <c r="G325" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H325" s="37" t="s">
+      <c r="H325" s="39" t="s">
         <v>215</v>
       </c>
-      <c r="I325" s="36" t="s">
+      <c r="I325" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="M325" s="34" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M325" s="35" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="326" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>13</v>
       </c>
       <c r="C326">
-        <v>325</v>
-      </c>
-      <c r="D326" s="35" t="s">
-        <v>963</v>
-      </c>
-      <c r="E326" s="38" t="s">
-        <v>990</v>
+        <v>332</v>
+      </c>
+      <c r="D326" s="34" t="s">
+        <v>896</v>
+      </c>
+      <c r="E326" s="36" t="s">
+        <v>926</v>
       </c>
       <c r="F326" t="s">
-        <v>1016</v>
+        <v>937</v>
       </c>
       <c r="G326" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H326" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="I326" s="38" t="s">
+      <c r="H326" s="37" t="s">
+        <v>904</v>
+      </c>
+      <c r="I326" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="M326" s="35" t="s">
-        <v>986</v>
+      <c r="M326" s="34" t="s">
+        <v>919</v>
       </c>
     </row>
     <row r="327" spans="1:13" x14ac:dyDescent="0.35">
@@ -16795,28 +17086,28 @@
         <v>13</v>
       </c>
       <c r="C327">
-        <v>326</v>
-      </c>
-      <c r="D327" s="34" t="s">
-        <v>964</v>
-      </c>
-      <c r="E327" s="36" t="s">
-        <v>990</v>
+        <v>333</v>
+      </c>
+      <c r="D327" s="35" t="s">
+        <v>897</v>
+      </c>
+      <c r="E327" s="38" t="s">
+        <v>926</v>
       </c>
       <c r="F327" t="s">
-        <v>1017</v>
+        <v>949</v>
       </c>
       <c r="G327" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H327" s="37" t="s">
-        <v>316</v>
-      </c>
-      <c r="I327" s="36" t="s">
+      <c r="H327" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="I327" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="M327" s="34" t="s">
-        <v>987</v>
+      <c r="M327" s="35" t="s">
+        <v>920</v>
       </c>
     </row>
     <row r="328" spans="1:13" x14ac:dyDescent="0.35">
@@ -16824,28 +17115,28 @@
         <v>13</v>
       </c>
       <c r="C328">
-        <v>327</v>
-      </c>
-      <c r="D328" s="35" t="s">
-        <v>965</v>
-      </c>
-      <c r="E328" s="38" t="s">
-        <v>990</v>
+        <v>334</v>
+      </c>
+      <c r="D328" s="34" t="s">
+        <v>898</v>
+      </c>
+      <c r="E328" s="36" t="s">
+        <v>926</v>
       </c>
       <c r="F328" t="s">
-        <v>1018</v>
+        <v>950</v>
       </c>
       <c r="G328" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H328" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="I328" s="38" t="s">
+      <c r="H328" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I328" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="M328" s="35" t="s">
-        <v>988</v>
+      <c r="M328" s="34" t="s">
+        <v>921</v>
       </c>
     </row>
     <row r="329" spans="1:13" x14ac:dyDescent="0.35">
@@ -16853,28 +17144,28 @@
         <v>13</v>
       </c>
       <c r="C329">
-        <v>328</v>
-      </c>
-      <c r="D329" s="34" t="s">
-        <v>966</v>
-      </c>
-      <c r="E329" s="36" t="s">
-        <v>990</v>
+        <v>335</v>
+      </c>
+      <c r="D329" s="35" t="s">
+        <v>899</v>
+      </c>
+      <c r="E329" s="38" t="s">
+        <v>926</v>
       </c>
       <c r="F329" t="s">
-        <v>1010</v>
+        <v>951</v>
       </c>
       <c r="G329" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H329" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="I329" s="36" t="s">
+      <c r="H329" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="I329" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="M329" s="34" t="s">
-        <v>989</v>
+      <c r="M329" s="35" t="s">
+        <v>922</v>
       </c>
     </row>
     <row r="330" spans="1:13" x14ac:dyDescent="0.35">
@@ -16882,31 +17173,28 @@
         <v>13</v>
       </c>
       <c r="C330">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="D330" s="34" t="s">
-        <v>1011</v>
+        <v>900</v>
       </c>
       <c r="E330" s="36" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F330" t="s">
-        <v>1012</v>
-      </c>
-      <c r="G330" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H330" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="I330" s="6" t="s">
+        <v>952</v>
+      </c>
+      <c r="G330" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H330" s="37" t="s">
+        <v>316</v>
+      </c>
+      <c r="I330" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="J330" s="6"/>
-      <c r="K330" s="6"/>
-      <c r="L330" s="6"/>
-      <c r="M330" s="30" t="s">
-        <v>216</v>
+      <c r="M330" s="34" t="s">
+        <v>923</v>
       </c>
     </row>
     <row r="331" spans="1:13" x14ac:dyDescent="0.35">
@@ -16914,31 +17202,408 @@
         <v>13</v>
       </c>
       <c r="C331">
-        <v>330</v>
-      </c>
-      <c r="D331" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="D331" s="35" t="s">
+        <v>901</v>
+      </c>
+      <c r="E331" s="38" t="s">
+        <v>926</v>
+      </c>
+      <c r="F331" t="s">
+        <v>953</v>
+      </c>
+      <c r="G331" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H331" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="I331" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="M331" s="35" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="332" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A332" t="s">
+        <v>13</v>
+      </c>
+      <c r="C332">
+        <v>338</v>
+      </c>
+      <c r="D332" s="34" t="s">
+        <v>902</v>
+      </c>
+      <c r="E332" s="36" t="s">
+        <v>926</v>
+      </c>
+      <c r="F332" t="s">
+        <v>945</v>
+      </c>
+      <c r="G332" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H332" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="I332" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M332" s="34" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="333" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A333" t="s">
+        <v>13</v>
+      </c>
+      <c r="C333">
+        <v>339</v>
+      </c>
+      <c r="D333" s="34" t="s">
+        <v>946</v>
+      </c>
+      <c r="E333" s="36" t="s">
+        <v>926</v>
+      </c>
+      <c r="F333" t="s">
+        <v>947</v>
+      </c>
+      <c r="G333" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H333" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="I333" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J333" s="6"/>
+      <c r="K333" s="6"/>
+      <c r="L333" s="6"/>
+      <c r="M333" s="30" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="334" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A334" t="s">
+        <v>13</v>
+      </c>
+      <c r="C334">
+        <v>340</v>
+      </c>
+      <c r="D334" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="E331" s="36" t="s">
+      <c r="E334" s="36" t="s">
+        <v>926</v>
+      </c>
+      <c r="F334" t="s">
+        <v>948</v>
+      </c>
+      <c r="G334" t="s">
+        <v>30</v>
+      </c>
+      <c r="H334" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I334" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J334" s="6"/>
+      <c r="K334" s="6"/>
+      <c r="L334" s="6"/>
+      <c r="M334" s="6" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="335" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A335" t="s">
+        <v>13</v>
+      </c>
+      <c r="B335" t="s">
+        <v>275</v>
+      </c>
+      <c r="C335">
+        <v>341</v>
+      </c>
+      <c r="D335" s="40" t="s">
+        <v>980</v>
+      </c>
+      <c r="E335" s="40" t="s">
+        <v>981</v>
+      </c>
+      <c r="F335" s="40" t="s">
+        <v>982</v>
+      </c>
+      <c r="G335" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="H335" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="I335" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="J335" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="K335" t="s">
+        <v>163</v>
+      </c>
+      <c r="L335" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M335" s="34" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="336" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A336" t="s">
+        <v>13</v>
+      </c>
+      <c r="B336" t="s">
+        <v>275</v>
+      </c>
+      <c r="C336">
+        <v>342</v>
+      </c>
+      <c r="D336" s="40" t="s">
+        <v>984</v>
+      </c>
+      <c r="E336" s="40" t="s">
+        <v>981</v>
+      </c>
+      <c r="F336" s="40" t="s">
+        <v>985</v>
+      </c>
+      <c r="G336" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="H336" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="I336" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="J336" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="K336" t="s">
+        <v>163</v>
+      </c>
+      <c r="L336" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M336" s="40" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="337" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A337" t="s">
+        <v>13</v>
+      </c>
+      <c r="B337" t="s">
+        <v>275</v>
+      </c>
+      <c r="C337">
+        <v>343</v>
+      </c>
+      <c r="D337" s="6" t="s">
+        <v>987</v>
+      </c>
+      <c r="E337" s="40" t="s">
+        <v>981</v>
+      </c>
+      <c r="F337" t="s">
+        <v>992</v>
+      </c>
+      <c r="G337" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H337" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="I337" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J337" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="K337" t="s">
+        <v>163</v>
+      </c>
+      <c r="L337" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M337" s="6" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="338" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A338" t="s">
+        <v>13</v>
+      </c>
+      <c r="B338" t="s">
+        <v>275</v>
+      </c>
+      <c r="C338">
+        <v>344</v>
+      </c>
+      <c r="D338" s="17" t="s">
+        <v>988</v>
+      </c>
+      <c r="E338" s="40" t="s">
+        <v>981</v>
+      </c>
+      <c r="F338" t="s">
+        <v>993</v>
+      </c>
+      <c r="G338" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H338" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="I338" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J338" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="K338" t="s">
+        <v>163</v>
+      </c>
+      <c r="L338" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M338" s="6" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="339" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A339" t="s">
+        <v>13</v>
+      </c>
+      <c r="B339" t="s">
+        <v>275</v>
+      </c>
+      <c r="C339">
+        <v>345</v>
+      </c>
+      <c r="D339" s="6" t="s">
+        <v>989</v>
+      </c>
+      <c r="E339" s="40" t="s">
+        <v>981</v>
+      </c>
+      <c r="F339" t="s">
+        <v>994</v>
+      </c>
+      <c r="G339" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H339" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I339" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J339" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="K339" t="s">
+        <v>163</v>
+      </c>
+      <c r="L339" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M339" s="6" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="340" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A340" t="s">
+        <v>13</v>
+      </c>
+      <c r="B340" t="s">
+        <v>275</v>
+      </c>
+      <c r="C340">
+        <v>346</v>
+      </c>
+      <c r="D340" s="6" t="s">
         <v>990</v>
       </c>
-      <c r="F331" t="s">
-        <v>1013</v>
-      </c>
-      <c r="G331" t="s">
-        <v>30</v>
-      </c>
-      <c r="H331" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="I331" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J331" s="6"/>
-      <c r="K331" s="6"/>
-      <c r="L331" s="6"/>
-      <c r="M331" s="6" t="s">
-        <v>527</v>
+      <c r="E340" s="40" t="s">
+        <v>981</v>
+      </c>
+      <c r="F340" t="s">
+        <v>995</v>
+      </c>
+      <c r="G340" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H340" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="I340" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J340" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="K340" t="s">
+        <v>163</v>
+      </c>
+      <c r="L340" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M340" s="6" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="341" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A341" t="s">
+        <v>13</v>
+      </c>
+      <c r="B341" t="s">
+        <v>275</v>
+      </c>
+      <c r="C341">
+        <v>347</v>
+      </c>
+      <c r="D341" s="6" t="s">
+        <v>991</v>
+      </c>
+      <c r="E341" s="40" t="s">
+        <v>981</v>
+      </c>
+      <c r="F341" t="s">
+        <v>996</v>
+      </c>
+      <c r="G341" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H341" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="I341" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J341" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="K341" t="s">
+        <v>163</v>
+      </c>
+      <c r="L341" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M341" s="6" t="s">
+        <v>859</v>
       </c>
     </row>
   </sheetData>
@@ -19812,7 +20477,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DD793A8-CD91-4786-8377-89E3BC40F96B}">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="8.54296875" customWidth="1"/>
@@ -19879,32 +20544,35 @@
       <c r="C2">
         <v>261</v>
       </c>
-      <c r="D2" s="25" t="s">
-        <v>827</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="E2" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F2" s="41" t="s">
+        <v>998</v>
+      </c>
+      <c r="G2" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="I2" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J2" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="F2" t="s">
-        <v>840</v>
-      </c>
-      <c r="G2" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="25" t="s">
-        <v>392</v>
-      </c>
-      <c r="I2" t="s">
-        <v>226</v>
-      </c>
-      <c r="J2" t="s">
-        <v>116</v>
-      </c>
-      <c r="L2" t="s">
-        <v>146</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>823</v>
+      <c r="K2" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="L2" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M2" s="41" t="s">
+        <v>999</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -19917,32 +20585,35 @@
       <c r="C3">
         <v>262</v>
       </c>
-      <c r="D3" s="25" t="s">
-        <v>828</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="D3" s="41" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="41" t="s">
+        <v>1002</v>
+      </c>
+      <c r="I3" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="F3" t="s">
-        <v>841</v>
-      </c>
-      <c r="G3" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="I3" t="s">
-        <v>226</v>
-      </c>
-      <c r="J3" t="s">
-        <v>116</v>
-      </c>
-      <c r="L3" t="s">
-        <v>146</v>
-      </c>
-      <c r="M3" s="18" t="s">
-        <v>823</v>
+      <c r="K3" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L3" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M3" s="41" t="s">
+        <v>1003</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -19955,32 +20626,35 @@
       <c r="C4">
         <v>263</v>
       </c>
-      <c r="D4" s="25" t="s">
-        <v>829</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D4" s="41" t="s">
+        <v>823</v>
+      </c>
+      <c r="E4" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G4" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="I4" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J4" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="F4" t="s">
-        <v>842</v>
-      </c>
-      <c r="G4" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="I4" t="s">
-        <v>226</v>
-      </c>
-      <c r="J4" t="s">
-        <v>116</v>
-      </c>
-      <c r="L4" t="s">
-        <v>146</v>
-      </c>
-      <c r="M4" s="18" t="s">
-        <v>823</v>
+      <c r="K4" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="L4" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M4" s="41" t="s">
+        <v>1005</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -19993,32 +20667,35 @@
       <c r="C5">
         <v>264</v>
       </c>
-      <c r="D5" s="25" t="s">
-        <v>830</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="D5" s="41" t="s">
+        <v>824</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F5" s="41" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="I5" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J5" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="F5" t="s">
-        <v>843</v>
-      </c>
-      <c r="G5" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="25" t="s">
-        <v>392</v>
-      </c>
-      <c r="I5" t="s">
-        <v>226</v>
-      </c>
-      <c r="J5" t="s">
-        <v>116</v>
-      </c>
-      <c r="L5" t="s">
-        <v>146</v>
-      </c>
-      <c r="M5" t="s">
-        <v>824</v>
+      <c r="K5" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="L5" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M5" s="41" t="s">
+        <v>1007</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -20031,32 +20708,35 @@
       <c r="C6">
         <v>265</v>
       </c>
-      <c r="D6" s="25" t="s">
-        <v>831</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="D6" s="41" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F6" s="41" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G6" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="I6" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J6" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="F6" t="s">
-        <v>844</v>
-      </c>
-      <c r="G6" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="I6" t="s">
-        <v>226</v>
-      </c>
-      <c r="J6" t="s">
-        <v>116</v>
-      </c>
-      <c r="L6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M6" t="s">
-        <v>824</v>
+      <c r="K6" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="L6" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M6" s="41" t="s">
+        <v>1010</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -20069,32 +20749,35 @@
       <c r="C7">
         <v>266</v>
       </c>
-      <c r="D7" s="25" t="s">
-        <v>832</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="D7" s="41" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G7" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>903</v>
+      </c>
+      <c r="I7" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J7" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="F7" t="s">
-        <v>845</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="I7" t="s">
-        <v>226</v>
-      </c>
-      <c r="J7" t="s">
-        <v>116</v>
-      </c>
-      <c r="L7" t="s">
-        <v>146</v>
-      </c>
-      <c r="M7" t="s">
-        <v>824</v>
+      <c r="K7" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L7" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M7" s="41" t="s">
+        <v>1013</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -20107,32 +20790,35 @@
       <c r="C8">
         <v>267</v>
       </c>
-      <c r="D8" s="25" t="s">
-        <v>833</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="D8" s="41" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F8" s="41" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="I8" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J8" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="F8" t="s">
-        <v>846</v>
-      </c>
-      <c r="G8" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="25" t="s">
-        <v>392</v>
-      </c>
-      <c r="I8" t="s">
-        <v>226</v>
-      </c>
-      <c r="J8" t="s">
-        <v>822</v>
-      </c>
-      <c r="L8" t="s">
-        <v>146</v>
-      </c>
-      <c r="M8" s="18" t="s">
-        <v>825</v>
+      <c r="K8" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="L8" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M8" s="41" t="s">
+        <v>1016</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -20145,32 +20831,35 @@
       <c r="C9">
         <v>268</v>
       </c>
-      <c r="D9" s="25" t="s">
-        <v>834</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="D9" s="41" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F9" s="41" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G9" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="I9" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="F9" t="s">
-        <v>847</v>
-      </c>
-      <c r="G9" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="I9" t="s">
-        <v>226</v>
-      </c>
-      <c r="J9" t="s">
-        <v>822</v>
-      </c>
-      <c r="L9" t="s">
-        <v>146</v>
-      </c>
-      <c r="M9" s="18" t="s">
-        <v>825</v>
+      <c r="K9" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L9" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M9" s="41" t="s">
+        <v>1019</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
@@ -20183,29 +20872,35 @@
       <c r="C10">
         <v>269</v>
       </c>
-      <c r="D10" s="25" t="s">
-        <v>835</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="D10" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="E10" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F10" s="41" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G10" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="I10" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J10" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="F10" t="s">
-        <v>838</v>
-      </c>
-      <c r="G10" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="I10" t="s">
-        <v>226</v>
-      </c>
-      <c r="L10" t="s">
-        <v>146</v>
-      </c>
-      <c r="M10" s="18" t="s">
-        <v>837</v>
+      <c r="K10" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L10" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M10" s="41" t="s">
+        <v>1021</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -20218,29 +20913,445 @@
       <c r="C11">
         <v>270</v>
       </c>
-      <c r="D11" s="25" t="s">
-        <v>836</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="D11" s="41" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E11" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>1023</v>
+      </c>
+      <c r="G11" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="I11" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="F11" t="s">
-        <v>839</v>
-      </c>
-      <c r="G11" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="K11" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L11" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M11" s="41" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C12">
+        <v>271</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>462</v>
+      </c>
+      <c r="E12" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F12" s="41" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G12" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="I12" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="L11" t="s">
-        <v>146</v>
-      </c>
-      <c r="M11" s="18" t="s">
+      <c r="J12" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="K12" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L12" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M12" s="41" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>275</v>
+      </c>
+      <c r="C13">
+        <v>272</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="E13" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F13" s="41" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G13" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="I13" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="K13" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L13" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M13" s="41" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>275</v>
+      </c>
+      <c r="C14">
+        <v>273</v>
+      </c>
+      <c r="D14" s="41" t="s">
+        <v>825</v>
+      </c>
+      <c r="E14" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F14" s="41" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G14" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="I14" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J14" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="K14" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L14" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M14" s="41" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C15">
+        <v>274</v>
+      </c>
+      <c r="D15" s="41" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E15" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F15" s="41" t="s">
+        <v>1031</v>
+      </c>
+      <c r="G15" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="I15" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="K15" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L15" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M15" s="41" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>275</v>
+      </c>
+      <c r="C16">
+        <v>275</v>
+      </c>
+      <c r="D16" s="41" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E16" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F16" s="41" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G16" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="I16" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="K16" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L16" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M16" s="41" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>275</v>
+      </c>
+      <c r="C17">
+        <v>276</v>
+      </c>
+      <c r="D17" s="41" t="s">
+        <v>825</v>
+      </c>
+      <c r="E17" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="F17" s="41" t="s">
+        <v>1036</v>
+      </c>
+      <c r="G17" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="I17" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J17" s="41" t="s">
+        <v>822</v>
+      </c>
+      <c r="K17" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="L17" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M17" s="41" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>275</v>
+      </c>
+      <c r="C18">
+        <v>277</v>
+      </c>
+      <c r="D18" s="41" t="s">
         <v>826</v>
+      </c>
+      <c r="E18" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="F18" s="41" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="I18" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J18" s="41" t="s">
+        <v>822</v>
+      </c>
+      <c r="K18" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="L18" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M18" s="41" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>275</v>
+      </c>
+      <c r="C19">
+        <v>278</v>
+      </c>
+      <c r="D19" s="41" t="s">
+        <v>823</v>
+      </c>
+      <c r="E19" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="F19" s="41" t="s">
+        <v>1040</v>
+      </c>
+      <c r="G19" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="I19" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J19" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="K19" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="L19" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M19" s="41" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>275</v>
+      </c>
+      <c r="C20">
+        <v>279</v>
+      </c>
+      <c r="D20" s="41" t="s">
+        <v>824</v>
+      </c>
+      <c r="E20" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" s="41" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G20" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="I20" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J20" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="K20" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L20" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M20" s="41" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s">
+        <v>275</v>
+      </c>
+      <c r="C21">
+        <v>280</v>
+      </c>
+      <c r="D21" s="41" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E21" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="F21" s="41" t="s">
+        <v>1045</v>
+      </c>
+      <c r="G21" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21" s="41" t="s">
+        <v>903</v>
+      </c>
+      <c r="I21" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="J21" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="K21" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="L21" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M21" s="41" t="s">
+        <v>1046</v>
       </c>
     </row>
   </sheetData>
@@ -20250,7 +21361,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF337E51-0D9D-46A6-9DB2-8DF5F9FC1667}">
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="43.6328125" customWidth="1"/>
@@ -20314,7 +21425,7 @@
         <v>275</v>
       </c>
       <c r="C2">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="D2" s="33" t="s">
         <v>481</v>
@@ -20323,20 +21434,23 @@
         <v>266</v>
       </c>
       <c r="F2" t="s">
-        <v>912</v>
-      </c>
-      <c r="G2" s="33" t="s">
+        <v>954</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="H2" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="I2" s="33" t="s">
+      <c r="I2" s="6" t="s">
         <v>20</v>
       </c>
       <c r="J2" s="6" t="s">
         <v>445</v>
       </c>
+      <c r="K2" s="6" t="s">
+        <v>145</v>
+      </c>
       <c r="L2" s="6" t="s">
         <v>146</v>
       </c>
@@ -20352,7 +21466,7 @@
         <v>275</v>
       </c>
       <c r="C3">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="D3" s="33" t="s">
         <v>483</v>
@@ -20361,20 +21475,23 @@
         <v>266</v>
       </c>
       <c r="F3" t="s">
-        <v>915</v>
-      </c>
-      <c r="G3" s="33" t="s">
+        <v>955</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="33" t="s">
+      <c r="H3" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="I3" s="33" t="s">
+      <c r="I3" s="6" t="s">
         <v>20</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>445</v>
       </c>
+      <c r="K3" s="6" t="s">
+        <v>145</v>
+      </c>
       <c r="L3" s="6" t="s">
         <v>146</v>
       </c>
@@ -20390,7 +21507,7 @@
         <v>275</v>
       </c>
       <c r="C4">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="D4" s="33" t="s">
         <v>479</v>
@@ -20399,20 +21516,23 @@
         <v>266</v>
       </c>
       <c r="F4" t="s">
-        <v>917</v>
-      </c>
-      <c r="G4" s="33" t="s">
+        <v>956</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="H4" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="I4" s="33" t="s">
+      <c r="I4" s="6" t="s">
         <v>20</v>
       </c>
       <c r="J4" s="6" t="s">
         <v>445</v>
       </c>
+      <c r="K4" s="6" t="s">
+        <v>145</v>
+      </c>
       <c r="L4" s="6" t="s">
         <v>146</v>
       </c>
@@ -20428,34 +21548,37 @@
         <v>275</v>
       </c>
       <c r="C5">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>848</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>16</v>
+        <v>827</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F5" t="s">
-        <v>913</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>18</v>
+        <v>957</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>143</v>
+        <v>219</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>445</v>
       </c>
+      <c r="K5" s="6" t="s">
+        <v>145</v>
+      </c>
       <c r="L5" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>871</v>
+        <v>842</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -20466,34 +21589,37 @@
         <v>275</v>
       </c>
       <c r="C6">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>849</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>16</v>
+        <v>828</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F6" t="s">
-        <v>916</v>
+        <v>958</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>143</v>
+        <v>219</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>20</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>445</v>
+        <v>841</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>872</v>
+        <v>843</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -20504,34 +21630,37 @@
         <v>275</v>
       </c>
       <c r="C7">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>850</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>16</v>
+        <v>829</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F7" t="s">
-        <v>918</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>30</v>
+        <v>959</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>219</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>445</v>
+        <v>841</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>873</v>
+        <v>844</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -20542,16 +21671,16 @@
         <v>275</v>
       </c>
       <c r="C8">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>851</v>
+        <v>830</v>
       </c>
       <c r="E8" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F8" t="s">
-        <v>919</v>
+        <v>960</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>18</v>
@@ -20563,13 +21692,16 @@
         <v>20</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>874</v>
+        <v>845</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -20580,34 +21712,37 @@
         <v>275</v>
       </c>
       <c r="C9">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>852</v>
+        <v>869</v>
       </c>
       <c r="E9" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F9" t="s">
-        <v>920</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>18</v>
+        <v>876</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>219</v>
+        <v>150</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>875</v>
+        <v>846</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
@@ -20618,34 +21753,37 @@
         <v>275</v>
       </c>
       <c r="C10">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>853</v>
+        <v>870</v>
       </c>
       <c r="E10" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F10" t="s">
-        <v>921</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>18</v>
+        <v>877</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>219</v>
+        <v>150</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>876</v>
+        <v>847</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -20656,34 +21794,37 @@
         <v>275</v>
       </c>
       <c r="C11">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>904</v>
+        <v>871</v>
       </c>
       <c r="E11" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F11" t="s">
-        <v>922</v>
+        <v>878</v>
       </c>
       <c r="G11" s="17" t="s">
         <v>30</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>144</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>877</v>
+        <v>848</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -20694,34 +21835,37 @@
         <v>275</v>
       </c>
       <c r="C12">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>905</v>
+        <v>872</v>
       </c>
       <c r="E12" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F12" t="s">
-        <v>923</v>
+        <v>879</v>
       </c>
       <c r="G12" s="17" t="s">
         <v>30</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>144</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>878</v>
+        <v>849</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -20732,16 +21876,16 @@
         <v>275</v>
       </c>
       <c r="C13">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>906</v>
+        <v>873</v>
       </c>
       <c r="E13" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F13" t="s">
-        <v>924</v>
+        <v>880</v>
       </c>
       <c r="G13" s="17" t="s">
         <v>30</v>
@@ -20753,13 +21897,16 @@
         <v>144</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>879</v>
+        <v>850</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -20770,16 +21917,16 @@
         <v>275</v>
       </c>
       <c r="C14">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>907</v>
+        <v>874</v>
       </c>
       <c r="E14" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F14" t="s">
-        <v>925</v>
+        <v>881</v>
       </c>
       <c r="G14" s="17" t="s">
         <v>30</v>
@@ -20791,13 +21938,16 @@
         <v>144</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>880</v>
+        <v>851</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -20808,16 +21958,16 @@
         <v>275</v>
       </c>
       <c r="C15">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>908</v>
+        <v>875</v>
       </c>
       <c r="E15" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F15" t="s">
-        <v>926</v>
+        <v>882</v>
       </c>
       <c r="G15" s="17" t="s">
         <v>30</v>
@@ -20829,13 +21979,16 @@
         <v>144</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>881</v>
+        <v>852</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -20846,16 +21999,16 @@
         <v>275</v>
       </c>
       <c r="C16">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>909</v>
+        <v>961</v>
       </c>
       <c r="E16" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F16" t="s">
-        <v>927</v>
+        <v>962</v>
       </c>
       <c r="G16" s="17" t="s">
         <v>30</v>
@@ -20867,13 +22020,16 @@
         <v>144</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>882</v>
+        <v>853</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
@@ -20884,34 +22040,37 @@
         <v>275</v>
       </c>
       <c r="C17">
-        <v>286</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>910</v>
+        <v>303</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>477</v>
       </c>
       <c r="E17" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F17" t="s">
-        <v>928</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>30</v>
+        <v>963</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>159</v>
+        <v>392</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>883</v>
+        <v>854</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
@@ -20922,34 +22081,37 @@
         <v>275</v>
       </c>
       <c r="C18">
-        <v>287</v>
-      </c>
-      <c r="D18" s="33" t="s">
-        <v>477</v>
+        <v>304</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>511</v>
       </c>
       <c r="E18" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F18" t="s">
-        <v>1002</v>
+        <v>964</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>392</v>
+        <v>143</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>20</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L18" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>884</v>
+        <v>852</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
@@ -20960,34 +22122,37 @@
         <v>275</v>
       </c>
       <c r="C19">
-        <v>288</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>511</v>
+        <v>305</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>831</v>
       </c>
       <c r="E19" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F19" t="s">
-        <v>929</v>
+        <v>965</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>20</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>885</v>
+        <v>860</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
@@ -20998,34 +22163,37 @@
         <v>275</v>
       </c>
       <c r="C20">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>854</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>911</v>
+        <v>832</v>
+      </c>
+      <c r="E20" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F20" t="s">
-        <v>940</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>30</v>
+        <v>966</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>886</v>
+        <v>861</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
@@ -21036,34 +22204,37 @@
         <v>275</v>
       </c>
       <c r="C21">
-        <v>290</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>855</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>911</v>
+        <v>307</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>833</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F21" t="s">
-        <v>941</v>
+        <v>967</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>20</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>887</v>
+        <v>862</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
@@ -21074,34 +22245,37 @@
         <v>275</v>
       </c>
       <c r="C22">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>265</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>911</v>
+        <v>834</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F22" t="s">
-        <v>942</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" s="6" t="s">
+        <v>968</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="17" t="s">
         <v>159</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M22" s="6" t="s">
-        <v>888</v>
+      <c r="M22" s="17" t="s">
+        <v>863</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
@@ -21112,34 +22286,37 @@
         <v>275</v>
       </c>
       <c r="C23">
-        <v>292</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>856</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>911</v>
+        <v>309</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="E23" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F23" t="s">
-        <v>943</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H23" s="6" t="s">
+        <v>969</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H23" s="17" t="s">
         <v>159</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L23" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>889</v>
+        <v>864</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
@@ -21150,34 +22327,37 @@
         <v>275</v>
       </c>
       <c r="C24">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>857</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>911</v>
+        <v>840</v>
+      </c>
+      <c r="E24" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F24" t="s">
-        <v>944</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>563</v>
+        <v>970</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L24" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>890</v>
+        <v>868</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
@@ -21188,34 +22368,37 @@
         <v>275</v>
       </c>
       <c r="C25">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>858</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>911</v>
+        <v>836</v>
+      </c>
+      <c r="E25" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F25" t="s">
-        <v>945</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H25" s="6" t="s">
+        <v>971</v>
+      </c>
+      <c r="G25" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25" s="17" t="s">
         <v>159</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L25" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>891</v>
+        <v>865</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
@@ -21226,34 +22409,37 @@
         <v>275</v>
       </c>
       <c r="C26">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>859</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>911</v>
+        <v>837</v>
+      </c>
+      <c r="E26" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F26" t="s">
-        <v>946</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H26" s="6" t="s">
+        <v>972</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H26" s="17" t="s">
         <v>159</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
@@ -21264,34 +22450,37 @@
         <v>275</v>
       </c>
       <c r="C27">
-        <v>296</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>269</v>
+        <v>313</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>838</v>
       </c>
       <c r="E27" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F27" t="s">
-        <v>930</v>
+        <v>973</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>18</v>
+        <v>563</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>219</v>
+        <v>143</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>20</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>870</v>
+        <v>841</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>163</v>
       </c>
       <c r="L27" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>893</v>
+        <v>974</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
@@ -21302,34 +22491,37 @@
         <v>275</v>
       </c>
       <c r="C28">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>860</v>
+        <v>839</v>
       </c>
       <c r="E28" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F28" t="s">
-        <v>931</v>
+        <v>975</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>20</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>870</v>
+        <v>445</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>163</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>894</v>
+        <v>867</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
@@ -21340,34 +22532,37 @@
         <v>275</v>
       </c>
       <c r="C29">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>861</v>
+        <v>976</v>
       </c>
       <c r="E29" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F29" t="s">
-        <v>932</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>18</v>
+        <v>977</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>219</v>
+        <v>159</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>870</v>
+        <v>445</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>163</v>
       </c>
       <c r="L29" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M29" s="6" t="s">
-        <v>895</v>
+      <c r="M29" t="s">
+        <v>978</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.35">
@@ -21378,300 +22573,37 @@
         <v>275</v>
       </c>
       <c r="C30">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>862</v>
+        <v>148</v>
       </c>
       <c r="E30" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F30" t="s">
-        <v>933</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>18</v>
+        <v>979</v>
+      </c>
+      <c r="G30" t="s">
+        <v>30</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>219</v>
+        <v>150</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>870</v>
+        <v>445</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>163</v>
       </c>
       <c r="L30" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" t="s">
-        <v>275</v>
-      </c>
-      <c r="C31">
-        <v>300</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>863</v>
-      </c>
-      <c r="E31" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F31" t="s">
-        <v>934</v>
-      </c>
-      <c r="G31" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H31" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>870</v>
-      </c>
-      <c r="L31" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M31" s="17" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" t="s">
-        <v>275</v>
-      </c>
-      <c r="C32">
-        <v>301</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>864</v>
-      </c>
-      <c r="E32" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F32" t="s">
-        <v>936</v>
-      </c>
-      <c r="G32" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>870</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M32" s="6" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>13</v>
-      </c>
-      <c r="B33" t="s">
-        <v>275</v>
-      </c>
-      <c r="C33">
-        <v>302</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>865</v>
-      </c>
-      <c r="E33" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F33" t="s">
-        <v>937</v>
-      </c>
-      <c r="G33" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H33" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>870</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M33" s="6" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>13</v>
-      </c>
-      <c r="B34" t="s">
-        <v>275</v>
-      </c>
-      <c r="C34">
-        <v>303</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>866</v>
-      </c>
-      <c r="E34" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F34" t="s">
-        <v>914</v>
-      </c>
-      <c r="G34" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H34" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>870</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M34" s="6" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>13</v>
-      </c>
-      <c r="B35" t="s">
-        <v>275</v>
-      </c>
-      <c r="C35">
-        <v>304</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>867</v>
-      </c>
-      <c r="E35" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F35" t="s">
-        <v>938</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>563</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>870</v>
-      </c>
-      <c r="L35" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M35" s="6" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>13</v>
-      </c>
-      <c r="B36" t="s">
-        <v>275</v>
-      </c>
-      <c r="C36">
-        <v>305</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>868</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F36" t="s">
-        <v>935</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J36" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L36" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M36" s="6" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>13</v>
-      </c>
-      <c r="B37" t="s">
-        <v>275</v>
-      </c>
-      <c r="C37">
-        <v>306</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>869</v>
-      </c>
-      <c r="E37" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F37" t="s">
-        <v>939</v>
-      </c>
-      <c r="G37" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J37" s="6" t="s">
-        <v>870</v>
-      </c>
-      <c r="L37" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M37" s="6" t="s">
-        <v>903</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>
@@ -21742,16 +22674,16 @@
         <v>13</v>
       </c>
       <c r="C2">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>947</v>
+        <v>883</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F2" t="s">
-        <v>1003</v>
+        <v>938</v>
       </c>
       <c r="G2" s="36" t="s">
         <v>18</v>
@@ -21763,7 +22695,7 @@
         <v>20</v>
       </c>
       <c r="M2" s="34" t="s">
-        <v>969</v>
+        <v>905</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -21771,16 +22703,16 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>1007</v>
+        <v>942</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F3" t="s">
-        <v>1008</v>
+        <v>943</v>
       </c>
       <c r="G3" s="36" t="s">
         <v>192</v>
@@ -21792,7 +22724,7 @@
         <v>144</v>
       </c>
       <c r="M3" s="34" t="s">
-        <v>1009</v>
+        <v>944</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -21800,16 +22732,16 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>948</v>
+        <v>884</v>
       </c>
       <c r="E4" s="38" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F4" t="s">
-        <v>1005</v>
+        <v>940</v>
       </c>
       <c r="G4" s="38" t="s">
         <v>18</v>
@@ -21821,7 +22753,7 @@
         <v>20</v>
       </c>
       <c r="M4" s="35" t="s">
-        <v>970</v>
+        <v>906</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -21829,16 +22761,16 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>949</v>
+        <v>885</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F5" t="s">
-        <v>1004</v>
+        <v>939</v>
       </c>
       <c r="G5" s="36" t="s">
         <v>18</v>
@@ -21850,7 +22782,7 @@
         <v>20</v>
       </c>
       <c r="M5" s="34" t="s">
-        <v>971</v>
+        <v>907</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -21858,16 +22790,16 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>950</v>
+        <v>886</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F6" t="s">
-        <v>1006</v>
+        <v>941</v>
       </c>
       <c r="G6" s="38" t="s">
         <v>18</v>
@@ -21879,7 +22811,7 @@
         <v>20</v>
       </c>
       <c r="M6" s="35" t="s">
-        <v>972</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -21887,16 +22819,16 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>951</v>
+        <v>887</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F7" t="s">
-        <v>991</v>
+        <v>927</v>
       </c>
       <c r="G7" s="36" t="s">
         <v>18</v>
@@ -21908,7 +22840,7 @@
         <v>20</v>
       </c>
       <c r="M7" s="34" t="s">
-        <v>973</v>
+        <v>909</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -21916,16 +22848,16 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>952</v>
+        <v>888</v>
       </c>
       <c r="E8" s="38" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F8" t="s">
-        <v>992</v>
+        <v>928</v>
       </c>
       <c r="G8" s="38" t="s">
         <v>18</v>
@@ -21937,7 +22869,7 @@
         <v>20</v>
       </c>
       <c r="M8" s="35" t="s">
-        <v>974</v>
+        <v>910</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -21945,16 +22877,16 @@
         <v>13</v>
       </c>
       <c r="C9">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>953</v>
+        <v>889</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F9" t="s">
-        <v>993</v>
+        <v>929</v>
       </c>
       <c r="G9" s="36" t="s">
         <v>18</v>
@@ -21966,7 +22898,7 @@
         <v>20</v>
       </c>
       <c r="M9" s="34" t="s">
-        <v>975</v>
+        <v>911</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
@@ -21974,16 +22906,16 @@
         <v>13</v>
       </c>
       <c r="C10">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>954</v>
+        <v>890</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F10" t="s">
-        <v>994</v>
+        <v>930</v>
       </c>
       <c r="G10" s="38" t="s">
         <v>18</v>
@@ -21995,7 +22927,7 @@
         <v>20</v>
       </c>
       <c r="M10" s="35" t="s">
-        <v>976</v>
+        <v>912</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -22003,16 +22935,16 @@
         <v>13</v>
       </c>
       <c r="C11">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>955</v>
+        <v>891</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F11" t="s">
-        <v>995</v>
+        <v>931</v>
       </c>
       <c r="G11" s="36" t="s">
         <v>18</v>
@@ -22024,7 +22956,7 @@
         <v>20</v>
       </c>
       <c r="M11" s="34" t="s">
-        <v>977</v>
+        <v>913</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -22032,16 +22964,16 @@
         <v>13</v>
       </c>
       <c r="C12">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>956</v>
+        <v>892</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F12" t="s">
-        <v>996</v>
+        <v>932</v>
       </c>
       <c r="G12" s="38" t="s">
         <v>18</v>
@@ -22053,7 +22985,7 @@
         <v>20</v>
       </c>
       <c r="M12" s="35" t="s">
-        <v>978</v>
+        <v>914</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -22061,16 +22993,16 @@
         <v>13</v>
       </c>
       <c r="C13">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>957</v>
+        <v>893</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F13" t="s">
-        <v>997</v>
+        <v>933</v>
       </c>
       <c r="G13" s="36" t="s">
         <v>30</v>
@@ -22082,7 +23014,7 @@
         <v>144</v>
       </c>
       <c r="M13" s="34" t="s">
-        <v>979</v>
+        <v>915</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -22090,28 +23022,28 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="D14" s="35" t="s">
         <v>288</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F14" t="s">
-        <v>998</v>
+        <v>934</v>
       </c>
       <c r="G14" s="38" t="s">
         <v>563</v>
       </c>
       <c r="H14" s="39" t="s">
-        <v>967</v>
+        <v>903</v>
       </c>
       <c r="I14" s="38" t="s">
         <v>20</v>
       </c>
       <c r="M14" s="35" t="s">
-        <v>980</v>
+        <v>916</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -22119,16 +23051,16 @@
         <v>13</v>
       </c>
       <c r="C15">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>958</v>
+        <v>894</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F15" t="s">
-        <v>999</v>
+        <v>935</v>
       </c>
       <c r="G15" s="36" t="s">
         <v>18</v>
@@ -22140,7 +23072,7 @@
         <v>20</v>
       </c>
       <c r="M15" s="34" t="s">
-        <v>981</v>
+        <v>917</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -22148,16 +23080,16 @@
         <v>13</v>
       </c>
       <c r="C16">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="D16" s="35" t="s">
-        <v>959</v>
+        <v>895</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F16" t="s">
-        <v>1000</v>
+        <v>936</v>
       </c>
       <c r="G16" s="38" t="s">
         <v>30</v>
@@ -22169,7 +23101,7 @@
         <v>144</v>
       </c>
       <c r="M16" s="35" t="s">
-        <v>982</v>
+        <v>918</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
@@ -22177,28 +23109,28 @@
         <v>13</v>
       </c>
       <c r="C17">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>960</v>
+        <v>896</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F17" t="s">
-        <v>1001</v>
+        <v>937</v>
       </c>
       <c r="G17" s="38" t="s">
         <v>30</v>
       </c>
       <c r="H17" s="37" t="s">
-        <v>968</v>
+        <v>904</v>
       </c>
       <c r="I17" s="36" t="s">
         <v>144</v>
       </c>
       <c r="M17" s="34" t="s">
-        <v>983</v>
+        <v>919</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
@@ -22206,16 +23138,16 @@
         <v>13</v>
       </c>
       <c r="C18">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="D18" s="35" t="s">
-        <v>961</v>
+        <v>897</v>
       </c>
       <c r="E18" s="38" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F18" t="s">
-        <v>1014</v>
+        <v>949</v>
       </c>
       <c r="G18" s="38" t="s">
         <v>30</v>
@@ -22227,7 +23159,7 @@
         <v>144</v>
       </c>
       <c r="M18" s="35" t="s">
-        <v>984</v>
+        <v>920</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
@@ -22235,16 +23167,16 @@
         <v>13</v>
       </c>
       <c r="C19">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="D19" s="34" t="s">
-        <v>962</v>
+        <v>898</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F19" t="s">
-        <v>1015</v>
+        <v>950</v>
       </c>
       <c r="G19" s="38" t="s">
         <v>30</v>
@@ -22256,7 +23188,7 @@
         <v>144</v>
       </c>
       <c r="M19" s="34" t="s">
-        <v>985</v>
+        <v>921</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
@@ -22264,16 +23196,16 @@
         <v>13</v>
       </c>
       <c r="C20">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="D20" s="35" t="s">
-        <v>963</v>
+        <v>899</v>
       </c>
       <c r="E20" s="38" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F20" t="s">
-        <v>1016</v>
+        <v>951</v>
       </c>
       <c r="G20" s="38" t="s">
         <v>30</v>
@@ -22285,7 +23217,7 @@
         <v>144</v>
       </c>
       <c r="M20" s="35" t="s">
-        <v>986</v>
+        <v>922</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
@@ -22293,16 +23225,16 @@
         <v>13</v>
       </c>
       <c r="C21">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="D21" s="34" t="s">
-        <v>964</v>
+        <v>900</v>
       </c>
       <c r="E21" s="36" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F21" t="s">
-        <v>1017</v>
+        <v>952</v>
       </c>
       <c r="G21" s="38" t="s">
         <v>30</v>
@@ -22314,7 +23246,7 @@
         <v>144</v>
       </c>
       <c r="M21" s="34" t="s">
-        <v>987</v>
+        <v>923</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
@@ -22322,16 +23254,16 @@
         <v>13</v>
       </c>
       <c r="C22">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="D22" s="35" t="s">
-        <v>965</v>
+        <v>901</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F22" t="s">
-        <v>1018</v>
+        <v>953</v>
       </c>
       <c r="G22" s="38" t="s">
         <v>30</v>
@@ -22343,7 +23275,7 @@
         <v>144</v>
       </c>
       <c r="M22" s="35" t="s">
-        <v>988</v>
+        <v>924</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
@@ -22351,16 +23283,16 @@
         <v>13</v>
       </c>
       <c r="C23">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>966</v>
+        <v>902</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F23" t="s">
-        <v>1010</v>
+        <v>945</v>
       </c>
       <c r="G23" s="38" t="s">
         <v>30</v>
@@ -22372,7 +23304,7 @@
         <v>144</v>
       </c>
       <c r="M23" s="34" t="s">
-        <v>989</v>
+        <v>925</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
@@ -22380,16 +23312,16 @@
         <v>13</v>
       </c>
       <c r="C24">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="D24" s="34" t="s">
-        <v>1011</v>
+        <v>946</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F24" t="s">
-        <v>1012</v>
+        <v>947</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>30</v>
@@ -22412,16 +23344,16 @@
         <v>13</v>
       </c>
       <c r="C25">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>148</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
       <c r="F25" t="s">
-        <v>1013</v>
+        <v>948</v>
       </c>
       <c r="G25" t="s">
         <v>30</v>
@@ -22437,6 +23369,356 @@
       <c r="L25" s="6"/>
       <c r="M25" s="6" t="s">
         <v>527</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{622E78EB-B9F1-4134-97AC-977CC5EE74AE}">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="37.90625" customWidth="1"/>
+    <col min="5" max="5" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="43.26953125" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" customWidth="1"/>
+    <col min="9" max="9" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.26953125" customWidth="1"/>
+    <col min="12" max="12" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="49.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2">
+        <v>341</v>
+      </c>
+      <c r="D2" s="40" t="s">
+        <v>980</v>
+      </c>
+      <c r="E2" s="40" t="s">
+        <v>981</v>
+      </c>
+      <c r="F2" s="40" t="s">
+        <v>982</v>
+      </c>
+      <c r="G2" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="I2" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="K2" t="s">
+        <v>163</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M2" s="34" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C3">
+        <v>342</v>
+      </c>
+      <c r="D3" s="40" t="s">
+        <v>984</v>
+      </c>
+      <c r="E3" s="40" t="s">
+        <v>981</v>
+      </c>
+      <c r="F3" s="40" t="s">
+        <v>985</v>
+      </c>
+      <c r="G3" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="I3" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="K3" t="s">
+        <v>163</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M3" s="40" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4">
+        <v>343</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>987</v>
+      </c>
+      <c r="E4" s="40" t="s">
+        <v>981</v>
+      </c>
+      <c r="F4" t="s">
+        <v>992</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="K4" t="s">
+        <v>163</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C5">
+        <v>344</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>988</v>
+      </c>
+      <c r="E5" s="40" t="s">
+        <v>981</v>
+      </c>
+      <c r="F5" t="s">
+        <v>993</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="K5" t="s">
+        <v>163</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>275</v>
+      </c>
+      <c r="C6">
+        <v>345</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>989</v>
+      </c>
+      <c r="E6" s="40" t="s">
+        <v>981</v>
+      </c>
+      <c r="F6" t="s">
+        <v>994</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="K6" t="s">
+        <v>163</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>275</v>
+      </c>
+      <c r="C7">
+        <v>346</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>990</v>
+      </c>
+      <c r="E7" s="40" t="s">
+        <v>981</v>
+      </c>
+      <c r="F7" t="s">
+        <v>995</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="K7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>275</v>
+      </c>
+      <c r="C8">
+        <v>347</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>991</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>981</v>
+      </c>
+      <c r="F8" t="s">
+        <v>996</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="K8" t="s">
+        <v>163</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>859</v>
       </c>
     </row>
   </sheetData>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/Round 2 Pods for Testing/Fast Track Pods/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="574" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{732AFFD1-6DEC-4C9D-926E-65D04E509589}"/>
+  <xr:revisionPtr revIDLastSave="595" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D7C2B54-7BC9-4C4A-8FF2-849228F2A4F1}"/>
   <bookViews>
-    <workbookView xWindow="-28155" yWindow="405" windowWidth="27570" windowHeight="14985" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8174" uniqueCount="1047">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8198" uniqueCount="1048">
   <si>
     <t>schema</t>
   </si>
@@ -3237,6 +3237,9 @@
   </si>
   <si>
     <t>Homepage URL of the registry organisation (as opposed to registry_project_link, the project's page).</t>
+  </si>
+  <si>
+    <t>Date of validation event</t>
   </si>
 </sst>
 </file>
@@ -3469,7 +3472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3558,6 +3561,12 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3892,7 +3901,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{752D3095-90A4-45FF-BD20-0492A3C6EFAC}">
-  <dimension ref="A1:M341"/>
+  <dimension ref="A1:M342"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="21.1796875" bestFit="1" customWidth="1"/>
@@ -16085,44 +16094,44 @@
       </c>
     </row>
     <row r="298" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A298" t="s">
-        <v>13</v>
-      </c>
-      <c r="B298" t="s">
+      <c r="A298" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="B298" s="42" t="s">
         <v>275</v>
       </c>
       <c r="C298">
         <v>304</v>
       </c>
-      <c r="D298" s="30" t="s">
-        <v>511</v>
-      </c>
-      <c r="E298" s="33" t="s">
+      <c r="D298" s="43" t="s">
+        <v>269</v>
+      </c>
+      <c r="E298" s="44" t="s">
         <v>266</v>
       </c>
-      <c r="F298" t="s">
-        <v>964</v>
-      </c>
-      <c r="G298" s="6" t="s">
+      <c r="F298" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="G298" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="H298" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="I298" s="6" t="s">
+      <c r="H298" s="45" t="s">
+        <v>219</v>
+      </c>
+      <c r="I298" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="J298" s="6" t="s">
+      <c r="J298" s="45" t="s">
         <v>841</v>
       </c>
-      <c r="K298" s="6" t="s">
+      <c r="K298" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="L298" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M298" s="6" t="s">
-        <v>852</v>
+      <c r="L298" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="M298" s="45" t="s">
+        <v>1047</v>
       </c>
     </row>
     <row r="299" spans="1:13" x14ac:dyDescent="0.35">
@@ -16135,20 +16144,20 @@
       <c r="C299">
         <v>305</v>
       </c>
-      <c r="D299" s="6" t="s">
-        <v>831</v>
+      <c r="D299" s="30" t="s">
+        <v>511</v>
       </c>
       <c r="E299" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F299" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="G299" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H299" s="6" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="I299" s="6" t="s">
         <v>20</v>
@@ -16163,7 +16172,7 @@
         <v>146</v>
       </c>
       <c r="M299" s="6" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
     </row>
     <row r="300" spans="1:13" x14ac:dyDescent="0.35">
@@ -16177,19 +16186,19 @@
         <v>306</v>
       </c>
       <c r="D300" s="6" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E300" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F300" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G300" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H300" s="6" t="s">
-        <v>219</v>
+        <v>150</v>
       </c>
       <c r="I300" s="6" t="s">
         <v>20</v>
@@ -16204,7 +16213,7 @@
         <v>146</v>
       </c>
       <c r="M300" s="6" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="301" spans="1:13" x14ac:dyDescent="0.35">
@@ -16218,13 +16227,13 @@
         <v>307</v>
       </c>
       <c r="D301" s="6" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E301" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F301" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G301" s="6" t="s">
         <v>18</v>
@@ -16245,7 +16254,7 @@
         <v>146</v>
       </c>
       <c r="M301" s="6" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="302" spans="1:13" x14ac:dyDescent="0.35">
@@ -16258,23 +16267,23 @@
       <c r="C302">
         <v>308</v>
       </c>
-      <c r="D302" s="17" t="s">
-        <v>834</v>
+      <c r="D302" s="6" t="s">
+        <v>833</v>
       </c>
       <c r="E302" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F302" t="s">
-        <v>968</v>
-      </c>
-      <c r="G302" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H302" s="17" t="s">
-        <v>159</v>
+        <v>967</v>
+      </c>
+      <c r="G302" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H302" s="6" t="s">
+        <v>219</v>
       </c>
       <c r="I302" s="6" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="J302" s="6" t="s">
         <v>841</v>
@@ -16285,8 +16294,8 @@
       <c r="L302" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M302" s="17" t="s">
-        <v>863</v>
+      <c r="M302" s="6" t="s">
+        <v>862</v>
       </c>
     </row>
     <row r="303" spans="1:13" x14ac:dyDescent="0.35">
@@ -16299,14 +16308,14 @@
       <c r="C303">
         <v>309</v>
       </c>
-      <c r="D303" s="6" t="s">
-        <v>835</v>
+      <c r="D303" s="17" t="s">
+        <v>834</v>
       </c>
       <c r="E303" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F303" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="G303" s="17" t="s">
         <v>30</v>
@@ -16326,8 +16335,8 @@
       <c r="L303" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M303" s="6" t="s">
-        <v>864</v>
+      <c r="M303" s="17" t="s">
+        <v>863</v>
       </c>
     </row>
     <row r="304" spans="1:13" x14ac:dyDescent="0.35">
@@ -16341,18 +16350,18 @@
         <v>310</v>
       </c>
       <c r="D304" s="6" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="E304" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F304" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="G304" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="H304" s="6" t="s">
+      <c r="H304" s="17" t="s">
         <v>159</v>
       </c>
       <c r="I304" s="6" t="s">
@@ -16368,7 +16377,7 @@
         <v>146</v>
       </c>
       <c r="M304" s="6" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
     </row>
     <row r="305" spans="1:13" x14ac:dyDescent="0.35">
@@ -16382,18 +16391,18 @@
         <v>311</v>
       </c>
       <c r="D305" s="6" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="E305" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F305" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="G305" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="H305" s="17" t="s">
+      <c r="H305" s="6" t="s">
         <v>159</v>
       </c>
       <c r="I305" s="6" t="s">
@@ -16409,7 +16418,7 @@
         <v>146</v>
       </c>
       <c r="M305" s="6" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
     </row>
     <row r="306" spans="1:13" x14ac:dyDescent="0.35">
@@ -16423,13 +16432,13 @@
         <v>312</v>
       </c>
       <c r="D306" s="6" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E306" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F306" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G306" s="17" t="s">
         <v>30</v>
@@ -16450,7 +16459,7 @@
         <v>146</v>
       </c>
       <c r="M306" s="6" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="307" spans="1:13" x14ac:dyDescent="0.35">
@@ -16464,34 +16473,34 @@
         <v>313</v>
       </c>
       <c r="D307" s="6" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="E307" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F307" t="s">
-        <v>973</v>
-      </c>
-      <c r="G307" s="6" t="s">
-        <v>563</v>
-      </c>
-      <c r="H307" s="6" t="s">
-        <v>143</v>
+        <v>972</v>
+      </c>
+      <c r="G307" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H307" s="17" t="s">
+        <v>159</v>
       </c>
       <c r="I307" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J307" s="6" t="s">
         <v>841</v>
       </c>
       <c r="K307" s="6" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="L307" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M307" s="6" t="s">
-        <v>974</v>
+        <v>866</v>
       </c>
     </row>
     <row r="308" spans="1:13" x14ac:dyDescent="0.35">
@@ -16505,16 +16514,16 @@
         <v>314</v>
       </c>
       <c r="D308" s="6" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="E308" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F308" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="G308" s="6" t="s">
-        <v>18</v>
+        <v>563</v>
       </c>
       <c r="H308" s="6" t="s">
         <v>143</v>
@@ -16523,7 +16532,7 @@
         <v>20</v>
       </c>
       <c r="J308" s="6" t="s">
-        <v>445</v>
+        <v>841</v>
       </c>
       <c r="K308" s="6" t="s">
         <v>163</v>
@@ -16532,7 +16541,7 @@
         <v>146</v>
       </c>
       <c r="M308" s="6" t="s">
-        <v>867</v>
+        <v>974</v>
       </c>
     </row>
     <row r="309" spans="1:13" x14ac:dyDescent="0.35">
@@ -16546,22 +16555,22 @@
         <v>315</v>
       </c>
       <c r="D309" s="6" t="s">
-        <v>976</v>
+        <v>839</v>
       </c>
       <c r="E309" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F309" t="s">
-        <v>977</v>
-      </c>
-      <c r="G309" s="17" t="s">
-        <v>30</v>
+        <v>975</v>
+      </c>
+      <c r="G309" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="H309" s="6" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="I309" s="6" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="J309" s="6" t="s">
         <v>445</v>
@@ -16572,8 +16581,8 @@
       <c r="L309" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M309" t="s">
-        <v>978</v>
+      <c r="M309" s="6" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="310" spans="1:13" x14ac:dyDescent="0.35">
@@ -16587,19 +16596,19 @@
         <v>316</v>
       </c>
       <c r="D310" s="6" t="s">
-        <v>148</v>
+        <v>976</v>
       </c>
       <c r="E310" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F310" t="s">
-        <v>979</v>
-      </c>
-      <c r="G310" t="s">
+        <v>977</v>
+      </c>
+      <c r="G310" s="17" t="s">
         <v>30</v>
       </c>
       <c r="H310" s="6" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="I310" s="6" t="s">
         <v>144</v>
@@ -16613,37 +16622,49 @@
       <c r="L310" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M310" s="6" t="s">
-        <v>527</v>
+      <c r="M310" t="s">
+        <v>978</v>
       </c>
     </row>
     <row r="311" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>13</v>
       </c>
+      <c r="B311" t="s">
+        <v>275</v>
+      </c>
       <c r="C311">
         <v>317</v>
       </c>
-      <c r="D311" s="34" t="s">
-        <v>883</v>
-      </c>
-      <c r="E311" s="36" t="s">
-        <v>926</v>
+      <c r="D311" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E311" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F311" t="s">
-        <v>938</v>
-      </c>
-      <c r="G311" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="H311" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="I311" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="M311" s="34" t="s">
-        <v>905</v>
+        <v>979</v>
+      </c>
+      <c r="G311" t="s">
+        <v>30</v>
+      </c>
+      <c r="H311" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I311" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J311" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="K311" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="L311" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M311" s="6" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="312" spans="1:13" x14ac:dyDescent="0.35">
@@ -16654,25 +16675,25 @@
         <v>318</v>
       </c>
       <c r="D312" s="34" t="s">
-        <v>942</v>
+        <v>883</v>
       </c>
       <c r="E312" s="36" t="s">
         <v>926</v>
       </c>
       <c r="F312" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="G312" s="36" t="s">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="H312" s="37" t="s">
         <v>215</v>
       </c>
       <c r="I312" s="36" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="M312" s="34" t="s">
-        <v>944</v>
+        <v>905</v>
       </c>
     </row>
     <row r="313" spans="1:13" x14ac:dyDescent="0.35">
@@ -16682,26 +16703,26 @@
       <c r="C313">
         <v>319</v>
       </c>
-      <c r="D313" s="35" t="s">
-        <v>884</v>
-      </c>
-      <c r="E313" s="38" t="s">
+      <c r="D313" s="34" t="s">
+        <v>942</v>
+      </c>
+      <c r="E313" s="36" t="s">
         <v>926</v>
       </c>
       <c r="F313" t="s">
-        <v>940</v>
-      </c>
-      <c r="G313" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="H313" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="I313" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M313" s="35" t="s">
-        <v>906</v>
+        <v>943</v>
+      </c>
+      <c r="G313" s="36" t="s">
+        <v>192</v>
+      </c>
+      <c r="H313" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I313" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M313" s="34" t="s">
+        <v>944</v>
       </c>
     </row>
     <row r="314" spans="1:13" x14ac:dyDescent="0.35">
@@ -16711,26 +16732,26 @@
       <c r="C314">
         <v>320</v>
       </c>
-      <c r="D314" s="34" t="s">
-        <v>885</v>
-      </c>
-      <c r="E314" s="36" t="s">
+      <c r="D314" s="35" t="s">
+        <v>884</v>
+      </c>
+      <c r="E314" s="38" t="s">
         <v>926</v>
       </c>
       <c r="F314" t="s">
-        <v>939</v>
-      </c>
-      <c r="G314" s="36" t="s">
+        <v>940</v>
+      </c>
+      <c r="G314" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H314" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="I314" s="36" t="s">
+      <c r="H314" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="I314" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="M314" s="34" t="s">
-        <v>907</v>
+      <c r="M314" s="35" t="s">
+        <v>906</v>
       </c>
     </row>
     <row r="315" spans="1:13" x14ac:dyDescent="0.35">
@@ -16740,26 +16761,26 @@
       <c r="C315">
         <v>321</v>
       </c>
-      <c r="D315" s="35" t="s">
-        <v>886</v>
-      </c>
-      <c r="E315" s="38" t="s">
+      <c r="D315" s="34" t="s">
+        <v>885</v>
+      </c>
+      <c r="E315" s="36" t="s">
         <v>926</v>
       </c>
       <c r="F315" t="s">
-        <v>941</v>
-      </c>
-      <c r="G315" s="38" t="s">
+        <v>939</v>
+      </c>
+      <c r="G315" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="H315" s="39" t="s">
+      <c r="H315" s="37" t="s">
         <v>215</v>
       </c>
-      <c r="I315" s="38" t="s">
+      <c r="I315" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="M315" s="35" t="s">
-        <v>908</v>
+      <c r="M315" s="34" t="s">
+        <v>907</v>
       </c>
     </row>
     <row r="316" spans="1:13" x14ac:dyDescent="0.35">
@@ -16769,26 +16790,26 @@
       <c r="C316">
         <v>322</v>
       </c>
-      <c r="D316" s="34" t="s">
-        <v>887</v>
-      </c>
-      <c r="E316" s="36" t="s">
+      <c r="D316" s="35" t="s">
+        <v>886</v>
+      </c>
+      <c r="E316" s="38" t="s">
         <v>926</v>
       </c>
       <c r="F316" t="s">
-        <v>927</v>
-      </c>
-      <c r="G316" s="36" t="s">
+        <v>941</v>
+      </c>
+      <c r="G316" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H316" s="37" t="s">
-        <v>219</v>
-      </c>
-      <c r="I316" s="36" t="s">
+      <c r="H316" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I316" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="M316" s="34" t="s">
-        <v>909</v>
+      <c r="M316" s="35" t="s">
+        <v>908</v>
       </c>
     </row>
     <row r="317" spans="1:13" x14ac:dyDescent="0.35">
@@ -16798,26 +16819,26 @@
       <c r="C317">
         <v>323</v>
       </c>
-      <c r="D317" s="35" t="s">
-        <v>888</v>
-      </c>
-      <c r="E317" s="38" t="s">
+      <c r="D317" s="34" t="s">
+        <v>887</v>
+      </c>
+      <c r="E317" s="36" t="s">
         <v>926</v>
       </c>
       <c r="F317" t="s">
-        <v>928</v>
-      </c>
-      <c r="G317" s="38" t="s">
+        <v>927</v>
+      </c>
+      <c r="G317" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="H317" s="39" t="s">
+      <c r="H317" s="37" t="s">
         <v>219</v>
       </c>
-      <c r="I317" s="38" t="s">
+      <c r="I317" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="M317" s="35" t="s">
-        <v>910</v>
+      <c r="M317" s="34" t="s">
+        <v>909</v>
       </c>
     </row>
     <row r="318" spans="1:13" x14ac:dyDescent="0.35">
@@ -16827,26 +16848,26 @@
       <c r="C318">
         <v>324</v>
       </c>
-      <c r="D318" s="34" t="s">
-        <v>889</v>
-      </c>
-      <c r="E318" s="36" t="s">
+      <c r="D318" s="35" t="s">
+        <v>888</v>
+      </c>
+      <c r="E318" s="38" t="s">
         <v>926</v>
       </c>
       <c r="F318" t="s">
-        <v>929</v>
-      </c>
-      <c r="G318" s="36" t="s">
+        <v>928</v>
+      </c>
+      <c r="G318" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H318" s="37" t="s">
+      <c r="H318" s="39" t="s">
         <v>219</v>
       </c>
-      <c r="I318" s="36" t="s">
+      <c r="I318" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="M318" s="34" t="s">
-        <v>911</v>
+      <c r="M318" s="35" t="s">
+        <v>910</v>
       </c>
     </row>
     <row r="319" spans="1:13" x14ac:dyDescent="0.35">
@@ -16856,26 +16877,26 @@
       <c r="C319">
         <v>325</v>
       </c>
-      <c r="D319" s="35" t="s">
-        <v>890</v>
-      </c>
-      <c r="E319" s="38" t="s">
+      <c r="D319" s="34" t="s">
+        <v>889</v>
+      </c>
+      <c r="E319" s="36" t="s">
         <v>926</v>
       </c>
       <c r="F319" t="s">
-        <v>930</v>
-      </c>
-      <c r="G319" s="38" t="s">
+        <v>929</v>
+      </c>
+      <c r="G319" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="H319" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="I319" s="38" t="s">
+      <c r="H319" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I319" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="M319" s="35" t="s">
-        <v>912</v>
+      <c r="M319" s="34" t="s">
+        <v>911</v>
       </c>
     </row>
     <row r="320" spans="1:13" x14ac:dyDescent="0.35">
@@ -16885,26 +16906,26 @@
       <c r="C320">
         <v>326</v>
       </c>
-      <c r="D320" s="34" t="s">
-        <v>891</v>
-      </c>
-      <c r="E320" s="36" t="s">
+      <c r="D320" s="35" t="s">
+        <v>890</v>
+      </c>
+      <c r="E320" s="38" t="s">
         <v>926</v>
       </c>
       <c r="F320" t="s">
-        <v>931</v>
-      </c>
-      <c r="G320" s="36" t="s">
+        <v>930</v>
+      </c>
+      <c r="G320" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H320" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="I320" s="36" t="s">
+      <c r="H320" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="I320" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="M320" s="34" t="s">
-        <v>913</v>
+      <c r="M320" s="35" t="s">
+        <v>912</v>
       </c>
     </row>
     <row r="321" spans="1:13" x14ac:dyDescent="0.35">
@@ -16914,26 +16935,26 @@
       <c r="C321">
         <v>327</v>
       </c>
-      <c r="D321" s="35" t="s">
-        <v>892</v>
-      </c>
-      <c r="E321" s="38" t="s">
+      <c r="D321" s="34" t="s">
+        <v>891</v>
+      </c>
+      <c r="E321" s="36" t="s">
         <v>926</v>
       </c>
       <c r="F321" t="s">
-        <v>932</v>
-      </c>
-      <c r="G321" s="38" t="s">
+        <v>931</v>
+      </c>
+      <c r="G321" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="H321" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="I321" s="38" t="s">
+      <c r="H321" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="I321" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="M321" s="35" t="s">
-        <v>914</v>
+      <c r="M321" s="34" t="s">
+        <v>913</v>
       </c>
     </row>
     <row r="322" spans="1:13" x14ac:dyDescent="0.35">
@@ -16943,26 +16964,26 @@
       <c r="C322">
         <v>328</v>
       </c>
-      <c r="D322" s="34" t="s">
-        <v>893</v>
-      </c>
-      <c r="E322" s="36" t="s">
+      <c r="D322" s="35" t="s">
+        <v>892</v>
+      </c>
+      <c r="E322" s="38" t="s">
         <v>926</v>
       </c>
       <c r="F322" t="s">
-        <v>933</v>
-      </c>
-      <c r="G322" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="H322" s="37" t="s">
+        <v>932</v>
+      </c>
+      <c r="G322" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H322" s="39" t="s">
         <v>215</v>
       </c>
-      <c r="I322" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="M322" s="34" t="s">
-        <v>915</v>
+      <c r="I322" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M322" s="35" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="323" spans="1:13" x14ac:dyDescent="0.35">
@@ -16972,26 +16993,26 @@
       <c r="C323">
         <v>329</v>
       </c>
-      <c r="D323" s="35" t="s">
-        <v>288</v>
-      </c>
-      <c r="E323" s="38" t="s">
+      <c r="D323" s="34" t="s">
+        <v>893</v>
+      </c>
+      <c r="E323" s="36" t="s">
         <v>926</v>
       </c>
       <c r="F323" t="s">
-        <v>934</v>
-      </c>
-      <c r="G323" s="38" t="s">
-        <v>563</v>
-      </c>
-      <c r="H323" s="39" t="s">
-        <v>903</v>
-      </c>
-      <c r="I323" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M323" s="35" t="s">
-        <v>916</v>
+        <v>933</v>
+      </c>
+      <c r="G323" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="H323" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I323" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M323" s="34" t="s">
+        <v>915</v>
       </c>
     </row>
     <row r="324" spans="1:13" x14ac:dyDescent="0.35">
@@ -17001,26 +17022,26 @@
       <c r="C324">
         <v>330</v>
       </c>
-      <c r="D324" s="34" t="s">
-        <v>894</v>
-      </c>
-      <c r="E324" s="36" t="s">
+      <c r="D324" s="35" t="s">
+        <v>288</v>
+      </c>
+      <c r="E324" s="38" t="s">
         <v>926</v>
       </c>
       <c r="F324" t="s">
-        <v>935</v>
-      </c>
-      <c r="G324" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="H324" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="I324" s="36" t="s">
+        <v>934</v>
+      </c>
+      <c r="G324" s="38" t="s">
+        <v>563</v>
+      </c>
+      <c r="H324" s="39" t="s">
+        <v>903</v>
+      </c>
+      <c r="I324" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="M324" s="34" t="s">
-        <v>917</v>
+      <c r="M324" s="35" t="s">
+        <v>916</v>
       </c>
     </row>
     <row r="325" spans="1:13" x14ac:dyDescent="0.35">
@@ -17030,84 +17051,84 @@
       <c r="C325">
         <v>331</v>
       </c>
-      <c r="D325" s="35" t="s">
-        <v>895</v>
-      </c>
-      <c r="E325" s="38" t="s">
+      <c r="D325" s="34" t="s">
+        <v>894</v>
+      </c>
+      <c r="E325" s="36" t="s">
         <v>926</v>
       </c>
       <c r="F325" t="s">
-        <v>936</v>
-      </c>
-      <c r="G325" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H325" s="39" t="s">
+        <v>935</v>
+      </c>
+      <c r="G325" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H325" s="37" t="s">
         <v>215</v>
       </c>
-      <c r="I325" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="M325" s="35" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="326" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="I325" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M325" s="34" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="326" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>13</v>
       </c>
       <c r="C326">
         <v>332</v>
       </c>
-      <c r="D326" s="34" t="s">
-        <v>896</v>
-      </c>
-      <c r="E326" s="36" t="s">
+      <c r="D326" s="35" t="s">
+        <v>895</v>
+      </c>
+      <c r="E326" s="38" t="s">
         <v>926</v>
       </c>
       <c r="F326" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G326" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H326" s="37" t="s">
-        <v>904</v>
-      </c>
-      <c r="I326" s="36" t="s">
+      <c r="H326" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I326" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="M326" s="34" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M326" s="35" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="327" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>13</v>
       </c>
       <c r="C327">
         <v>333</v>
       </c>
-      <c r="D327" s="35" t="s">
-        <v>897</v>
-      </c>
-      <c r="E327" s="38" t="s">
+      <c r="D327" s="34" t="s">
+        <v>896</v>
+      </c>
+      <c r="E327" s="36" t="s">
         <v>926</v>
       </c>
       <c r="F327" t="s">
-        <v>949</v>
+        <v>937</v>
       </c>
       <c r="G327" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H327" s="39" t="s">
-        <v>150</v>
-      </c>
-      <c r="I327" s="38" t="s">
+      <c r="H327" s="37" t="s">
+        <v>904</v>
+      </c>
+      <c r="I327" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="M327" s="35" t="s">
-        <v>920</v>
+      <c r="M327" s="34" t="s">
+        <v>919</v>
       </c>
     </row>
     <row r="328" spans="1:13" x14ac:dyDescent="0.35">
@@ -17117,26 +17138,26 @@
       <c r="C328">
         <v>334</v>
       </c>
-      <c r="D328" s="34" t="s">
-        <v>898</v>
-      </c>
-      <c r="E328" s="36" t="s">
+      <c r="D328" s="35" t="s">
+        <v>897</v>
+      </c>
+      <c r="E328" s="38" t="s">
         <v>926</v>
       </c>
       <c r="F328" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="G328" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H328" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="I328" s="36" t="s">
+      <c r="H328" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="I328" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="M328" s="34" t="s">
-        <v>921</v>
+      <c r="M328" s="35" t="s">
+        <v>920</v>
       </c>
     </row>
     <row r="329" spans="1:13" x14ac:dyDescent="0.35">
@@ -17146,26 +17167,26 @@
       <c r="C329">
         <v>335</v>
       </c>
-      <c r="D329" s="35" t="s">
-        <v>899</v>
-      </c>
-      <c r="E329" s="38" t="s">
+      <c r="D329" s="34" t="s">
+        <v>898</v>
+      </c>
+      <c r="E329" s="36" t="s">
         <v>926</v>
       </c>
       <c r="F329" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G329" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H329" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="I329" s="38" t="s">
+      <c r="H329" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I329" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="M329" s="35" t="s">
-        <v>922</v>
+      <c r="M329" s="34" t="s">
+        <v>921</v>
       </c>
     </row>
     <row r="330" spans="1:13" x14ac:dyDescent="0.35">
@@ -17175,26 +17196,26 @@
       <c r="C330">
         <v>336</v>
       </c>
-      <c r="D330" s="34" t="s">
-        <v>900</v>
-      </c>
-      <c r="E330" s="36" t="s">
+      <c r="D330" s="35" t="s">
+        <v>899</v>
+      </c>
+      <c r="E330" s="38" t="s">
         <v>926</v>
       </c>
       <c r="F330" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G330" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H330" s="37" t="s">
+      <c r="H330" s="39" t="s">
         <v>316</v>
       </c>
-      <c r="I330" s="36" t="s">
+      <c r="I330" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="M330" s="34" t="s">
-        <v>923</v>
+      <c r="M330" s="35" t="s">
+        <v>922</v>
       </c>
     </row>
     <row r="331" spans="1:13" x14ac:dyDescent="0.35">
@@ -17204,26 +17225,26 @@
       <c r="C331">
         <v>337</v>
       </c>
-      <c r="D331" s="35" t="s">
-        <v>901</v>
-      </c>
-      <c r="E331" s="38" t="s">
+      <c r="D331" s="34" t="s">
+        <v>900</v>
+      </c>
+      <c r="E331" s="36" t="s">
         <v>926</v>
       </c>
       <c r="F331" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="G331" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H331" s="39" t="s">
+      <c r="H331" s="37" t="s">
         <v>316</v>
       </c>
-      <c r="I331" s="38" t="s">
+      <c r="I331" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="M331" s="35" t="s">
-        <v>924</v>
+      <c r="M331" s="34" t="s">
+        <v>923</v>
       </c>
     </row>
     <row r="332" spans="1:13" x14ac:dyDescent="0.35">
@@ -17233,26 +17254,26 @@
       <c r="C332">
         <v>338</v>
       </c>
-      <c r="D332" s="34" t="s">
-        <v>902</v>
-      </c>
-      <c r="E332" s="36" t="s">
+      <c r="D332" s="35" t="s">
+        <v>901</v>
+      </c>
+      <c r="E332" s="38" t="s">
         <v>926</v>
       </c>
       <c r="F332" t="s">
-        <v>945</v>
+        <v>953</v>
       </c>
       <c r="G332" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H332" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="I332" s="36" t="s">
+      <c r="H332" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="I332" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="M332" s="34" t="s">
-        <v>925</v>
+      <c r="M332" s="35" t="s">
+        <v>924</v>
       </c>
     </row>
     <row r="333" spans="1:13" x14ac:dyDescent="0.35">
@@ -17263,28 +17284,25 @@
         <v>339</v>
       </c>
       <c r="D333" s="34" t="s">
-        <v>946</v>
+        <v>902</v>
       </c>
       <c r="E333" s="36" t="s">
         <v>926</v>
       </c>
       <c r="F333" t="s">
-        <v>947</v>
-      </c>
-      <c r="G333" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H333" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="I333" s="6" t="s">
+        <v>945</v>
+      </c>
+      <c r="G333" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H333" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="I333" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="J333" s="6"/>
-      <c r="K333" s="6"/>
-      <c r="L333" s="6"/>
-      <c r="M333" s="30" t="s">
-        <v>216</v>
+      <c r="M333" s="34" t="s">
+        <v>925</v>
       </c>
     </row>
     <row r="334" spans="1:13" x14ac:dyDescent="0.35">
@@ -17294,70 +17312,61 @@
       <c r="C334">
         <v>340</v>
       </c>
-      <c r="D334" s="6" t="s">
-        <v>148</v>
+      <c r="D334" s="34" t="s">
+        <v>946</v>
       </c>
       <c r="E334" s="36" t="s">
         <v>926</v>
       </c>
       <c r="F334" t="s">
-        <v>948</v>
-      </c>
-      <c r="G334" t="s">
+        <v>947</v>
+      </c>
+      <c r="G334" s="6" t="s">
         <v>30</v>
       </c>
       <c r="H334" s="6" t="s">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="I334" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J334" s="6"/>
       <c r="K334" s="6"/>
       <c r="L334" s="6"/>
-      <c r="M334" s="6" t="s">
-        <v>527</v>
+      <c r="M334" s="30" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="335" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>13</v>
       </c>
-      <c r="B335" t="s">
-        <v>275</v>
-      </c>
       <c r="C335">
         <v>341</v>
       </c>
-      <c r="D335" s="40" t="s">
-        <v>980</v>
-      </c>
-      <c r="E335" s="40" t="s">
-        <v>981</v>
-      </c>
-      <c r="F335" s="40" t="s">
-        <v>982</v>
-      </c>
-      <c r="G335" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="H335" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="I335" s="40" t="s">
+      <c r="D335" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E335" s="36" t="s">
+        <v>926</v>
+      </c>
+      <c r="F335" t="s">
+        <v>948</v>
+      </c>
+      <c r="G335" t="s">
+        <v>30</v>
+      </c>
+      <c r="H335" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I335" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J335" s="6" t="s">
-        <v>841</v>
-      </c>
-      <c r="K335" t="s">
-        <v>163</v>
-      </c>
-      <c r="L335" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M335" s="34" t="s">
-        <v>983</v>
+      <c r="J335" s="6"/>
+      <c r="K335" s="6"/>
+      <c r="L335" s="6"/>
+      <c r="M335" s="6" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="336" spans="1:13" x14ac:dyDescent="0.35">
@@ -17371,19 +17380,19 @@
         <v>342</v>
       </c>
       <c r="D336" s="40" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="E336" s="40" t="s">
         <v>981</v>
       </c>
       <c r="F336" s="40" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="G336" s="40" t="s">
         <v>18</v>
       </c>
       <c r="H336" s="40" t="s">
-        <v>143</v>
+        <v>215</v>
       </c>
       <c r="I336" s="40" t="s">
         <v>20</v>
@@ -17397,8 +17406,8 @@
       <c r="L336" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M336" s="40" t="s">
-        <v>986</v>
+      <c r="M336" s="34" t="s">
+        <v>983</v>
       </c>
     </row>
     <row r="337" spans="1:13" x14ac:dyDescent="0.35">
@@ -17411,23 +17420,23 @@
       <c r="C337">
         <v>343</v>
       </c>
-      <c r="D337" s="6" t="s">
-        <v>987</v>
+      <c r="D337" s="40" t="s">
+        <v>984</v>
       </c>
       <c r="E337" s="40" t="s">
         <v>981</v>
       </c>
-      <c r="F337" t="s">
-        <v>992</v>
-      </c>
-      <c r="G337" s="17" t="s">
-        <v>30</v>
+      <c r="F337" s="40" t="s">
+        <v>985</v>
+      </c>
+      <c r="G337" s="40" t="s">
+        <v>18</v>
       </c>
       <c r="H337" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="I337" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
+      </c>
+      <c r="I337" s="40" t="s">
+        <v>20</v>
       </c>
       <c r="J337" s="6" t="s">
         <v>841</v>
@@ -17438,8 +17447,8 @@
       <c r="L337" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M337" s="6" t="s">
-        <v>855</v>
+      <c r="M337" s="40" t="s">
+        <v>986</v>
       </c>
     </row>
     <row r="338" spans="1:13" x14ac:dyDescent="0.35">
@@ -17452,23 +17461,23 @@
       <c r="C338">
         <v>344</v>
       </c>
-      <c r="D338" s="17" t="s">
-        <v>988</v>
+      <c r="D338" s="6" t="s">
+        <v>987</v>
       </c>
       <c r="E338" s="40" t="s">
         <v>981</v>
       </c>
       <c r="F338" t="s">
-        <v>993</v>
-      </c>
-      <c r="G338" s="6" t="s">
-        <v>18</v>
+        <v>992</v>
+      </c>
+      <c r="G338" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="H338" s="40" t="s">
         <v>215</v>
       </c>
       <c r="I338" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J338" s="6" t="s">
         <v>841</v>
@@ -17480,7 +17489,7 @@
         <v>146</v>
       </c>
       <c r="M338" s="6" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="339" spans="1:13" x14ac:dyDescent="0.35">
@@ -17493,23 +17502,23 @@
       <c r="C339">
         <v>345</v>
       </c>
-      <c r="D339" s="6" t="s">
-        <v>989</v>
+      <c r="D339" s="17" t="s">
+        <v>988</v>
       </c>
       <c r="E339" s="40" t="s">
         <v>981</v>
       </c>
       <c r="F339" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="G339" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="H339" s="6" t="s">
-        <v>143</v>
+        <v>18</v>
+      </c>
+      <c r="H339" s="40" t="s">
+        <v>215</v>
       </c>
       <c r="I339" s="6" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="J339" s="6" t="s">
         <v>841</v>
@@ -17521,7 +17530,7 @@
         <v>146</v>
       </c>
       <c r="M339" s="6" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="340" spans="1:13" x14ac:dyDescent="0.35">
@@ -17535,19 +17544,19 @@
         <v>346</v>
       </c>
       <c r="D340" s="6" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E340" s="40" t="s">
         <v>981</v>
       </c>
       <c r="F340" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="G340" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H340" s="40" t="s">
-        <v>215</v>
+        <v>192</v>
+      </c>
+      <c r="H340" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="I340" s="6" t="s">
         <v>144</v>
@@ -17562,7 +17571,7 @@
         <v>146</v>
       </c>
       <c r="M340" s="6" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="341" spans="1:13" x14ac:dyDescent="0.35">
@@ -17576,13 +17585,13 @@
         <v>347</v>
       </c>
       <c r="D341" s="6" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="E341" s="40" t="s">
         <v>981</v>
       </c>
       <c r="F341" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="G341" s="6" t="s">
         <v>30</v>
@@ -17603,6 +17612,47 @@
         <v>146</v>
       </c>
       <c r="M341" s="6" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="342" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A342" t="s">
+        <v>13</v>
+      </c>
+      <c r="B342" t="s">
+        <v>275</v>
+      </c>
+      <c r="C342">
+        <v>348</v>
+      </c>
+      <c r="D342" s="6" t="s">
+        <v>991</v>
+      </c>
+      <c r="E342" s="40" t="s">
+        <v>981</v>
+      </c>
+      <c r="F342" t="s">
+        <v>996</v>
+      </c>
+      <c r="G342" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H342" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="I342" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J342" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="K342" t="s">
+        <v>163</v>
+      </c>
+      <c r="L342" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M342" s="6" t="s">
         <v>859</v>
       </c>
     </row>
@@ -21361,7 +21411,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF337E51-0D9D-46A6-9DB2-8DF5F9FC1667}">
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="43.6328125" customWidth="1"/>
@@ -22073,45 +22123,45 @@
         <v>854</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" t="s">
+    <row r="18" spans="1:13" s="42" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="42" t="s">
         <v>275</v>
       </c>
       <c r="C18">
         <v>304</v>
       </c>
-      <c r="D18" s="30" t="s">
-        <v>511</v>
-      </c>
-      <c r="E18" s="33" t="s">
+      <c r="D18" s="43" t="s">
+        <v>269</v>
+      </c>
+      <c r="E18" s="44" t="s">
         <v>266</v>
       </c>
-      <c r="F18" t="s">
-        <v>964</v>
-      </c>
-      <c r="G18" s="6" t="s">
+      <c r="F18" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="G18" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="H18" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="I18" s="6" t="s">
+      <c r="H18" s="45" t="s">
+        <v>219</v>
+      </c>
+      <c r="I18" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="J18" s="6" t="s">
+      <c r="J18" s="45" t="s">
         <v>841</v>
       </c>
-      <c r="K18" s="6" t="s">
+      <c r="K18" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="L18" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>852</v>
+      <c r="L18" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="M18" s="45" t="s">
+        <v>1047</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
@@ -22124,20 +22174,20 @@
       <c r="C19">
         <v>305</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>831</v>
+      <c r="D19" s="30" t="s">
+        <v>511</v>
       </c>
       <c r="E19" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F19" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>20</v>
@@ -22152,7 +22202,7 @@
         <v>146</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
@@ -22166,19 +22216,19 @@
         <v>306</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E20" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>219</v>
+        <v>150</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>20</v>
@@ -22193,7 +22243,7 @@
         <v>146</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
@@ -22207,13 +22257,13 @@
         <v>307</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E21" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F21" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>18</v>
@@ -22234,7 +22284,7 @@
         <v>146</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
@@ -22247,23 +22297,23 @@
       <c r="C22">
         <v>308</v>
       </c>
-      <c r="D22" s="17" t="s">
-        <v>834</v>
+      <c r="D22" s="6" t="s">
+        <v>833</v>
       </c>
       <c r="E22" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F22" t="s">
-        <v>968</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H22" s="17" t="s">
-        <v>159</v>
+        <v>967</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>219</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>841</v>
@@ -22274,8 +22324,8 @@
       <c r="L22" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M22" s="17" t="s">
-        <v>863</v>
+      <c r="M22" s="6" t="s">
+        <v>862</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
@@ -22288,14 +22338,14 @@
       <c r="C23">
         <v>309</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>835</v>
+      <c r="D23" s="17" t="s">
+        <v>834</v>
       </c>
       <c r="E23" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F23" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="G23" s="17" t="s">
         <v>30</v>
@@ -22315,8 +22365,8 @@
       <c r="L23" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M23" s="6" t="s">
-        <v>864</v>
+      <c r="M23" s="17" t="s">
+        <v>863</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
@@ -22330,18 +22380,18 @@
         <v>310</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="E24" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F24" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="G24" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="H24" s="17" t="s">
         <v>159</v>
       </c>
       <c r="I24" s="6" t="s">
@@ -22357,7 +22407,7 @@
         <v>146</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
@@ -22371,18 +22421,18 @@
         <v>311</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="E25" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F25" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="G25" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="H25" s="17" t="s">
+      <c r="H25" s="6" t="s">
         <v>159</v>
       </c>
       <c r="I25" s="6" t="s">
@@ -22398,7 +22448,7 @@
         <v>146</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
@@ -22412,13 +22462,13 @@
         <v>312</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E26" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F26" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G26" s="17" t="s">
         <v>30</v>
@@ -22439,7 +22489,7 @@
         <v>146</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
@@ -22453,34 +22503,34 @@
         <v>313</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="E27" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F27" t="s">
-        <v>973</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>563</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>143</v>
+        <v>972</v>
+      </c>
+      <c r="G27" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H27" s="17" t="s">
+        <v>159</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J27" s="6" t="s">
         <v>841</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="L27" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>974</v>
+        <v>866</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
@@ -22494,16 +22544,16 @@
         <v>314</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="E28" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F28" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>18</v>
+        <v>563</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>143</v>
@@ -22512,7 +22562,7 @@
         <v>20</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>445</v>
+        <v>841</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>163</v>
@@ -22521,7 +22571,7 @@
         <v>146</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>867</v>
+        <v>974</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
@@ -22535,22 +22585,22 @@
         <v>315</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>976</v>
+        <v>839</v>
       </c>
       <c r="E29" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F29" t="s">
-        <v>977</v>
-      </c>
-      <c r="G29" s="17" t="s">
-        <v>30</v>
+        <v>975</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="J29" s="6" t="s">
         <v>445</v>
@@ -22561,8 +22611,8 @@
       <c r="L29" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M29" t="s">
-        <v>978</v>
+      <c r="M29" s="6" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.35">
@@ -22576,19 +22626,19 @@
         <v>316</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>148</v>
+        <v>976</v>
       </c>
       <c r="E30" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F30" t="s">
-        <v>979</v>
-      </c>
-      <c r="G30" t="s">
+        <v>977</v>
+      </c>
+      <c r="G30" s="17" t="s">
         <v>30</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="I30" s="6" t="s">
         <v>144</v>
@@ -22602,7 +22652,48 @@
       <c r="L30" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M30" s="6" t="s">
+      <c r="M30" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" t="s">
+        <v>275</v>
+      </c>
+      <c r="C31">
+        <v>317</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E31" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F31" t="s">
+        <v>979</v>
+      </c>
+      <c r="G31" t="s">
+        <v>30</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M31" s="6" t="s">
         <v>527</v>
       </c>
     </row>
@@ -22674,7 +22765,7 @@
         <v>13</v>
       </c>
       <c r="C2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D2" s="34" t="s">
         <v>883</v>
@@ -22703,7 +22794,7 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D3" s="34" t="s">
         <v>942</v>
@@ -22732,7 +22823,7 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D4" s="35" t="s">
         <v>884</v>
@@ -22761,7 +22852,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D5" s="34" t="s">
         <v>885</v>
@@ -22790,7 +22881,7 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D6" s="35" t="s">
         <v>886</v>
@@ -22819,7 +22910,7 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D7" s="34" t="s">
         <v>887</v>
@@ -22848,7 +22939,7 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D8" s="35" t="s">
         <v>888</v>
@@ -22877,7 +22968,7 @@
         <v>13</v>
       </c>
       <c r="C9">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D9" s="34" t="s">
         <v>889</v>
@@ -22906,7 +22997,7 @@
         <v>13</v>
       </c>
       <c r="C10">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D10" s="35" t="s">
         <v>890</v>
@@ -22935,7 +23026,7 @@
         <v>13</v>
       </c>
       <c r="C11">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D11" s="34" t="s">
         <v>891</v>
@@ -22964,7 +23055,7 @@
         <v>13</v>
       </c>
       <c r="C12">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D12" s="35" t="s">
         <v>892</v>
@@ -22993,7 +23084,7 @@
         <v>13</v>
       </c>
       <c r="C13">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D13" s="34" t="s">
         <v>893</v>
@@ -23022,7 +23113,7 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D14" s="35" t="s">
         <v>288</v>
@@ -23051,7 +23142,7 @@
         <v>13</v>
       </c>
       <c r="C15">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D15" s="34" t="s">
         <v>894</v>
@@ -23080,7 +23171,7 @@
         <v>13</v>
       </c>
       <c r="C16">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D16" s="35" t="s">
         <v>895</v>
@@ -23109,7 +23200,7 @@
         <v>13</v>
       </c>
       <c r="C17">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D17" s="34" t="s">
         <v>896</v>
@@ -23138,7 +23229,7 @@
         <v>13</v>
       </c>
       <c r="C18">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D18" s="35" t="s">
         <v>897</v>
@@ -23167,7 +23258,7 @@
         <v>13</v>
       </c>
       <c r="C19">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D19" s="34" t="s">
         <v>898</v>
@@ -23196,7 +23287,7 @@
         <v>13</v>
       </c>
       <c r="C20">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D20" s="35" t="s">
         <v>899</v>
@@ -23225,7 +23316,7 @@
         <v>13</v>
       </c>
       <c r="C21">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D21" s="34" t="s">
         <v>900</v>
@@ -23254,7 +23345,7 @@
         <v>13</v>
       </c>
       <c r="C22">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D22" s="35" t="s">
         <v>901</v>
@@ -23283,7 +23374,7 @@
         <v>13</v>
       </c>
       <c r="C23">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D23" s="34" t="s">
         <v>902</v>
@@ -23312,7 +23403,7 @@
         <v>13</v>
       </c>
       <c r="C24">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D24" s="34" t="s">
         <v>946</v>
@@ -23344,7 +23435,7 @@
         <v>13</v>
       </c>
       <c r="C25">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>148</v>
@@ -23442,7 +23533,7 @@
         <v>275</v>
       </c>
       <c r="C2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D2" s="40" t="s">
         <v>980</v>
@@ -23483,7 +23574,7 @@
         <v>275</v>
       </c>
       <c r="C3">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D3" s="40" t="s">
         <v>984</v>
@@ -23524,7 +23615,7 @@
         <v>275</v>
       </c>
       <c r="C4">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>987</v>
@@ -23565,7 +23656,7 @@
         <v>275</v>
       </c>
       <c r="C5">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>988</v>
@@ -23606,7 +23697,7 @@
         <v>275</v>
       </c>
       <c r="C6">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>989</v>
@@ -23647,7 +23738,7 @@
         <v>275</v>
       </c>
       <c r="C7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>990</v>
@@ -23688,7 +23779,7 @@
         <v>275</v>
       </c>
       <c r="C8">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>991</v>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/Round 2 Pods for Testing/Fast Track Pods/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="595" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D7C2B54-7BC9-4C4A-8FF2-849228F2A4F1}"/>
+  <xr:revisionPtr revIDLastSave="602" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACF60EE7-0997-4B4B-95EF-F59CAE9782D5}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView minimized="1" xWindow="-27780" yWindow="360" windowWidth="26910" windowHeight="14940" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -2663,21 +2663,6 @@
     <t>Type of validation being carried out</t>
   </si>
   <si>
-    <t>List any accreditations of the validation body</t>
-  </si>
-  <si>
-    <t>Name of the validation body</t>
-  </si>
-  <si>
-    <t>List the sectoral scopes the validation body is accredited to validate</t>
-  </si>
-  <si>
-    <t>Describe how the validation body was selected</t>
-  </si>
-  <si>
-    <t>List the names of any other validation body team members and their roles (FIRST NAME - LAST NAME, ROLE)</t>
-  </si>
-  <si>
     <t>Indicate whether the valiation event is planned.</t>
   </si>
   <si>
@@ -3240,6 +3225,21 @@
   </si>
   <si>
     <t>Date of validation event</t>
+  </si>
+  <si>
+    <t>List any accreditations of the VVB</t>
+  </si>
+  <si>
+    <t>Name of the VVB</t>
+  </si>
+  <si>
+    <t>List the sectoral scopes the VVB is accredited to validate</t>
+  </si>
+  <si>
+    <t>Describe how the VVB was selected</t>
+  </si>
+  <si>
+    <t>List the names of any other VVB team members and their roles (FIRST NAME - LAST NAME, ROLE)</t>
   </si>
 </sst>
 </file>
@@ -3472,7 +3472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3561,12 +3561,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14631,10 +14625,10 @@
         <v>276</v>
       </c>
       <c r="E262" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F262" s="41" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="G262" s="41" t="s">
         <v>18</v>
@@ -14655,7 +14649,7 @@
         <v>146</v>
       </c>
       <c r="M262" s="41" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
     </row>
     <row r="263" spans="1:13" x14ac:dyDescent="0.35">
@@ -14669,19 +14663,19 @@
         <v>262</v>
       </c>
       <c r="D263" s="41" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="E263" s="41" t="s">
+        <v>992</v>
+      </c>
+      <c r="F263" s="41" t="s">
+        <v>996</v>
+      </c>
+      <c r="G263" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H263" s="41" t="s">
         <v>997</v>
-      </c>
-      <c r="F263" s="41" t="s">
-        <v>1001</v>
-      </c>
-      <c r="G263" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="H263" s="41" t="s">
-        <v>1002</v>
       </c>
       <c r="I263" s="41" t="s">
         <v>31</v>
@@ -14696,7 +14690,7 @@
         <v>146</v>
       </c>
       <c r="M263" s="41" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
     </row>
     <row r="264" spans="1:13" x14ac:dyDescent="0.35">
@@ -14713,10 +14707,10 @@
         <v>823</v>
       </c>
       <c r="E264" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F264" s="41" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="G264" s="41" t="s">
         <v>18</v>
@@ -14737,7 +14731,7 @@
         <v>146</v>
       </c>
       <c r="M264" s="41" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="265" spans="1:13" x14ac:dyDescent="0.35">
@@ -14754,10 +14748,10 @@
         <v>824</v>
       </c>
       <c r="E265" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F265" s="41" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="G265" s="41" t="s">
         <v>18</v>
@@ -14778,7 +14772,7 @@
         <v>146</v>
       </c>
       <c r="M265" s="41" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="266" spans="1:13" x14ac:dyDescent="0.35">
@@ -14792,13 +14786,13 @@
         <v>265</v>
       </c>
       <c r="D266" s="41" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="E266" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F266" s="41" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="G266" s="41" t="s">
         <v>18</v>
@@ -14819,7 +14813,7 @@
         <v>146</v>
       </c>
       <c r="M266" s="41" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="267" spans="1:13" x14ac:dyDescent="0.35">
@@ -14833,19 +14827,19 @@
         <v>266</v>
       </c>
       <c r="D267" s="41" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="E267" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F267" s="41" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="G267" s="41" t="s">
         <v>18</v>
       </c>
       <c r="H267" s="41" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="I267" s="41" t="s">
         <v>226</v>
@@ -14860,7 +14854,7 @@
         <v>146</v>
       </c>
       <c r="M267" s="41" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="268" spans="1:13" x14ac:dyDescent="0.35">
@@ -14874,13 +14868,13 @@
         <v>267</v>
       </c>
       <c r="D268" s="41" t="s">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="E268" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F268" s="41" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="G268" s="41" t="s">
         <v>18</v>
@@ -14901,7 +14895,7 @@
         <v>146</v>
       </c>
       <c r="M268" s="41" t="s">
-        <v>1016</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="269" spans="1:13" x14ac:dyDescent="0.35">
@@ -14915,13 +14909,13 @@
         <v>268</v>
       </c>
       <c r="D269" s="41" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="E269" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F269" s="41" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="G269" s="41" t="s">
         <v>30</v>
@@ -14942,7 +14936,7 @@
         <v>146</v>
       </c>
       <c r="M269" s="41" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="270" spans="1:13" x14ac:dyDescent="0.35">
@@ -14959,10 +14953,10 @@
         <v>148</v>
       </c>
       <c r="E270" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F270" s="41" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G270" s="41" t="s">
         <v>18</v>
@@ -14983,7 +14977,7 @@
         <v>146</v>
       </c>
       <c r="M270" s="41" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="271" spans="1:13" x14ac:dyDescent="0.35">
@@ -14997,13 +14991,13 @@
         <v>270</v>
       </c>
       <c r="D271" s="41" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="E271" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F271" s="41" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="G271" s="41" t="s">
         <v>30</v>
@@ -15024,7 +15018,7 @@
         <v>146</v>
       </c>
       <c r="M271" s="41" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="272" spans="1:13" x14ac:dyDescent="0.35">
@@ -15041,10 +15035,10 @@
         <v>462</v>
       </c>
       <c r="E272" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F272" s="41" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="G272" s="41" t="s">
         <v>30</v>
@@ -15065,7 +15059,7 @@
         <v>146</v>
       </c>
       <c r="M272" s="41" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="273" spans="1:13" x14ac:dyDescent="0.35">
@@ -15082,10 +15076,10 @@
         <v>148</v>
       </c>
       <c r="E273" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F273" s="41" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="G273" s="41" t="s">
         <v>30</v>
@@ -15123,10 +15117,10 @@
         <v>825</v>
       </c>
       <c r="E274" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F274" s="41" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="G274" s="41" t="s">
         <v>18</v>
@@ -15147,7 +15141,7 @@
         <v>146</v>
       </c>
       <c r="M274" s="41" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="275" spans="1:13" x14ac:dyDescent="0.35">
@@ -15161,13 +15155,13 @@
         <v>274</v>
       </c>
       <c r="D275" s="41" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="E275" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F275" s="41" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="G275" s="41" t="s">
         <v>30</v>
@@ -15188,7 +15182,7 @@
         <v>146</v>
       </c>
       <c r="M275" s="41" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="276" spans="1:13" x14ac:dyDescent="0.35">
@@ -15202,13 +15196,13 @@
         <v>275</v>
       </c>
       <c r="D276" s="41" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="E276" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F276" s="41" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="G276" s="41" t="s">
         <v>30</v>
@@ -15229,7 +15223,7 @@
         <v>146</v>
       </c>
       <c r="M276" s="41" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="277" spans="1:13" x14ac:dyDescent="0.35">
@@ -15249,7 +15243,7 @@
         <v>141</v>
       </c>
       <c r="F277" s="41" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="G277" s="41" t="s">
         <v>18</v>
@@ -15270,7 +15264,7 @@
         <v>146</v>
       </c>
       <c r="M277" s="41" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="278" spans="1:13" x14ac:dyDescent="0.35">
@@ -15290,7 +15284,7 @@
         <v>141</v>
       </c>
       <c r="F278" s="41" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="G278" s="41" t="s">
         <v>18</v>
@@ -15311,7 +15305,7 @@
         <v>146</v>
       </c>
       <c r="M278" s="41" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="279" spans="1:13" x14ac:dyDescent="0.35">
@@ -15331,7 +15325,7 @@
         <v>116</v>
       </c>
       <c r="F279" s="41" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="G279" s="41" t="s">
         <v>18</v>
@@ -15352,7 +15346,7 @@
         <v>146</v>
       </c>
       <c r="M279" s="41" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="280" spans="1:13" x14ac:dyDescent="0.35">
@@ -15372,7 +15366,7 @@
         <v>116</v>
       </c>
       <c r="F280" s="41" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="G280" s="41" t="s">
         <v>18</v>
@@ -15393,7 +15387,7 @@
         <v>146</v>
       </c>
       <c r="M280" s="41" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="281" spans="1:13" x14ac:dyDescent="0.35">
@@ -15407,19 +15401,19 @@
         <v>280</v>
       </c>
       <c r="D281" s="41" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="E281" s="41" t="s">
         <v>116</v>
       </c>
       <c r="F281" s="41" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="G281" s="41" t="s">
         <v>30</v>
       </c>
       <c r="H281" s="41" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="I281" s="41" t="s">
         <v>31</v>
@@ -15434,7 +15428,7 @@
         <v>146</v>
       </c>
       <c r="M281" s="41" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="282" spans="1:13" x14ac:dyDescent="0.35">
@@ -15454,7 +15448,7 @@
         <v>266</v>
       </c>
       <c r="F282" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="G282" s="6" t="s">
         <v>18</v>
@@ -15495,7 +15489,7 @@
         <v>266</v>
       </c>
       <c r="F283" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="G283" s="6" t="s">
         <v>18</v>
@@ -15536,7 +15530,7 @@
         <v>266</v>
       </c>
       <c r="F284" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="G284" s="6" t="s">
         <v>18</v>
@@ -15577,7 +15571,7 @@
         <v>266</v>
       </c>
       <c r="F285" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="G285" s="17" t="s">
         <v>30</v>
@@ -15618,7 +15612,7 @@
         <v>266</v>
       </c>
       <c r="F286" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="G286" s="6" t="s">
         <v>18</v>
@@ -15659,7 +15653,7 @@
         <v>266</v>
       </c>
       <c r="F287" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="G287" s="6" t="s">
         <v>18</v>
@@ -15700,7 +15694,7 @@
         <v>266</v>
       </c>
       <c r="F288" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="G288" s="6" t="s">
         <v>18</v>
@@ -15735,13 +15729,13 @@
         <v>295</v>
       </c>
       <c r="D289" s="6" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="E289" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F289" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="G289" s="17" t="s">
         <v>30</v>
@@ -15776,13 +15770,13 @@
         <v>296</v>
       </c>
       <c r="D290" s="6" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="E290" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F290" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="G290" s="17" t="s">
         <v>30</v>
@@ -15817,13 +15811,13 @@
         <v>297</v>
       </c>
       <c r="D291" s="6" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="E291" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F291" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="G291" s="17" t="s">
         <v>30</v>
@@ -15858,13 +15852,13 @@
         <v>298</v>
       </c>
       <c r="D292" s="6" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="E292" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F292" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="G292" s="17" t="s">
         <v>30</v>
@@ -15899,13 +15893,13 @@
         <v>299</v>
       </c>
       <c r="D293" s="6" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="E293" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F293" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G293" s="17" t="s">
         <v>30</v>
@@ -15940,13 +15934,13 @@
         <v>300</v>
       </c>
       <c r="D294" s="6" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="E294" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F294" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="G294" s="17" t="s">
         <v>30</v>
@@ -15981,13 +15975,13 @@
         <v>301</v>
       </c>
       <c r="D295" s="6" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="E295" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F295" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G295" s="17" t="s">
         <v>30</v>
@@ -16022,13 +16016,13 @@
         <v>302</v>
       </c>
       <c r="D296" s="6" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="E296" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F296" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="G296" s="17" t="s">
         <v>30</v>
@@ -16069,7 +16063,7 @@
         <v>266</v>
       </c>
       <c r="F297" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="G297" s="6" t="s">
         <v>18</v>
@@ -16094,44 +16088,44 @@
       </c>
     </row>
     <row r="298" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A298" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="B298" s="42" t="s">
+      <c r="A298" t="s">
+        <v>13</v>
+      </c>
+      <c r="B298" t="s">
         <v>275</v>
       </c>
       <c r="C298">
         <v>304</v>
       </c>
-      <c r="D298" s="43" t="s">
+      <c r="D298" s="17" t="s">
         <v>269</v>
       </c>
-      <c r="E298" s="44" t="s">
+      <c r="E298" s="33" t="s">
         <v>266</v>
       </c>
-      <c r="F298" s="42" t="s">
+      <c r="F298" t="s">
         <v>270</v>
       </c>
-      <c r="G298" s="45" t="s">
+      <c r="G298" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H298" s="45" t="s">
+      <c r="H298" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="I298" s="45" t="s">
+      <c r="I298" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J298" s="45" t="s">
+      <c r="J298" s="6" t="s">
         <v>841</v>
       </c>
-      <c r="K298" s="45" t="s">
+      <c r="K298" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="L298" s="45" t="s">
-        <v>146</v>
-      </c>
-      <c r="M298" s="45" t="s">
-        <v>1047</v>
+      <c r="L298" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M298" s="6" t="s">
+        <v>1042</v>
       </c>
     </row>
     <row r="299" spans="1:13" x14ac:dyDescent="0.35">
@@ -16151,7 +16145,7 @@
         <v>266</v>
       </c>
       <c r="F299" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="G299" s="6" t="s">
         <v>18</v>
@@ -16192,7 +16186,7 @@
         <v>266</v>
       </c>
       <c r="F300" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="G300" s="6" t="s">
         <v>18</v>
@@ -16213,7 +16207,7 @@
         <v>146</v>
       </c>
       <c r="M300" s="6" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
     </row>
     <row r="301" spans="1:13" x14ac:dyDescent="0.35">
@@ -16233,7 +16227,7 @@
         <v>266</v>
       </c>
       <c r="F301" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="G301" s="6" t="s">
         <v>18</v>
@@ -16254,7 +16248,7 @@
         <v>146</v>
       </c>
       <c r="M301" s="6" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
     </row>
     <row r="302" spans="1:13" x14ac:dyDescent="0.35">
@@ -16274,7 +16268,7 @@
         <v>266</v>
       </c>
       <c r="F302" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
       <c r="G302" s="6" t="s">
         <v>18</v>
@@ -16295,7 +16289,7 @@
         <v>146</v>
       </c>
       <c r="M302" s="6" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
     </row>
     <row r="303" spans="1:13" x14ac:dyDescent="0.35">
@@ -16315,7 +16309,7 @@
         <v>266</v>
       </c>
       <c r="F303" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="G303" s="17" t="s">
         <v>30</v>
@@ -16336,7 +16330,7 @@
         <v>146</v>
       </c>
       <c r="M303" s="17" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
     </row>
     <row r="304" spans="1:13" x14ac:dyDescent="0.35">
@@ -16356,7 +16350,7 @@
         <v>266</v>
       </c>
       <c r="F304" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="G304" s="17" t="s">
         <v>30</v>
@@ -16377,7 +16371,7 @@
         <v>146</v>
       </c>
       <c r="M304" s="6" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="305" spans="1:13" x14ac:dyDescent="0.35">
@@ -16397,7 +16391,7 @@
         <v>266</v>
       </c>
       <c r="F305" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="G305" s="17" t="s">
         <v>30</v>
@@ -16418,7 +16412,7 @@
         <v>146</v>
       </c>
       <c r="M305" s="6" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
     </row>
     <row r="306" spans="1:13" x14ac:dyDescent="0.35">
@@ -16438,7 +16432,7 @@
         <v>266</v>
       </c>
       <c r="F306" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="G306" s="17" t="s">
         <v>30</v>
@@ -16459,7 +16453,7 @@
         <v>146</v>
       </c>
       <c r="M306" s="6" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
     </row>
     <row r="307" spans="1:13" x14ac:dyDescent="0.35">
@@ -16479,7 +16473,7 @@
         <v>266</v>
       </c>
       <c r="F307" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="G307" s="17" t="s">
         <v>30</v>
@@ -16500,7 +16494,7 @@
         <v>146</v>
       </c>
       <c r="M307" s="6" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
     </row>
     <row r="308" spans="1:13" x14ac:dyDescent="0.35">
@@ -16520,7 +16514,7 @@
         <v>266</v>
       </c>
       <c r="F308" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="G308" s="6" t="s">
         <v>563</v>
@@ -16541,7 +16535,7 @@
         <v>146</v>
       </c>
       <c r="M308" s="6" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
     </row>
     <row r="309" spans="1:13" x14ac:dyDescent="0.35">
@@ -16561,7 +16555,7 @@
         <v>266</v>
       </c>
       <c r="F309" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="G309" s="6" t="s">
         <v>18</v>
@@ -16582,7 +16576,7 @@
         <v>146</v>
       </c>
       <c r="M309" s="6" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
     </row>
     <row r="310" spans="1:13" x14ac:dyDescent="0.35">
@@ -16596,13 +16590,13 @@
         <v>316</v>
       </c>
       <c r="D310" s="6" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="E310" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F310" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="G310" s="17" t="s">
         <v>30</v>
@@ -16623,7 +16617,7 @@
         <v>146</v>
       </c>
       <c r="M310" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
     </row>
     <row r="311" spans="1:13" x14ac:dyDescent="0.35">
@@ -16643,7 +16637,7 @@
         <v>266</v>
       </c>
       <c r="F311" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="G311" t="s">
         <v>30</v>
@@ -16675,13 +16669,13 @@
         <v>318</v>
       </c>
       <c r="D312" s="34" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="E312" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F312" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="G312" s="36" t="s">
         <v>18</v>
@@ -16693,7 +16687,7 @@
         <v>20</v>
       </c>
       <c r="M312" s="34" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
     </row>
     <row r="313" spans="1:13" x14ac:dyDescent="0.35">
@@ -16704,13 +16698,13 @@
         <v>319</v>
       </c>
       <c r="D313" s="34" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="E313" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F313" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="G313" s="36" t="s">
         <v>192</v>
@@ -16722,7 +16716,7 @@
         <v>144</v>
       </c>
       <c r="M313" s="34" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
     </row>
     <row r="314" spans="1:13" x14ac:dyDescent="0.35">
@@ -16733,13 +16727,13 @@
         <v>320</v>
       </c>
       <c r="D314" s="35" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="E314" s="38" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F314" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="G314" s="38" t="s">
         <v>18</v>
@@ -16751,7 +16745,7 @@
         <v>20</v>
       </c>
       <c r="M314" s="35" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
     </row>
     <row r="315" spans="1:13" x14ac:dyDescent="0.35">
@@ -16762,13 +16756,13 @@
         <v>321</v>
       </c>
       <c r="D315" s="34" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="E315" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F315" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="G315" s="36" t="s">
         <v>18</v>
@@ -16780,7 +16774,7 @@
         <v>20</v>
       </c>
       <c r="M315" s="34" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
     </row>
     <row r="316" spans="1:13" x14ac:dyDescent="0.35">
@@ -16791,13 +16785,13 @@
         <v>322</v>
       </c>
       <c r="D316" s="35" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="E316" s="38" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F316" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="G316" s="38" t="s">
         <v>18</v>
@@ -16809,7 +16803,7 @@
         <v>20</v>
       </c>
       <c r="M316" s="35" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
     </row>
     <row r="317" spans="1:13" x14ac:dyDescent="0.35">
@@ -16820,13 +16814,13 @@
         <v>323</v>
       </c>
       <c r="D317" s="34" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="E317" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F317" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="G317" s="36" t="s">
         <v>18</v>
@@ -16838,7 +16832,7 @@
         <v>20</v>
       </c>
       <c r="M317" s="34" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
     </row>
     <row r="318" spans="1:13" x14ac:dyDescent="0.35">
@@ -16849,13 +16843,13 @@
         <v>324</v>
       </c>
       <c r="D318" s="35" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="E318" s="38" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F318" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="G318" s="38" t="s">
         <v>18</v>
@@ -16867,7 +16861,7 @@
         <v>20</v>
       </c>
       <c r="M318" s="35" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
     </row>
     <row r="319" spans="1:13" x14ac:dyDescent="0.35">
@@ -16878,13 +16872,13 @@
         <v>325</v>
       </c>
       <c r="D319" s="34" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="E319" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F319" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="G319" s="36" t="s">
         <v>18</v>
@@ -16896,7 +16890,7 @@
         <v>20</v>
       </c>
       <c r="M319" s="34" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
     </row>
     <row r="320" spans="1:13" x14ac:dyDescent="0.35">
@@ -16907,13 +16901,13 @@
         <v>326</v>
       </c>
       <c r="D320" s="35" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="E320" s="38" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F320" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="G320" s="38" t="s">
         <v>18</v>
@@ -16925,7 +16919,7 @@
         <v>20</v>
       </c>
       <c r="M320" s="35" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
     </row>
     <row r="321" spans="1:13" x14ac:dyDescent="0.35">
@@ -16936,13 +16930,13 @@
         <v>327</v>
       </c>
       <c r="D321" s="34" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="E321" s="36" t="s">
+        <v>921</v>
+      </c>
+      <c r="F321" t="s">
         <v>926</v>
-      </c>
-      <c r="F321" t="s">
-        <v>931</v>
       </c>
       <c r="G321" s="36" t="s">
         <v>18</v>
@@ -16954,7 +16948,7 @@
         <v>20</v>
       </c>
       <c r="M321" s="34" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
     </row>
     <row r="322" spans="1:13" x14ac:dyDescent="0.35">
@@ -16965,13 +16959,13 @@
         <v>328</v>
       </c>
       <c r="D322" s="35" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="E322" s="38" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F322" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="G322" s="38" t="s">
         <v>18</v>
@@ -16983,7 +16977,7 @@
         <v>20</v>
       </c>
       <c r="M322" s="35" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
     </row>
     <row r="323" spans="1:13" x14ac:dyDescent="0.35">
@@ -16994,13 +16988,13 @@
         <v>329</v>
       </c>
       <c r="D323" s="34" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="E323" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F323" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="G323" s="36" t="s">
         <v>30</v>
@@ -17012,7 +17006,7 @@
         <v>144</v>
       </c>
       <c r="M323" s="34" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
     </row>
     <row r="324" spans="1:13" x14ac:dyDescent="0.35">
@@ -17026,22 +17020,22 @@
         <v>288</v>
       </c>
       <c r="E324" s="38" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F324" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="G324" s="38" t="s">
         <v>563</v>
       </c>
       <c r="H324" s="39" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="I324" s="38" t="s">
         <v>20</v>
       </c>
       <c r="M324" s="35" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
     </row>
     <row r="325" spans="1:13" x14ac:dyDescent="0.35">
@@ -17052,13 +17046,13 @@
         <v>331</v>
       </c>
       <c r="D325" s="34" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="E325" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F325" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="G325" s="36" t="s">
         <v>18</v>
@@ -17070,7 +17064,7 @@
         <v>20</v>
       </c>
       <c r="M325" s="34" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
     </row>
     <row r="326" spans="1:13" x14ac:dyDescent="0.35">
@@ -17081,13 +17075,13 @@
         <v>332</v>
       </c>
       <c r="D326" s="35" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="E326" s="38" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F326" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="G326" s="38" t="s">
         <v>30</v>
@@ -17099,7 +17093,7 @@
         <v>144</v>
       </c>
       <c r="M326" s="35" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
     </row>
     <row r="327" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -17110,25 +17104,25 @@
         <v>333</v>
       </c>
       <c r="D327" s="34" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="E327" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F327" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="G327" s="38" t="s">
         <v>30</v>
       </c>
       <c r="H327" s="37" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="I327" s="36" t="s">
         <v>144</v>
       </c>
       <c r="M327" s="34" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
     </row>
     <row r="328" spans="1:13" x14ac:dyDescent="0.35">
@@ -17139,13 +17133,13 @@
         <v>334</v>
       </c>
       <c r="D328" s="35" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="E328" s="38" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F328" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="G328" s="38" t="s">
         <v>30</v>
@@ -17157,7 +17151,7 @@
         <v>144</v>
       </c>
       <c r="M328" s="35" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
     </row>
     <row r="329" spans="1:13" x14ac:dyDescent="0.35">
@@ -17168,13 +17162,13 @@
         <v>335</v>
       </c>
       <c r="D329" s="34" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="E329" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F329" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="G329" s="38" t="s">
         <v>30</v>
@@ -17186,7 +17180,7 @@
         <v>144</v>
       </c>
       <c r="M329" s="34" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
     </row>
     <row r="330" spans="1:13" x14ac:dyDescent="0.35">
@@ -17197,13 +17191,13 @@
         <v>336</v>
       </c>
       <c r="D330" s="35" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="E330" s="38" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F330" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="G330" s="38" t="s">
         <v>30</v>
@@ -17215,7 +17209,7 @@
         <v>144</v>
       </c>
       <c r="M330" s="35" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
     </row>
     <row r="331" spans="1:13" x14ac:dyDescent="0.35">
@@ -17226,13 +17220,13 @@
         <v>337</v>
       </c>
       <c r="D331" s="34" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="E331" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F331" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="G331" s="38" t="s">
         <v>30</v>
@@ -17244,7 +17238,7 @@
         <v>144</v>
       </c>
       <c r="M331" s="34" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
     </row>
     <row r="332" spans="1:13" x14ac:dyDescent="0.35">
@@ -17255,13 +17249,13 @@
         <v>338</v>
       </c>
       <c r="D332" s="35" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="E332" s="38" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F332" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="G332" s="38" t="s">
         <v>30</v>
@@ -17273,7 +17267,7 @@
         <v>144</v>
       </c>
       <c r="M332" s="35" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
     </row>
     <row r="333" spans="1:13" x14ac:dyDescent="0.35">
@@ -17284,13 +17278,13 @@
         <v>339</v>
       </c>
       <c r="D333" s="34" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="E333" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F333" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="G333" s="38" t="s">
         <v>30</v>
@@ -17302,7 +17296,7 @@
         <v>144</v>
       </c>
       <c r="M333" s="34" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
     </row>
     <row r="334" spans="1:13" x14ac:dyDescent="0.35">
@@ -17313,13 +17307,13 @@
         <v>340</v>
       </c>
       <c r="D334" s="34" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="E334" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F334" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="G334" s="6" t="s">
         <v>30</v>
@@ -17348,10 +17342,10 @@
         <v>148</v>
       </c>
       <c r="E335" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F335" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="G335" t="s">
         <v>30</v>
@@ -17380,13 +17374,13 @@
         <v>342</v>
       </c>
       <c r="D336" s="40" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="E336" s="40" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="F336" s="40" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="G336" s="40" t="s">
         <v>18</v>
@@ -17407,7 +17401,7 @@
         <v>146</v>
       </c>
       <c r="M336" s="34" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
     </row>
     <row r="337" spans="1:13" x14ac:dyDescent="0.35">
@@ -17421,16 +17415,16 @@
         <v>343</v>
       </c>
       <c r="D337" s="40" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="E337" s="40" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="F337" s="40" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="G337" s="40" t="s">
-        <v>18</v>
+        <v>563</v>
       </c>
       <c r="H337" s="40" t="s">
         <v>143</v>
@@ -17448,7 +17442,7 @@
         <v>146</v>
       </c>
       <c r="M337" s="40" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
     </row>
     <row r="338" spans="1:13" x14ac:dyDescent="0.35">
@@ -17462,13 +17456,13 @@
         <v>344</v>
       </c>
       <c r="D338" s="6" t="s">
+        <v>982</v>
+      </c>
+      <c r="E338" s="40" t="s">
+        <v>976</v>
+      </c>
+      <c r="F338" t="s">
         <v>987</v>
-      </c>
-      <c r="E338" s="40" t="s">
-        <v>981</v>
-      </c>
-      <c r="F338" t="s">
-        <v>992</v>
       </c>
       <c r="G338" s="17" t="s">
         <v>30</v>
@@ -17489,7 +17483,7 @@
         <v>146</v>
       </c>
       <c r="M338" s="6" t="s">
-        <v>855</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="339" spans="1:13" x14ac:dyDescent="0.35">
@@ -17503,13 +17497,13 @@
         <v>345</v>
       </c>
       <c r="D339" s="17" t="s">
+        <v>983</v>
+      </c>
+      <c r="E339" s="40" t="s">
+        <v>976</v>
+      </c>
+      <c r="F339" t="s">
         <v>988</v>
-      </c>
-      <c r="E339" s="40" t="s">
-        <v>981</v>
-      </c>
-      <c r="F339" t="s">
-        <v>993</v>
       </c>
       <c r="G339" s="6" t="s">
         <v>18</v>
@@ -17530,7 +17524,7 @@
         <v>146</v>
       </c>
       <c r="M339" s="6" t="s">
-        <v>856</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="340" spans="1:13" x14ac:dyDescent="0.35">
@@ -17544,13 +17538,13 @@
         <v>346</v>
       </c>
       <c r="D340" s="6" t="s">
+        <v>984</v>
+      </c>
+      <c r="E340" s="40" t="s">
+        <v>976</v>
+      </c>
+      <c r="F340" t="s">
         <v>989</v>
-      </c>
-      <c r="E340" s="40" t="s">
-        <v>981</v>
-      </c>
-      <c r="F340" t="s">
-        <v>994</v>
       </c>
       <c r="G340" s="6" t="s">
         <v>192</v>
@@ -17571,7 +17565,7 @@
         <v>146</v>
       </c>
       <c r="M340" s="6" t="s">
-        <v>857</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="341" spans="1:13" x14ac:dyDescent="0.35">
@@ -17585,13 +17579,13 @@
         <v>347</v>
       </c>
       <c r="D341" s="6" t="s">
+        <v>985</v>
+      </c>
+      <c r="E341" s="40" t="s">
+        <v>976</v>
+      </c>
+      <c r="F341" t="s">
         <v>990</v>
-      </c>
-      <c r="E341" s="40" t="s">
-        <v>981</v>
-      </c>
-      <c r="F341" t="s">
-        <v>995</v>
       </c>
       <c r="G341" s="6" t="s">
         <v>30</v>
@@ -17612,7 +17606,7 @@
         <v>146</v>
       </c>
       <c r="M341" s="6" t="s">
-        <v>858</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="342" spans="1:13" x14ac:dyDescent="0.35">
@@ -17626,13 +17620,13 @@
         <v>348</v>
       </c>
       <c r="D342" s="6" t="s">
+        <v>986</v>
+      </c>
+      <c r="E342" s="40" t="s">
+        <v>976</v>
+      </c>
+      <c r="F342" t="s">
         <v>991</v>
-      </c>
-      <c r="E342" s="40" t="s">
-        <v>981</v>
-      </c>
-      <c r="F342" t="s">
-        <v>996</v>
       </c>
       <c r="G342" s="6" t="s">
         <v>30</v>
@@ -17653,7 +17647,7 @@
         <v>146</v>
       </c>
       <c r="M342" s="6" t="s">
-        <v>859</v>
+        <v>1047</v>
       </c>
     </row>
   </sheetData>
@@ -20598,10 +20592,10 @@
         <v>276</v>
       </c>
       <c r="E2" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F2" s="41" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="G2" s="41" t="s">
         <v>18</v>
@@ -20622,7 +20616,7 @@
         <v>146</v>
       </c>
       <c r="M2" s="41" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -20636,19 +20630,19 @@
         <v>262</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="E3" s="41" t="s">
+        <v>992</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>996</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="41" t="s">
         <v>997</v>
-      </c>
-      <c r="F3" s="41" t="s">
-        <v>1001</v>
-      </c>
-      <c r="G3" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="41" t="s">
-        <v>1002</v>
       </c>
       <c r="I3" s="41" t="s">
         <v>31</v>
@@ -20663,7 +20657,7 @@
         <v>146</v>
       </c>
       <c r="M3" s="41" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -20680,10 +20674,10 @@
         <v>823</v>
       </c>
       <c r="E4" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F4" s="41" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="G4" s="41" t="s">
         <v>18</v>
@@ -20704,7 +20698,7 @@
         <v>146</v>
       </c>
       <c r="M4" s="41" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -20721,10 +20715,10 @@
         <v>824</v>
       </c>
       <c r="E5" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F5" s="41" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="G5" s="41" t="s">
         <v>18</v>
@@ -20745,7 +20739,7 @@
         <v>146</v>
       </c>
       <c r="M5" s="41" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -20759,13 +20753,13 @@
         <v>265</v>
       </c>
       <c r="D6" s="41" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="E6" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F6" s="41" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="G6" s="41" t="s">
         <v>18</v>
@@ -20786,7 +20780,7 @@
         <v>146</v>
       </c>
       <c r="M6" s="41" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -20800,19 +20794,19 @@
         <v>266</v>
       </c>
       <c r="D7" s="41" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="E7" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F7" s="41" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="G7" s="41" t="s">
         <v>18</v>
       </c>
       <c r="H7" s="41" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="I7" s="41" t="s">
         <v>226</v>
@@ -20827,7 +20821,7 @@
         <v>146</v>
       </c>
       <c r="M7" s="41" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -20841,13 +20835,13 @@
         <v>267</v>
       </c>
       <c r="D8" s="41" t="s">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="E8" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F8" s="41" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="G8" s="41" t="s">
         <v>18</v>
@@ -20868,7 +20862,7 @@
         <v>146</v>
       </c>
       <c r="M8" s="41" t="s">
-        <v>1016</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -20882,13 +20876,13 @@
         <v>268</v>
       </c>
       <c r="D9" s="41" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="E9" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F9" s="41" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="G9" s="41" t="s">
         <v>30</v>
@@ -20909,7 +20903,7 @@
         <v>146</v>
       </c>
       <c r="M9" s="41" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
@@ -20926,10 +20920,10 @@
         <v>148</v>
       </c>
       <c r="E10" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F10" s="41" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G10" s="41" t="s">
         <v>18</v>
@@ -20950,7 +20944,7 @@
         <v>146</v>
       </c>
       <c r="M10" s="41" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -20964,13 +20958,13 @@
         <v>270</v>
       </c>
       <c r="D11" s="41" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="E11" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F11" s="41" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="G11" s="41" t="s">
         <v>30</v>
@@ -20991,7 +20985,7 @@
         <v>146</v>
       </c>
       <c r="M11" s="41" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -21008,10 +21002,10 @@
         <v>462</v>
       </c>
       <c r="E12" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F12" s="41" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="G12" s="41" t="s">
         <v>30</v>
@@ -21032,7 +21026,7 @@
         <v>146</v>
       </c>
       <c r="M12" s="41" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -21049,10 +21043,10 @@
         <v>148</v>
       </c>
       <c r="E13" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="G13" s="41" t="s">
         <v>30</v>
@@ -21090,10 +21084,10 @@
         <v>825</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F14" s="41" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="G14" s="41" t="s">
         <v>18</v>
@@ -21114,7 +21108,7 @@
         <v>146</v>
       </c>
       <c r="M14" s="41" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -21128,13 +21122,13 @@
         <v>274</v>
       </c>
       <c r="D15" s="41" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F15" s="41" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="G15" s="41" t="s">
         <v>30</v>
@@ -21155,7 +21149,7 @@
         <v>146</v>
       </c>
       <c r="M15" s="41" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -21169,13 +21163,13 @@
         <v>275</v>
       </c>
       <c r="D16" s="41" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F16" s="41" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="G16" s="41" t="s">
         <v>30</v>
@@ -21196,7 +21190,7 @@
         <v>146</v>
       </c>
       <c r="M16" s="41" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
@@ -21216,7 +21210,7 @@
         <v>141</v>
       </c>
       <c r="F17" s="41" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="G17" s="41" t="s">
         <v>18</v>
@@ -21237,7 +21231,7 @@
         <v>146</v>
       </c>
       <c r="M17" s="41" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
@@ -21257,7 +21251,7 @@
         <v>141</v>
       </c>
       <c r="F18" s="41" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="G18" s="41" t="s">
         <v>18</v>
@@ -21278,7 +21272,7 @@
         <v>146</v>
       </c>
       <c r="M18" s="41" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
@@ -21298,7 +21292,7 @@
         <v>116</v>
       </c>
       <c r="F19" s="41" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="G19" s="41" t="s">
         <v>18</v>
@@ -21319,7 +21313,7 @@
         <v>146</v>
       </c>
       <c r="M19" s="41" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
@@ -21339,7 +21333,7 @@
         <v>116</v>
       </c>
       <c r="F20" s="41" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="G20" s="41" t="s">
         <v>18</v>
@@ -21360,7 +21354,7 @@
         <v>146</v>
       </c>
       <c r="M20" s="41" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
@@ -21374,19 +21368,19 @@
         <v>280</v>
       </c>
       <c r="D21" s="41" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="E21" s="41" t="s">
         <v>116</v>
       </c>
       <c r="F21" s="41" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="G21" s="41" t="s">
         <v>30</v>
       </c>
       <c r="H21" s="41" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="I21" s="41" t="s">
         <v>31</v>
@@ -21401,7 +21395,7 @@
         <v>146</v>
       </c>
       <c r="M21" s="41" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
     </row>
   </sheetData>
@@ -21484,7 +21478,7 @@
         <v>266</v>
       </c>
       <c r="F2" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>18</v>
@@ -21525,7 +21519,7 @@
         <v>266</v>
       </c>
       <c r="F3" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>18</v>
@@ -21566,7 +21560,7 @@
         <v>266</v>
       </c>
       <c r="F4" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>18</v>
@@ -21607,7 +21601,7 @@
         <v>266</v>
       </c>
       <c r="F5" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="G5" s="17" t="s">
         <v>30</v>
@@ -21648,7 +21642,7 @@
         <v>266</v>
       </c>
       <c r="F6" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>18</v>
@@ -21689,7 +21683,7 @@
         <v>266</v>
       </c>
       <c r="F7" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>18</v>
@@ -21730,7 +21724,7 @@
         <v>266</v>
       </c>
       <c r="F8" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>18</v>
@@ -21765,13 +21759,13 @@
         <v>295</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="E9" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F9" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="G9" s="17" t="s">
         <v>30</v>
@@ -21806,13 +21800,13 @@
         <v>296</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="E10" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F10" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="G10" s="17" t="s">
         <v>30</v>
@@ -21847,13 +21841,13 @@
         <v>297</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="E11" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F11" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="G11" s="17" t="s">
         <v>30</v>
@@ -21888,13 +21882,13 @@
         <v>298</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="E12" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F12" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="G12" s="17" t="s">
         <v>30</v>
@@ -21929,13 +21923,13 @@
         <v>299</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="E13" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F13" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G13" s="17" t="s">
         <v>30</v>
@@ -21970,13 +21964,13 @@
         <v>300</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="E14" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F14" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="G14" s="17" t="s">
         <v>30</v>
@@ -22011,13 +22005,13 @@
         <v>301</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="E15" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F15" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G15" s="17" t="s">
         <v>30</v>
@@ -22052,13 +22046,13 @@
         <v>302</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="E16" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F16" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="G16" s="17" t="s">
         <v>30</v>
@@ -22099,7 +22093,7 @@
         <v>266</v>
       </c>
       <c r="F17" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>18</v>
@@ -22123,45 +22117,45 @@
         <v>854</v>
       </c>
     </row>
-    <row r="18" spans="1:13" s="42" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="42" t="s">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
         <v>275</v>
       </c>
       <c r="C18">
         <v>304</v>
       </c>
-      <c r="D18" s="43" t="s">
+      <c r="D18" s="17" t="s">
         <v>269</v>
       </c>
-      <c r="E18" s="44" t="s">
+      <c r="E18" s="33" t="s">
         <v>266</v>
       </c>
-      <c r="F18" s="42" t="s">
+      <c r="F18" t="s">
         <v>270</v>
       </c>
-      <c r="G18" s="45" t="s">
+      <c r="G18" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H18" s="45" t="s">
+      <c r="H18" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="I18" s="45" t="s">
+      <c r="I18" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J18" s="45" t="s">
+      <c r="J18" s="6" t="s">
         <v>841</v>
       </c>
-      <c r="K18" s="45" t="s">
+      <c r="K18" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="L18" s="45" t="s">
-        <v>146</v>
-      </c>
-      <c r="M18" s="45" t="s">
-        <v>1047</v>
+      <c r="L18" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>1042</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
@@ -22181,7 +22175,7 @@
         <v>266</v>
       </c>
       <c r="F19" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>18</v>
@@ -22222,7 +22216,7 @@
         <v>266</v>
       </c>
       <c r="F20" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>18</v>
@@ -22243,7 +22237,7 @@
         <v>146</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
@@ -22263,7 +22257,7 @@
         <v>266</v>
       </c>
       <c r="F21" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>18</v>
@@ -22284,7 +22278,7 @@
         <v>146</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
@@ -22304,7 +22298,7 @@
         <v>266</v>
       </c>
       <c r="F22" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>18</v>
@@ -22325,7 +22319,7 @@
         <v>146</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
@@ -22345,7 +22339,7 @@
         <v>266</v>
       </c>
       <c r="F23" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="G23" s="17" t="s">
         <v>30</v>
@@ -22366,7 +22360,7 @@
         <v>146</v>
       </c>
       <c r="M23" s="17" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
@@ -22386,7 +22380,7 @@
         <v>266</v>
       </c>
       <c r="F24" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="G24" s="17" t="s">
         <v>30</v>
@@ -22407,7 +22401,7 @@
         <v>146</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
@@ -22427,7 +22421,7 @@
         <v>266</v>
       </c>
       <c r="F25" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="G25" s="17" t="s">
         <v>30</v>
@@ -22448,7 +22442,7 @@
         <v>146</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
@@ -22468,7 +22462,7 @@
         <v>266</v>
       </c>
       <c r="F26" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="G26" s="17" t="s">
         <v>30</v>
@@ -22489,7 +22483,7 @@
         <v>146</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
@@ -22509,7 +22503,7 @@
         <v>266</v>
       </c>
       <c r="F27" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="G27" s="17" t="s">
         <v>30</v>
@@ -22530,7 +22524,7 @@
         <v>146</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
@@ -22550,7 +22544,7 @@
         <v>266</v>
       </c>
       <c r="F28" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>563</v>
@@ -22571,7 +22565,7 @@
         <v>146</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
@@ -22591,7 +22585,7 @@
         <v>266</v>
       </c>
       <c r="F29" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>18</v>
@@ -22612,7 +22606,7 @@
         <v>146</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.35">
@@ -22626,13 +22620,13 @@
         <v>316</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="E30" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F30" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="G30" s="17" t="s">
         <v>30</v>
@@ -22653,7 +22647,7 @@
         <v>146</v>
       </c>
       <c r="M30" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
@@ -22673,7 +22667,7 @@
         <v>266</v>
       </c>
       <c r="F31" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="G31" t="s">
         <v>30</v>
@@ -22768,13 +22762,13 @@
         <v>318</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F2" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="G2" s="36" t="s">
         <v>18</v>
@@ -22786,7 +22780,7 @@
         <v>20</v>
       </c>
       <c r="M2" s="34" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -22797,13 +22791,13 @@
         <v>319</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F3" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="G3" s="36" t="s">
         <v>192</v>
@@ -22815,7 +22809,7 @@
         <v>144</v>
       </c>
       <c r="M3" s="34" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -22826,13 +22820,13 @@
         <v>320</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="E4" s="38" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F4" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="G4" s="38" t="s">
         <v>18</v>
@@ -22844,7 +22838,7 @@
         <v>20</v>
       </c>
       <c r="M4" s="35" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -22855,13 +22849,13 @@
         <v>321</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F5" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="G5" s="36" t="s">
         <v>18</v>
@@ -22873,7 +22867,7 @@
         <v>20</v>
       </c>
       <c r="M5" s="34" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -22884,13 +22878,13 @@
         <v>322</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F6" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="G6" s="38" t="s">
         <v>18</v>
@@ -22902,7 +22896,7 @@
         <v>20</v>
       </c>
       <c r="M6" s="35" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -22913,13 +22907,13 @@
         <v>323</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F7" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="G7" s="36" t="s">
         <v>18</v>
@@ -22931,7 +22925,7 @@
         <v>20</v>
       </c>
       <c r="M7" s="34" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -22942,13 +22936,13 @@
         <v>324</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="E8" s="38" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F8" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="G8" s="38" t="s">
         <v>18</v>
@@ -22960,7 +22954,7 @@
         <v>20</v>
       </c>
       <c r="M8" s="35" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -22971,13 +22965,13 @@
         <v>325</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F9" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="G9" s="36" t="s">
         <v>18</v>
@@ -22989,7 +22983,7 @@
         <v>20</v>
       </c>
       <c r="M9" s="34" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
@@ -23000,13 +22994,13 @@
         <v>326</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F10" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="G10" s="38" t="s">
         <v>18</v>
@@ -23018,7 +23012,7 @@
         <v>20</v>
       </c>
       <c r="M10" s="35" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -23029,13 +23023,13 @@
         <v>327</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="E11" s="36" t="s">
+        <v>921</v>
+      </c>
+      <c r="F11" t="s">
         <v>926</v>
-      </c>
-      <c r="F11" t="s">
-        <v>931</v>
       </c>
       <c r="G11" s="36" t="s">
         <v>18</v>
@@ -23047,7 +23041,7 @@
         <v>20</v>
       </c>
       <c r="M11" s="34" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -23058,13 +23052,13 @@
         <v>328</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F12" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="G12" s="38" t="s">
         <v>18</v>
@@ -23076,7 +23070,7 @@
         <v>20</v>
       </c>
       <c r="M12" s="35" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -23087,13 +23081,13 @@
         <v>329</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F13" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="G13" s="36" t="s">
         <v>30</v>
@@ -23105,7 +23099,7 @@
         <v>144</v>
       </c>
       <c r="M13" s="34" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -23119,22 +23113,22 @@
         <v>288</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F14" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="G14" s="38" t="s">
         <v>563</v>
       </c>
       <c r="H14" s="39" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="I14" s="38" t="s">
         <v>20</v>
       </c>
       <c r="M14" s="35" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -23145,13 +23139,13 @@
         <v>331</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F15" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="G15" s="36" t="s">
         <v>18</v>
@@ -23163,7 +23157,7 @@
         <v>20</v>
       </c>
       <c r="M15" s="34" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -23174,13 +23168,13 @@
         <v>332</v>
       </c>
       <c r="D16" s="35" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F16" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="G16" s="38" t="s">
         <v>30</v>
@@ -23192,7 +23186,7 @@
         <v>144</v>
       </c>
       <c r="M16" s="35" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
@@ -23203,25 +23197,25 @@
         <v>333</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F17" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="G17" s="38" t="s">
         <v>30</v>
       </c>
       <c r="H17" s="37" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="I17" s="36" t="s">
         <v>144</v>
       </c>
       <c r="M17" s="34" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
@@ -23232,13 +23226,13 @@
         <v>334</v>
       </c>
       <c r="D18" s="35" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="E18" s="38" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F18" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="G18" s="38" t="s">
         <v>30</v>
@@ -23250,7 +23244,7 @@
         <v>144</v>
       </c>
       <c r="M18" s="35" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
@@ -23261,13 +23255,13 @@
         <v>335</v>
       </c>
       <c r="D19" s="34" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F19" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="G19" s="38" t="s">
         <v>30</v>
@@ -23279,7 +23273,7 @@
         <v>144</v>
       </c>
       <c r="M19" s="34" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
@@ -23290,13 +23284,13 @@
         <v>336</v>
       </c>
       <c r="D20" s="35" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="E20" s="38" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F20" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="G20" s="38" t="s">
         <v>30</v>
@@ -23308,7 +23302,7 @@
         <v>144</v>
       </c>
       <c r="M20" s="35" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
@@ -23319,13 +23313,13 @@
         <v>337</v>
       </c>
       <c r="D21" s="34" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="E21" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F21" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="G21" s="38" t="s">
         <v>30</v>
@@ -23337,7 +23331,7 @@
         <v>144</v>
       </c>
       <c r="M21" s="34" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
@@ -23348,13 +23342,13 @@
         <v>338</v>
       </c>
       <c r="D22" s="35" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F22" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="G22" s="38" t="s">
         <v>30</v>
@@ -23366,7 +23360,7 @@
         <v>144</v>
       </c>
       <c r="M22" s="35" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
@@ -23377,13 +23371,13 @@
         <v>339</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F23" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="G23" s="38" t="s">
         <v>30</v>
@@ -23395,7 +23389,7 @@
         <v>144</v>
       </c>
       <c r="M23" s="34" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
@@ -23406,13 +23400,13 @@
         <v>340</v>
       </c>
       <c r="D24" s="34" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F24" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>30</v>
@@ -23441,10 +23435,10 @@
         <v>148</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="F25" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="G25" t="s">
         <v>30</v>
@@ -23536,13 +23530,13 @@
         <v>342</v>
       </c>
       <c r="D2" s="40" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="E2" s="40" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="F2" s="40" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="G2" s="40" t="s">
         <v>18</v>
@@ -23563,7 +23557,7 @@
         <v>146</v>
       </c>
       <c r="M2" s="34" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -23577,16 +23571,16 @@
         <v>343</v>
       </c>
       <c r="D3" s="40" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="E3" s="40" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="G3" s="40" t="s">
-        <v>18</v>
+        <v>563</v>
       </c>
       <c r="H3" s="40" t="s">
         <v>143</v>
@@ -23604,7 +23598,7 @@
         <v>146</v>
       </c>
       <c r="M3" s="40" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -23618,13 +23612,13 @@
         <v>344</v>
       </c>
       <c r="D4" s="6" t="s">
+        <v>982</v>
+      </c>
+      <c r="E4" s="40" t="s">
+        <v>976</v>
+      </c>
+      <c r="F4" t="s">
         <v>987</v>
-      </c>
-      <c r="E4" s="40" t="s">
-        <v>981</v>
-      </c>
-      <c r="F4" t="s">
-        <v>992</v>
       </c>
       <c r="G4" s="17" t="s">
         <v>30</v>
@@ -23645,7 +23639,7 @@
         <v>146</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>855</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -23659,13 +23653,13 @@
         <v>345</v>
       </c>
       <c r="D5" s="17" t="s">
+        <v>983</v>
+      </c>
+      <c r="E5" s="40" t="s">
+        <v>976</v>
+      </c>
+      <c r="F5" t="s">
         <v>988</v>
-      </c>
-      <c r="E5" s="40" t="s">
-        <v>981</v>
-      </c>
-      <c r="F5" t="s">
-        <v>993</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>18</v>
@@ -23686,7 +23680,7 @@
         <v>146</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>856</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -23700,13 +23694,13 @@
         <v>346</v>
       </c>
       <c r="D6" s="6" t="s">
+        <v>984</v>
+      </c>
+      <c r="E6" s="40" t="s">
+        <v>976</v>
+      </c>
+      <c r="F6" t="s">
         <v>989</v>
-      </c>
-      <c r="E6" s="40" t="s">
-        <v>981</v>
-      </c>
-      <c r="F6" t="s">
-        <v>994</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>192</v>
@@ -23727,7 +23721,7 @@
         <v>146</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>857</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -23741,13 +23735,13 @@
         <v>347</v>
       </c>
       <c r="D7" s="6" t="s">
+        <v>985</v>
+      </c>
+      <c r="E7" s="40" t="s">
+        <v>976</v>
+      </c>
+      <c r="F7" t="s">
         <v>990</v>
-      </c>
-      <c r="E7" s="40" t="s">
-        <v>981</v>
-      </c>
-      <c r="F7" t="s">
-        <v>995</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>30</v>
@@ -23768,7 +23762,7 @@
         <v>146</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>858</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -23782,13 +23776,13 @@
         <v>348</v>
       </c>
       <c r="D8" s="6" t="s">
+        <v>986</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>976</v>
+      </c>
+      <c r="F8" t="s">
         <v>991</v>
-      </c>
-      <c r="E8" s="40" t="s">
-        <v>981</v>
-      </c>
-      <c r="F8" t="s">
-        <v>996</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>30</v>
@@ -23809,7 +23803,7 @@
         <v>146</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>859</v>
+        <v>1047</v>
       </c>
     </row>
   </sheetData>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/Round 2 Pods for Testing/Fast Track Pods/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="602" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACF60EE7-0997-4B4B-95EF-F59CAE9782D5}"/>
+  <xr:revisionPtr revIDLastSave="631" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22B6BA6E-C255-43A1-AFE6-2C6FDD1E53D8}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-27780" yWindow="360" windowWidth="26910" windowHeight="14940" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView xWindow="-28230" yWindow="570" windowWidth="26910" windowHeight="14940" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8198" uniqueCount="1048">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8222" uniqueCount="1050">
   <si>
     <t>schema</t>
   </si>
@@ -3240,6 +3240,12 @@
   </si>
   <si>
     <t>List the names of any other VVB team members and their roles (FIRST NAME - LAST NAME, ROLE)</t>
+  </si>
+  <si>
+    <t>validation_vvb_id</t>
+  </si>
+  <si>
+    <t>validation.validation_vvb_id</t>
   </si>
 </sst>
 </file>
@@ -3895,7 +3901,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{752D3095-90A4-45FF-BD20-0492A3C6EFAC}">
-  <dimension ref="A1:M342"/>
+  <dimension ref="A1:M343"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="21.1796875" bestFit="1" customWidth="1"/>
@@ -16097,23 +16103,23 @@
       <c r="C298">
         <v>304</v>
       </c>
-      <c r="D298" s="17" t="s">
-        <v>269</v>
+      <c r="D298" s="33" t="s">
+        <v>1048</v>
       </c>
       <c r="E298" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F298" t="s">
-        <v>270</v>
+        <v>1049</v>
       </c>
       <c r="G298" s="6" t="s">
-        <v>18</v>
+        <v>192</v>
       </c>
       <c r="H298" s="6" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="I298" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J298" s="6" t="s">
         <v>841</v>
@@ -16125,7 +16131,7 @@
         <v>146</v>
       </c>
       <c r="M298" s="6" t="s">
-        <v>1042</v>
+        <v>939</v>
       </c>
     </row>
     <row r="299" spans="1:13" x14ac:dyDescent="0.35">
@@ -16138,20 +16144,20 @@
       <c r="C299">
         <v>305</v>
       </c>
-      <c r="D299" s="30" t="s">
-        <v>511</v>
+      <c r="D299" s="17" t="s">
+        <v>269</v>
       </c>
       <c r="E299" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F299" t="s">
-        <v>959</v>
+        <v>270</v>
       </c>
       <c r="G299" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H299" s="6" t="s">
-        <v>143</v>
+        <v>219</v>
       </c>
       <c r="I299" s="6" t="s">
         <v>20</v>
@@ -16166,7 +16172,7 @@
         <v>146</v>
       </c>
       <c r="M299" s="6" t="s">
-        <v>852</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="300" spans="1:13" x14ac:dyDescent="0.35">
@@ -16179,20 +16185,20 @@
       <c r="C300">
         <v>306</v>
       </c>
-      <c r="D300" s="6" t="s">
-        <v>831</v>
+      <c r="D300" s="30" t="s">
+        <v>511</v>
       </c>
       <c r="E300" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F300" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="G300" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H300" s="6" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="I300" s="6" t="s">
         <v>20</v>
@@ -16207,7 +16213,7 @@
         <v>146</v>
       </c>
       <c r="M300" s="6" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
     </row>
     <row r="301" spans="1:13" x14ac:dyDescent="0.35">
@@ -16221,19 +16227,19 @@
         <v>307</v>
       </c>
       <c r="D301" s="6" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E301" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F301" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="G301" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H301" s="6" t="s">
-        <v>219</v>
+        <v>150</v>
       </c>
       <c r="I301" s="6" t="s">
         <v>20</v>
@@ -16248,7 +16254,7 @@
         <v>146</v>
       </c>
       <c r="M301" s="6" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="302" spans="1:13" x14ac:dyDescent="0.35">
@@ -16262,13 +16268,13 @@
         <v>308</v>
       </c>
       <c r="D302" s="6" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E302" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F302" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="G302" s="6" t="s">
         <v>18</v>
@@ -16289,7 +16295,7 @@
         <v>146</v>
       </c>
       <c r="M302" s="6" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="303" spans="1:13" x14ac:dyDescent="0.35">
@@ -16302,23 +16308,23 @@
       <c r="C303">
         <v>309</v>
       </c>
-      <c r="D303" s="17" t="s">
-        <v>834</v>
+      <c r="D303" s="6" t="s">
+        <v>833</v>
       </c>
       <c r="E303" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F303" t="s">
-        <v>963</v>
-      </c>
-      <c r="G303" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H303" s="17" t="s">
-        <v>159</v>
+        <v>962</v>
+      </c>
+      <c r="G303" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H303" s="6" t="s">
+        <v>219</v>
       </c>
       <c r="I303" s="6" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="J303" s="6" t="s">
         <v>841</v>
@@ -16329,8 +16335,8 @@
       <c r="L303" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M303" s="17" t="s">
-        <v>858</v>
+      <c r="M303" s="6" t="s">
+        <v>857</v>
       </c>
     </row>
     <row r="304" spans="1:13" x14ac:dyDescent="0.35">
@@ -16343,14 +16349,14 @@
       <c r="C304">
         <v>310</v>
       </c>
-      <c r="D304" s="6" t="s">
-        <v>835</v>
+      <c r="D304" s="17" t="s">
+        <v>834</v>
       </c>
       <c r="E304" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F304" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="G304" s="17" t="s">
         <v>30</v>
@@ -16370,8 +16376,8 @@
       <c r="L304" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M304" s="6" t="s">
-        <v>859</v>
+      <c r="M304" s="17" t="s">
+        <v>858</v>
       </c>
     </row>
     <row r="305" spans="1:13" x14ac:dyDescent="0.35">
@@ -16385,18 +16391,18 @@
         <v>311</v>
       </c>
       <c r="D305" s="6" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="E305" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F305" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="G305" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="H305" s="6" t="s">
+      <c r="H305" s="17" t="s">
         <v>159</v>
       </c>
       <c r="I305" s="6" t="s">
@@ -16412,7 +16418,7 @@
         <v>146</v>
       </c>
       <c r="M305" s="6" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
     </row>
     <row r="306" spans="1:13" x14ac:dyDescent="0.35">
@@ -16426,18 +16432,18 @@
         <v>312</v>
       </c>
       <c r="D306" s="6" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="E306" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F306" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G306" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="H306" s="17" t="s">
+      <c r="H306" s="6" t="s">
         <v>159</v>
       </c>
       <c r="I306" s="6" t="s">
@@ -16453,7 +16459,7 @@
         <v>146</v>
       </c>
       <c r="M306" s="6" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
     </row>
     <row r="307" spans="1:13" x14ac:dyDescent="0.35">
@@ -16467,13 +16473,13 @@
         <v>313</v>
       </c>
       <c r="D307" s="6" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E307" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F307" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G307" s="17" t="s">
         <v>30</v>
@@ -16494,7 +16500,7 @@
         <v>146</v>
       </c>
       <c r="M307" s="6" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="308" spans="1:13" x14ac:dyDescent="0.35">
@@ -16508,34 +16514,34 @@
         <v>314</v>
       </c>
       <c r="D308" s="6" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="E308" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F308" t="s">
-        <v>968</v>
-      </c>
-      <c r="G308" s="6" t="s">
-        <v>563</v>
-      </c>
-      <c r="H308" s="6" t="s">
-        <v>143</v>
+        <v>967</v>
+      </c>
+      <c r="G308" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H308" s="17" t="s">
+        <v>159</v>
       </c>
       <c r="I308" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J308" s="6" t="s">
         <v>841</v>
       </c>
       <c r="K308" s="6" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="L308" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M308" s="6" t="s">
-        <v>969</v>
+        <v>861</v>
       </c>
     </row>
     <row r="309" spans="1:13" x14ac:dyDescent="0.35">
@@ -16549,16 +16555,16 @@
         <v>315</v>
       </c>
       <c r="D309" s="6" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="E309" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F309" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="G309" s="6" t="s">
-        <v>18</v>
+        <v>563</v>
       </c>
       <c r="H309" s="6" t="s">
         <v>143</v>
@@ -16567,7 +16573,7 @@
         <v>20</v>
       </c>
       <c r="J309" s="6" t="s">
-        <v>445</v>
+        <v>841</v>
       </c>
       <c r="K309" s="6" t="s">
         <v>163</v>
@@ -16576,7 +16582,7 @@
         <v>146</v>
       </c>
       <c r="M309" s="6" t="s">
-        <v>862</v>
+        <v>969</v>
       </c>
     </row>
     <row r="310" spans="1:13" x14ac:dyDescent="0.35">
@@ -16590,22 +16596,22 @@
         <v>316</v>
       </c>
       <c r="D310" s="6" t="s">
-        <v>971</v>
+        <v>839</v>
       </c>
       <c r="E310" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F310" t="s">
-        <v>972</v>
-      </c>
-      <c r="G310" s="17" t="s">
-        <v>30</v>
+        <v>970</v>
+      </c>
+      <c r="G310" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="H310" s="6" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="I310" s="6" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="J310" s="6" t="s">
         <v>445</v>
@@ -16616,8 +16622,8 @@
       <c r="L310" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M310" t="s">
-        <v>973</v>
+      <c r="M310" s="6" t="s">
+        <v>862</v>
       </c>
     </row>
     <row r="311" spans="1:13" x14ac:dyDescent="0.35">
@@ -16631,19 +16637,19 @@
         <v>317</v>
       </c>
       <c r="D311" s="6" t="s">
-        <v>148</v>
+        <v>971</v>
       </c>
       <c r="E311" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F311" t="s">
-        <v>974</v>
-      </c>
-      <c r="G311" t="s">
+        <v>972</v>
+      </c>
+      <c r="G311" s="17" t="s">
         <v>30</v>
       </c>
       <c r="H311" s="6" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="I311" s="6" t="s">
         <v>144</v>
@@ -16657,37 +16663,49 @@
       <c r="L311" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M311" s="6" t="s">
-        <v>527</v>
+      <c r="M311" t="s">
+        <v>973</v>
       </c>
     </row>
     <row r="312" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>13</v>
       </c>
+      <c r="B312" t="s">
+        <v>275</v>
+      </c>
       <c r="C312">
         <v>318</v>
       </c>
-      <c r="D312" s="34" t="s">
-        <v>878</v>
-      </c>
-      <c r="E312" s="36" t="s">
-        <v>921</v>
+      <c r="D312" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E312" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="F312" t="s">
-        <v>933</v>
-      </c>
-      <c r="G312" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="H312" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="I312" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="M312" s="34" t="s">
-        <v>900</v>
+        <v>974</v>
+      </c>
+      <c r="G312" t="s">
+        <v>30</v>
+      </c>
+      <c r="H312" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I312" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J312" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="K312" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="L312" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M312" s="6" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="313" spans="1:13" x14ac:dyDescent="0.35">
@@ -16698,25 +16716,25 @@
         <v>319</v>
       </c>
       <c r="D313" s="34" t="s">
-        <v>937</v>
+        <v>878</v>
       </c>
       <c r="E313" s="36" t="s">
         <v>921</v>
       </c>
       <c r="F313" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="G313" s="36" t="s">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="H313" s="37" t="s">
         <v>215</v>
       </c>
       <c r="I313" s="36" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="M313" s="34" t="s">
-        <v>939</v>
+        <v>900</v>
       </c>
     </row>
     <row r="314" spans="1:13" x14ac:dyDescent="0.35">
@@ -16726,26 +16744,26 @@
       <c r="C314">
         <v>320</v>
       </c>
-      <c r="D314" s="35" t="s">
-        <v>879</v>
-      </c>
-      <c r="E314" s="38" t="s">
+      <c r="D314" s="34" t="s">
+        <v>937</v>
+      </c>
+      <c r="E314" s="36" t="s">
         <v>921</v>
       </c>
       <c r="F314" t="s">
-        <v>935</v>
-      </c>
-      <c r="G314" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="H314" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="I314" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M314" s="35" t="s">
-        <v>901</v>
+        <v>938</v>
+      </c>
+      <c r="G314" s="36" t="s">
+        <v>192</v>
+      </c>
+      <c r="H314" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I314" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M314" s="34" t="s">
+        <v>939</v>
       </c>
     </row>
     <row r="315" spans="1:13" x14ac:dyDescent="0.35">
@@ -16755,26 +16773,26 @@
       <c r="C315">
         <v>321</v>
       </c>
-      <c r="D315" s="34" t="s">
-        <v>880</v>
-      </c>
-      <c r="E315" s="36" t="s">
+      <c r="D315" s="35" t="s">
+        <v>879</v>
+      </c>
+      <c r="E315" s="38" t="s">
         <v>921</v>
       </c>
       <c r="F315" t="s">
-        <v>934</v>
-      </c>
-      <c r="G315" s="36" t="s">
+        <v>935</v>
+      </c>
+      <c r="G315" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H315" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="I315" s="36" t="s">
+      <c r="H315" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="I315" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="M315" s="34" t="s">
-        <v>902</v>
+      <c r="M315" s="35" t="s">
+        <v>901</v>
       </c>
     </row>
     <row r="316" spans="1:13" x14ac:dyDescent="0.35">
@@ -16784,26 +16802,26 @@
       <c r="C316">
         <v>322</v>
       </c>
-      <c r="D316" s="35" t="s">
-        <v>881</v>
-      </c>
-      <c r="E316" s="38" t="s">
+      <c r="D316" s="34" t="s">
+        <v>880</v>
+      </c>
+      <c r="E316" s="36" t="s">
         <v>921</v>
       </c>
       <c r="F316" t="s">
-        <v>936</v>
-      </c>
-      <c r="G316" s="38" t="s">
+        <v>934</v>
+      </c>
+      <c r="G316" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="H316" s="39" t="s">
+      <c r="H316" s="37" t="s">
         <v>215</v>
       </c>
-      <c r="I316" s="38" t="s">
+      <c r="I316" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="M316" s="35" t="s">
-        <v>903</v>
+      <c r="M316" s="34" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="317" spans="1:13" x14ac:dyDescent="0.35">
@@ -16813,26 +16831,26 @@
       <c r="C317">
         <v>323</v>
       </c>
-      <c r="D317" s="34" t="s">
-        <v>882</v>
-      </c>
-      <c r="E317" s="36" t="s">
+      <c r="D317" s="35" t="s">
+        <v>881</v>
+      </c>
+      <c r="E317" s="38" t="s">
         <v>921</v>
       </c>
       <c r="F317" t="s">
-        <v>922</v>
-      </c>
-      <c r="G317" s="36" t="s">
+        <v>936</v>
+      </c>
+      <c r="G317" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H317" s="37" t="s">
-        <v>219</v>
-      </c>
-      <c r="I317" s="36" t="s">
+      <c r="H317" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I317" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="M317" s="34" t="s">
-        <v>904</v>
+      <c r="M317" s="35" t="s">
+        <v>903</v>
       </c>
     </row>
     <row r="318" spans="1:13" x14ac:dyDescent="0.35">
@@ -16842,26 +16860,26 @@
       <c r="C318">
         <v>324</v>
       </c>
-      <c r="D318" s="35" t="s">
-        <v>883</v>
-      </c>
-      <c r="E318" s="38" t="s">
+      <c r="D318" s="34" t="s">
+        <v>882</v>
+      </c>
+      <c r="E318" s="36" t="s">
         <v>921</v>
       </c>
       <c r="F318" t="s">
-        <v>923</v>
-      </c>
-      <c r="G318" s="38" t="s">
+        <v>922</v>
+      </c>
+      <c r="G318" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="H318" s="39" t="s">
+      <c r="H318" s="37" t="s">
         <v>219</v>
       </c>
-      <c r="I318" s="38" t="s">
+      <c r="I318" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="M318" s="35" t="s">
-        <v>905</v>
+      <c r="M318" s="34" t="s">
+        <v>904</v>
       </c>
     </row>
     <row r="319" spans="1:13" x14ac:dyDescent="0.35">
@@ -16871,26 +16889,26 @@
       <c r="C319">
         <v>325</v>
       </c>
-      <c r="D319" s="34" t="s">
-        <v>884</v>
-      </c>
-      <c r="E319" s="36" t="s">
+      <c r="D319" s="35" t="s">
+        <v>883</v>
+      </c>
+      <c r="E319" s="38" t="s">
         <v>921</v>
       </c>
       <c r="F319" t="s">
-        <v>924</v>
-      </c>
-      <c r="G319" s="36" t="s">
+        <v>923</v>
+      </c>
+      <c r="G319" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H319" s="37" t="s">
+      <c r="H319" s="39" t="s">
         <v>219</v>
       </c>
-      <c r="I319" s="36" t="s">
+      <c r="I319" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="M319" s="34" t="s">
-        <v>906</v>
+      <c r="M319" s="35" t="s">
+        <v>905</v>
       </c>
     </row>
     <row r="320" spans="1:13" x14ac:dyDescent="0.35">
@@ -16900,26 +16918,26 @@
       <c r="C320">
         <v>326</v>
       </c>
-      <c r="D320" s="35" t="s">
-        <v>885</v>
-      </c>
-      <c r="E320" s="38" t="s">
+      <c r="D320" s="34" t="s">
+        <v>884</v>
+      </c>
+      <c r="E320" s="36" t="s">
         <v>921</v>
       </c>
       <c r="F320" t="s">
-        <v>925</v>
-      </c>
-      <c r="G320" s="38" t="s">
+        <v>924</v>
+      </c>
+      <c r="G320" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="H320" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="I320" s="38" t="s">
+      <c r="H320" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I320" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="M320" s="35" t="s">
-        <v>907</v>
+      <c r="M320" s="34" t="s">
+        <v>906</v>
       </c>
     </row>
     <row r="321" spans="1:13" x14ac:dyDescent="0.35">
@@ -16929,26 +16947,26 @@
       <c r="C321">
         <v>327</v>
       </c>
-      <c r="D321" s="34" t="s">
-        <v>886</v>
-      </c>
-      <c r="E321" s="36" t="s">
+      <c r="D321" s="35" t="s">
+        <v>885</v>
+      </c>
+      <c r="E321" s="38" t="s">
         <v>921</v>
       </c>
       <c r="F321" t="s">
-        <v>926</v>
-      </c>
-      <c r="G321" s="36" t="s">
+        <v>925</v>
+      </c>
+      <c r="G321" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H321" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="I321" s="36" t="s">
+      <c r="H321" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="I321" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="M321" s="34" t="s">
-        <v>908</v>
+      <c r="M321" s="35" t="s">
+        <v>907</v>
       </c>
     </row>
     <row r="322" spans="1:13" x14ac:dyDescent="0.35">
@@ -16958,26 +16976,26 @@
       <c r="C322">
         <v>328</v>
       </c>
-      <c r="D322" s="35" t="s">
-        <v>887</v>
-      </c>
-      <c r="E322" s="38" t="s">
+      <c r="D322" s="34" t="s">
+        <v>886</v>
+      </c>
+      <c r="E322" s="36" t="s">
         <v>921</v>
       </c>
       <c r="F322" t="s">
-        <v>927</v>
-      </c>
-      <c r="G322" s="38" t="s">
+        <v>926</v>
+      </c>
+      <c r="G322" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="H322" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="I322" s="38" t="s">
+      <c r="H322" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="I322" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="M322" s="35" t="s">
-        <v>909</v>
+      <c r="M322" s="34" t="s">
+        <v>908</v>
       </c>
     </row>
     <row r="323" spans="1:13" x14ac:dyDescent="0.35">
@@ -16987,26 +17005,26 @@
       <c r="C323">
         <v>329</v>
       </c>
-      <c r="D323" s="34" t="s">
-        <v>888</v>
-      </c>
-      <c r="E323" s="36" t="s">
+      <c r="D323" s="35" t="s">
+        <v>887</v>
+      </c>
+      <c r="E323" s="38" t="s">
         <v>921</v>
       </c>
       <c r="F323" t="s">
-        <v>928</v>
-      </c>
-      <c r="G323" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="H323" s="37" t="s">
+        <v>927</v>
+      </c>
+      <c r="G323" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H323" s="39" t="s">
         <v>215</v>
       </c>
-      <c r="I323" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="M323" s="34" t="s">
-        <v>910</v>
+      <c r="I323" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M323" s="35" t="s">
+        <v>909</v>
       </c>
     </row>
     <row r="324" spans="1:13" x14ac:dyDescent="0.35">
@@ -17016,26 +17034,26 @@
       <c r="C324">
         <v>330</v>
       </c>
-      <c r="D324" s="35" t="s">
-        <v>288</v>
-      </c>
-      <c r="E324" s="38" t="s">
+      <c r="D324" s="34" t="s">
+        <v>888</v>
+      </c>
+      <c r="E324" s="36" t="s">
         <v>921</v>
       </c>
       <c r="F324" t="s">
-        <v>929</v>
-      </c>
-      <c r="G324" s="38" t="s">
-        <v>563</v>
-      </c>
-      <c r="H324" s="39" t="s">
-        <v>898</v>
-      </c>
-      <c r="I324" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M324" s="35" t="s">
-        <v>911</v>
+        <v>928</v>
+      </c>
+      <c r="G324" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="H324" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I324" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M324" s="34" t="s">
+        <v>910</v>
       </c>
     </row>
     <row r="325" spans="1:13" x14ac:dyDescent="0.35">
@@ -17045,26 +17063,26 @@
       <c r="C325">
         <v>331</v>
       </c>
-      <c r="D325" s="34" t="s">
-        <v>889</v>
-      </c>
-      <c r="E325" s="36" t="s">
+      <c r="D325" s="35" t="s">
+        <v>288</v>
+      </c>
+      <c r="E325" s="38" t="s">
         <v>921</v>
       </c>
       <c r="F325" t="s">
-        <v>930</v>
-      </c>
-      <c r="G325" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="H325" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="I325" s="36" t="s">
+        <v>929</v>
+      </c>
+      <c r="G325" s="38" t="s">
+        <v>563</v>
+      </c>
+      <c r="H325" s="39" t="s">
+        <v>898</v>
+      </c>
+      <c r="I325" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="M325" s="34" t="s">
-        <v>912</v>
+      <c r="M325" s="35" t="s">
+        <v>911</v>
       </c>
     </row>
     <row r="326" spans="1:13" x14ac:dyDescent="0.35">
@@ -17074,84 +17092,84 @@
       <c r="C326">
         <v>332</v>
       </c>
-      <c r="D326" s="35" t="s">
-        <v>890</v>
-      </c>
-      <c r="E326" s="38" t="s">
+      <c r="D326" s="34" t="s">
+        <v>889</v>
+      </c>
+      <c r="E326" s="36" t="s">
         <v>921</v>
       </c>
       <c r="F326" t="s">
-        <v>931</v>
-      </c>
-      <c r="G326" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H326" s="39" t="s">
+        <v>930</v>
+      </c>
+      <c r="G326" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H326" s="37" t="s">
         <v>215</v>
       </c>
-      <c r="I326" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="M326" s="35" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="327" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="I326" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M326" s="34" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="327" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>13</v>
       </c>
       <c r="C327">
         <v>333</v>
       </c>
-      <c r="D327" s="34" t="s">
-        <v>891</v>
-      </c>
-      <c r="E327" s="36" t="s">
+      <c r="D327" s="35" t="s">
+        <v>890</v>
+      </c>
+      <c r="E327" s="38" t="s">
         <v>921</v>
       </c>
       <c r="F327" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="G327" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H327" s="37" t="s">
-        <v>899</v>
-      </c>
-      <c r="I327" s="36" t="s">
+      <c r="H327" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I327" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="M327" s="34" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M327" s="35" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="328" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>13</v>
       </c>
       <c r="C328">
         <v>334</v>
       </c>
-      <c r="D328" s="35" t="s">
-        <v>892</v>
-      </c>
-      <c r="E328" s="38" t="s">
+      <c r="D328" s="34" t="s">
+        <v>891</v>
+      </c>
+      <c r="E328" s="36" t="s">
         <v>921</v>
       </c>
       <c r="F328" t="s">
-        <v>944</v>
+        <v>932</v>
       </c>
       <c r="G328" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H328" s="39" t="s">
-        <v>150</v>
-      </c>
-      <c r="I328" s="38" t="s">
+      <c r="H328" s="37" t="s">
+        <v>899</v>
+      </c>
+      <c r="I328" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="M328" s="35" t="s">
-        <v>915</v>
+      <c r="M328" s="34" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="329" spans="1:13" x14ac:dyDescent="0.35">
@@ -17161,26 +17179,26 @@
       <c r="C329">
         <v>335</v>
       </c>
-      <c r="D329" s="34" t="s">
-        <v>893</v>
-      </c>
-      <c r="E329" s="36" t="s">
+      <c r="D329" s="35" t="s">
+        <v>892</v>
+      </c>
+      <c r="E329" s="38" t="s">
         <v>921</v>
       </c>
       <c r="F329" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="G329" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H329" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="I329" s="36" t="s">
+      <c r="H329" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="I329" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="M329" s="34" t="s">
-        <v>916</v>
+      <c r="M329" s="35" t="s">
+        <v>915</v>
       </c>
     </row>
     <row r="330" spans="1:13" x14ac:dyDescent="0.35">
@@ -17190,26 +17208,26 @@
       <c r="C330">
         <v>336</v>
       </c>
-      <c r="D330" s="35" t="s">
-        <v>894</v>
-      </c>
-      <c r="E330" s="38" t="s">
+      <c r="D330" s="34" t="s">
+        <v>893</v>
+      </c>
+      <c r="E330" s="36" t="s">
         <v>921</v>
       </c>
       <c r="F330" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="G330" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H330" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="I330" s="38" t="s">
+      <c r="H330" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I330" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="M330" s="35" t="s">
-        <v>917</v>
+      <c r="M330" s="34" t="s">
+        <v>916</v>
       </c>
     </row>
     <row r="331" spans="1:13" x14ac:dyDescent="0.35">
@@ -17219,26 +17237,26 @@
       <c r="C331">
         <v>337</v>
       </c>
-      <c r="D331" s="34" t="s">
-        <v>895</v>
-      </c>
-      <c r="E331" s="36" t="s">
+      <c r="D331" s="35" t="s">
+        <v>894</v>
+      </c>
+      <c r="E331" s="38" t="s">
         <v>921</v>
       </c>
       <c r="F331" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="G331" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H331" s="37" t="s">
+      <c r="H331" s="39" t="s">
         <v>316</v>
       </c>
-      <c r="I331" s="36" t="s">
+      <c r="I331" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="M331" s="34" t="s">
-        <v>918</v>
+      <c r="M331" s="35" t="s">
+        <v>917</v>
       </c>
     </row>
     <row r="332" spans="1:13" x14ac:dyDescent="0.35">
@@ -17248,26 +17266,26 @@
       <c r="C332">
         <v>338</v>
       </c>
-      <c r="D332" s="35" t="s">
-        <v>896</v>
-      </c>
-      <c r="E332" s="38" t="s">
+      <c r="D332" s="34" t="s">
+        <v>895</v>
+      </c>
+      <c r="E332" s="36" t="s">
         <v>921</v>
       </c>
       <c r="F332" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="G332" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H332" s="39" t="s">
+      <c r="H332" s="37" t="s">
         <v>316</v>
       </c>
-      <c r="I332" s="38" t="s">
+      <c r="I332" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="M332" s="35" t="s">
-        <v>919</v>
+      <c r="M332" s="34" t="s">
+        <v>918</v>
       </c>
     </row>
     <row r="333" spans="1:13" x14ac:dyDescent="0.35">
@@ -17277,26 +17295,26 @@
       <c r="C333">
         <v>339</v>
       </c>
-      <c r="D333" s="34" t="s">
-        <v>897</v>
-      </c>
-      <c r="E333" s="36" t="s">
+      <c r="D333" s="35" t="s">
+        <v>896</v>
+      </c>
+      <c r="E333" s="38" t="s">
         <v>921</v>
       </c>
       <c r="F333" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="G333" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H333" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="I333" s="36" t="s">
+      <c r="H333" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="I333" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="M333" s="34" t="s">
-        <v>920</v>
+      <c r="M333" s="35" t="s">
+        <v>919</v>
       </c>
     </row>
     <row r="334" spans="1:13" x14ac:dyDescent="0.35">
@@ -17307,28 +17325,25 @@
         <v>340</v>
       </c>
       <c r="D334" s="34" t="s">
-        <v>941</v>
+        <v>897</v>
       </c>
       <c r="E334" s="36" t="s">
         <v>921</v>
       </c>
       <c r="F334" t="s">
-        <v>942</v>
-      </c>
-      <c r="G334" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H334" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="I334" s="6" t="s">
+        <v>940</v>
+      </c>
+      <c r="G334" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H334" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="I334" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="J334" s="6"/>
-      <c r="K334" s="6"/>
-      <c r="L334" s="6"/>
-      <c r="M334" s="30" t="s">
-        <v>216</v>
+      <c r="M334" s="34" t="s">
+        <v>920</v>
       </c>
     </row>
     <row r="335" spans="1:13" x14ac:dyDescent="0.35">
@@ -17338,70 +17353,61 @@
       <c r="C335">
         <v>341</v>
       </c>
-      <c r="D335" s="6" t="s">
-        <v>148</v>
+      <c r="D335" s="34" t="s">
+        <v>941</v>
       </c>
       <c r="E335" s="36" t="s">
         <v>921</v>
       </c>
       <c r="F335" t="s">
-        <v>943</v>
-      </c>
-      <c r="G335" t="s">
+        <v>942</v>
+      </c>
+      <c r="G335" s="6" t="s">
         <v>30</v>
       </c>
       <c r="H335" s="6" t="s">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="I335" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J335" s="6"/>
       <c r="K335" s="6"/>
       <c r="L335" s="6"/>
-      <c r="M335" s="6" t="s">
-        <v>527</v>
+      <c r="M335" s="30" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="336" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>13</v>
       </c>
-      <c r="B336" t="s">
-        <v>275</v>
-      </c>
       <c r="C336">
         <v>342</v>
       </c>
-      <c r="D336" s="40" t="s">
-        <v>975</v>
-      </c>
-      <c r="E336" s="40" t="s">
-        <v>976</v>
-      </c>
-      <c r="F336" s="40" t="s">
-        <v>977</v>
-      </c>
-      <c r="G336" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="H336" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="I336" s="40" t="s">
+      <c r="D336" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E336" s="36" t="s">
+        <v>921</v>
+      </c>
+      <c r="F336" t="s">
+        <v>943</v>
+      </c>
+      <c r="G336" t="s">
+        <v>30</v>
+      </c>
+      <c r="H336" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I336" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J336" s="6" t="s">
-        <v>841</v>
-      </c>
-      <c r="K336" t="s">
-        <v>163</v>
-      </c>
-      <c r="L336" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M336" s="34" t="s">
-        <v>978</v>
+      <c r="J336" s="6"/>
+      <c r="K336" s="6"/>
+      <c r="L336" s="6"/>
+      <c r="M336" s="6" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="337" spans="1:13" x14ac:dyDescent="0.35">
@@ -17415,19 +17421,19 @@
         <v>343</v>
       </c>
       <c r="D337" s="40" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="E337" s="40" t="s">
         <v>976</v>
       </c>
       <c r="F337" s="40" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="G337" s="40" t="s">
-        <v>563</v>
+        <v>18</v>
       </c>
       <c r="H337" s="40" t="s">
-        <v>143</v>
+        <v>215</v>
       </c>
       <c r="I337" s="40" t="s">
         <v>20</v>
@@ -17441,8 +17447,8 @@
       <c r="L337" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M337" s="40" t="s">
-        <v>981</v>
+      <c r="M337" s="34" t="s">
+        <v>978</v>
       </c>
     </row>
     <row r="338" spans="1:13" x14ac:dyDescent="0.35">
@@ -17455,23 +17461,23 @@
       <c r="C338">
         <v>344</v>
       </c>
-      <c r="D338" s="6" t="s">
-        <v>982</v>
+      <c r="D338" s="40" t="s">
+        <v>979</v>
       </c>
       <c r="E338" s="40" t="s">
         <v>976</v>
       </c>
-      <c r="F338" t="s">
-        <v>987</v>
-      </c>
-      <c r="G338" s="17" t="s">
-        <v>30</v>
+      <c r="F338" s="40" t="s">
+        <v>980</v>
+      </c>
+      <c r="G338" s="40" t="s">
+        <v>563</v>
       </c>
       <c r="H338" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="I338" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
+      </c>
+      <c r="I338" s="40" t="s">
+        <v>20</v>
       </c>
       <c r="J338" s="6" t="s">
         <v>841</v>
@@ -17482,8 +17488,8 @@
       <c r="L338" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M338" s="6" t="s">
-        <v>1043</v>
+      <c r="M338" s="40" t="s">
+        <v>981</v>
       </c>
     </row>
     <row r="339" spans="1:13" x14ac:dyDescent="0.35">
@@ -17496,23 +17502,23 @@
       <c r="C339">
         <v>345</v>
       </c>
-      <c r="D339" s="17" t="s">
-        <v>983</v>
+      <c r="D339" s="6" t="s">
+        <v>982</v>
       </c>
       <c r="E339" s="40" t="s">
         <v>976</v>
       </c>
       <c r="F339" t="s">
-        <v>988</v>
-      </c>
-      <c r="G339" s="6" t="s">
-        <v>18</v>
+        <v>987</v>
+      </c>
+      <c r="G339" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="H339" s="40" t="s">
         <v>215</v>
       </c>
       <c r="I339" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J339" s="6" t="s">
         <v>841</v>
@@ -17524,7 +17530,7 @@
         <v>146</v>
       </c>
       <c r="M339" s="6" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="340" spans="1:13" x14ac:dyDescent="0.35">
@@ -17537,23 +17543,23 @@
       <c r="C340">
         <v>346</v>
       </c>
-      <c r="D340" s="6" t="s">
-        <v>984</v>
+      <c r="D340" s="17" t="s">
+        <v>983</v>
       </c>
       <c r="E340" s="40" t="s">
         <v>976</v>
       </c>
       <c r="F340" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="G340" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="H340" s="6" t="s">
-        <v>143</v>
+        <v>18</v>
+      </c>
+      <c r="H340" s="40" t="s">
+        <v>215</v>
       </c>
       <c r="I340" s="6" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="J340" s="6" t="s">
         <v>841</v>
@@ -17565,7 +17571,7 @@
         <v>146</v>
       </c>
       <c r="M340" s="6" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="341" spans="1:13" x14ac:dyDescent="0.35">
@@ -17579,19 +17585,19 @@
         <v>347</v>
       </c>
       <c r="D341" s="6" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="E341" s="40" t="s">
         <v>976</v>
       </c>
       <c r="F341" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="G341" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H341" s="40" t="s">
-        <v>215</v>
+        <v>192</v>
+      </c>
+      <c r="H341" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="I341" s="6" t="s">
         <v>144</v>
@@ -17606,7 +17612,7 @@
         <v>146</v>
       </c>
       <c r="M341" s="6" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="342" spans="1:13" x14ac:dyDescent="0.35">
@@ -17620,13 +17626,13 @@
         <v>348</v>
       </c>
       <c r="D342" s="6" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E342" s="40" t="s">
         <v>976</v>
       </c>
       <c r="F342" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="G342" s="6" t="s">
         <v>30</v>
@@ -17647,6 +17653,47 @@
         <v>146</v>
       </c>
       <c r="M342" s="6" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="343" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A343" t="s">
+        <v>13</v>
+      </c>
+      <c r="B343" t="s">
+        <v>275</v>
+      </c>
+      <c r="C343">
+        <v>349</v>
+      </c>
+      <c r="D343" s="6" t="s">
+        <v>986</v>
+      </c>
+      <c r="E343" s="40" t="s">
+        <v>976</v>
+      </c>
+      <c r="F343" t="s">
+        <v>991</v>
+      </c>
+      <c r="G343" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H343" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="I343" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J343" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="K343" t="s">
+        <v>163</v>
+      </c>
+      <c r="L343" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M343" s="6" t="s">
         <v>1047</v>
       </c>
     </row>
@@ -21405,7 +21452,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF337E51-0D9D-46A6-9DB2-8DF5F9FC1667}">
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="43.6328125" customWidth="1"/>
@@ -22127,23 +22174,23 @@
       <c r="C18">
         <v>304</v>
       </c>
-      <c r="D18" s="17" t="s">
-        <v>269</v>
+      <c r="D18" s="33" t="s">
+        <v>1048</v>
       </c>
       <c r="E18" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F18" t="s">
-        <v>270</v>
+        <v>1049</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>18</v>
+        <v>192</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>841</v>
@@ -22155,7 +22202,7 @@
         <v>146</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>1042</v>
+        <v>939</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
@@ -22168,20 +22215,20 @@
       <c r="C19">
         <v>305</v>
       </c>
-      <c r="D19" s="30" t="s">
-        <v>511</v>
+      <c r="D19" s="17" t="s">
+        <v>269</v>
       </c>
       <c r="E19" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F19" t="s">
-        <v>959</v>
+        <v>270</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>143</v>
+        <v>219</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>20</v>
@@ -22196,7 +22243,7 @@
         <v>146</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>852</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
@@ -22209,20 +22256,20 @@
       <c r="C20">
         <v>306</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>831</v>
+      <c r="D20" s="30" t="s">
+        <v>511</v>
       </c>
       <c r="E20" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F20" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>20</v>
@@ -22237,7 +22284,7 @@
         <v>146</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
@@ -22251,19 +22298,19 @@
         <v>307</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E21" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F21" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>219</v>
+        <v>150</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>20</v>
@@ -22278,7 +22325,7 @@
         <v>146</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
@@ -22292,13 +22339,13 @@
         <v>308</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E22" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F22" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>18</v>
@@ -22319,7 +22366,7 @@
         <v>146</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
@@ -22332,23 +22379,23 @@
       <c r="C23">
         <v>309</v>
       </c>
-      <c r="D23" s="17" t="s">
-        <v>834</v>
+      <c r="D23" s="6" t="s">
+        <v>833</v>
       </c>
       <c r="E23" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F23" t="s">
-        <v>963</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H23" s="17" t="s">
-        <v>159</v>
+        <v>962</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>219</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>841</v>
@@ -22359,8 +22406,8 @@
       <c r="L23" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M23" s="17" t="s">
-        <v>858</v>
+      <c r="M23" s="6" t="s">
+        <v>857</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
@@ -22373,14 +22420,14 @@
       <c r="C24">
         <v>310</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>835</v>
+      <c r="D24" s="17" t="s">
+        <v>834</v>
       </c>
       <c r="E24" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F24" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="G24" s="17" t="s">
         <v>30</v>
@@ -22400,8 +22447,8 @@
       <c r="L24" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M24" s="6" t="s">
-        <v>859</v>
+      <c r="M24" s="17" t="s">
+        <v>858</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
@@ -22415,18 +22462,18 @@
         <v>311</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="E25" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F25" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="G25" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H25" s="17" t="s">
         <v>159</v>
       </c>
       <c r="I25" s="6" t="s">
@@ -22442,7 +22489,7 @@
         <v>146</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
@@ -22456,18 +22503,18 @@
         <v>312</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="E26" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F26" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G26" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="H26" s="17" t="s">
+      <c r="H26" s="6" t="s">
         <v>159</v>
       </c>
       <c r="I26" s="6" t="s">
@@ -22483,7 +22530,7 @@
         <v>146</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
@@ -22497,13 +22544,13 @@
         <v>313</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E27" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F27" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G27" s="17" t="s">
         <v>30</v>
@@ -22524,7 +22571,7 @@
         <v>146</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
@@ -22538,34 +22585,34 @@
         <v>314</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="E28" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F28" t="s">
-        <v>968</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>563</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>143</v>
+        <v>967</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H28" s="17" t="s">
+        <v>159</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="J28" s="6" t="s">
         <v>841</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>969</v>
+        <v>861</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
@@ -22579,16 +22626,16 @@
         <v>315</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="E29" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F29" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>18</v>
+        <v>563</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>143</v>
@@ -22597,7 +22644,7 @@
         <v>20</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>445</v>
+        <v>841</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>163</v>
@@ -22606,7 +22653,7 @@
         <v>146</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>862</v>
+        <v>969</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.35">
@@ -22620,22 +22667,22 @@
         <v>316</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>971</v>
+        <v>839</v>
       </c>
       <c r="E30" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F30" t="s">
-        <v>972</v>
-      </c>
-      <c r="G30" s="17" t="s">
-        <v>30</v>
+        <v>970</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="J30" s="6" t="s">
         <v>445</v>
@@ -22646,8 +22693,8 @@
       <c r="L30" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M30" t="s">
-        <v>973</v>
+      <c r="M30" s="6" t="s">
+        <v>862</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
@@ -22661,19 +22708,19 @@
         <v>317</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>148</v>
+        <v>971</v>
       </c>
       <c r="E31" s="33" t="s">
         <v>266</v>
       </c>
       <c r="F31" t="s">
-        <v>974</v>
-      </c>
-      <c r="G31" t="s">
+        <v>972</v>
+      </c>
+      <c r="G31" s="17" t="s">
         <v>30</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="I31" s="6" t="s">
         <v>144</v>
@@ -22687,7 +22734,48 @@
       <c r="L31" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M31" s="6" t="s">
+      <c r="M31" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" t="s">
+        <v>275</v>
+      </c>
+      <c r="C32">
+        <v>318</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E32" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F32" t="s">
+        <v>974</v>
+      </c>
+      <c r="G32" t="s">
+        <v>30</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M32" s="6" t="s">
         <v>527</v>
       </c>
     </row>
@@ -22759,7 +22847,7 @@
         <v>13</v>
       </c>
       <c r="C2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D2" s="34" t="s">
         <v>878</v>
@@ -22788,7 +22876,7 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D3" s="34" t="s">
         <v>937</v>
@@ -22817,7 +22905,7 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D4" s="35" t="s">
         <v>879</v>
@@ -22846,7 +22934,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D5" s="34" t="s">
         <v>880</v>
@@ -22875,7 +22963,7 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D6" s="35" t="s">
         <v>881</v>
@@ -22904,7 +22992,7 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D7" s="34" t="s">
         <v>882</v>
@@ -22933,7 +23021,7 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D8" s="35" t="s">
         <v>883</v>
@@ -22962,7 +23050,7 @@
         <v>13</v>
       </c>
       <c r="C9">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D9" s="34" t="s">
         <v>884</v>
@@ -22991,7 +23079,7 @@
         <v>13</v>
       </c>
       <c r="C10">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D10" s="35" t="s">
         <v>885</v>
@@ -23020,7 +23108,7 @@
         <v>13</v>
       </c>
       <c r="C11">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D11" s="34" t="s">
         <v>886</v>
@@ -23049,7 +23137,7 @@
         <v>13</v>
       </c>
       <c r="C12">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D12" s="35" t="s">
         <v>887</v>
@@ -23078,7 +23166,7 @@
         <v>13</v>
       </c>
       <c r="C13">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D13" s="34" t="s">
         <v>888</v>
@@ -23107,7 +23195,7 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D14" s="35" t="s">
         <v>288</v>
@@ -23136,7 +23224,7 @@
         <v>13</v>
       </c>
       <c r="C15">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D15" s="34" t="s">
         <v>889</v>
@@ -23165,7 +23253,7 @@
         <v>13</v>
       </c>
       <c r="C16">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D16" s="35" t="s">
         <v>890</v>
@@ -23194,7 +23282,7 @@
         <v>13</v>
       </c>
       <c r="C17">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D17" s="34" t="s">
         <v>891</v>
@@ -23223,7 +23311,7 @@
         <v>13</v>
       </c>
       <c r="C18">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D18" s="35" t="s">
         <v>892</v>
@@ -23252,7 +23340,7 @@
         <v>13</v>
       </c>
       <c r="C19">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D19" s="34" t="s">
         <v>893</v>
@@ -23281,7 +23369,7 @@
         <v>13</v>
       </c>
       <c r="C20">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D20" s="35" t="s">
         <v>894</v>
@@ -23310,7 +23398,7 @@
         <v>13</v>
       </c>
       <c r="C21">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D21" s="34" t="s">
         <v>895</v>
@@ -23339,7 +23427,7 @@
         <v>13</v>
       </c>
       <c r="C22">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D22" s="35" t="s">
         <v>896</v>
@@ -23368,7 +23456,7 @@
         <v>13</v>
       </c>
       <c r="C23">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D23" s="34" t="s">
         <v>897</v>
@@ -23397,7 +23485,7 @@
         <v>13</v>
       </c>
       <c r="C24">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D24" s="34" t="s">
         <v>941</v>
@@ -23429,7 +23517,7 @@
         <v>13</v>
       </c>
       <c r="C25">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>148</v>
@@ -23527,7 +23615,7 @@
         <v>275</v>
       </c>
       <c r="C2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D2" s="40" t="s">
         <v>975</v>
@@ -23568,7 +23656,7 @@
         <v>275</v>
       </c>
       <c r="C3">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D3" s="40" t="s">
         <v>979</v>
@@ -23609,7 +23697,7 @@
         <v>275</v>
       </c>
       <c r="C4">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>982</v>
@@ -23650,7 +23738,7 @@
         <v>275</v>
       </c>
       <c r="C5">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>983</v>
@@ -23691,7 +23779,7 @@
         <v>275</v>
       </c>
       <c r="C6">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>984</v>
@@ -23732,7 +23820,7 @@
         <v>275</v>
       </c>
       <c r="C7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>985</v>
@@ -23773,7 +23861,7 @@
         <v>275</v>
       </c>
       <c r="C8">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>986</v>
